--- a/mi_cartera_balanz/data/cuentacorriente.xlsx
+++ b/mi_cartera_balanz/data/cuentacorriente.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F388"/>
+  <dimension ref="A1:F389"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -399,50 +399,50 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="D2" t="str">
         <v>Pesos</v>
       </c>
       <c r="E2">
-        <v>-1015702.61</v>
+        <v>2089759.48</v>
       </c>
       <c r="F2">
-        <v>11086.91</v>
+        <v>2100846.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Comprobante de Pago / 2204947</v>
+        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D3" t="str">
         <v>Pesos</v>
       </c>
       <c r="E3">
-        <v>-100000</v>
+        <v>-1015702.61</v>
       </c>
       <c r="F3">
-        <v>1026789.52</v>
+        <v>11086.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2204947</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -451,78 +451,78 @@
         <v>Pesos</v>
       </c>
       <c r="E4">
-        <v>-2000000</v>
+        <v>-100000</v>
       </c>
       <c r="F4">
-        <v>1126789.52</v>
+        <v>1026789.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B5" t="str">
         <v>2026-09-15</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D5" t="str">
         <v>Pesos</v>
       </c>
       <c r="E5">
-        <v>898438.45</v>
+        <v>-2000000</v>
       </c>
       <c r="F5">
-        <v>3126789.52</v>
+        <v>1126789.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="C6">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D6" t="str">
         <v>Pesos</v>
       </c>
       <c r="E6">
-        <v>-1981985.21</v>
+        <v>898438.45</v>
       </c>
       <c r="F6">
-        <v>2228351.07</v>
+        <v>3126789.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Recibo de Cobro / 2547929</v>
+        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B7" t="str">
         <v>2026-09-14</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D7" t="str">
         <v>Pesos</v>
       </c>
       <c r="E7">
-        <v>120000</v>
+        <v>-1981985.21</v>
       </c>
       <c r="F7">
-        <v>4210336.28</v>
+        <v>2228351.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Comprobante de Pago / 2167536</v>
+        <v>Recibo de Cobro / 2547929</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-14</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -531,18 +531,18 @@
         <v>Pesos</v>
       </c>
       <c r="E8">
-        <v>-50000</v>
+        <v>120000</v>
       </c>
       <c r="F8">
-        <v>4090336.28</v>
+        <v>4210336.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2167536</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-09-10</v>
+        <v>2026-09-12</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -551,18 +551,18 @@
         <v>Pesos</v>
       </c>
       <c r="E9">
-        <v>3404580.41</v>
+        <v>-50000</v>
       </c>
       <c r="F9">
-        <v>4140336.28</v>
+        <v>4090336.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Comprobante de Pago / 2105708</v>
+        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-10</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -571,18 +571,18 @@
         <v>Pesos</v>
       </c>
       <c r="E10">
-        <v>-30000</v>
+        <v>3404580.41</v>
       </c>
       <c r="F10">
-        <v>735755.87</v>
+        <v>4140336.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Comprobante de Pago / 2057077</v>
+        <v>Comprobante de Pago / 2105708</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-06</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -591,18 +591,18 @@
         <v>Pesos</v>
       </c>
       <c r="E11">
-        <v>-80000</v>
+        <v>-30000</v>
       </c>
       <c r="F11">
-        <v>765755.87</v>
+        <v>735755.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2057077</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -611,118 +611,118 @@
         <v>Pesos</v>
       </c>
       <c r="E12">
-        <v>-3371333.8</v>
+        <v>-80000</v>
       </c>
       <c r="F12">
-        <v>845755.87</v>
+        <v>765755.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
+        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B13" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C13">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D13" t="str">
         <v>Pesos</v>
       </c>
       <c r="E13">
-        <v>918459.06</v>
+        <v>-3371333.8</v>
       </c>
       <c r="F13">
-        <v>4217089.67</v>
+        <v>845755.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B14" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C14">
-        <v>503</v>
+        <v>278</v>
       </c>
       <c r="D14" t="str">
         <v>Pesos</v>
       </c>
       <c r="E14">
-        <v>3298630.61</v>
+        <v>918459.06</v>
       </c>
       <c r="F14">
-        <v>3298630.61</v>
+        <v>4217089.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Comprobante de Pago / 1944836</v>
+        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-21</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D15" t="str">
         <v>Pesos</v>
       </c>
       <c r="E15">
-        <v>-34658.23</v>
+        <v>3298630.61</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>3298630.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1944836</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-19</v>
       </c>
       <c r="C16">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="D16" t="str">
         <v>Pesos</v>
       </c>
       <c r="E16">
-        <v>-3589249.15</v>
+        <v>-34658.23</v>
       </c>
       <c r="F16">
-        <v>34658.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Comprobante de Pago / 1817656</v>
+        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-14</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D17" t="str">
         <v>Pesos</v>
       </c>
       <c r="E17">
-        <v>-40000</v>
+        <v>-3589249.15</v>
       </c>
       <c r="F17">
-        <v>3623907.38</v>
+        <v>34658.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Comprobante de Pago / 1732595</v>
+        <v>Comprobante de Pago / 1817656</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-07-25</v>
+        <v>2026-08-04</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -731,18 +731,18 @@
         <v>Pesos</v>
       </c>
       <c r="E18">
-        <v>-100000</v>
+        <v>-40000</v>
       </c>
       <c r="F18">
-        <v>3663907.38</v>
+        <v>3623907.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Comprobante de Pago / 1561578</v>
+        <v>Comprobante de Pago / 1732595</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-25</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -751,18 +751,18 @@
         <v>Pesos</v>
       </c>
       <c r="E19">
-        <v>-300000</v>
+        <v>-100000</v>
       </c>
       <c r="F19">
-        <v>3763907.38</v>
+        <v>3663907.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Comprobante de Pago / 1545516</v>
+        <v>Comprobante de Pago / 1561578</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-04</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -771,70 +771,70 @@
         <v>Pesos</v>
       </c>
       <c r="E20">
-        <v>-100000</v>
+        <v>-300000</v>
       </c>
       <c r="F20">
-        <v>4063907.38</v>
+        <v>3763907.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1545516</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-02</v>
       </c>
       <c r="C21">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D21" t="str">
         <v>Pesos</v>
       </c>
       <c r="E21">
-        <v>488924.13</v>
+        <v>-100000</v>
       </c>
       <c r="F21">
-        <v>4163907.38</v>
+        <v>4063907.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-06-29</v>
+        <v>2026-07-01</v>
       </c>
       <c r="C22">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" t="str">
         <v>Pesos</v>
       </c>
       <c r="E22">
-        <v>515910.2</v>
+        <v>488924.13</v>
       </c>
       <c r="F22">
-        <v>3674983.25</v>
+        <v>4163907.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B23" t="str">
         <v>2026-06-29</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D23" t="str">
         <v>Pesos</v>
       </c>
       <c r="E23">
-        <v>-6.27</v>
+        <v>515910.2</v>
       </c>
       <c r="F23">
-        <v>3159073.05</v>
+        <v>3674983.25</v>
       </c>
     </row>
     <row r="24">
@@ -848,118 +848,118 @@
         <v>0</v>
       </c>
       <c r="D24" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E24">
-        <v>0.99</v>
+        <v>-6.27</v>
       </c>
       <c r="F24">
-        <v>2.01</v>
+        <v>3159073.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-29</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D25" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E25">
-        <v>-944671.87</v>
+        <v>0.99</v>
       </c>
       <c r="F25">
-        <v>3159079.32</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B26" t="str">
         <v>2026-06-24</v>
       </c>
       <c r="C26">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D26" t="str">
         <v>Pesos</v>
       </c>
       <c r="E26">
-        <v>-1001112.31</v>
+        <v>-944671.87</v>
       </c>
       <c r="F26">
-        <v>4103751.19</v>
+        <v>3159079.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Comprobante de Pago / 1465742</v>
+        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-24</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D27" t="str">
         <v>Pesos</v>
       </c>
       <c r="E27">
-        <v>-50000</v>
+        <v>-1001112.31</v>
       </c>
       <c r="F27">
-        <v>5104863.5</v>
+        <v>4103751.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1465742</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-22</v>
       </c>
       <c r="C28">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="D28" t="str">
         <v>Pesos</v>
       </c>
       <c r="E28">
-        <v>2137654.07</v>
+        <v>-50000</v>
       </c>
       <c r="F28">
-        <v>5154863.5</v>
+        <v>5104863.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C29">
-        <v>879</v>
+        <v>540</v>
       </c>
       <c r="D29" t="str">
         <v>Pesos</v>
       </c>
       <c r="E29">
-        <v>820145.97</v>
+        <v>2137654.07</v>
       </c>
       <c r="F29">
-        <v>3017209.43</v>
+        <v>5154863.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B30" t="str">
         <v>2026-06-09</v>
@@ -968,13 +968,13 @@
         <v>879</v>
       </c>
       <c r="D30" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E30">
-        <v>-567.43</v>
+        <v>820145.97</v>
       </c>
       <c r="F30">
-        <v>11.75</v>
+        <v>3017209.43</v>
       </c>
     </row>
     <row r="31">
@@ -985,124 +985,124 @@
         <v>2026-06-09</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="D31" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E31">
-        <v>-20.4</v>
+        <v>-567.43</v>
       </c>
       <c r="F31">
-        <v>2197063.46</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B32" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C32">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D32" t="str">
         <v>Pesos</v>
       </c>
       <c r="E32">
-        <v>1867138.55</v>
+        <v>-20.4</v>
       </c>
       <c r="F32">
-        <v>2197083.86</v>
+        <v>2197063.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Recibo de Cobro / 1530471</v>
+        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D33" t="str">
         <v>Pesos</v>
       </c>
       <c r="E33">
-        <v>300000</v>
+        <v>1867138.55</v>
       </c>
       <c r="F33">
-        <v>329945.31</v>
+        <v>2197083.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
+        <v>Recibo de Cobro / 1530471</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C34">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D34" t="str">
         <v>Pesos</v>
       </c>
       <c r="E34">
-        <v>-1996802.3</v>
+        <v>300000</v>
       </c>
       <c r="F34">
-        <v>29945.31</v>
+        <v>329945.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Recibo de Cobro / 1484184</v>
+        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B35" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D35" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E35">
-        <v>579.18</v>
+        <v>-1996802.3</v>
       </c>
       <c r="F35">
-        <v>579.18</v>
+        <v>29945.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Comprobante de Pago / 1167141</v>
+        <v>Recibo de Cobro / 1484184</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-05-13</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E36">
-        <v>-20000</v>
+        <v>579.18</v>
       </c>
       <c r="F36">
-        <v>2026747.61</v>
+        <v>579.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Comprobante de Pago / 1116351</v>
+        <v>Comprobante de Pago / 1167141</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1111,90 +1111,90 @@
         <v>Pesos</v>
       </c>
       <c r="E37">
-        <v>-100000</v>
+        <v>-20000</v>
       </c>
       <c r="F37">
-        <v>2046747.61</v>
+        <v>2026747.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1116351</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C38">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="D38" t="str">
         <v>Pesos</v>
       </c>
       <c r="E38">
-        <v>-3174961.2</v>
+        <v>-100000</v>
       </c>
       <c r="F38">
-        <v>2146747.61</v>
+        <v>2046747.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Comprobante de Pago / 925746</v>
+        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="D39" t="str">
         <v>Pesos</v>
       </c>
       <c r="E39">
-        <v>-160000</v>
+        <v>-3174961.2</v>
       </c>
       <c r="F39">
-        <v>5321708.81</v>
+        <v>2146747.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 925746</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C40">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="D40" t="str">
         <v>Pesos</v>
       </c>
       <c r="E40">
-        <v>3896669.74</v>
+        <v>-160000</v>
       </c>
       <c r="F40">
-        <v>5481708.81</v>
+        <v>5321708.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="D41" t="str">
         <v>Pesos</v>
       </c>
       <c r="E41">
-        <v>-0.83</v>
+        <v>3896669.74</v>
       </c>
       <c r="F41">
-        <v>1585039.07</v>
+        <v>5481708.81</v>
       </c>
     </row>
     <row r="42">
@@ -1208,153 +1208,153 @@
         <v>0</v>
       </c>
       <c r="D42" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E42">
-        <v>0.14</v>
+        <v>-0.83</v>
       </c>
       <c r="F42">
-        <v>1.02</v>
+        <v>1585039.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Comprobante de Pago / 738461</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E43">
-        <v>-90000</v>
+        <v>0.14</v>
       </c>
       <c r="F43">
-        <v>1585039.9</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
+        <v>Comprobante de Pago / 738461</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C44">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D44" t="str">
         <v>Pesos</v>
       </c>
       <c r="E44">
-        <v>992035.79</v>
+        <v>-90000</v>
       </c>
       <c r="F44">
-        <v>1675039.9</v>
+        <v>1585039.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B45" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C45">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D45" t="str">
         <v>Pesos</v>
       </c>
       <c r="E45">
-        <v>1090257.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F45">
-        <v>683004.11</v>
+        <v>1675039.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B46" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D46" t="str">
         <v>Pesos</v>
       </c>
       <c r="E46">
-        <v>-407253.05</v>
+        <v>1090257.16</v>
       </c>
       <c r="F46">
-        <v>-407253.05</v>
+        <v>683004.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Comprobante de Pago / 642036</v>
+        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D47" t="str">
         <v>Pesos</v>
       </c>
       <c r="E47">
-        <v>-992034.79</v>
+        <v>-407253.05</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>-407253.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 642036</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C48">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D48" t="str">
         <v>Pesos</v>
       </c>
       <c r="E48">
-        <v>992035.79</v>
+        <v>-992034.79</v>
       </c>
       <c r="F48">
-        <v>992034.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B49" t="str">
-        <v>2025-12-29</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D49" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E49">
-        <v>0.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F49">
-        <v>0.88</v>
+        <v>992034.79</v>
       </c>
     </row>
     <row r="50">
@@ -1368,21 +1368,21 @@
         <v>0</v>
       </c>
       <c r="D50" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E50">
-        <v>-1</v>
+        <v>0.16</v>
       </c>
       <c r="F50">
-        <v>-1</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Comprobante de Pago / 2852932</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-11-13</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1391,78 +1391,78 @@
         <v>Pesos</v>
       </c>
       <c r="E51">
-        <v>-11190.76</v>
+        <v>-1</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2852932</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-11-04</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D52" t="str">
         <v>Pesos</v>
       </c>
       <c r="E52">
-        <v>-90093.05</v>
+        <v>-11190.76</v>
       </c>
       <c r="F52">
-        <v>11190.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Recibo de Cobro / 2884603</v>
+        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-04</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D53" t="str">
         <v>Pesos</v>
       </c>
       <c r="E53">
-        <v>50000</v>
+        <v>-90093.05</v>
       </c>
       <c r="F53">
-        <v>101283.81</v>
+        <v>11190.76</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
+        <v>Recibo de Cobro / 2884603</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-10-22</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D54" t="str">
         <v>Pesos</v>
       </c>
       <c r="E54">
-        <v>48024.29</v>
+        <v>50000</v>
       </c>
       <c r="F54">
-        <v>51283.81</v>
+        <v>101283.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-10-20</v>
+        <v>2025-10-22</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -1471,50 +1471,50 @@
         <v>Pesos</v>
       </c>
       <c r="E55">
-        <v>-46739.74</v>
+        <v>48024.29</v>
       </c>
       <c r="F55">
-        <v>3259.52</v>
+        <v>51283.81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Recibo de Cobro / 2742989</v>
+        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B56" t="str">
         <v>2025-10-20</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D56" t="str">
         <v>Pesos</v>
       </c>
       <c r="E56">
-        <v>50000</v>
+        <v>-46739.74</v>
       </c>
       <c r="F56">
-        <v>49999.26</v>
+        <v>3259.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Recibo de Cobro / 2742989</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E57">
-        <v>0.12</v>
+        <v>50000</v>
       </c>
       <c r="F57">
-        <v>0.72</v>
+        <v>49999.26</v>
       </c>
     </row>
     <row r="58">
@@ -1528,21 +1528,21 @@
         <v>0</v>
       </c>
       <c r="D58" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E58">
-        <v>-0.74</v>
+        <v>0.12</v>
       </c>
       <c r="F58">
-        <v>-0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Comprobante de Pago / 2317908</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-09-24</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1551,195 +1551,195 @@
         <v>Pesos</v>
       </c>
       <c r="E59">
-        <v>-6736.66</v>
+        <v>-0.74</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2317908</v>
       </c>
       <c r="B60" t="str">
         <v>2025-09-24</v>
       </c>
       <c r="C60">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D60" t="str">
         <v>Pesos</v>
       </c>
       <c r="E60">
-        <v>-403777.1</v>
+        <v>-6736.66</v>
       </c>
       <c r="F60">
-        <v>6736.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-09-22</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C61">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D61" t="str">
         <v>Pesos</v>
       </c>
       <c r="E61">
-        <v>388789.81</v>
+        <v>-403777.1</v>
       </c>
       <c r="F61">
-        <v>410513.76</v>
+        <v>6736.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B62" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C62">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D62" t="str">
         <v>Pesos</v>
       </c>
       <c r="E62">
-        <v>-1307333.32</v>
+        <v>388789.81</v>
       </c>
       <c r="F62">
-        <v>21723.95</v>
+        <v>410513.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B63" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C63">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="D63" t="str">
         <v>Pesos</v>
       </c>
       <c r="E63">
-        <v>999074.31</v>
+        <v>-1307333.32</v>
       </c>
       <c r="F63">
-        <v>1329057.27</v>
+        <v>21723.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B64" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C64">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D64" t="str">
         <v>Pesos</v>
       </c>
       <c r="E64">
-        <v>236100.29</v>
+        <v>999074.31</v>
       </c>
       <c r="F64">
-        <v>329982.96</v>
+        <v>1329057.27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B65" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C65">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D65" t="str">
         <v>Pesos</v>
       </c>
       <c r="E65">
-        <v>93882.67</v>
+        <v>236100.29</v>
       </c>
       <c r="F65">
-        <v>93882.67</v>
+        <v>329982.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Comprobante de Pago / 2284129</v>
+        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-09-20</v>
+        <v>2025-09-22</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D66" t="str">
         <v>Pesos</v>
       </c>
       <c r="E66">
-        <v>-6165.47</v>
+        <v>93882.67</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>93882.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2284129</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-09-18</v>
+        <v>2025-09-20</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67" t="str">
         <v>Pesos</v>
       </c>
       <c r="E67">
-        <v>-76616.13</v>
+        <v>-6165.47</v>
       </c>
       <c r="F67">
-        <v>6165.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B68" t="str">
         <v>2025-09-18</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="str">
         <v>Pesos</v>
       </c>
       <c r="E68">
-        <v>-20136.94</v>
+        <v>-76616.13</v>
       </c>
       <c r="F68">
-        <v>82781.6</v>
+        <v>6165.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B69" t="str">
         <v>2025-09-18</v>
@@ -1751,298 +1751,298 @@
         <v>Pesos</v>
       </c>
       <c r="E69">
-        <v>89518.34</v>
+        <v>-20136.94</v>
       </c>
       <c r="F69">
-        <v>102918.54</v>
+        <v>82781.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-18</v>
       </c>
       <c r="C70">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D70" t="str">
         <v>Pesos</v>
       </c>
       <c r="E70">
-        <v>138894.77</v>
+        <v>89518.34</v>
       </c>
       <c r="F70">
-        <v>13400.2</v>
+        <v>102918.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B71" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D71" t="str">
         <v>Pesos</v>
       </c>
       <c r="E71">
-        <v>-85739.5</v>
+        <v>138894.77</v>
       </c>
       <c r="F71">
-        <v>-125494.57</v>
+        <v>13400.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Comprobante de Pago / 2176779</v>
+        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B72" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72" t="str">
         <v>Pesos</v>
       </c>
       <c r="E72">
-        <v>-45869.67</v>
+        <v>-85739.5</v>
       </c>
       <c r="F72">
-        <v>-39755.07</v>
+        <v>-125494.57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2176779</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="C73">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D73" t="str">
         <v>Pesos</v>
       </c>
       <c r="E73">
-        <v>-952298.2</v>
+        <v>-45869.67</v>
       </c>
       <c r="F73">
-        <v>6114.6</v>
+        <v>-39755.07</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B74" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C74">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D74" t="str">
         <v>Pesos</v>
       </c>
       <c r="E74">
-        <v>-226481.32</v>
+        <v>-952298.2</v>
       </c>
       <c r="F74">
-        <v>958412.8</v>
+        <v>6114.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
+        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B75" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C75">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D75" t="str">
         <v>Pesos</v>
       </c>
       <c r="E75">
-        <v>-491658.83</v>
+        <v>-226481.32</v>
       </c>
       <c r="F75">
-        <v>1184894.12</v>
+        <v>958412.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Comprobante de Pago / 2093390</v>
+        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D76" t="str">
         <v>Pesos</v>
       </c>
       <c r="E76">
-        <v>-14000</v>
+        <v>-491658.83</v>
       </c>
       <c r="F76">
-        <v>1676552.95</v>
+        <v>1184894.12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2093390</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C77">
-        <v>3447</v>
+        <v>0</v>
       </c>
       <c r="D77" t="str">
         <v>Pesos</v>
       </c>
       <c r="E77">
-        <v>2699870.67</v>
+        <v>-14000</v>
       </c>
       <c r="F77">
-        <v>1690552.95</v>
+        <v>1676552.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B78" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C78">
-        <v>413</v>
+        <v>3447</v>
       </c>
       <c r="D78" t="str">
         <v>Pesos</v>
       </c>
       <c r="E78">
-        <v>-4194203.97</v>
+        <v>2699870.67</v>
       </c>
       <c r="F78">
-        <v>-1009317.72</v>
+        <v>1690552.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B79" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C79">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="D79" t="str">
         <v>Pesos</v>
       </c>
       <c r="E79">
-        <v>509153.55</v>
+        <v>-4194203.97</v>
       </c>
       <c r="F79">
-        <v>3184886.25</v>
+        <v>-1009317.72</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B80" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C80">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="D80" t="str">
         <v>Pesos</v>
       </c>
       <c r="E80">
-        <v>777951.6</v>
+        <v>509153.55</v>
       </c>
       <c r="F80">
-        <v>2675732.7</v>
+        <v>3184886.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B81" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C81">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="D81" t="str">
         <v>Pesos</v>
       </c>
       <c r="E81">
-        <v>1314506.19</v>
+        <v>777951.6</v>
       </c>
       <c r="F81">
-        <v>1897781.1</v>
+        <v>2675732.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B82" t="str">
-        <v>2025-08-18</v>
+        <v>2025-08-25</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D82" t="str">
         <v>Pesos</v>
       </c>
       <c r="E82">
-        <v>-19758.9</v>
+        <v>1314506.19</v>
       </c>
       <c r="F82">
-        <v>583274.91</v>
+        <v>1897781.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Comprobante de Pago / 1961788</v>
+        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B83" t="str">
         <v>2025-08-18</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83" t="str">
         <v>Pesos</v>
       </c>
       <c r="E83">
-        <v>-20000</v>
+        <v>-19758.9</v>
       </c>
       <c r="F83">
-        <v>603033.81</v>
+        <v>583274.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Comprobante de Pago / 1961788</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-18</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2051,15 +2051,15 @@
         <v>Pesos</v>
       </c>
       <c r="E84">
-        <v>-338.57</v>
+        <v>-20000</v>
       </c>
       <c r="F84">
-        <v>623033.81</v>
+        <v>603033.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B85" t="str">
         <v>2025-08-12</v>
@@ -2071,610 +2071,610 @@
         <v>Pesos</v>
       </c>
       <c r="E85">
-        <v>4824.94</v>
+        <v>-338.57</v>
       </c>
       <c r="F85">
-        <v>623372.38</v>
+        <v>623033.81</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B86" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D86" t="str">
         <v>Pesos</v>
       </c>
       <c r="E86">
-        <v>-100004.21</v>
+        <v>4824.94</v>
       </c>
       <c r="F86">
-        <v>618547.44</v>
+        <v>623372.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B87" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C87">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D87" t="str">
         <v>Pesos</v>
       </c>
       <c r="E87">
-        <v>710418.57</v>
+        <v>-100004.21</v>
       </c>
       <c r="F87">
-        <v>718551.65</v>
+        <v>618547.44</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-08-05</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D88" t="str">
         <v>Pesos</v>
       </c>
       <c r="E88">
-        <v>-190965.71</v>
+        <v>710418.57</v>
       </c>
       <c r="F88">
-        <v>8133.08</v>
+        <v>718551.65</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B89" t="str">
         <v>2025-08-05</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D89" t="str">
         <v>Pesos</v>
       </c>
       <c r="E89">
-        <v>182607.5</v>
+        <v>-190965.71</v>
       </c>
       <c r="F89">
-        <v>199098.79</v>
+        <v>8133.08</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
+        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-08-04</v>
+        <v>2025-08-05</v>
       </c>
       <c r="C90">
-        <v>2626</v>
+        <v>4</v>
       </c>
       <c r="D90" t="str">
         <v>Pesos</v>
       </c>
       <c r="E90">
-        <v>41762.85</v>
+        <v>182607.5</v>
       </c>
       <c r="F90">
-        <v>16491.29</v>
+        <v>199098.79</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
       </c>
       <c r="B91" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C91">
-        <v>1848</v>
+        <v>2626</v>
       </c>
       <c r="D91" t="str">
         <v>Pesos</v>
       </c>
       <c r="E91">
-        <v>1490983.97</v>
+        <v>41762.85</v>
       </c>
       <c r="F91">
-        <v>-25271.56</v>
+        <v>16491.29</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B92" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C92">
-        <v>225</v>
+        <v>1848</v>
       </c>
       <c r="D92" t="str">
         <v>Pesos</v>
       </c>
       <c r="E92">
-        <v>-1521989.55</v>
+        <v>1490983.97</v>
       </c>
       <c r="F92">
-        <v>-1516255.53</v>
+        <v>-25271.56</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-04</v>
       </c>
       <c r="C93">
-        <v>620</v>
+        <v>225</v>
       </c>
       <c r="D93" t="str">
         <v>Pesos</v>
       </c>
       <c r="E93">
-        <v>488389.62</v>
+        <v>-1521989.55</v>
       </c>
       <c r="F93">
-        <v>5734.02</v>
+        <v>-1516255.53</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B94" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C94">
-        <v>58</v>
+        <v>620</v>
       </c>
       <c r="D94" t="str">
         <v>Pesos</v>
       </c>
       <c r="E94">
-        <v>194738.35</v>
+        <v>488389.62</v>
       </c>
       <c r="F94">
-        <v>-482655.6</v>
+        <v>5734.02</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B95" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C95">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="D95" t="str">
         <v>Pesos</v>
       </c>
       <c r="E95">
-        <v>-393010.51</v>
+        <v>194738.35</v>
       </c>
       <c r="F95">
-        <v>-677393.95</v>
+        <v>-482655.6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B96" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C96">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D96" t="str">
         <v>Pesos</v>
       </c>
       <c r="E96">
-        <v>-285344.68</v>
+        <v>-393010.51</v>
       </c>
       <c r="F96">
-        <v>-284383.44</v>
+        <v>-677393.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-07-29</v>
+        <v>2025-07-30</v>
       </c>
       <c r="C97">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D97" t="str">
         <v>Pesos</v>
       </c>
       <c r="E97">
-        <v>-87826.28</v>
+        <v>-285344.68</v>
       </c>
       <c r="F97">
-        <v>961.24</v>
+        <v>-284383.44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-07-28</v>
+        <v>2025-07-29</v>
       </c>
       <c r="C98">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D98" t="str">
         <v>Pesos</v>
       </c>
       <c r="E98">
-        <v>-133937.09</v>
+        <v>-87826.28</v>
       </c>
       <c r="F98">
-        <v>88787.52</v>
+        <v>961.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B99" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C99">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D99" t="str">
         <v>Pesos</v>
       </c>
       <c r="E99">
-        <v>94844.81</v>
+        <v>-133937.09</v>
       </c>
       <c r="F99">
-        <v>222724.61</v>
+        <v>88787.52</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B100" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D100" t="str">
         <v>Pesos</v>
       </c>
       <c r="E100">
-        <v>127879.8</v>
+        <v>94844.81</v>
       </c>
       <c r="F100">
-        <v>127879.8</v>
+        <v>222724.61</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-07-24</v>
+        <v>2025-07-28</v>
       </c>
       <c r="C101">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D101" t="str">
         <v>Pesos</v>
       </c>
       <c r="E101">
-        <v>88972.8</v>
+        <v>127879.8</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>127879.8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Comprobante de Pago / 1761847</v>
+        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B102" t="str">
         <v>2025-07-24</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D102" t="str">
         <v>Pesos</v>
       </c>
       <c r="E102">
-        <v>-89024.62</v>
+        <v>88972.8</v>
       </c>
       <c r="F102">
-        <v>-88972.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
+        <v>Comprobante de Pago / 1761847</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-07-22</v>
+        <v>2025-07-24</v>
       </c>
       <c r="C103">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="D103" t="str">
         <v>Pesos</v>
       </c>
       <c r="E103">
-        <v>-3646.72</v>
+        <v>-89024.62</v>
       </c>
       <c r="F103">
-        <v>51.82</v>
+        <v>-88972.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B104" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C104">
-        <v>1984</v>
+        <v>235</v>
       </c>
       <c r="D104" t="str">
         <v>Pesos</v>
       </c>
       <c r="E104">
-        <v>-1482793.93</v>
+        <v>-3646.72</v>
       </c>
       <c r="F104">
-        <v>3698.54</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B105" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C105">
-        <v>121</v>
+        <v>1984</v>
       </c>
       <c r="D105" t="str">
         <v>Pesos</v>
       </c>
       <c r="E105">
-        <v>-345815.98</v>
+        <v>-1482793.93</v>
       </c>
       <c r="F105">
-        <v>1486492.47</v>
+        <v>3698.54</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B106" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C106">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D106" t="str">
         <v>Pesos</v>
       </c>
       <c r="E106">
-        <v>-354299.21</v>
+        <v>-345815.98</v>
       </c>
       <c r="F106">
-        <v>1832308.45</v>
+        <v>1486492.47</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-07-16</v>
+        <v>2025-07-22</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D107" t="str">
         <v>Pesos</v>
       </c>
       <c r="E107">
-        <v>2185800.13</v>
+        <v>-354299.21</v>
       </c>
       <c r="F107">
-        <v>2186607.66</v>
+        <v>1832308.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B108" t="str">
         <v>2025-07-16</v>
       </c>
       <c r="C108">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D108" t="str">
         <v>Pesos</v>
       </c>
       <c r="E108">
-        <v>-9888.53</v>
+        <v>2185800.13</v>
       </c>
       <c r="F108">
-        <v>807.53</v>
+        <v>2186607.66</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-07-14</v>
+        <v>2025-07-16</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D109" t="str">
         <v>Pesos</v>
       </c>
       <c r="E109">
-        <v>-1151507.11</v>
+        <v>-9888.53</v>
       </c>
       <c r="F109">
-        <v>10696.06</v>
+        <v>807.53</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B110" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C110">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="D110" t="str">
         <v>Pesos</v>
       </c>
       <c r="E110">
-        <v>-950578.94</v>
+        <v>-1151507.11</v>
       </c>
       <c r="F110">
-        <v>1162203.17</v>
+        <v>10696.06</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B111" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>1230</v>
       </c>
       <c r="D111" t="str">
         <v>Pesos</v>
       </c>
       <c r="E111">
-        <v>319945.64</v>
+        <v>-950578.94</v>
       </c>
       <c r="F111">
-        <v>2112782.11</v>
+        <v>1162203.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B112" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C112">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D112" t="str">
         <v>Pesos</v>
       </c>
       <c r="E112">
-        <v>641329.36</v>
+        <v>319945.64</v>
       </c>
       <c r="F112">
-        <v>1792836.47</v>
+        <v>2112782.11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Comprobante de Pago / 1676382</v>
+        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-07-12</v>
+        <v>2025-07-14</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D113" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E113">
-        <v>-0.48</v>
+        <v>641329.36</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>1792836.47</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 1676382</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-07-11</v>
+        <v>2025-07-12</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E114">
-        <v>1152116.72</v>
+        <v>-0.48</v>
       </c>
       <c r="F114">
-        <v>1151507.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
+        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B115" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C115">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D115" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E115">
-        <v>-218.93</v>
+        <v>1152116.72</v>
       </c>
       <c r="F115">
-        <v>0.48</v>
+        <v>1151507.11</v>
       </c>
     </row>
     <row r="116">
@@ -2685,61 +2685,61 @@
         <v>2025-07-11</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D116" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E116">
-        <v>-609.62</v>
+        <v>-218.93</v>
       </c>
       <c r="F116">
-        <v>-609.61</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
       </c>
       <c r="B117" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C117">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D117" t="str">
         <v>Pesos</v>
       </c>
       <c r="E117">
-        <v>-49685.47</v>
+        <v>-609.62</v>
       </c>
       <c r="F117">
-        <v>0.01</v>
+        <v>-609.61</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Comprobante de Pago / 1668056</v>
+        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B118" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D118" t="str">
         <v>Pesos</v>
       </c>
       <c r="E118">
-        <v>-3923.46</v>
+        <v>-49685.47</v>
       </c>
       <c r="F118">
-        <v>49685.48</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Comprobante de Pago / 1668048</v>
+        <v>Comprobante de Pago / 1668056</v>
       </c>
       <c r="B119" t="str">
         <v>2025-07-11</v>
@@ -2748,18 +2748,18 @@
         <v>0</v>
       </c>
       <c r="D119" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E119">
-        <v>-4.52</v>
+        <v>-3923.46</v>
       </c>
       <c r="F119">
-        <v>219.41</v>
+        <v>49685.48</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Recibo de Cobro / 1772632</v>
+        <v>Comprobante de Pago / 1668048</v>
       </c>
       <c r="B120" t="str">
         <v>2025-07-11</v>
@@ -2768,33 +2768,33 @@
         <v>0</v>
       </c>
       <c r="D120" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E120">
-        <v>50000</v>
+        <v>-4.52</v>
       </c>
       <c r="F120">
-        <v>53608.94</v>
+        <v>219.41</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Recibo de Cobro / 1772632</v>
       </c>
       <c r="B121" t="str">
-        <v>2025-07-10</v>
+        <v>2025-07-11</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E121">
-        <v>223.91</v>
+        <v>50000</v>
       </c>
       <c r="F121">
-        <v>223.93</v>
+        <v>53608.94</v>
       </c>
     </row>
     <row r="122">
@@ -2808,21 +2808,21 @@
         <v>0</v>
       </c>
       <c r="D122" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E122">
-        <v>-5.65</v>
+        <v>223.91</v>
       </c>
       <c r="F122">
-        <v>3608.94</v>
+        <v>223.93</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B123" t="str">
-        <v>2025-06-11</v>
+        <v>2025-07-10</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -2831,15 +2831,15 @@
         <v>Pesos</v>
       </c>
       <c r="E123">
-        <v>-552.42</v>
+        <v>-5.65</v>
       </c>
       <c r="F123">
-        <v>3614.59</v>
+        <v>3608.94</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dividendo en efectivo / TGSU2</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
       </c>
       <c r="B124" t="str">
         <v>2025-06-11</v>
@@ -2851,55 +2851,55 @@
         <v>Pesos</v>
       </c>
       <c r="E124">
-        <v>3975.67</v>
+        <v>-552.42</v>
       </c>
       <c r="F124">
-        <v>4167.01</v>
+        <v>3614.59</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
+        <v>Dividendo en efectivo / TGSU2</v>
       </c>
       <c r="B125" t="str">
-        <v>2025-06-09</v>
+        <v>2025-06-11</v>
       </c>
       <c r="C125">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="D125" t="str">
         <v>Pesos</v>
       </c>
       <c r="E125">
-        <v>-16502.47</v>
+        <v>3975.67</v>
       </c>
       <c r="F125">
-        <v>191.34</v>
+        <v>4167.01</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B126" t="str">
-        <v>2025-05-15</v>
+        <v>2025-06-09</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="D126" t="str">
         <v>Pesos</v>
       </c>
       <c r="E126">
-        <v>-958.17</v>
+        <v>-16502.47</v>
       </c>
       <c r="F126">
-        <v>16693.81</v>
+        <v>191.34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B127" t="str">
         <v>2025-05-15</v>
@@ -2911,18 +2911,18 @@
         <v>Pesos</v>
       </c>
       <c r="E127">
-        <v>13655.11</v>
+        <v>-958.17</v>
       </c>
       <c r="F127">
-        <v>17651.98</v>
+        <v>16693.81</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Renta y Amortización / TX28</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B128" t="str">
-        <v>2025-05-09</v>
+        <v>2025-05-15</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -2931,78 +2931,78 @@
         <v>Pesos</v>
       </c>
       <c r="E128">
-        <v>3718.21</v>
+        <v>13655.11</v>
       </c>
       <c r="F128">
-        <v>3996.87</v>
+        <v>17651.98</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
+        <v>Renta y Amortización / TX28</v>
       </c>
       <c r="B129" t="str">
-        <v>2025-04-25</v>
+        <v>2025-05-09</v>
       </c>
       <c r="C129">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="D129" t="str">
         <v>Pesos</v>
       </c>
       <c r="E129">
-        <v>-24260.75</v>
+        <v>3718.21</v>
       </c>
       <c r="F129">
-        <v>278.66</v>
+        <v>3996.87</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B130" t="str">
         <v>2025-04-25</v>
       </c>
       <c r="C130">
-        <v>25</v>
+        <v>1359</v>
       </c>
       <c r="D130" t="str">
         <v>Pesos</v>
       </c>
       <c r="E130">
-        <v>-975460.59</v>
+        <v>-24260.75</v>
       </c>
       <c r="F130">
-        <v>24539.41</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B131" t="str">
-        <v>2025-04-24</v>
+        <v>2025-04-25</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D131" t="str">
         <v>Pesos</v>
       </c>
       <c r="E131">
-        <v>1000000</v>
+        <v>-975460.59</v>
       </c>
       <c r="F131">
-        <v>1000000</v>
+        <v>24539.41</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B132" t="str">
-        <v>2025-04-21</v>
+        <v>2025-04-24</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3011,18 +3011,18 @@
         <v>Pesos</v>
       </c>
       <c r="E132">
-        <v>-999993.87</v>
+        <v>1000000</v>
       </c>
       <c r="F132">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B133" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-21</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3031,30 +3031,30 @@
         <v>Pesos</v>
       </c>
       <c r="E133">
-        <v>1000000</v>
+        <v>-999993.87</v>
       </c>
       <c r="F133">
-        <v>999993.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
+        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B134" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-16</v>
       </c>
       <c r="C134">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="D134" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E134">
-        <v>-206.02</v>
+        <v>1000000</v>
       </c>
       <c r="F134">
-        <v>0.02</v>
+        <v>999993.87</v>
       </c>
     </row>
     <row r="135">
@@ -3065,21 +3065,21 @@
         <v>2025-04-15</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="D135" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E135">
-        <v>-6.13</v>
+        <v>-206.02</v>
       </c>
       <c r="F135">
-        <v>-6.13</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Comprobante de Pago / 1061406</v>
+        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B136" t="str">
         <v>2025-04-15</v>
@@ -3088,18 +3088,18 @@
         <v>0</v>
       </c>
       <c r="D136" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E136">
-        <v>-2.85</v>
+        <v>-6.13</v>
       </c>
       <c r="F136">
-        <v>206.04</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Comprobante de Pago / 1061395</v>
+        <v>Comprobante de Pago / 1061406</v>
       </c>
       <c r="B137" t="str">
         <v>2025-04-15</v>
@@ -3108,33 +3108,33 @@
         <v>0</v>
       </c>
       <c r="D137" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E137">
-        <v>-2526.78</v>
+        <v>-2.85</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>206.04</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 1061395</v>
       </c>
       <c r="B138" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-15</v>
       </c>
       <c r="C138">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D138" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E138">
-        <v>208.88</v>
+        <v>-2526.78</v>
       </c>
       <c r="F138">
-        <v>208.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -3145,324 +3145,324 @@
         <v>2025-04-14</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D139" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E139">
-        <v>-5.66</v>
+        <v>208.88</v>
       </c>
       <c r="F139">
-        <v>2526.78</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B140" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C140">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D140" t="str">
         <v>Pesos</v>
       </c>
       <c r="E140">
-        <v>-257928.71</v>
+        <v>-5.66</v>
       </c>
       <c r="F140">
-        <v>2532.44</v>
+        <v>2526.78</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B141" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C141">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="D141" t="str">
         <v>Pesos</v>
       </c>
       <c r="E141">
-        <v>248438.89</v>
+        <v>-257928.71</v>
       </c>
       <c r="F141">
-        <v>260461.15</v>
+        <v>2532.44</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B142" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-14</v>
       </c>
       <c r="C142">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D142" t="str">
         <v>Pesos</v>
       </c>
       <c r="E142">
-        <v>-98040.09</v>
+        <v>248438.89</v>
       </c>
       <c r="F142">
-        <v>12022.26</v>
+        <v>260461.15</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B143" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D143" t="str">
         <v>Pesos</v>
       </c>
       <c r="E143">
-        <v>-486646.45</v>
+        <v>-98040.09</v>
       </c>
       <c r="F143">
-        <v>110062.35</v>
+        <v>12022.26</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B144" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C144">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D144" t="str">
         <v>Pesos</v>
       </c>
       <c r="E144">
-        <v>-93664.38</v>
+        <v>-486646.45</v>
       </c>
       <c r="F144">
-        <v>596708.8</v>
+        <v>110062.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B145" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C145">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D145" t="str">
         <v>Pesos</v>
       </c>
       <c r="E145">
-        <v>-309626.82</v>
+        <v>-93664.38</v>
       </c>
       <c r="F145">
-        <v>690373.18</v>
+        <v>596708.8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B146" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-08</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D146" t="str">
         <v>Pesos</v>
       </c>
       <c r="E146">
-        <v>1000000</v>
+        <v>-309626.82</v>
       </c>
       <c r="F146">
-        <v>1000000</v>
+        <v>690373.18</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B147" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-07</v>
       </c>
       <c r="C147">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D147" t="str">
         <v>Pesos</v>
       </c>
       <c r="E147">
-        <v>292856.94</v>
+        <v>1000000</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Comprobante de Pago / 945180</v>
+        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B148" t="str">
         <v>2025-04-04</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="D148" t="str">
         <v>Pesos</v>
       </c>
       <c r="E148">
-        <v>-292856.9</v>
+        <v>292856.94</v>
       </c>
       <c r="F148">
-        <v>-292856.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 945180</v>
       </c>
       <c r="B149" t="str">
-        <v>2025-03-27</v>
+        <v>2025-04-04</v>
       </c>
       <c r="C149">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D149" t="str">
         <v>Pesos</v>
       </c>
       <c r="E149">
-        <v>58913.7</v>
+        <v>-292856.9</v>
       </c>
       <c r="F149">
-        <v>-0.04</v>
+        <v>-292856.94</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Comprobante de Pago / 868926</v>
+        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B150" t="str">
         <v>2025-03-27</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D150" t="str">
         <v>Pesos</v>
       </c>
       <c r="E150">
-        <v>-58913.74</v>
+        <v>58913.7</v>
       </c>
       <c r="F150">
-        <v>-58913.74</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 868926</v>
       </c>
       <c r="B151" t="str">
-        <v>2025-03-20</v>
+        <v>2025-03-27</v>
       </c>
       <c r="C151">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D151" t="str">
         <v>Pesos</v>
       </c>
       <c r="E151">
-        <v>39165.79</v>
+        <v>-58913.74</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>-58913.74</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Comprobante de Pago / 814860</v>
+        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B152" t="str">
         <v>2025-03-20</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D152" t="str">
         <v>Pesos</v>
       </c>
       <c r="E152">
-        <v>-39165.79</v>
+        <v>39165.79</v>
       </c>
       <c r="F152">
-        <v>-39165.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 814860</v>
       </c>
       <c r="B153" t="str">
-        <v>2025-03-05</v>
+        <v>2025-03-20</v>
       </c>
       <c r="C153">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D153" t="str">
         <v>Pesos</v>
       </c>
       <c r="E153">
-        <v>48845.52</v>
+        <v>-39165.79</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>-39165.79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Comprobante de Pago / 636155</v>
+        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B154" t="str">
         <v>2025-03-05</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D154" t="str">
         <v>Pesos</v>
       </c>
       <c r="E154">
-        <v>-48845.53</v>
+        <v>48845.52</v>
       </c>
       <c r="F154">
-        <v>-48845.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 636155</v>
       </c>
       <c r="B155" t="str">
-        <v>2025-02-13</v>
+        <v>2025-03-05</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3471,58 +3471,58 @@
         <v>Pesos</v>
       </c>
       <c r="E155">
-        <v>-2208405.65</v>
+        <v>-48845.53</v>
       </c>
       <c r="F155">
-        <v>0.01</v>
+        <v>-48845.52</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B156" t="str">
-        <v>2025-02-12</v>
+        <v>2025-02-13</v>
       </c>
       <c r="C156">
-        <v>1921</v>
+        <v>0</v>
       </c>
       <c r="D156" t="str">
         <v>Pesos</v>
       </c>
       <c r="E156">
-        <v>-1490594.34</v>
+        <v>-2208405.65</v>
       </c>
       <c r="F156">
-        <v>2208405.66</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Recibo de Cobro / 513307</v>
+        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B157" t="str">
         <v>2025-02-12</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1921</v>
       </c>
       <c r="D157" t="str">
         <v>Pesos</v>
       </c>
       <c r="E157">
-        <v>149000</v>
+        <v>-1490594.34</v>
       </c>
       <c r="F157">
-        <v>3699000</v>
+        <v>2208405.66</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Comprobante de Pago / 451447</v>
+        <v>Recibo de Cobro / 513307</v>
       </c>
       <c r="B158" t="str">
-        <v>2025-02-11</v>
+        <v>2025-02-12</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3531,18 +3531,18 @@
         <v>Pesos</v>
       </c>
       <c r="E158">
-        <v>-300000</v>
+        <v>149000</v>
       </c>
       <c r="F158">
-        <v>3550000</v>
+        <v>3699000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Comprobante de Pago / 422123</v>
+        <v>Comprobante de Pago / 451447</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-02-10</v>
+        <v>2025-02-11</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3551,18 +3551,18 @@
         <v>Pesos</v>
       </c>
       <c r="E159">
-        <v>-150000</v>
+        <v>-300000</v>
       </c>
       <c r="F159">
-        <v>3850000</v>
+        <v>3550000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Recibo de Cobro / 392207</v>
+        <v>Comprobante de Pago / 422123</v>
       </c>
       <c r="B160" t="str">
-        <v>2025-02-03</v>
+        <v>2025-02-10</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3571,15 +3571,15 @@
         <v>Pesos</v>
       </c>
       <c r="E160">
-        <v>2000000</v>
+        <v>-150000</v>
       </c>
       <c r="F160">
-        <v>4000000</v>
+        <v>3850000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Recibo de Cobro / 392198</v>
+        <v>Recibo de Cobro / 392207</v>
       </c>
       <c r="B161" t="str">
         <v>2025-02-03</v>
@@ -3594,15 +3594,15 @@
         <v>2000000</v>
       </c>
       <c r="F161">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 392198</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-01-24</v>
+        <v>2025-02-03</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3611,18 +3611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E162">
-        <v>-284993.55</v>
+        <v>2000000</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Recibo de Cobro / 259074</v>
+        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-01-21</v>
+        <v>2025-01-24</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3631,30 +3631,30 @@
         <v>Pesos</v>
       </c>
       <c r="E163">
-        <v>285000</v>
+        <v>-284993.55</v>
       </c>
       <c r="F163">
-        <v>284993.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
+        <v>Recibo de Cobro / 259074</v>
       </c>
       <c r="B164" t="str">
         <v>2025-01-21</v>
       </c>
       <c r="C164">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="D164" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E164">
-        <v>244.89</v>
+        <v>285000</v>
       </c>
       <c r="F164">
-        <v>0.01</v>
+        <v>284993.55</v>
       </c>
     </row>
     <row r="165">
@@ -3665,21 +3665,21 @@
         <v>2025-01-21</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="D165" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E165">
-        <v>-6.45</v>
+        <v>244.89</v>
       </c>
       <c r="F165">
-        <v>-6.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Comprobante de Pago / 229359</v>
+        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B166" t="str">
         <v>2025-01-21</v>
@@ -3688,61 +3688,61 @@
         <v>0</v>
       </c>
       <c r="D166" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E166">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
       <c r="F166">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
+        <v>Comprobante de Pago / 229359</v>
       </c>
       <c r="B167" t="str">
-        <v>2025-01-17</v>
+        <v>2025-01-21</v>
       </c>
       <c r="C167">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D167" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E167">
-        <v>164237.44</v>
+        <v>-244.88</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>-244.88</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Comprobante de Pago / 195368</v>
+        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
       </c>
       <c r="B168" t="str">
         <v>2025-01-17</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D168" t="str">
         <v>Pesos</v>
       </c>
       <c r="E168">
-        <v>-164237.44</v>
+        <v>164237.44</v>
       </c>
       <c r="F168">
-        <v>-164237.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Comprobante de Pago / 128971</v>
+        <v>Comprobante de Pago / 195368</v>
       </c>
       <c r="B169" t="str">
-        <v>2025-01-11</v>
+        <v>2025-01-17</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3751,15 +3751,15 @@
         <v>Pesos</v>
       </c>
       <c r="E169">
-        <v>-1858.46</v>
+        <v>-164237.44</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>-164237.44</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comprobante de Pago / 128969</v>
+        <v>Comprobante de Pago / 128971</v>
       </c>
       <c r="B170" t="str">
         <v>2025-01-11</v>
@@ -3768,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="D170" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E170">
-        <v>-1.67</v>
+        <v>-1858.46</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -3779,27 +3779,27 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 128969</v>
       </c>
       <c r="B171" t="str">
-        <v>2025-01-09</v>
+        <v>2025-01-11</v>
       </c>
       <c r="C171">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D171" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E171">
-        <v>115257.86</v>
+        <v>-1.67</v>
       </c>
       <c r="F171">
-        <v>1858.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B172" t="str">
         <v>2025-01-09</v>
@@ -3808,13 +3808,13 @@
         <v>145</v>
       </c>
       <c r="D172" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E172">
-        <v>-100.23</v>
+        <v>115257.86</v>
       </c>
       <c r="F172">
-        <v>1.67</v>
+        <v>1858.46</v>
       </c>
     </row>
     <row r="173">
@@ -3825,56 +3825,56 @@
         <v>2025-01-09</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D173" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E173">
-        <v>-2.58</v>
+        <v>-100.23</v>
       </c>
       <c r="F173">
-        <v>-113399.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B174" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C174">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="D174" t="str">
         <v>Pesos</v>
       </c>
       <c r="E174">
-        <v>-113394.51</v>
+        <v>-2.58</v>
       </c>
       <c r="F174">
-        <v>-113396.82</v>
+        <v>-113399.4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B175" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D175" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E175">
-        <v>101.9</v>
+        <v>-113394.51</v>
       </c>
       <c r="F175">
-        <v>101.9</v>
+        <v>-113396.82</v>
       </c>
     </row>
     <row r="176">
@@ -3888,21 +3888,21 @@
         <v>0</v>
       </c>
       <c r="D176" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E176">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
       <c r="F176">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B177" t="str">
-        <v>2025-01-07</v>
+        <v>2025-01-09</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3911,18 +3911,18 @@
         <v>Pesos</v>
       </c>
       <c r="E177">
-        <v>-134999.75</v>
+        <v>-2.31</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Recibo de Cobro / 70445</v>
+        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B178" t="str">
-        <v>2025-01-06</v>
+        <v>2025-01-07</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3931,18 +3931,18 @@
         <v>Pesos</v>
       </c>
       <c r="E178">
-        <v>135000</v>
+        <v>-134999.75</v>
       </c>
       <c r="F178">
-        <v>134999.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 70445</v>
       </c>
       <c r="B179" t="str">
-        <v>2024-12-26</v>
+        <v>2025-01-06</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -3951,15 +3951,15 @@
         <v>Pesos</v>
       </c>
       <c r="E179">
-        <v>-57777.54</v>
+        <v>135000</v>
       </c>
       <c r="F179">
-        <v>-0.25</v>
+        <v>134999.75</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Comprobante de Pago / 3498761</v>
+        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B180" t="str">
         <v>2024-12-26</v>
@@ -3968,33 +3968,33 @@
         <v>0</v>
       </c>
       <c r="D180" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E180">
-        <v>-1.01</v>
+        <v>-57777.54</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
+        <v>Comprobante de Pago / 3498761</v>
       </c>
       <c r="B181" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181" t="str">
         <v>Dólares</v>
       </c>
       <c r="E181">
-        <v>1.01</v>
+        <v>-1.01</v>
       </c>
       <c r="F181">
-        <v>1.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -4005,176 +4005,176 @@
         <v>2024-12-26</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E182">
-        <v>-0.03</v>
+        <v>1.01</v>
       </c>
       <c r="F182">
-        <v>57777.29</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
+        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
       </c>
       <c r="B183" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D183" t="str">
         <v>Pesos</v>
       </c>
       <c r="E183">
-        <v>27372.9</v>
+        <v>-0.03</v>
       </c>
       <c r="F183">
-        <v>57777.32</v>
+        <v>57777.29</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
+        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
       </c>
       <c r="B184" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="str">
         <v>Pesos</v>
       </c>
       <c r="E184">
-        <v>29356.45</v>
+        <v>27372.9</v>
       </c>
       <c r="F184">
-        <v>30404.42</v>
+        <v>57777.32</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
       </c>
       <c r="B185" t="str">
-        <v>2024-12-18</v>
+        <v>2024-12-26</v>
       </c>
       <c r="C185">
-        <v>299</v>
+        <v>2</v>
       </c>
       <c r="D185" t="str">
         <v>Pesos</v>
       </c>
       <c r="E185">
-        <v>-255135.69</v>
+        <v>29356.45</v>
       </c>
       <c r="F185">
-        <v>1047.97</v>
+        <v>30404.42</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B186" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C186">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="D186" t="str">
         <v>Pesos</v>
       </c>
       <c r="E186">
-        <v>65556.13</v>
+        <v>-255135.69</v>
       </c>
       <c r="F186">
-        <v>256183.66</v>
+        <v>1047.97</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B187" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C187">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D187" t="str">
         <v>Pesos</v>
       </c>
       <c r="E187">
-        <v>58613.72</v>
+        <v>65556.13</v>
       </c>
       <c r="F187">
-        <v>190627.53</v>
+        <v>256183.66</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
+        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B188" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C188">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D188" t="str">
         <v>Pesos</v>
       </c>
       <c r="E188">
-        <v>69622.4</v>
+        <v>58613.72</v>
       </c>
       <c r="F188">
-        <v>132013.81</v>
+        <v>190627.53</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
       </c>
       <c r="B189" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C189">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D189" t="str">
         <v>Pesos</v>
       </c>
       <c r="E189">
-        <v>62392.37</v>
+        <v>69622.4</v>
       </c>
       <c r="F189">
-        <v>62391.41</v>
+        <v>132013.81</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B190" t="str">
-        <v>2024-12-17</v>
+        <v>2024-12-18</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D190" t="str">
         <v>Pesos</v>
       </c>
       <c r="E190">
-        <v>-0.53</v>
+        <v>62392.37</v>
       </c>
       <c r="F190">
-        <v>-0.96</v>
+        <v>62391.41</v>
       </c>
     </row>
     <row r="191">
@@ -4188,18 +4188,18 @@
         <v>0</v>
       </c>
       <c r="D191" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E191">
-        <v>0.12</v>
+        <v>-0.53</v>
       </c>
       <c r="F191">
-        <v>0.6</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B192" t="str">
         <v>2024-12-17</v>
@@ -4208,13 +4208,13 @@
         <v>0</v>
       </c>
       <c r="D192" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E192">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F192">
-        <v>-0.43</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="193">
@@ -4228,33 +4228,33 @@
         <v>0</v>
       </c>
       <c r="D193" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E193">
-        <v>0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F193">
-        <v>0.48</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B194" t="str">
-        <v>2024-12-13</v>
+        <v>2024-12-17</v>
       </c>
       <c r="C194">
         <v>0</v>
       </c>
       <c r="D194" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E194">
-        <v>-0.3</v>
+        <v>0.03</v>
       </c>
       <c r="F194">
-        <v>-0.3</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="195">
@@ -4268,293 +4268,293 @@
         <v>0</v>
       </c>
       <c r="D195" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E195">
-        <v>0.07</v>
+        <v>-0.3</v>
       </c>
       <c r="F195">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B196" t="str">
-        <v>2024-12-12</v>
+        <v>2024-12-13</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E196">
-        <v>-103588.95</v>
+        <v>0.07</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
+        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B197" t="str">
-        <v>2024-12-06</v>
+        <v>2024-12-12</v>
       </c>
       <c r="C197">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D197" t="str">
         <v>Pesos</v>
       </c>
       <c r="E197">
-        <v>102379.42</v>
+        <v>-103588.95</v>
       </c>
       <c r="F197">
-        <v>103588.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
       </c>
       <c r="B198" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C198">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="D198" t="str">
         <v>Pesos</v>
       </c>
       <c r="E198">
-        <v>-117184.31</v>
+        <v>102379.42</v>
       </c>
       <c r="F198">
-        <v>1209.53</v>
+        <v>103588.95</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
+        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B199" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C199">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="D199" t="str">
         <v>Pesos</v>
       </c>
       <c r="E199">
-        <v>27546.46</v>
+        <v>-117184.31</v>
       </c>
       <c r="F199">
-        <v>118393.84</v>
+        <v>1209.53</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
       </c>
       <c r="B200" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C200">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D200" t="str">
         <v>Pesos</v>
       </c>
       <c r="E200">
-        <v>89904.13</v>
+        <v>27546.46</v>
       </c>
       <c r="F200">
-        <v>90847.38</v>
+        <v>118393.84</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B201" t="str">
-        <v>2024-11-27</v>
+        <v>2024-12-06</v>
       </c>
       <c r="C201">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="D201" t="str">
         <v>Pesos</v>
       </c>
       <c r="E201">
-        <v>-91403.91</v>
+        <v>89904.13</v>
       </c>
       <c r="F201">
-        <v>943.25</v>
+        <v>90847.38</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
+        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B202" t="str">
         <v>2024-11-27</v>
       </c>
       <c r="C202">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D202" t="str">
         <v>Pesos</v>
       </c>
       <c r="E202">
-        <v>91674.44</v>
+        <v>-91403.91</v>
       </c>
       <c r="F202">
-        <v>92347.16</v>
+        <v>943.25</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
       </c>
       <c r="B203" t="str">
-        <v>2024-11-25</v>
+        <v>2024-11-27</v>
       </c>
       <c r="C203">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="D203" t="str">
         <v>Pesos</v>
       </c>
       <c r="E203">
-        <v>140157.43</v>
+        <v>91674.44</v>
       </c>
       <c r="F203">
-        <v>672.72</v>
+        <v>92347.16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Comprobante de Pago / 3169919</v>
+        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B204" t="str">
         <v>2024-11-25</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D204" t="str">
         <v>Pesos</v>
       </c>
       <c r="E204">
-        <v>-140000</v>
+        <v>140157.43</v>
       </c>
       <c r="F204">
-        <v>-139484.71</v>
+        <v>672.72</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 3169919</v>
       </c>
       <c r="B205" t="str">
-        <v>2024-11-21</v>
+        <v>2024-11-25</v>
       </c>
       <c r="C205">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="D205" t="str">
         <v>Pesos</v>
       </c>
       <c r="E205">
-        <v>-66912.23</v>
+        <v>-140000</v>
       </c>
       <c r="F205">
-        <v>515.29</v>
+        <v>-139484.71</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B206" t="str">
         <v>2024-11-21</v>
       </c>
       <c r="C206">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D206" t="str">
         <v>Pesos</v>
       </c>
       <c r="E206">
-        <v>66349.55</v>
+        <v>-66912.23</v>
       </c>
       <c r="F206">
-        <v>67427.52</v>
+        <v>515.29</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B207" t="str">
-        <v>2024-11-20</v>
+        <v>2024-11-21</v>
       </c>
       <c r="C207">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D207" t="str">
         <v>Pesos</v>
       </c>
       <c r="E207">
-        <v>-73882.48</v>
+        <v>66349.55</v>
       </c>
       <c r="F207">
-        <v>1077.97</v>
+        <v>67427.52</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
+        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B208" t="str">
         <v>2024-11-20</v>
       </c>
       <c r="C208">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="D208" t="str">
         <v>Pesos</v>
       </c>
       <c r="E208">
-        <v>73936.61</v>
+        <v>-73882.48</v>
       </c>
       <c r="F208">
-        <v>74960.45</v>
+        <v>1077.97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
       </c>
       <c r="B209" t="str">
-        <v>2024-11-15</v>
+        <v>2024-11-20</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D209" t="str">
         <v>Pesos</v>
       </c>
       <c r="E209">
-        <v>-0.22</v>
+        <v>73936.61</v>
       </c>
       <c r="F209">
-        <v>1023.84</v>
+        <v>74960.45</v>
       </c>
     </row>
     <row r="210">
@@ -4568,313 +4568,313 @@
         <v>0</v>
       </c>
       <c r="D210" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E210">
-        <v>0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="F210">
-        <v>0.38</v>
+        <v>1023.84</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B211" t="str">
-        <v>2024-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C211">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="D211" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E211">
-        <v>-139049.36</v>
+        <v>0.05</v>
       </c>
       <c r="F211">
-        <v>1024.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B212" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C212">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="D212" t="str">
         <v>Pesos</v>
       </c>
       <c r="E212">
-        <v>-52427.86</v>
+        <v>-139049.36</v>
       </c>
       <c r="F212">
-        <v>140073.42</v>
+        <v>1024.06</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
+        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B213" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C213">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D213" t="str">
         <v>Pesos</v>
       </c>
       <c r="E213">
-        <v>31736.7</v>
+        <v>-52427.86</v>
       </c>
       <c r="F213">
-        <v>192501.28</v>
+        <v>140073.42</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
       </c>
       <c r="B214" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C214">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="D214" t="str">
         <v>Pesos</v>
       </c>
       <c r="E214">
-        <v>99970.62</v>
+        <v>31736.7</v>
       </c>
       <c r="F214">
-        <v>160764.58</v>
+        <v>192501.28</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B215" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C215">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="D215" t="str">
         <v>Pesos</v>
       </c>
       <c r="E215">
-        <v>58861.67</v>
+        <v>99970.62</v>
       </c>
       <c r="F215">
-        <v>60793.96</v>
+        <v>160764.58</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
+        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B216" t="str">
-        <v>2024-10-29</v>
+        <v>2024-11-01</v>
       </c>
       <c r="C216">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="D216" t="str">
         <v>Pesos</v>
       </c>
       <c r="E216">
-        <v>-225944.56</v>
+        <v>58861.67</v>
       </c>
       <c r="F216">
-        <v>1932.29</v>
+        <v>60793.96</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
+        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
       </c>
       <c r="B217" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C217">
-        <v>100</v>
+        <v>297</v>
       </c>
       <c r="D217" t="str">
         <v>Pesos</v>
       </c>
       <c r="E217">
-        <v>102687.56</v>
+        <v>-225944.56</v>
       </c>
       <c r="F217">
-        <v>227876.85</v>
+        <v>1932.29</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
+        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
       </c>
       <c r="B218" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D218" t="str">
         <v>Pesos</v>
       </c>
       <c r="E218">
-        <v>37241.04</v>
+        <v>102687.56</v>
       </c>
       <c r="F218">
-        <v>125189.29</v>
+        <v>227876.85</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
       </c>
       <c r="B219" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C219">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D219" t="str">
         <v>Pesos</v>
       </c>
       <c r="E219">
-        <v>68729.8</v>
+        <v>37241.04</v>
       </c>
       <c r="F219">
-        <v>87948.25</v>
+        <v>125189.29</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
+        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B220" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C220">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D220" t="str">
         <v>Pesos</v>
       </c>
       <c r="E220">
-        <v>18248.61</v>
+        <v>68729.8</v>
       </c>
       <c r="F220">
-        <v>19218.45</v>
+        <v>87948.25</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Comprobante de Pago / 2861824</v>
+        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
       </c>
       <c r="B221" t="str">
-        <v>2024-10-25</v>
+        <v>2024-10-29</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D221" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E221">
-        <v>-8.71</v>
+        <v>18248.61</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>19218.45</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2861824</v>
       </c>
       <c r="B222" t="str">
-        <v>2024-10-23</v>
+        <v>2024-10-25</v>
       </c>
       <c r="C222">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D222" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E222">
-        <v>-71739.34</v>
+        <v>-8.71</v>
       </c>
       <c r="F222">
-        <v>969.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B223" t="str">
         <v>2024-10-23</v>
       </c>
       <c r="C223">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D223" t="str">
         <v>Pesos</v>
       </c>
       <c r="E223">
-        <v>52196.96</v>
+        <v>-71739.34</v>
       </c>
       <c r="F223">
-        <v>72709.18</v>
+        <v>969.84</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
+        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B224" t="str">
-        <v>2024-10-22</v>
+        <v>2024-10-23</v>
       </c>
       <c r="C224">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D224" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E224">
-        <v>-100</v>
+        <v>52196.96</v>
       </c>
       <c r="F224">
-        <v>8.71</v>
+        <v>72709.18</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
+        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
       </c>
       <c r="B225" t="str">
         <v>2024-10-22</v>
       </c>
       <c r="C225">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D225" t="str">
         <v>Dólares</v>
       </c>
       <c r="E225">
-        <v>99.71</v>
+        <v>-100</v>
       </c>
       <c r="F225">
-        <v>108.71</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="226">
@@ -4885,21 +4885,21 @@
         <v>2024-10-22</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="D226" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E226">
-        <v>-2.47</v>
+        <v>99.71</v>
       </c>
       <c r="F226">
-        <v>20512.22</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Recibo de Cobro / 3253687</v>
+        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B227" t="str">
         <v>2024-10-22</v>
@@ -4908,18 +4908,18 @@
         <v>0</v>
       </c>
       <c r="D227" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E227">
-        <v>100</v>
+        <v>-2.47</v>
       </c>
       <c r="F227">
-        <v>9</v>
+        <v>20512.22</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Comprobante de Pago / 2830288</v>
+        <v>Recibo de Cobro / 3253687</v>
       </c>
       <c r="B228" t="str">
         <v>2024-10-22</v>
@@ -4931,210 +4931,210 @@
         <v>Dólares</v>
       </c>
       <c r="E228">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F228">
-        <v>-91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
+        <v>Comprobante de Pago / 2830288</v>
       </c>
       <c r="B229" t="str">
-        <v>2024-10-21</v>
+        <v>2024-10-22</v>
       </c>
       <c r="C229">
         <v>0</v>
       </c>
       <c r="D229" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E229">
-        <v>185034.38</v>
+        <v>-100</v>
       </c>
       <c r="F229">
-        <v>20514.69</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
+        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B230" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D230" t="str">
         <v>Pesos</v>
       </c>
       <c r="E230">
-        <v>-1199.18</v>
+        <v>185034.38</v>
       </c>
       <c r="F230">
-        <v>-164519.69</v>
+        <v>20514.69</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
       </c>
       <c r="B231" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231" t="str">
         <v>Pesos</v>
       </c>
       <c r="E231">
-        <v>-243469.32</v>
+        <v>-1199.18</v>
       </c>
       <c r="F231">
-        <v>-163320.51</v>
+        <v>-164519.69</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B232" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C232">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D232" t="str">
         <v>Pesos</v>
       </c>
       <c r="E232">
-        <v>-129746.54</v>
+        <v>-243469.32</v>
       </c>
       <c r="F232">
-        <v>80148.81</v>
+        <v>-163320.51</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
+        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B233" t="str">
-        <v>2024-10-18</v>
+        <v>2024-10-21</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D233" t="str">
         <v>Pesos</v>
       </c>
       <c r="E233">
-        <v>-33573.99</v>
+        <v>-129746.54</v>
       </c>
       <c r="F233">
-        <v>209895.35</v>
+        <v>80148.81</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
       </c>
       <c r="B234" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C234">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D234" t="str">
         <v>Pesos</v>
       </c>
       <c r="E234">
-        <v>142249.86</v>
+        <v>-33573.99</v>
       </c>
       <c r="F234">
-        <v>243469.34</v>
+        <v>209895.35</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B235" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C235">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D235" t="str">
         <v>Pesos</v>
       </c>
       <c r="E235">
-        <v>9746.15</v>
+        <v>142249.86</v>
       </c>
       <c r="F235">
-        <v>101219.48</v>
+        <v>243469.34</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B236" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C236">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D236" t="str">
         <v>Pesos</v>
       </c>
       <c r="E236">
-        <v>29703.57</v>
+        <v>9746.15</v>
       </c>
       <c r="F236">
-        <v>91473.33</v>
+        <v>101219.48</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B237" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C237">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D237" t="str">
         <v>Pesos</v>
       </c>
       <c r="E237">
-        <v>57840.15</v>
+        <v>29703.57</v>
       </c>
       <c r="F237">
-        <v>61769.76</v>
+        <v>91473.33</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B238" t="str">
-        <v>2024-10-04</v>
+        <v>2024-10-18</v>
       </c>
       <c r="C238">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D238" t="str">
         <v>Pesos</v>
       </c>
       <c r="E238">
-        <v>-0.04</v>
+        <v>57840.15</v>
       </c>
       <c r="F238">
-        <v>3929.61</v>
+        <v>61769.76</v>
       </c>
     </row>
     <row r="239">
@@ -5148,33 +5148,33 @@
         <v>0</v>
       </c>
       <c r="D239" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E239">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F239">
-        <v>0.33</v>
+        <v>3929.61</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B240" t="str">
-        <v>2024-10-02</v>
+        <v>2024-10-04</v>
       </c>
       <c r="C240">
         <v>0</v>
       </c>
       <c r="D240" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E240">
-        <v>-0.51</v>
+        <v>0.01</v>
       </c>
       <c r="F240">
-        <v>3929.65</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="241">
@@ -5188,38 +5188,38 @@
         <v>0</v>
       </c>
       <c r="D241" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E241">
-        <v>0.12</v>
+        <v>-0.51</v>
       </c>
       <c r="F241">
-        <v>0.32</v>
+        <v>3929.65</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B242" t="str">
-        <v>2024-10-01</v>
+        <v>2024-10-02</v>
       </c>
       <c r="C242">
         <v>0</v>
       </c>
       <c r="D242" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E242">
-        <v>-296.59</v>
+        <v>0.12</v>
       </c>
       <c r="F242">
-        <v>3930.16</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B243" t="str">
         <v>2024-10-01</v>
@@ -5231,30 +5231,30 @@
         <v>Pesos</v>
       </c>
       <c r="E243">
-        <v>4226.79</v>
+        <v>-296.59</v>
       </c>
       <c r="F243">
-        <v>4226.75</v>
+        <v>3930.16</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B244" t="str">
-        <v>2024-09-27</v>
+        <v>2024-10-01</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E244">
-        <v>0.01</v>
+        <v>4226.79</v>
       </c>
       <c r="F244">
-        <v>0.2</v>
+        <v>4226.75</v>
       </c>
     </row>
     <row r="245">
@@ -5268,21 +5268,21 @@
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E245">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F245">
-        <v>-0.04</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B246" t="str">
-        <v>2024-09-25</v>
+        <v>2024-09-27</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -5291,50 +5291,50 @@
         <v>Pesos</v>
       </c>
       <c r="E246">
-        <v>-48646.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B247" t="str">
         <v>2024-09-25</v>
       </c>
       <c r="C247">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D247" t="str">
         <v>Pesos</v>
       </c>
       <c r="E247">
-        <v>48646.42</v>
+        <v>-48646.1</v>
       </c>
       <c r="F247">
-        <v>48646.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B248" t="str">
-        <v>2024-09-17</v>
+        <v>2024-09-25</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D248" t="str">
         <v>Pesos</v>
       </c>
       <c r="E248">
-        <v>-0.12</v>
+        <v>48646.42</v>
       </c>
       <c r="F248">
-        <v>-0.32</v>
+        <v>48646.1</v>
       </c>
     </row>
     <row r="249">
@@ -5348,33 +5348,33 @@
         <v>0</v>
       </c>
       <c r="D249" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E249">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F249">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B250" t="str">
-        <v>2024-09-13</v>
+        <v>2024-09-17</v>
       </c>
       <c r="C250">
         <v>0</v>
       </c>
       <c r="D250" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E250">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="F250">
-        <v>-0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="251">
@@ -5388,113 +5388,113 @@
         <v>0</v>
       </c>
       <c r="D251" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E251">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F251">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Renta / BPY26</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B252" t="str">
-        <v>2024-09-02</v>
+        <v>2024-09-13</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252" t="str">
-        <v>Dólares</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E252">
-        <v>1.45</v>
+        <v>0.03</v>
       </c>
       <c r="F252">
-        <v>9</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta / BPY26</v>
       </c>
       <c r="B253" t="str">
-        <v>2024-08-20</v>
+        <v>2024-09-02</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E253">
-        <v>-171669.97</v>
+        <v>1.45</v>
       </c>
       <c r="F253">
-        <v>-0.08</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B254" t="str">
-        <v>2024-08-19</v>
+        <v>2024-08-20</v>
       </c>
       <c r="C254">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D254" t="str">
         <v>Pesos</v>
       </c>
       <c r="E254">
-        <v>-243839.94</v>
+        <v>-171669.97</v>
       </c>
       <c r="F254">
-        <v>171669.89</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B255" t="str">
         <v>2024-08-19</v>
       </c>
       <c r="C255">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D255" t="str">
         <v>Pesos</v>
       </c>
       <c r="E255">
-        <v>-196906.93</v>
+        <v>-243839.94</v>
       </c>
       <c r="F255">
-        <v>415509.83</v>
+        <v>171669.89</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B256" t="str">
-        <v>2024-08-16</v>
+        <v>2024-08-19</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D256" t="str">
         <v>Pesos</v>
       </c>
       <c r="E256">
-        <v>-0.08</v>
+        <v>-196906.93</v>
       </c>
       <c r="F256">
-        <v>612416.76</v>
+        <v>415509.83</v>
       </c>
     </row>
     <row r="257">
@@ -5508,41 +5508,41 @@
         <v>0</v>
       </c>
       <c r="D257" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E257">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="F257">
-        <v>0.13</v>
+        <v>612416.76</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B258" t="str">
         <v>2024-08-16</v>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D258" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E258">
-        <v>13250.08</v>
+        <v>0.02</v>
       </c>
       <c r="F258">
-        <v>612416.84</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
+        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B259" t="str">
-        <v>2024-08-13</v>
+        <v>2024-08-16</v>
       </c>
       <c r="C259">
         <v>2</v>
@@ -5551,55 +5551,55 @@
         <v>Pesos</v>
       </c>
       <c r="E259">
-        <v>-35187.15</v>
+        <v>13250.08</v>
       </c>
       <c r="F259">
-        <v>599166.76</v>
+        <v>612416.84</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
       </c>
       <c r="B260" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C260">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D260" t="str">
         <v>Pesos</v>
       </c>
       <c r="E260">
-        <v>-31679.73</v>
+        <v>-35187.15</v>
       </c>
       <c r="F260">
-        <v>634353.91</v>
+        <v>599166.76</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
+        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B261" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C261">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D261" t="str">
         <v>Pesos</v>
       </c>
       <c r="E261">
-        <v>-18430.41</v>
+        <v>-31679.73</v>
       </c>
       <c r="F261">
-        <v>666033.64</v>
+        <v>634353.91</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
+        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
       </c>
       <c r="B262" t="str">
         <v>2024-08-13</v>
@@ -5611,355 +5611,355 @@
         <v>Pesos</v>
       </c>
       <c r="E262">
-        <v>-36144.97</v>
+        <v>-18430.41</v>
       </c>
       <c r="F262">
-        <v>684464.05</v>
+        <v>666033.64</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
+        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
       </c>
       <c r="B263" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C263">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D263" t="str">
         <v>Pesos</v>
       </c>
       <c r="E263">
-        <v>-30045.2</v>
+        <v>-36144.97</v>
       </c>
       <c r="F263">
-        <v>720609.02</v>
+        <v>684464.05</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
+        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
       </c>
       <c r="B264" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C264">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D264" t="str">
         <v>Pesos</v>
       </c>
       <c r="E264">
-        <v>-35590.45</v>
+        <v>-30045.2</v>
       </c>
       <c r="F264">
-        <v>750654.22</v>
+        <v>720609.02</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
       </c>
       <c r="B265" t="str">
-        <v>2024-08-12</v>
+        <v>2024-08-13</v>
       </c>
       <c r="C265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D265" t="str">
         <v>Pesos</v>
       </c>
       <c r="E265">
-        <v>-500000</v>
+        <v>-35590.45</v>
       </c>
       <c r="F265">
-        <v>786244.67</v>
+        <v>750654.22</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
+        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B266" t="str">
-        <v>2024-08-09</v>
+        <v>2024-08-12</v>
       </c>
       <c r="C266">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D266" t="str">
         <v>Pesos</v>
       </c>
       <c r="E266">
-        <v>-18274.14</v>
+        <v>-500000</v>
       </c>
       <c r="F266">
-        <v>1286244.67</v>
+        <v>786244.67</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B267" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C267">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D267" t="str">
         <v>Pesos</v>
       </c>
       <c r="E267">
-        <v>-17417.14</v>
+        <v>-18274.14</v>
       </c>
       <c r="F267">
-        <v>1304518.81</v>
+        <v>1286244.67</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B268" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C268">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D268" t="str">
         <v>Pesos</v>
       </c>
       <c r="E268">
-        <v>-49536.26</v>
+        <v>-17417.14</v>
       </c>
       <c r="F268">
-        <v>1321935.95</v>
+        <v>1304518.81</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B269" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D269" t="str">
         <v>Pesos</v>
       </c>
       <c r="E269">
-        <v>-14089.99</v>
+        <v>-49536.26</v>
       </c>
       <c r="F269">
-        <v>1371472.21</v>
+        <v>1321935.95</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B270" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C270">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D270" t="str">
         <v>Pesos</v>
       </c>
       <c r="E270">
-        <v>-85669.13</v>
+        <v>-14089.99</v>
       </c>
       <c r="F270">
-        <v>1385562.2</v>
+        <v>1371472.21</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B271" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C271">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D271" t="str">
         <v>Pesos</v>
       </c>
       <c r="E271">
-        <v>-14926.81</v>
+        <v>-85669.13</v>
       </c>
       <c r="F271">
-        <v>1471231.33</v>
+        <v>1385562.2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
+        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B272" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C272">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="D272" t="str">
         <v>Pesos</v>
       </c>
       <c r="E272">
-        <v>-88949.9</v>
+        <v>-14926.81</v>
       </c>
       <c r="F272">
-        <v>1486158.14</v>
+        <v>1471231.33</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
       </c>
       <c r="B273" t="str">
-        <v>2024-08-08</v>
+        <v>2024-08-09</v>
       </c>
       <c r="C273">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D273" t="str">
         <v>Pesos</v>
       </c>
       <c r="E273">
-        <v>-500000</v>
+        <v>-88949.9</v>
       </c>
       <c r="F273">
-        <v>1575108.04</v>
+        <v>1486158.14</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B274" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C274">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D274" t="str">
         <v>Pesos</v>
       </c>
       <c r="E274">
-        <v>-20325.87</v>
+        <v>-500000</v>
       </c>
       <c r="F274">
-        <v>2075108.04</v>
+        <v>1575108.04</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B275" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C275">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D275" t="str">
         <v>Pesos</v>
       </c>
       <c r="E275">
-        <v>-46136.52</v>
+        <v>-20325.87</v>
       </c>
       <c r="F275">
-        <v>2095433.91</v>
+        <v>2075108.04</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
+        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B276" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D276" t="str">
         <v>Pesos</v>
       </c>
       <c r="E276">
-        <v>-27927.91</v>
+        <v>-46136.52</v>
       </c>
       <c r="F276">
-        <v>2141570.43</v>
+        <v>2095433.91</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
       </c>
       <c r="B277" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C277">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D277" t="str">
         <v>Pesos</v>
       </c>
       <c r="E277">
-        <v>-50260.67</v>
+        <v>-27927.91</v>
       </c>
       <c r="F277">
-        <v>2169498.34</v>
+        <v>2141570.43</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
+        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B278" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C278">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="D278" t="str">
         <v>Pesos</v>
       </c>
       <c r="E278">
-        <v>-37506.08</v>
+        <v>-50260.67</v>
       </c>
       <c r="F278">
-        <v>2219759.01</v>
+        <v>2169498.34</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
       </c>
       <c r="B279" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C279">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D279" t="str">
         <v>Pesos</v>
       </c>
       <c r="E279">
-        <v>-28280.79</v>
+        <v>-37506.08</v>
       </c>
       <c r="F279">
-        <v>2257265.09</v>
+        <v>2219759.01</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B280" t="str">
         <v>2024-08-08</v>
@@ -5971,115 +5971,115 @@
         <v>Pesos</v>
       </c>
       <c r="E280">
-        <v>-53133.61</v>
+        <v>-28280.79</v>
       </c>
       <c r="F280">
-        <v>2285545.88</v>
+        <v>2257265.09</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B281" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C281">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D281" t="str">
         <v>Pesos</v>
       </c>
       <c r="E281">
-        <v>-28069.07</v>
+        <v>-53133.61</v>
       </c>
       <c r="F281">
-        <v>2338679.49</v>
+        <v>2285545.88</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B282" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D282" t="str">
         <v>Pesos</v>
       </c>
       <c r="E282">
-        <v>-19937.71</v>
+        <v>-28069.07</v>
       </c>
       <c r="F282">
-        <v>2366748.56</v>
+        <v>2338679.49</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
+        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B283" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C283">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D283" t="str">
         <v>Pesos</v>
       </c>
       <c r="E283">
-        <v>-40228.29</v>
+        <v>-19937.71</v>
       </c>
       <c r="F283">
-        <v>2386686.27</v>
+        <v>2366748.56</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
       </c>
       <c r="B284" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C284">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D284" t="str">
         <v>Pesos</v>
       </c>
       <c r="E284">
-        <v>-25407.34</v>
+        <v>-40228.29</v>
       </c>
       <c r="F284">
-        <v>2426914.56</v>
+        <v>2386686.27</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B285" t="str">
-        <v>2024-08-05</v>
+        <v>2024-08-08</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D285" t="str">
         <v>Pesos</v>
       </c>
       <c r="E285">
-        <v>1000000</v>
+        <v>-25407.34</v>
       </c>
       <c r="F285">
-        <v>2452321.9</v>
+        <v>2426914.56</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B286" t="str">
         <v>2024-08-05</v>
@@ -6091,15 +6091,15 @@
         <v>Pesos</v>
       </c>
       <c r="E286">
-        <v>218666.47</v>
+        <v>1000000</v>
       </c>
       <c r="F286">
-        <v>1452321.9</v>
+        <v>2452321.9</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
+        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B287" t="str">
         <v>2024-08-05</v>
@@ -6111,15 +6111,15 @@
         <v>Pesos</v>
       </c>
       <c r="E287">
-        <v>164626.92</v>
+        <v>218666.47</v>
       </c>
       <c r="F287">
-        <v>1233655.43</v>
+        <v>1452321.9</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B288" t="str">
         <v>2024-08-05</v>
@@ -6131,155 +6131,155 @@
         <v>Pesos</v>
       </c>
       <c r="E288">
-        <v>152793.11</v>
+        <v>164626.92</v>
       </c>
       <c r="F288">
-        <v>1069028.51</v>
+        <v>1233655.43</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
+        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B289" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C289">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D289" t="str">
         <v>Pesos</v>
       </c>
       <c r="E289">
-        <v>55836.76</v>
+        <v>152793.11</v>
       </c>
       <c r="F289">
-        <v>916235.4</v>
+        <v>1069028.51</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
       </c>
       <c r="B290" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C290">
-        <v>1416</v>
+        <v>4</v>
       </c>
       <c r="D290" t="str">
         <v>Pesos</v>
       </c>
       <c r="E290">
-        <v>-879220.78</v>
+        <v>55836.76</v>
       </c>
       <c r="F290">
-        <v>860398.64</v>
+        <v>916235.4</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B291" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C291">
-        <v>46</v>
+        <v>1416</v>
       </c>
       <c r="D291" t="str">
         <v>Pesos</v>
       </c>
       <c r="E291">
-        <v>96717.6</v>
+        <v>-879220.78</v>
       </c>
       <c r="F291">
-        <v>1739619.42</v>
+        <v>860398.64</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B292" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C292">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D292" t="str">
         <v>Pesos</v>
       </c>
       <c r="E292">
-        <v>159943.07</v>
+        <v>96717.6</v>
       </c>
       <c r="F292">
-        <v>1642901.82</v>
+        <v>1739619.42</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B293" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C293">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D293" t="str">
         <v>Pesos</v>
       </c>
       <c r="E293">
-        <v>70757.98</v>
+        <v>159943.07</v>
       </c>
       <c r="F293">
-        <v>1482958.75</v>
+        <v>1642901.82</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B294" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C294">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D294" t="str">
         <v>Pesos</v>
       </c>
       <c r="E294">
-        <v>96479.58</v>
+        <v>70757.98</v>
       </c>
       <c r="F294">
-        <v>1412200.77</v>
+        <v>1482958.75</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
+        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B295" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D295" t="str">
         <v>Pesos</v>
       </c>
       <c r="E295">
-        <v>52117.62</v>
+        <v>96479.58</v>
       </c>
       <c r="F295">
-        <v>1315721.19</v>
+        <v>1412200.77</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
       </c>
       <c r="B296" t="str">
         <v>2024-08-05</v>
@@ -6291,135 +6291,135 @@
         <v>Pesos</v>
       </c>
       <c r="E296">
-        <v>45423.16</v>
+        <v>52117.62</v>
       </c>
       <c r="F296">
-        <v>1263603.57</v>
+        <v>1315721.19</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B297" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C297">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="D297" t="str">
         <v>Pesos</v>
       </c>
       <c r="E297">
-        <v>59565.82</v>
+        <v>45423.16</v>
       </c>
       <c r="F297">
-        <v>1218180.41</v>
+        <v>1263603.57</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B298" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C298">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="D298" t="str">
         <v>Pesos</v>
       </c>
       <c r="E298">
-        <v>101983.91</v>
+        <v>59565.82</v>
       </c>
       <c r="F298">
-        <v>1158614.59</v>
+        <v>1218180.41</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B299" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C299">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D299" t="str">
         <v>Pesos</v>
       </c>
       <c r="E299">
-        <v>59530.13</v>
+        <v>101983.91</v>
       </c>
       <c r="F299">
-        <v>1056630.68</v>
+        <v>1158614.59</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B300" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C300">
-        <v>1536</v>
+        <v>61</v>
       </c>
       <c r="D300" t="str">
         <v>Pesos</v>
       </c>
       <c r="E300">
-        <v>942562.63</v>
+        <v>59530.13</v>
       </c>
       <c r="F300">
-        <v>997100.55</v>
+        <v>1056630.68</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B301" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C301">
-        <v>16</v>
+        <v>1536</v>
       </c>
       <c r="D301" t="str">
         <v>Pesos</v>
       </c>
       <c r="E301">
-        <v>53000.3</v>
+        <v>942562.63</v>
       </c>
       <c r="F301">
-        <v>54537.92</v>
+        <v>997100.55</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B302" t="str">
-        <v>2024-07-24</v>
+        <v>2024-08-05</v>
       </c>
       <c r="C302">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D302" t="str">
         <v>Pesos</v>
       </c>
       <c r="E302">
-        <v>-116.05</v>
+        <v>53000.3</v>
       </c>
       <c r="F302">
-        <v>1537.62</v>
+        <v>54537.92</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B303" t="str">
         <v>2024-07-24</v>
@@ -6431,18 +6431,18 @@
         <v>Pesos</v>
       </c>
       <c r="E303">
-        <v>1653.89</v>
+        <v>-116.05</v>
       </c>
       <c r="F303">
-        <v>1653.67</v>
+        <v>1537.62</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B304" t="str">
-        <v>2024-07-10</v>
+        <v>2024-07-24</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -6451,10 +6451,10 @@
         <v>Pesos</v>
       </c>
       <c r="E304">
-        <v>-0.21</v>
+        <v>1653.89</v>
       </c>
       <c r="F304">
-        <v>-0.22</v>
+        <v>1653.67</v>
       </c>
     </row>
     <row r="305">
@@ -6468,158 +6468,158 @@
         <v>0</v>
       </c>
       <c r="D305" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E305">
-        <v>5.25</v>
+        <v>-0.21</v>
       </c>
       <c r="F305">
-        <v>7.55</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B306" t="str">
-        <v>2024-07-08</v>
+        <v>2024-07-10</v>
       </c>
       <c r="C306">
         <v>0</v>
       </c>
       <c r="D306" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E306">
-        <v>-4402.49</v>
+        <v>5.25</v>
       </c>
       <c r="F306">
-        <v>-0.01</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
+        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B307" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D307" t="str">
         <v>Pesos</v>
       </c>
       <c r="E307">
-        <v>-38067.66</v>
+        <v>-4402.49</v>
       </c>
       <c r="F307">
-        <v>4402.48</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
       </c>
       <c r="B308" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D308" t="str">
         <v>Pesos</v>
       </c>
       <c r="E308">
-        <v>-47346.39</v>
+        <v>-38067.66</v>
       </c>
       <c r="F308">
-        <v>42470.14</v>
+        <v>4402.48</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B309" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D309" t="str">
         <v>Pesos</v>
       </c>
       <c r="E309">
-        <v>15580.74</v>
+        <v>-47346.39</v>
       </c>
       <c r="F309">
-        <v>89816.53</v>
+        <v>42470.14</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B310" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C310">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D310" t="str">
         <v>Pesos</v>
       </c>
       <c r="E310">
-        <v>34892.52</v>
+        <v>15580.74</v>
       </c>
       <c r="F310">
-        <v>74235.79</v>
+        <v>89816.53</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B311" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C311">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D311" t="str">
         <v>Pesos</v>
       </c>
       <c r="E311">
-        <v>37865.35</v>
+        <v>34892.52</v>
       </c>
       <c r="F311">
-        <v>39343.27</v>
+        <v>74235.79</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
+        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B312" t="str">
-        <v>2024-07-02</v>
+        <v>2024-07-08</v>
       </c>
       <c r="C312">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D312" t="str">
         <v>Pesos</v>
       </c>
       <c r="E312">
-        <v>-152584.35</v>
+        <v>37865.35</v>
       </c>
       <c r="F312">
-        <v>1477.92</v>
+        <v>39343.27</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
+        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B313" t="str">
         <v>2024-07-02</v>
@@ -6631,90 +6631,90 @@
         <v>Pesos</v>
       </c>
       <c r="E313">
-        <v>151114.01</v>
+        <v>-152584.35</v>
       </c>
       <c r="F313">
-        <v>154062.27</v>
+        <v>1477.92</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
+        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B314" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C314">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D314" t="str">
         <v>Pesos</v>
       </c>
       <c r="E314">
-        <v>-108902.21</v>
+        <v>151114.01</v>
       </c>
       <c r="F314">
-        <v>2948.26</v>
+        <v>154062.27</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
       </c>
       <c r="B315" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C315">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D315" t="str">
         <v>Pesos</v>
       </c>
       <c r="E315">
-        <v>-41051.01</v>
+        <v>-108902.21</v>
       </c>
       <c r="F315">
-        <v>111850.47</v>
+        <v>2948.26</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
+        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B316" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C316">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D316" t="str">
         <v>Pesos</v>
       </c>
       <c r="E316">
-        <v>151431.18</v>
+        <v>-41051.01</v>
       </c>
       <c r="F316">
-        <v>152901.48</v>
+        <v>111850.47</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B317" t="str">
-        <v>2024-07-01</v>
+        <v>2024-07-02</v>
       </c>
       <c r="C317">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D317" t="str">
         <v>Pesos</v>
       </c>
       <c r="E317">
-        <v>-0.04</v>
+        <v>151431.18</v>
       </c>
       <c r="F317">
-        <v>1470.3</v>
+        <v>152901.48</v>
       </c>
     </row>
     <row r="318">
@@ -6728,18 +6728,18 @@
         <v>0</v>
       </c>
       <c r="D318" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E318">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F318">
-        <v>0.11</v>
+        <v>1470.3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B319" t="str">
         <v>2024-07-01</v>
@@ -6748,18 +6748,18 @@
         <v>0</v>
       </c>
       <c r="D319" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E319">
-        <v>-110.98</v>
+        <v>0.01</v>
       </c>
       <c r="F319">
-        <v>1470.34</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B320" t="str">
         <v>2024-07-01</v>
@@ -6771,18 +6771,18 @@
         <v>Pesos</v>
       </c>
       <c r="E320">
-        <v>1581.51</v>
+        <v>-110.98</v>
       </c>
       <c r="F320">
-        <v>1581.32</v>
+        <v>1470.34</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B321" t="str">
-        <v>2024-06-27</v>
+        <v>2024-07-01</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -6791,10 +6791,10 @@
         <v>Pesos</v>
       </c>
       <c r="E321">
-        <v>-0.12</v>
+        <v>1581.51</v>
       </c>
       <c r="F321">
-        <v>-0.19</v>
+        <v>1581.32</v>
       </c>
     </row>
     <row r="322">
@@ -6808,38 +6808,38 @@
         <v>0</v>
       </c>
       <c r="D322" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E322">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F322">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B323" t="str">
-        <v>2024-06-24</v>
+        <v>2024-06-27</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E323">
-        <v>-175.43</v>
+        <v>0.03</v>
       </c>
       <c r="F323">
-        <v>-0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
+        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
       </c>
       <c r="B324" t="str">
         <v>2024-06-24</v>
@@ -6851,15 +6851,15 @@
         <v>Pesos</v>
       </c>
       <c r="E324">
-        <v>-150000</v>
+        <v>-175.43</v>
       </c>
       <c r="F324">
-        <v>175.36</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B325" t="str">
         <v>2024-06-24</v>
@@ -6871,18 +6871,18 @@
         <v>Pesos</v>
       </c>
       <c r="E325">
-        <v>-150447.89</v>
+        <v>-150000</v>
       </c>
       <c r="F325">
-        <v>150175.36</v>
+        <v>175.36</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B326" t="str">
-        <v>2024-06-19</v>
+        <v>2024-06-24</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -6891,10 +6891,10 @@
         <v>Pesos</v>
       </c>
       <c r="E326">
-        <v>-0.07</v>
+        <v>-150447.89</v>
       </c>
       <c r="F326">
-        <v>300623.25</v>
+        <v>150175.36</v>
       </c>
     </row>
     <row r="327">
@@ -6908,18 +6908,18 @@
         <v>0</v>
       </c>
       <c r="D327" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E327">
-        <v>0.02</v>
+        <v>-0.07</v>
       </c>
       <c r="F327">
-        <v>0.07</v>
+        <v>300623.25</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B328" t="str">
         <v>2024-06-19</v>
@@ -6928,21 +6928,21 @@
         <v>0</v>
       </c>
       <c r="D328" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E328">
-        <v>300000</v>
+        <v>0.02</v>
       </c>
       <c r="F328">
-        <v>300623.32</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Dividendo en efectivo / INTC</v>
+        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B329" t="str">
-        <v>2024-06-04</v>
+        <v>2024-06-19</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -6951,10 +6951,10 @@
         <v>Pesos</v>
       </c>
       <c r="E329">
-        <v>-0.19</v>
+        <v>300000</v>
       </c>
       <c r="F329">
-        <v>623.32</v>
+        <v>300623.32</v>
       </c>
     </row>
     <row r="330">
@@ -6968,161 +6968,161 @@
         <v>0</v>
       </c>
       <c r="D330" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E330">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="F330">
-        <v>0.05</v>
+        <v>623.32</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
+        <v>Dividendo en efectivo / INTC</v>
       </c>
       <c r="B331" t="str">
-        <v>2024-05-31</v>
+        <v>2024-06-04</v>
       </c>
       <c r="C331">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D331" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E331">
-        <v>55120.7</v>
+        <v>0.05</v>
       </c>
       <c r="F331">
-        <v>623.51</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B332" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C332">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D332" t="str">
         <v>Pesos</v>
       </c>
       <c r="E332">
-        <v>-36734.79</v>
+        <v>55120.7</v>
       </c>
       <c r="F332">
-        <v>-54497.19</v>
+        <v>623.51</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
+        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B333" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C333">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D333" t="str">
         <v>Pesos</v>
       </c>
       <c r="E333">
-        <v>-59561.06</v>
+        <v>-36734.79</v>
       </c>
       <c r="F333">
-        <v>-17762.4</v>
+        <v>-54497.19</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
+        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
       </c>
       <c r="B334" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C334">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D334" t="str">
         <v>Pesos</v>
       </c>
       <c r="E334">
-        <v>38496.62</v>
+        <v>-59561.06</v>
       </c>
       <c r="F334">
-        <v>41798.66</v>
+        <v>-17762.4</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
+        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
       </c>
       <c r="B335" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C335">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D335" t="str">
         <v>Pesos</v>
       </c>
       <c r="E335">
-        <v>48021.6</v>
+        <v>38496.62</v>
       </c>
       <c r="F335">
-        <v>3302.04</v>
+        <v>41798.66</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
+        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
       </c>
       <c r="B336" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C336">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D336" t="str">
         <v>Pesos</v>
       </c>
       <c r="E336">
-        <v>-47487.54</v>
+        <v>48021.6</v>
       </c>
       <c r="F336">
-        <v>-44719.56</v>
+        <v>3302.04</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Movimiento Manual / Ret IIGG - GGAL</v>
+        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
       </c>
       <c r="B337" t="str">
-        <v>2024-05-27</v>
+        <v>2024-05-31</v>
       </c>
       <c r="C337">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D337" t="str">
         <v>Pesos</v>
       </c>
       <c r="E337">
-        <v>-73.45</v>
+        <v>-47487.54</v>
       </c>
       <c r="F337">
-        <v>2767.98</v>
+        <v>-44719.56</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG - GGAL</v>
       </c>
       <c r="B338" t="str">
-        <v>2024-05-24</v>
+        <v>2024-05-27</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -7131,55 +7131,55 @@
         <v>Pesos</v>
       </c>
       <c r="E338">
-        <v>1518.11</v>
+        <v>-73.45</v>
       </c>
       <c r="F338">
-        <v>2841.43</v>
+        <v>2767.98</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B339" t="str">
-        <v>2024-05-23</v>
+        <v>2024-05-24</v>
       </c>
       <c r="C339">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D339" t="str">
         <v>Pesos</v>
       </c>
       <c r="E339">
-        <v>-81669.11</v>
+        <v>1518.11</v>
       </c>
       <c r="F339">
-        <v>1323.32</v>
+        <v>2841.43</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
+        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B340" t="str">
-        <v>2024-05-21</v>
+        <v>2024-05-23</v>
       </c>
       <c r="C340">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D340" t="str">
         <v>Pesos</v>
       </c>
       <c r="E340">
-        <v>21949.4</v>
+        <v>-81669.11</v>
       </c>
       <c r="F340">
-        <v>82992.43</v>
+        <v>1323.32</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
+        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
       </c>
       <c r="B341" t="str">
         <v>2024-05-21</v>
@@ -7191,38 +7191,38 @@
         <v>Pesos</v>
       </c>
       <c r="E341">
-        <v>57393.84</v>
+        <v>21949.4</v>
       </c>
       <c r="F341">
-        <v>61043.03</v>
+        <v>82992.43</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
       </c>
       <c r="B342" t="str">
-        <v>2024-05-15</v>
+        <v>2024-05-21</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D342" t="str">
         <v>Pesos</v>
       </c>
       <c r="E342">
-        <v>703.51</v>
+        <v>57393.84</v>
       </c>
       <c r="F342">
-        <v>3649.19</v>
+        <v>61043.03</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B343" t="str">
-        <v>2024-05-14</v>
+        <v>2024-05-15</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -7231,335 +7231,335 @@
         <v>Pesos</v>
       </c>
       <c r="E343">
-        <v>-130000</v>
+        <v>703.51</v>
       </c>
       <c r="F343">
-        <v>2945.68</v>
+        <v>3649.19</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Distribución de acciones por Capitalización / BYMA</v>
+        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B344" t="str">
         <v>2024-05-14</v>
       </c>
       <c r="C344">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D344" t="str">
         <v>Pesos</v>
       </c>
       <c r="E344">
-        <v>-0.44</v>
+        <v>-130000</v>
       </c>
       <c r="F344">
-        <v>132945.68</v>
+        <v>2945.68</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
+        <v>Distribución de acciones por Capitalización / BYMA</v>
       </c>
       <c r="B345" t="str">
-        <v>2024-05-07</v>
+        <v>2024-05-14</v>
       </c>
       <c r="C345">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="D345" t="str">
         <v>Pesos</v>
       </c>
       <c r="E345">
-        <v>5097.7</v>
+        <v>-0.44</v>
       </c>
       <c r="F345">
-        <v>132946.12</v>
+        <v>132945.68</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B346" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C346">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D346" t="str">
         <v>Pesos</v>
       </c>
       <c r="E346">
-        <v>23635.91</v>
+        <v>5097.7</v>
       </c>
       <c r="F346">
-        <v>127848.42</v>
+        <v>132946.12</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B347" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C347">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D347" t="str">
         <v>Pesos</v>
       </c>
       <c r="E347">
-        <v>20921.43</v>
+        <v>23635.91</v>
       </c>
       <c r="F347">
-        <v>104212.51</v>
+        <v>127848.42</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B348" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C348">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D348" t="str">
         <v>Pesos</v>
       </c>
       <c r="E348">
-        <v>11618.11</v>
+        <v>20921.43</v>
       </c>
       <c r="F348">
-        <v>83291.08</v>
+        <v>104212.51</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
+        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B349" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C349">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D349" t="str">
         <v>Pesos</v>
       </c>
       <c r="E349">
-        <v>52241.19</v>
+        <v>11618.11</v>
       </c>
       <c r="F349">
-        <v>71672.97</v>
+        <v>83291.08</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B350" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C350">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D350" t="str">
         <v>Pesos</v>
       </c>
       <c r="E350">
-        <v>19431.78</v>
+        <v>52241.19</v>
       </c>
       <c r="F350">
-        <v>19431.78</v>
+        <v>71672.97</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B351" t="str">
-        <v>2024-05-06</v>
+        <v>2024-05-07</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D351" t="str">
         <v>Pesos</v>
       </c>
       <c r="E351">
-        <v>-222622.08</v>
+        <v>19431.78</v>
       </c>
       <c r="F351">
-        <v>0</v>
+        <v>19431.78</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B352" t="str">
-        <v>2024-05-02</v>
+        <v>2024-05-06</v>
       </c>
       <c r="C352">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D352" t="str">
         <v>Pesos</v>
       </c>
       <c r="E352">
-        <v>99355.72</v>
+        <v>-222622.08</v>
       </c>
       <c r="F352">
-        <v>222622.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
+        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B353" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C353">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D353" t="str">
         <v>Pesos</v>
       </c>
       <c r="E353">
-        <v>66604.92</v>
+        <v>99355.72</v>
       </c>
       <c r="F353">
-        <v>123266.36</v>
+        <v>222622.08</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
       </c>
       <c r="B354" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C354">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D354" t="str">
         <v>Pesos</v>
       </c>
       <c r="E354">
-        <v>6069.65</v>
+        <v>66604.92</v>
       </c>
       <c r="F354">
-        <v>56661.44</v>
+        <v>123266.36</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
+        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B355" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C355">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D355" t="str">
         <v>Pesos</v>
       </c>
       <c r="E355">
-        <v>2488.36</v>
+        <v>6069.65</v>
       </c>
       <c r="F355">
-        <v>50591.79</v>
+        <v>56661.44</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B356" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C356">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D356" t="str">
         <v>Pesos</v>
       </c>
       <c r="E356">
-        <v>14202.18</v>
+        <v>2488.36</v>
       </c>
       <c r="F356">
-        <v>48103.43</v>
+        <v>50591.79</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B357" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C357">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D357" t="str">
         <v>Pesos</v>
       </c>
       <c r="E357">
-        <v>12418.97</v>
+        <v>14202.18</v>
       </c>
       <c r="F357">
-        <v>33901.25</v>
+        <v>48103.43</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B358" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C358">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D358" t="str">
         <v>Pesos</v>
       </c>
       <c r="E358">
-        <v>20579.26</v>
+        <v>12418.97</v>
       </c>
       <c r="F358">
-        <v>21482.28</v>
+        <v>33901.25</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
+        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B359" t="str">
-        <v>2024-04-17</v>
+        <v>2024-05-02</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D359" t="str">
         <v>Pesos</v>
       </c>
       <c r="E359">
-        <v>-34.33</v>
+        <v>20579.26</v>
       </c>
       <c r="F359">
-        <v>903.02</v>
+        <v>21482.28</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
       </c>
       <c r="B360" t="str">
         <v>2024-04-17</v>
@@ -7571,15 +7571,15 @@
         <v>Pesos</v>
       </c>
       <c r="E360">
-        <v>489.31</v>
+        <v>-34.33</v>
       </c>
       <c r="F360">
-        <v>937.35</v>
+        <v>903.02</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Movimiento Manual / Ret IIGG - BYMA</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B361" t="str">
         <v>2024-04-17</v>
@@ -7588,18 +7588,18 @@
         <v>0</v>
       </c>
       <c r="D361" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E361">
-        <v>-0.18</v>
+        <v>489.31</v>
       </c>
       <c r="F361">
-        <v>2.3</v>
+        <v>937.35</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG - BYMA</v>
       </c>
       <c r="B362" t="str">
         <v>2024-04-17</v>
@@ -7608,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="D362" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E362">
-        <v>-2.6</v>
+        <v>-0.18</v>
       </c>
       <c r="F362">
-        <v>448.04</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="363">
@@ -7628,218 +7628,218 @@
         <v>0</v>
       </c>
       <c r="D363" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E363">
-        <v>2.48</v>
+        <v>-2.6</v>
       </c>
       <c r="F363">
-        <v>2.48</v>
+        <v>448.04</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B364" t="str">
-        <v>2024-04-10</v>
+        <v>2024-04-17</v>
       </c>
       <c r="C364">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D364" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E364">
-        <v>-80932.98</v>
+        <v>2.48</v>
       </c>
       <c r="F364">
-        <v>450.64</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
+        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
       </c>
       <c r="B365" t="str">
-        <v>2024-04-09</v>
+        <v>2024-04-10</v>
       </c>
       <c r="C365">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D365" t="str">
         <v>Pesos</v>
       </c>
       <c r="E365">
-        <v>104967.66</v>
+        <v>-80932.98</v>
       </c>
       <c r="F365">
-        <v>81383.62</v>
+        <v>450.64</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
+        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
       </c>
       <c r="B366" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C366">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D366" t="str">
         <v>Pesos</v>
       </c>
       <c r="E366">
-        <v>16388.53</v>
+        <v>104967.66</v>
       </c>
       <c r="F366">
-        <v>-23584.04</v>
+        <v>81383.62</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
+        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
       </c>
       <c r="B367" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C367">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D367" t="str">
         <v>Pesos</v>
       </c>
       <c r="E367">
-        <v>-77278.67</v>
+        <v>16388.53</v>
       </c>
       <c r="F367">
-        <v>-39972.57</v>
+        <v>-23584.04</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
+        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
       </c>
       <c r="B368" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C368">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D368" t="str">
         <v>Pesos</v>
       </c>
       <c r="E368">
-        <v>35352.22</v>
+        <v>-77278.67</v>
       </c>
       <c r="F368">
-        <v>37306.1</v>
+        <v>-39972.57</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
       </c>
       <c r="B369" t="str">
-        <v>2024-04-08</v>
+        <v>2024-04-09</v>
       </c>
       <c r="C369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D369" t="str">
         <v>Pesos</v>
       </c>
       <c r="E369">
-        <v>-733461</v>
+        <v>35352.22</v>
       </c>
       <c r="F369">
-        <v>1953.88</v>
+        <v>37306.1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B370" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C370">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D370" t="str">
         <v>Pesos</v>
       </c>
       <c r="E370">
-        <v>-229304.33</v>
+        <v>-733461</v>
       </c>
       <c r="F370">
-        <v>735414.88</v>
+        <v>1953.88</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
+        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
       </c>
       <c r="B371" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C371">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D371" t="str">
         <v>Pesos</v>
       </c>
       <c r="E371">
-        <v>-35550.12</v>
+        <v>-229304.33</v>
       </c>
       <c r="F371">
-        <v>964719.21</v>
+        <v>735414.88</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
+        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
       </c>
       <c r="B372" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C372">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D372" t="str">
         <v>Pesos</v>
       </c>
       <c r="E372">
-        <v>-197072.27</v>
+        <v>-35550.12</v>
       </c>
       <c r="F372">
-        <v>1000269.33</v>
+        <v>964719.21</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
+        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
       </c>
       <c r="B373" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C373">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D373" t="str">
         <v>Pesos</v>
       </c>
       <c r="E373">
-        <v>-24084.05</v>
+        <v>-197072.27</v>
       </c>
       <c r="F373">
-        <v>1197341.6</v>
+        <v>1000269.33</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
+        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
       </c>
       <c r="B374" t="str">
         <v>2024-04-08</v>
@@ -7851,178 +7851,178 @@
         <v>Pesos</v>
       </c>
       <c r="E374">
-        <v>-53459.78</v>
+        <v>-24084.05</v>
       </c>
       <c r="F374">
-        <v>1221425.65</v>
+        <v>1197341.6</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
+        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
       </c>
       <c r="B375" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C375">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D375" t="str">
         <v>Pesos</v>
       </c>
       <c r="E375">
-        <v>-100325.74</v>
+        <v>-53459.78</v>
       </c>
       <c r="F375">
-        <v>1274885.43</v>
+        <v>1221425.65</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
+        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
       </c>
       <c r="B376" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C376">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D376" t="str">
         <v>Pesos</v>
       </c>
       <c r="E376">
-        <v>-180029.2</v>
+        <v>-100325.74</v>
       </c>
       <c r="F376">
-        <v>1375211.17</v>
+        <v>1274885.43</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
+        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
       </c>
       <c r="B377" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C377">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D377" t="str">
         <v>Pesos</v>
       </c>
       <c r="E377">
-        <v>-62547.44</v>
+        <v>-180029.2</v>
       </c>
       <c r="F377">
-        <v>1555240.37</v>
+        <v>1375211.17</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
+        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
       </c>
       <c r="B378" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C378">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D378" t="str">
         <v>Pesos</v>
       </c>
       <c r="E378">
-        <v>-60307.16</v>
+        <v>-62547.44</v>
       </c>
       <c r="F378">
-        <v>1617787.81</v>
+        <v>1555240.37</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
+        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
       </c>
       <c r="B379" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C379">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D379" t="str">
         <v>Pesos</v>
       </c>
       <c r="E379">
-        <v>-16504.2</v>
+        <v>-60307.16</v>
       </c>
       <c r="F379">
-        <v>1678094.97</v>
+        <v>1617787.81</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
+        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
       </c>
       <c r="B380" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C380">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D380" t="str">
         <v>Pesos</v>
       </c>
       <c r="E380">
-        <v>-197617.73</v>
+        <v>-16504.2</v>
       </c>
       <c r="F380">
-        <v>1694599.17</v>
+        <v>1678094.97</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
+        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
       </c>
       <c r="B381" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C381">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D381" t="str">
         <v>Pesos</v>
       </c>
       <c r="E381">
-        <v>-107783.1</v>
+        <v>-197617.73</v>
       </c>
       <c r="F381">
-        <v>1892216.9</v>
+        <v>1694599.17</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Liquidación de Rescate / 562376 / BCACC A</v>
+        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
       </c>
       <c r="B382" t="str">
-        <v>2024-04-03</v>
+        <v>2024-04-08</v>
       </c>
       <c r="C382">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D382" t="str">
         <v>Pesos</v>
       </c>
       <c r="E382">
-        <v>2000000</v>
+        <v>-107783.1</v>
       </c>
       <c r="F382">
-        <v>2000000</v>
+        <v>1892216.9</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 562376 / BCACC A</v>
       </c>
       <c r="B383" t="str">
-        <v>2024-03-25</v>
+        <v>2024-04-03</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -8031,18 +8031,18 @@
         <v>Pesos</v>
       </c>
       <c r="E383">
-        <v>-1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F383">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Recibo de Cobro / 844439</v>
+        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B384" t="str">
-        <v>2024-03-22</v>
+        <v>2024-03-25</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -8051,18 +8051,18 @@
         <v>Pesos</v>
       </c>
       <c r="E384">
-        <v>1000000</v>
+        <v>-1000000</v>
       </c>
       <c r="F384">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 844439</v>
       </c>
       <c r="B385" t="str">
-        <v>2024-03-11</v>
+        <v>2024-03-22</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -8071,18 +8071,18 @@
         <v>Pesos</v>
       </c>
       <c r="E385">
-        <v>-1002419.25</v>
+        <v>1000000</v>
       </c>
       <c r="F385">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
+        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B386" t="str">
-        <v>2024-03-06</v>
+        <v>2024-03-11</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -8091,15 +8091,15 @@
         <v>Pesos</v>
       </c>
       <c r="E386">
-        <v>1002419.25</v>
+        <v>-1002419.25</v>
       </c>
       <c r="F386">
-        <v>1002419.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
+        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
       </c>
       <c r="B387" t="str">
         <v>2024-03-06</v>
@@ -8111,15 +8111,15 @@
         <v>Pesos</v>
       </c>
       <c r="E387">
-        <v>-1000000</v>
+        <v>1002419.25</v>
       </c>
       <c r="F387">
-        <v>0</v>
+        <v>1002419.25</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Recibo de Cobro / 691819</v>
+        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
       </c>
       <c r="B388" t="str">
         <v>2024-03-06</v>
@@ -8131,15 +8131,35 @@
         <v>Pesos</v>
       </c>
       <c r="E388">
+        <v>-1000000</v>
+      </c>
+      <c r="F388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Recibo de Cobro / 691819</v>
+      </c>
+      <c r="B389" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389" t="str">
+        <v>Pesos</v>
+      </c>
+      <c r="E389">
         <v>1000000</v>
       </c>
-      <c r="F388">
+      <c r="F389">
         <v>1000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F388"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F389"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/mi_cartera_balanz/data/cuentacorriente.xlsx
+++ b/mi_cartera_balanz/data/cuentacorriente.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F389"/>
+  <dimension ref="A1:F391"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -399,170 +399,170 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
+        <v>Liquidación de Rescate / 2021758 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B2" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="C2">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D2" t="str">
         <v>Pesos</v>
       </c>
       <c r="E2">
-        <v>2089759.48</v>
+        <v>2006044.36</v>
       </c>
       <c r="F2">
-        <v>2100846.39</v>
+        <v>2113593.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 10668132 / COMPRA / 1 / YPFD / $</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="D3" t="str">
         <v>Pesos</v>
       </c>
       <c r="E3">
-        <v>-1015702.61</v>
+        <v>-1993297.7</v>
       </c>
       <c r="F3">
-        <v>11086.91</v>
+        <v>107548.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Comprobante de Pago / 2204947</v>
+        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D4" t="str">
         <v>Pesos</v>
       </c>
       <c r="E4">
-        <v>-100000</v>
+        <v>2089759.48</v>
       </c>
       <c r="F4">
-        <v>1026789.52</v>
+        <v>2100846.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
+        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-18</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D5" t="str">
         <v>Pesos</v>
       </c>
       <c r="E5">
-        <v>-2000000</v>
+        <v>-1015702.61</v>
       </c>
       <c r="F5">
-        <v>1126789.52</v>
+        <v>11086.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
+        <v>Comprobante de Pago / 2204947</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6" t="str">
         <v>Pesos</v>
       </c>
       <c r="E6">
-        <v>898438.45</v>
+        <v>-100000</v>
       </c>
       <c r="F6">
-        <v>3126789.52</v>
+        <v>1026789.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="C7">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D7" t="str">
         <v>Pesos</v>
       </c>
       <c r="E7">
-        <v>-1981985.21</v>
+        <v>-2000000</v>
       </c>
       <c r="F7">
-        <v>2228351.07</v>
+        <v>1126789.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Recibo de Cobro / 2547929</v>
+        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8" t="str">
         <v>Pesos</v>
       </c>
       <c r="E8">
-        <v>120000</v>
+        <v>898438.45</v>
       </c>
       <c r="F8">
-        <v>4210336.28</v>
+        <v>3126789.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Comprobante de Pago / 2167536</v>
+        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-14</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D9" t="str">
         <v>Pesos</v>
       </c>
       <c r="E9">
-        <v>-50000</v>
+        <v>-1981985.21</v>
       </c>
       <c r="F9">
-        <v>4090336.28</v>
+        <v>2228351.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
+        <v>Recibo de Cobro / 2547929</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-10</v>
+        <v>2026-09-14</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -571,18 +571,18 @@
         <v>Pesos</v>
       </c>
       <c r="E10">
-        <v>3404580.41</v>
+        <v>120000</v>
       </c>
       <c r="F10">
-        <v>4140336.28</v>
+        <v>4210336.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Comprobante de Pago / 2105708</v>
+        <v>Comprobante de Pago / 2167536</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-12</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -591,18 +591,18 @@
         <v>Pesos</v>
       </c>
       <c r="E11">
-        <v>-30000</v>
+        <v>-50000</v>
       </c>
       <c r="F11">
-        <v>735755.87</v>
+        <v>4090336.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Comprobante de Pago / 2057077</v>
+        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-10</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -611,18 +611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E12">
-        <v>-80000</v>
+        <v>3404580.41</v>
       </c>
       <c r="F12">
-        <v>765755.87</v>
+        <v>4140336.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2105708</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-06</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -631,78 +631,78 @@
         <v>Pesos</v>
       </c>
       <c r="E13">
-        <v>-3371333.8</v>
+        <v>-30000</v>
       </c>
       <c r="F13">
-        <v>845755.87</v>
+        <v>735755.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 2057077</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C14">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D14" t="str">
         <v>Pesos</v>
       </c>
       <c r="E14">
-        <v>918459.06</v>
+        <v>-80000</v>
       </c>
       <c r="F14">
-        <v>4217089.67</v>
+        <v>765755.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
+        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B15" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C15">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="D15" t="str">
         <v>Pesos</v>
       </c>
       <c r="E15">
-        <v>3298630.61</v>
+        <v>-3371333.8</v>
       </c>
       <c r="F15">
-        <v>3298630.61</v>
+        <v>845755.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Comprobante de Pago / 1944836</v>
+        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-21</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D16" t="str">
         <v>Pesos</v>
       </c>
       <c r="E16">
-        <v>-34658.23</v>
+        <v>918459.06</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>4217089.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-21</v>
       </c>
       <c r="C17">
         <v>503</v>
@@ -711,18 +711,18 @@
         <v>Pesos</v>
       </c>
       <c r="E17">
-        <v>-3589249.15</v>
+        <v>3298630.61</v>
       </c>
       <c r="F17">
-        <v>34658.23</v>
+        <v>3298630.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Comprobante de Pago / 1817656</v>
+        <v>Comprobante de Pago / 1944836</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-19</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -731,38 +731,38 @@
         <v>Pesos</v>
       </c>
       <c r="E18">
-        <v>-40000</v>
+        <v>-34658.23</v>
       </c>
       <c r="F18">
-        <v>3623907.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Comprobante de Pago / 1732595</v>
+        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-07-25</v>
+        <v>2026-08-14</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D19" t="str">
         <v>Pesos</v>
       </c>
       <c r="E19">
-        <v>-100000</v>
+        <v>-3589249.15</v>
       </c>
       <c r="F19">
-        <v>3663907.38</v>
+        <v>34658.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Comprobante de Pago / 1561578</v>
+        <v>Comprobante de Pago / 1817656</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-07-04</v>
+        <v>2026-08-04</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -771,18 +771,18 @@
         <v>Pesos</v>
       </c>
       <c r="E20">
-        <v>-300000</v>
+        <v>-40000</v>
       </c>
       <c r="F20">
-        <v>3763907.38</v>
+        <v>3623907.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Comprobante de Pago / 1545516</v>
+        <v>Comprobante de Pago / 1732595</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-25</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -794,255 +794,255 @@
         <v>-100000</v>
       </c>
       <c r="F21">
-        <v>4063907.38</v>
+        <v>3663907.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1561578</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-04</v>
       </c>
       <c r="C22">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D22" t="str">
         <v>Pesos</v>
       </c>
       <c r="E22">
-        <v>488924.13</v>
+        <v>-300000</v>
       </c>
       <c r="F22">
-        <v>4163907.38</v>
+        <v>3763907.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1545516</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
       <c r="C23">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D23" t="str">
         <v>Pesos</v>
       </c>
       <c r="E23">
-        <v>515910.2</v>
+        <v>-100000</v>
       </c>
       <c r="F23">
-        <v>3674983.25</v>
+        <v>4063907.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-29</v>
+        <v>2026-07-01</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D24" t="str">
         <v>Pesos</v>
       </c>
       <c r="E24">
-        <v>-6.27</v>
+        <v>488924.13</v>
       </c>
       <c r="F24">
-        <v>3159073.05</v>
+        <v>4163907.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B25" t="str">
         <v>2026-06-29</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D25" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E25">
-        <v>0.99</v>
+        <v>515910.2</v>
       </c>
       <c r="F25">
-        <v>2.01</v>
+        <v>3674983.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-29</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D26" t="str">
         <v>Pesos</v>
       </c>
       <c r="E26">
-        <v>-944671.87</v>
+        <v>-6.27</v>
       </c>
       <c r="F26">
-        <v>3159079.32</v>
+        <v>3159073.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-29</v>
       </c>
       <c r="C27">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D27" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E27">
-        <v>-1001112.31</v>
+        <v>0.99</v>
       </c>
       <c r="F27">
-        <v>4103751.19</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Comprobante de Pago / 1465742</v>
+        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-24</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D28" t="str">
         <v>Pesos</v>
       </c>
       <c r="E28">
-        <v>-50000</v>
+        <v>-944671.87</v>
       </c>
       <c r="F28">
-        <v>5104863.5</v>
+        <v>3159079.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
+        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-24</v>
       </c>
       <c r="C29">
-        <v>540</v>
+        <v>129</v>
       </c>
       <c r="D29" t="str">
         <v>Pesos</v>
       </c>
       <c r="E29">
-        <v>2137654.07</v>
+        <v>-1001112.31</v>
       </c>
       <c r="F29">
-        <v>5154863.5</v>
+        <v>4103751.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 1465742</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-22</v>
       </c>
       <c r="C30">
-        <v>879</v>
+        <v>0</v>
       </c>
       <c r="D30" t="str">
         <v>Pesos</v>
       </c>
       <c r="E30">
-        <v>820145.97</v>
+        <v>-50000</v>
       </c>
       <c r="F30">
-        <v>3017209.43</v>
+        <v>5104863.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C31">
-        <v>879</v>
+        <v>540</v>
       </c>
       <c r="D31" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E31">
-        <v>-567.43</v>
+        <v>2137654.07</v>
       </c>
       <c r="F31">
-        <v>11.75</v>
+        <v>5154863.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B32" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="D32" t="str">
         <v>Pesos</v>
       </c>
       <c r="E32">
-        <v>-20.4</v>
+        <v>820145.97</v>
       </c>
       <c r="F32">
-        <v>2197063.46</v>
+        <v>3017209.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B33" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C33">
-        <v>146</v>
+        <v>879</v>
       </c>
       <c r="D33" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E33">
-        <v>1867138.55</v>
+        <v>-567.43</v>
       </c>
       <c r="F33">
-        <v>2197083.86</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Recibo de Cobro / 1530471</v>
+        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1051,18 +1051,18 @@
         <v>Pesos</v>
       </c>
       <c r="E34">
-        <v>300000</v>
+        <v>-20.4</v>
       </c>
       <c r="F34">
-        <v>329945.31</v>
+        <v>2197063.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C35">
         <v>146</v>
@@ -1071,98 +1071,98 @@
         <v>Pesos</v>
       </c>
       <c r="E35">
-        <v>-1996802.3</v>
+        <v>1867138.55</v>
       </c>
       <c r="F35">
-        <v>29945.31</v>
+        <v>2197083.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Recibo de Cobro / 1484184</v>
+        <v>Recibo de Cobro / 1530471</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E36">
-        <v>579.18</v>
+        <v>300000</v>
       </c>
       <c r="F36">
-        <v>579.18</v>
+        <v>329945.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Comprobante de Pago / 1167141</v>
+        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-05-13</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D37" t="str">
         <v>Pesos</v>
       </c>
       <c r="E37">
-        <v>-20000</v>
+        <v>-1996802.3</v>
       </c>
       <c r="F37">
-        <v>2026747.61</v>
+        <v>29945.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Comprobante de Pago / 1116351</v>
+        <v>Recibo de Cobro / 1484184</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-05-08</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E38">
-        <v>-100000</v>
+        <v>579.18</v>
       </c>
       <c r="F38">
-        <v>2046747.61</v>
+        <v>579.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1167141</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C39">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="D39" t="str">
         <v>Pesos</v>
       </c>
       <c r="E39">
-        <v>-3174961.2</v>
+        <v>-20000</v>
       </c>
       <c r="F39">
-        <v>2146747.61</v>
+        <v>2026747.61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Comprobante de Pago / 925746</v>
+        <v>Comprobante de Pago / 1116351</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-04-15</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1171,38 +1171,38 @@
         <v>Pesos</v>
       </c>
       <c r="E40">
-        <v>-160000</v>
+        <v>-100000</v>
       </c>
       <c r="F40">
-        <v>5321708.81</v>
+        <v>2046747.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C41">
-        <v>338</v>
+        <v>818</v>
       </c>
       <c r="D41" t="str">
         <v>Pesos</v>
       </c>
       <c r="E41">
-        <v>3896669.74</v>
+        <v>-3174961.2</v>
       </c>
       <c r="F41">
-        <v>5481708.81</v>
+        <v>2146747.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Comprobante de Pago / 925746</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1211,38 +1211,38 @@
         <v>Pesos</v>
       </c>
       <c r="E42">
-        <v>-0.83</v>
+        <v>-160000</v>
       </c>
       <c r="F42">
-        <v>1585039.07</v>
+        <v>5321708.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="D43" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E43">
-        <v>0.14</v>
+        <v>3896669.74</v>
       </c>
       <c r="F43">
-        <v>1.02</v>
+        <v>5481708.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Comprobante de Pago / 738461</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1251,198 +1251,198 @@
         <v>Pesos</v>
       </c>
       <c r="E44">
-        <v>-90000</v>
+        <v>-0.83</v>
       </c>
       <c r="F44">
-        <v>1585039.9</v>
+        <v>1585039.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-03-18</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C45">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D45" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E45">
-        <v>992035.79</v>
+        <v>0.14</v>
       </c>
       <c r="F45">
-        <v>1675039.9</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 738461</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C46">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D46" t="str">
         <v>Pesos</v>
       </c>
       <c r="E46">
-        <v>1090257.16</v>
+        <v>-90000</v>
       </c>
       <c r="F46">
-        <v>683004.11</v>
+        <v>1585039.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B47" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="D47" t="str">
         <v>Pesos</v>
       </c>
       <c r="E47">
-        <v>-407253.05</v>
+        <v>992035.79</v>
       </c>
       <c r="F47">
-        <v>-407253.05</v>
+        <v>1675039.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Comprobante de Pago / 642036</v>
+        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D48" t="str">
         <v>Pesos</v>
       </c>
       <c r="E48">
-        <v>-992034.79</v>
+        <v>1090257.16</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>683004.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C49">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="D49" t="str">
         <v>Pesos</v>
       </c>
       <c r="E49">
-        <v>992035.79</v>
+        <v>-407253.05</v>
       </c>
       <c r="F49">
-        <v>992034.79</v>
+        <v>-407253.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Comprobante de Pago / 642036</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-12-29</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E50">
-        <v>0.16</v>
+        <v>-992034.79</v>
       </c>
       <c r="F50">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-12-29</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D51" t="str">
         <v>Pesos</v>
       </c>
       <c r="E51">
-        <v>-1</v>
+        <v>992035.79</v>
       </c>
       <c r="F51">
-        <v>-1</v>
+        <v>992034.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Comprobante de Pago / 2852932</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-11-13</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E52">
-        <v>-11190.76</v>
+        <v>0.16</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-11-04</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D53" t="str">
         <v>Pesos</v>
       </c>
       <c r="E53">
-        <v>-90093.05</v>
+        <v>-1</v>
       </c>
       <c r="F53">
-        <v>11190.76</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Recibo de Cobro / 2884603</v>
+        <v>Comprobante de Pago / 2852932</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1451,18 +1451,18 @@
         <v>Pesos</v>
       </c>
       <c r="E54">
-        <v>50000</v>
+        <v>-11190.76</v>
       </c>
       <c r="F54">
-        <v>101283.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-10-22</v>
+        <v>2025-11-04</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -1471,78 +1471,78 @@
         <v>Pesos</v>
       </c>
       <c r="E55">
-        <v>48024.29</v>
+        <v>-90093.05</v>
       </c>
       <c r="F55">
-        <v>51283.81</v>
+        <v>11190.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Recibo de Cobro / 2884603</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-10-20</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D56" t="str">
         <v>Pesos</v>
       </c>
       <c r="E56">
-        <v>-46739.74</v>
+        <v>50000</v>
       </c>
       <c r="F56">
-        <v>3259.52</v>
+        <v>101283.81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Recibo de Cobro / 2742989</v>
+        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-10-20</v>
+        <v>2025-10-22</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D57" t="str">
         <v>Pesos</v>
       </c>
       <c r="E57">
-        <v>50000</v>
+        <v>48024.29</v>
       </c>
       <c r="F57">
-        <v>49999.26</v>
+        <v>51283.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D58" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E58">
-        <v>0.12</v>
+        <v>-46739.74</v>
       </c>
       <c r="F58">
-        <v>0.72</v>
+        <v>3259.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Recibo de Cobro / 2742989</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1551,258 +1551,258 @@
         <v>Pesos</v>
       </c>
       <c r="E59">
-        <v>-0.74</v>
+        <v>50000</v>
       </c>
       <c r="F59">
-        <v>-0.74</v>
+        <v>49999.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Comprobante de Pago / 2317908</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-09-24</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E60">
-        <v>-6736.66</v>
+        <v>0.12</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-09-24</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C61">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D61" t="str">
         <v>Pesos</v>
       </c>
       <c r="E61">
-        <v>-403777.1</v>
+        <v>-0.74</v>
       </c>
       <c r="F61">
-        <v>6736.66</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
+        <v>Comprobante de Pago / 2317908</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-09-22</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C62">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="D62" t="str">
         <v>Pesos</v>
       </c>
       <c r="E62">
-        <v>388789.81</v>
+        <v>-6736.66</v>
       </c>
       <c r="F62">
-        <v>410513.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-09-22</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C63">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="D63" t="str">
         <v>Pesos</v>
       </c>
       <c r="E63">
-        <v>-1307333.32</v>
+        <v>-403777.1</v>
       </c>
       <c r="F63">
-        <v>21723.95</v>
+        <v>6736.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B64" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C64">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D64" t="str">
         <v>Pesos</v>
       </c>
       <c r="E64">
-        <v>999074.31</v>
+        <v>388789.81</v>
       </c>
       <c r="F64">
-        <v>1329057.27</v>
+        <v>410513.76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B65" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C65">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="D65" t="str">
         <v>Pesos</v>
       </c>
       <c r="E65">
-        <v>236100.29</v>
+        <v>-1307333.32</v>
       </c>
       <c r="F65">
-        <v>329982.96</v>
+        <v>21723.95</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B66" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C66">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D66" t="str">
         <v>Pesos</v>
       </c>
       <c r="E66">
-        <v>93882.67</v>
+        <v>999074.31</v>
       </c>
       <c r="F66">
-        <v>93882.67</v>
+        <v>1329057.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Comprobante de Pago / 2284129</v>
+        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-09-20</v>
+        <v>2025-09-22</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D67" t="str">
         <v>Pesos</v>
       </c>
       <c r="E67">
-        <v>-6165.47</v>
+        <v>236100.29</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>329982.96</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-09-18</v>
+        <v>2025-09-22</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D68" t="str">
         <v>Pesos</v>
       </c>
       <c r="E68">
-        <v>-76616.13</v>
+        <v>93882.67</v>
       </c>
       <c r="F68">
-        <v>6165.47</v>
+        <v>93882.67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 2284129</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-09-18</v>
+        <v>2025-09-20</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D69" t="str">
         <v>Pesos</v>
       </c>
       <c r="E69">
-        <v>-20136.94</v>
+        <v>-6165.47</v>
       </c>
       <c r="F69">
-        <v>82781.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B70" t="str">
         <v>2025-09-18</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="str">
         <v>Pesos</v>
       </c>
       <c r="E70">
-        <v>89518.34</v>
+        <v>-76616.13</v>
       </c>
       <c r="F70">
-        <v>102918.54</v>
+        <v>6165.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-18</v>
       </c>
       <c r="C71">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D71" t="str">
         <v>Pesos</v>
       </c>
       <c r="E71">
-        <v>138894.77</v>
+        <v>-20136.94</v>
       </c>
       <c r="F71">
-        <v>13400.2</v>
+        <v>82781.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-18</v>
       </c>
       <c r="C72">
         <v>5</v>
@@ -1811,278 +1811,278 @@
         <v>Pesos</v>
       </c>
       <c r="E72">
-        <v>-85739.5</v>
+        <v>89518.34</v>
       </c>
       <c r="F72">
-        <v>-125494.57</v>
+        <v>102918.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Comprobante de Pago / 2176779</v>
+        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B73" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D73" t="str">
         <v>Pesos</v>
       </c>
       <c r="E73">
-        <v>-45869.67</v>
+        <v>138894.77</v>
       </c>
       <c r="F73">
-        <v>-39755.07</v>
+        <v>13400.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="C74">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D74" t="str">
         <v>Pesos</v>
       </c>
       <c r="E74">
-        <v>-952298.2</v>
+        <v>-85739.5</v>
       </c>
       <c r="F74">
-        <v>6114.6</v>
+        <v>-125494.57</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 2176779</v>
       </c>
       <c r="B75" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="C75">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D75" t="str">
         <v>Pesos</v>
       </c>
       <c r="E75">
-        <v>-226481.32</v>
+        <v>-45869.67</v>
       </c>
       <c r="F75">
-        <v>958412.8</v>
+        <v>-39755.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
+        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B76" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C76">
-        <v>103</v>
+        <v>24</v>
       </c>
       <c r="D76" t="str">
         <v>Pesos</v>
       </c>
       <c r="E76">
-        <v>-491658.83</v>
+        <v>-952298.2</v>
       </c>
       <c r="F76">
-        <v>1184894.12</v>
+        <v>6114.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Comprobante de Pago / 2093390</v>
+        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D77" t="str">
         <v>Pesos</v>
       </c>
       <c r="E77">
-        <v>-14000</v>
+        <v>-226481.32</v>
       </c>
       <c r="F77">
-        <v>1676552.95</v>
+        <v>958412.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
       </c>
       <c r="B78" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-08</v>
       </c>
       <c r="C78">
-        <v>3447</v>
+        <v>103</v>
       </c>
       <c r="D78" t="str">
         <v>Pesos</v>
       </c>
       <c r="E78">
-        <v>2699870.67</v>
+        <v>-491658.83</v>
       </c>
       <c r="F78">
-        <v>1690552.95</v>
+        <v>1184894.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2093390</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C79">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="D79" t="str">
         <v>Pesos</v>
       </c>
       <c r="E79">
-        <v>-4194203.97</v>
+        <v>-14000</v>
       </c>
       <c r="F79">
-        <v>-1009317.72</v>
+        <v>1676552.95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B80" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C80">
-        <v>153</v>
+        <v>3447</v>
       </c>
       <c r="D80" t="str">
         <v>Pesos</v>
       </c>
       <c r="E80">
-        <v>509153.55</v>
+        <v>2699870.67</v>
       </c>
       <c r="F80">
-        <v>3184886.25</v>
+        <v>1690552.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B81" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C81">
-        <v>107</v>
+        <v>413</v>
       </c>
       <c r="D81" t="str">
         <v>Pesos</v>
       </c>
       <c r="E81">
-        <v>777951.6</v>
+        <v>-4194203.97</v>
       </c>
       <c r="F81">
-        <v>2675732.7</v>
+        <v>-1009317.72</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B82" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C82">
-        <v>225</v>
+        <v>153</v>
       </c>
       <c r="D82" t="str">
         <v>Pesos</v>
       </c>
       <c r="E82">
-        <v>1314506.19</v>
+        <v>509153.55</v>
       </c>
       <c r="F82">
-        <v>1897781.1</v>
+        <v>3184886.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B83" t="str">
-        <v>2025-08-18</v>
+        <v>2025-08-25</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="D83" t="str">
         <v>Pesos</v>
       </c>
       <c r="E83">
-        <v>-19758.9</v>
+        <v>777951.6</v>
       </c>
       <c r="F83">
-        <v>583274.91</v>
+        <v>2675732.7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Comprobante de Pago / 1961788</v>
+        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B84" t="str">
-        <v>2025-08-18</v>
+        <v>2025-08-25</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="D84" t="str">
         <v>Pesos</v>
       </c>
       <c r="E84">
-        <v>-20000</v>
+        <v>1314506.19</v>
       </c>
       <c r="F84">
-        <v>603033.81</v>
+        <v>1897781.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-18</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D85" t="str">
         <v>Pesos</v>
       </c>
       <c r="E85">
-        <v>-338.57</v>
+        <v>-19758.9</v>
       </c>
       <c r="F85">
-        <v>623033.81</v>
+        <v>583274.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Comprobante de Pago / 1961788</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-18</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -2091,478 +2091,478 @@
         <v>Pesos</v>
       </c>
       <c r="E86">
-        <v>4824.94</v>
+        <v>-20000</v>
       </c>
       <c r="F86">
-        <v>623372.38</v>
+        <v>603033.81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B87" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D87" t="str">
         <v>Pesos</v>
       </c>
       <c r="E87">
-        <v>-100004.21</v>
+        <v>-338.57</v>
       </c>
       <c r="F87">
-        <v>618547.44</v>
+        <v>623033.81</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B88" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C88">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D88" t="str">
         <v>Pesos</v>
       </c>
       <c r="E88">
-        <v>710418.57</v>
+        <v>4824.94</v>
       </c>
       <c r="F88">
-        <v>718551.65</v>
+        <v>623372.38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B89" t="str">
-        <v>2025-08-05</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C89">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D89" t="str">
         <v>Pesos</v>
       </c>
       <c r="E89">
-        <v>-190965.71</v>
+        <v>-100004.21</v>
       </c>
       <c r="F89">
-        <v>8133.08</v>
+        <v>618547.44</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B90" t="str">
-        <v>2025-08-05</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D90" t="str">
         <v>Pesos</v>
       </c>
       <c r="E90">
-        <v>182607.5</v>
+        <v>710418.57</v>
       </c>
       <c r="F90">
-        <v>199098.79</v>
+        <v>718551.65</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
+        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-08-04</v>
+        <v>2025-08-05</v>
       </c>
       <c r="C91">
-        <v>2626</v>
+        <v>19</v>
       </c>
       <c r="D91" t="str">
         <v>Pesos</v>
       </c>
       <c r="E91">
-        <v>41762.85</v>
+        <v>-190965.71</v>
       </c>
       <c r="F91">
-        <v>16491.29</v>
+        <v>8133.08</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-08-04</v>
+        <v>2025-08-05</v>
       </c>
       <c r="C92">
-        <v>1848</v>
+        <v>4</v>
       </c>
       <c r="D92" t="str">
         <v>Pesos</v>
       </c>
       <c r="E92">
-        <v>1490983.97</v>
+        <v>182607.5</v>
       </c>
       <c r="F92">
-        <v>-25271.56</v>
+        <v>199098.79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
       </c>
       <c r="B93" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C93">
-        <v>225</v>
+        <v>2626</v>
       </c>
       <c r="D93" t="str">
         <v>Pesos</v>
       </c>
       <c r="E93">
-        <v>-1521989.55</v>
+        <v>41762.85</v>
       </c>
       <c r="F93">
-        <v>-1516255.53</v>
+        <v>16491.29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-04</v>
       </c>
       <c r="C94">
-        <v>620</v>
+        <v>1848</v>
       </c>
       <c r="D94" t="str">
         <v>Pesos</v>
       </c>
       <c r="E94">
-        <v>488389.62</v>
+        <v>1490983.97</v>
       </c>
       <c r="F94">
-        <v>5734.02</v>
+        <v>-25271.56</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B95" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-04</v>
       </c>
       <c r="C95">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="D95" t="str">
         <v>Pesos</v>
       </c>
       <c r="E95">
-        <v>194738.35</v>
+        <v>-1521989.55</v>
       </c>
       <c r="F95">
-        <v>-482655.6</v>
+        <v>-1516255.53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B96" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C96">
-        <v>115</v>
+        <v>620</v>
       </c>
       <c r="D96" t="str">
         <v>Pesos</v>
       </c>
       <c r="E96">
-        <v>-393010.51</v>
+        <v>488389.62</v>
       </c>
       <c r="F96">
-        <v>-677393.95</v>
+        <v>5734.02</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B97" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C97">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D97" t="str">
         <v>Pesos</v>
       </c>
       <c r="E97">
-        <v>-285344.68</v>
+        <v>194738.35</v>
       </c>
       <c r="F97">
-        <v>-284383.44</v>
+        <v>-482655.6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B98" t="str">
-        <v>2025-07-29</v>
+        <v>2025-07-30</v>
       </c>
       <c r="C98">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="D98" t="str">
         <v>Pesos</v>
       </c>
       <c r="E98">
-        <v>-87826.28</v>
+        <v>-393010.51</v>
       </c>
       <c r="F98">
-        <v>961.24</v>
+        <v>-677393.95</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B99" t="str">
-        <v>2025-07-28</v>
+        <v>2025-07-30</v>
       </c>
       <c r="C99">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D99" t="str">
         <v>Pesos</v>
       </c>
       <c r="E99">
-        <v>-133937.09</v>
+        <v>-285344.68</v>
       </c>
       <c r="F99">
-        <v>88787.52</v>
+        <v>-284383.44</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-07-28</v>
+        <v>2025-07-29</v>
       </c>
       <c r="C100">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D100" t="str">
         <v>Pesos</v>
       </c>
       <c r="E100">
-        <v>94844.81</v>
+        <v>-87826.28</v>
       </c>
       <c r="F100">
-        <v>222724.61</v>
+        <v>961.24</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B101" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C101">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D101" t="str">
         <v>Pesos</v>
       </c>
       <c r="E101">
-        <v>127879.8</v>
+        <v>-133937.09</v>
       </c>
       <c r="F101">
-        <v>127879.8</v>
+        <v>88787.52</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-07-24</v>
+        <v>2025-07-28</v>
       </c>
       <c r="C102">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D102" t="str">
         <v>Pesos</v>
       </c>
       <c r="E102">
-        <v>88972.8</v>
+        <v>94844.81</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>222724.61</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Comprobante de Pago / 1761847</v>
+        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B103" t="str">
-        <v>2025-07-24</v>
+        <v>2025-07-28</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D103" t="str">
         <v>Pesos</v>
       </c>
       <c r="E103">
-        <v>-89024.62</v>
+        <v>127879.8</v>
       </c>
       <c r="F103">
-        <v>-88972.8</v>
+        <v>127879.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
+        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-07-22</v>
+        <v>2025-07-24</v>
       </c>
       <c r="C104">
-        <v>235</v>
+        <v>30</v>
       </c>
       <c r="D104" t="str">
         <v>Pesos</v>
       </c>
       <c r="E104">
-        <v>-3646.72</v>
+        <v>88972.8</v>
       </c>
       <c r="F104">
-        <v>51.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 1761847</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-07-22</v>
+        <v>2025-07-24</v>
       </c>
       <c r="C105">
-        <v>1984</v>
+        <v>0</v>
       </c>
       <c r="D105" t="str">
         <v>Pesos</v>
       </c>
       <c r="E105">
-        <v>-1482793.93</v>
+        <v>-89024.62</v>
       </c>
       <c r="F105">
-        <v>3698.54</v>
+        <v>-88972.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B106" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C106">
-        <v>121</v>
+        <v>235</v>
       </c>
       <c r="D106" t="str">
         <v>Pesos</v>
       </c>
       <c r="E106">
-        <v>-345815.98</v>
+        <v>-3646.72</v>
       </c>
       <c r="F106">
-        <v>1486492.47</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B107" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C107">
-        <v>55</v>
+        <v>1984</v>
       </c>
       <c r="D107" t="str">
         <v>Pesos</v>
       </c>
       <c r="E107">
-        <v>-354299.21</v>
+        <v>-1482793.93</v>
       </c>
       <c r="F107">
-        <v>1832308.45</v>
+        <v>3698.54</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B108" t="str">
-        <v>2025-07-16</v>
+        <v>2025-07-22</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="D108" t="str">
         <v>Pesos</v>
       </c>
       <c r="E108">
-        <v>2185800.13</v>
+        <v>-345815.98</v>
       </c>
       <c r="F108">
-        <v>2186607.66</v>
+        <v>1486492.47</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B109" t="str">
-        <v>2025-07-16</v>
+        <v>2025-07-22</v>
       </c>
       <c r="C109">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D109" t="str">
         <v>Pesos</v>
       </c>
       <c r="E109">
-        <v>-9888.53</v>
+        <v>-354299.21</v>
       </c>
       <c r="F109">
-        <v>807.53</v>
+        <v>1832308.45</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-07-14</v>
+        <v>2025-07-16</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2571,135 +2571,135 @@
         <v>Pesos</v>
       </c>
       <c r="E110">
-        <v>-1151507.11</v>
+        <v>2185800.13</v>
       </c>
       <c r="F110">
-        <v>10696.06</v>
+        <v>2186607.66</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-07-14</v>
+        <v>2025-07-16</v>
       </c>
       <c r="C111">
-        <v>1230</v>
+        <v>13</v>
       </c>
       <c r="D111" t="str">
         <v>Pesos</v>
       </c>
       <c r="E111">
-        <v>-950578.94</v>
+        <v>-9888.53</v>
       </c>
       <c r="F111">
-        <v>1162203.17</v>
+        <v>807.53</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B112" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D112" t="str">
         <v>Pesos</v>
       </c>
       <c r="E112">
-        <v>319945.64</v>
+        <v>-1151507.11</v>
       </c>
       <c r="F112">
-        <v>2112782.11</v>
+        <v>10696.06</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B113" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C113">
-        <v>175</v>
+        <v>1230</v>
       </c>
       <c r="D113" t="str">
         <v>Pesos</v>
       </c>
       <c r="E113">
-        <v>641329.36</v>
+        <v>-950578.94</v>
       </c>
       <c r="F113">
-        <v>1792836.47</v>
+        <v>1162203.17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Comprobante de Pago / 1676382</v>
+        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B114" t="str">
-        <v>2025-07-12</v>
+        <v>2025-07-14</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D114" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E114">
-        <v>-0.48</v>
+        <v>319945.64</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>2112782.11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B115" t="str">
-        <v>2025-07-11</v>
+        <v>2025-07-14</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D115" t="str">
         <v>Pesos</v>
       </c>
       <c r="E115">
-        <v>1152116.72</v>
+        <v>641329.36</v>
       </c>
       <c r="F115">
-        <v>1151507.11</v>
+        <v>1792836.47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
+        <v>Comprobante de Pago / 1676382</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-07-11</v>
+        <v>2025-07-12</v>
       </c>
       <c r="C116">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D116" t="str">
         <v>Dólares</v>
       </c>
       <c r="E116">
-        <v>-218.93</v>
+        <v>-0.48</v>
       </c>
       <c r="F116">
-        <v>0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
+        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B117" t="str">
         <v>2025-07-11</v>
@@ -2711,35 +2711,35 @@
         <v>Pesos</v>
       </c>
       <c r="E117">
-        <v>-609.62</v>
+        <v>1152116.72</v>
       </c>
       <c r="F117">
-        <v>-609.61</v>
+        <v>1151507.11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
       </c>
       <c r="B118" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C118">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="D118" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E118">
-        <v>-49685.47</v>
+        <v>-218.93</v>
       </c>
       <c r="F118">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Comprobante de Pago / 1668056</v>
+        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
       </c>
       <c r="B119" t="str">
         <v>2025-07-11</v>
@@ -2751,35 +2751,35 @@
         <v>Pesos</v>
       </c>
       <c r="E119">
-        <v>-3923.46</v>
+        <v>-609.62</v>
       </c>
       <c r="F119">
-        <v>49685.48</v>
+        <v>-609.61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Comprobante de Pago / 1668048</v>
+        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B120" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D120" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E120">
-        <v>-4.52</v>
+        <v>-49685.47</v>
       </c>
       <c r="F120">
-        <v>219.41</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Recibo de Cobro / 1772632</v>
+        <v>Comprobante de Pago / 1668056</v>
       </c>
       <c r="B121" t="str">
         <v>2025-07-11</v>
@@ -2791,18 +2791,18 @@
         <v>Pesos</v>
       </c>
       <c r="E121">
-        <v>50000</v>
+        <v>-3923.46</v>
       </c>
       <c r="F121">
-        <v>53608.94</v>
+        <v>49685.48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Comprobante de Pago / 1668048</v>
       </c>
       <c r="B122" t="str">
-        <v>2025-07-10</v>
+        <v>2025-07-11</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -2811,18 +2811,18 @@
         <v>Dólares</v>
       </c>
       <c r="E122">
-        <v>223.91</v>
+        <v>-4.52</v>
       </c>
       <c r="F122">
-        <v>223.93</v>
+        <v>219.41</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Recibo de Cobro / 1772632</v>
       </c>
       <c r="B123" t="str">
-        <v>2025-07-10</v>
+        <v>2025-07-11</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -2831,38 +2831,38 @@
         <v>Pesos</v>
       </c>
       <c r="E123">
-        <v>-5.65</v>
+        <v>50000</v>
       </c>
       <c r="F123">
-        <v>3608.94</v>
+        <v>53608.94</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B124" t="str">
-        <v>2025-06-11</v>
+        <v>2025-07-10</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E124">
-        <v>-552.42</v>
+        <v>223.91</v>
       </c>
       <c r="F124">
-        <v>3614.59</v>
+        <v>223.93</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Dividendo en efectivo / TGSU2</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B125" t="str">
-        <v>2025-06-11</v>
+        <v>2025-07-10</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -2871,38 +2871,38 @@
         <v>Pesos</v>
       </c>
       <c r="E125">
-        <v>3975.67</v>
+        <v>-5.65</v>
       </c>
       <c r="F125">
-        <v>4167.01</v>
+        <v>3608.94</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
       </c>
       <c r="B126" t="str">
-        <v>2025-06-09</v>
+        <v>2025-06-11</v>
       </c>
       <c r="C126">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="D126" t="str">
         <v>Pesos</v>
       </c>
       <c r="E126">
-        <v>-16502.47</v>
+        <v>-552.42</v>
       </c>
       <c r="F126">
-        <v>191.34</v>
+        <v>3614.59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Dividendo en efectivo / TGSU2</v>
       </c>
       <c r="B127" t="str">
-        <v>2025-05-15</v>
+        <v>2025-06-11</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -2911,38 +2911,38 @@
         <v>Pesos</v>
       </c>
       <c r="E127">
-        <v>-958.17</v>
+        <v>3975.67</v>
       </c>
       <c r="F127">
-        <v>16693.81</v>
+        <v>4167.01</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B128" t="str">
-        <v>2025-05-15</v>
+        <v>2025-06-09</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="D128" t="str">
         <v>Pesos</v>
       </c>
       <c r="E128">
-        <v>13655.11</v>
+        <v>-16502.47</v>
       </c>
       <c r="F128">
-        <v>17651.98</v>
+        <v>191.34</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Renta y Amortización / TX28</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B129" t="str">
-        <v>2025-05-09</v>
+        <v>2025-05-15</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -2951,98 +2951,98 @@
         <v>Pesos</v>
       </c>
       <c r="E129">
-        <v>3718.21</v>
+        <v>-958.17</v>
       </c>
       <c r="F129">
-        <v>3996.87</v>
+        <v>16693.81</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B130" t="str">
-        <v>2025-04-25</v>
+        <v>2025-05-15</v>
       </c>
       <c r="C130">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="D130" t="str">
         <v>Pesos</v>
       </c>
       <c r="E130">
-        <v>-24260.75</v>
+        <v>13655.11</v>
       </c>
       <c r="F130">
-        <v>278.66</v>
+        <v>17651.98</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
+        <v>Renta y Amortización / TX28</v>
       </c>
       <c r="B131" t="str">
-        <v>2025-04-25</v>
+        <v>2025-05-09</v>
       </c>
       <c r="C131">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D131" t="str">
         <v>Pesos</v>
       </c>
       <c r="E131">
-        <v>-975460.59</v>
+        <v>3718.21</v>
       </c>
       <c r="F131">
-        <v>24539.41</v>
+        <v>3996.87</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B132" t="str">
-        <v>2025-04-24</v>
+        <v>2025-04-25</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="D132" t="str">
         <v>Pesos</v>
       </c>
       <c r="E132">
-        <v>1000000</v>
+        <v>-24260.75</v>
       </c>
       <c r="F132">
-        <v>1000000</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B133" t="str">
-        <v>2025-04-21</v>
+        <v>2025-04-25</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D133" t="str">
         <v>Pesos</v>
       </c>
       <c r="E133">
-        <v>-999993.87</v>
+        <v>-975460.59</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>24539.41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B134" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-24</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3054,35 +3054,35 @@
         <v>1000000</v>
       </c>
       <c r="F134">
-        <v>999993.87</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
+        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B135" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-21</v>
       </c>
       <c r="C135">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="D135" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E135">
-        <v>-206.02</v>
+        <v>-999993.87</v>
       </c>
       <c r="F135">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
+        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B136" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-16</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3091,35 +3091,35 @@
         <v>Pesos</v>
       </c>
       <c r="E136">
-        <v>-6.13</v>
+        <v>1000000</v>
       </c>
       <c r="F136">
-        <v>-6.13</v>
+        <v>999993.87</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Comprobante de Pago / 1061406</v>
+        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B137" t="str">
         <v>2025-04-15</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="D137" t="str">
         <v>Dólares</v>
       </c>
       <c r="E137">
-        <v>-2.85</v>
+        <v>-206.02</v>
       </c>
       <c r="F137">
-        <v>206.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Comprobante de Pago / 1061395</v>
+        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B138" t="str">
         <v>2025-04-15</v>
@@ -3131,38 +3131,38 @@
         <v>Pesos</v>
       </c>
       <c r="E138">
-        <v>-2526.78</v>
+        <v>-6.13</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 1061406</v>
       </c>
       <c r="B139" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-15</v>
       </c>
       <c r="C139">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D139" t="str">
         <v>Dólares</v>
       </c>
       <c r="E139">
-        <v>208.88</v>
+        <v>-2.85</v>
       </c>
       <c r="F139">
-        <v>208.89</v>
+        <v>206.04</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 1061395</v>
       </c>
       <c r="B140" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-15</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3171,15 +3171,15 @@
         <v>Pesos</v>
       </c>
       <c r="E140">
-        <v>-5.66</v>
+        <v>-2526.78</v>
       </c>
       <c r="F140">
-        <v>2526.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B141" t="str">
         <v>2025-04-14</v>
@@ -3188,161 +3188,161 @@
         <v>320</v>
       </c>
       <c r="D141" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E141">
-        <v>-257928.71</v>
+        <v>208.88</v>
       </c>
       <c r="F141">
-        <v>2532.44</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B142" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C142">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D142" t="str">
         <v>Pesos</v>
       </c>
       <c r="E142">
-        <v>248438.89</v>
+        <v>-5.66</v>
       </c>
       <c r="F142">
-        <v>260461.15</v>
+        <v>2526.78</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B143" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-14</v>
       </c>
       <c r="C143">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="D143" t="str">
         <v>Pesos</v>
       </c>
       <c r="E143">
-        <v>-98040.09</v>
+        <v>-257928.71</v>
       </c>
       <c r="F143">
-        <v>12022.26</v>
+        <v>2532.44</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B144" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-14</v>
       </c>
       <c r="C144">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D144" t="str">
         <v>Pesos</v>
       </c>
       <c r="E144">
-        <v>-486646.45</v>
+        <v>248438.89</v>
       </c>
       <c r="F144">
-        <v>110062.35</v>
+        <v>260461.15</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B145" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C145">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D145" t="str">
         <v>Pesos</v>
       </c>
       <c r="E145">
-        <v>-93664.38</v>
+        <v>-98040.09</v>
       </c>
       <c r="F145">
-        <v>596708.8</v>
+        <v>12022.26</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B146" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C146">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D146" t="str">
         <v>Pesos</v>
       </c>
       <c r="E146">
-        <v>-309626.82</v>
+        <v>-486646.45</v>
       </c>
       <c r="F146">
-        <v>690373.18</v>
+        <v>110062.35</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B147" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-08</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D147" t="str">
         <v>Pesos</v>
       </c>
       <c r="E147">
-        <v>1000000</v>
+        <v>-93664.38</v>
       </c>
       <c r="F147">
-        <v>1000000</v>
+        <v>596708.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B148" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-08</v>
       </c>
       <c r="C148">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="D148" t="str">
         <v>Pesos</v>
       </c>
       <c r="E148">
-        <v>292856.94</v>
+        <v>-309626.82</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>690373.18</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Comprobante de Pago / 945180</v>
+        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B149" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-07</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3351,38 +3351,38 @@
         <v>Pesos</v>
       </c>
       <c r="E149">
-        <v>-292856.9</v>
+        <v>1000000</v>
       </c>
       <c r="F149">
-        <v>-292856.94</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B150" t="str">
-        <v>2025-03-27</v>
+        <v>2025-04-04</v>
       </c>
       <c r="C150">
-        <v>71</v>
+        <v>357</v>
       </c>
       <c r="D150" t="str">
         <v>Pesos</v>
       </c>
       <c r="E150">
-        <v>58913.7</v>
+        <v>292856.94</v>
       </c>
       <c r="F150">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Comprobante de Pago / 868926</v>
+        <v>Comprobante de Pago / 945180</v>
       </c>
       <c r="B151" t="str">
-        <v>2025-03-27</v>
+        <v>2025-04-04</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3391,38 +3391,38 @@
         <v>Pesos</v>
       </c>
       <c r="E151">
-        <v>-58913.74</v>
+        <v>-292856.9</v>
       </c>
       <c r="F151">
-        <v>-58913.74</v>
+        <v>-292856.94</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B152" t="str">
-        <v>2025-03-20</v>
+        <v>2025-03-27</v>
       </c>
       <c r="C152">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D152" t="str">
         <v>Pesos</v>
       </c>
       <c r="E152">
-        <v>39165.79</v>
+        <v>58913.7</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Comprobante de Pago / 814860</v>
+        <v>Comprobante de Pago / 868926</v>
       </c>
       <c r="B153" t="str">
-        <v>2025-03-20</v>
+        <v>2025-03-27</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3431,27 +3431,27 @@
         <v>Pesos</v>
       </c>
       <c r="E153">
-        <v>-39165.79</v>
+        <v>-58913.74</v>
       </c>
       <c r="F153">
-        <v>-39165.79</v>
+        <v>-58913.74</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B154" t="str">
-        <v>2025-03-05</v>
+        <v>2025-03-20</v>
       </c>
       <c r="C154">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D154" t="str">
         <v>Pesos</v>
       </c>
       <c r="E154">
-        <v>48845.52</v>
+        <v>39165.79</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Comprobante de Pago / 636155</v>
+        <v>Comprobante de Pago / 814860</v>
       </c>
       <c r="B155" t="str">
-        <v>2025-03-05</v>
+        <v>2025-03-20</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3471,58 +3471,58 @@
         <v>Pesos</v>
       </c>
       <c r="E155">
-        <v>-48845.53</v>
+        <v>-39165.79</v>
       </c>
       <c r="F155">
-        <v>-48845.52</v>
+        <v>-39165.79</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B156" t="str">
-        <v>2025-02-13</v>
+        <v>2025-03-05</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D156" t="str">
         <v>Pesos</v>
       </c>
       <c r="E156">
-        <v>-2208405.65</v>
+        <v>48845.52</v>
       </c>
       <c r="F156">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 636155</v>
       </c>
       <c r="B157" t="str">
-        <v>2025-02-12</v>
+        <v>2025-03-05</v>
       </c>
       <c r="C157">
-        <v>1921</v>
+        <v>0</v>
       </c>
       <c r="D157" t="str">
         <v>Pesos</v>
       </c>
       <c r="E157">
-        <v>-1490594.34</v>
+        <v>-48845.53</v>
       </c>
       <c r="F157">
-        <v>2208405.66</v>
+        <v>-48845.52</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Recibo de Cobro / 513307</v>
+        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B158" t="str">
-        <v>2025-02-12</v>
+        <v>2025-02-13</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3531,38 +3531,38 @@
         <v>Pesos</v>
       </c>
       <c r="E158">
-        <v>149000</v>
+        <v>-2208405.65</v>
       </c>
       <c r="F158">
-        <v>3699000</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Comprobante de Pago / 451447</v>
+        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-02-11</v>
+        <v>2025-02-12</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1921</v>
       </c>
       <c r="D159" t="str">
         <v>Pesos</v>
       </c>
       <c r="E159">
-        <v>-300000</v>
+        <v>-1490594.34</v>
       </c>
       <c r="F159">
-        <v>3550000</v>
+        <v>2208405.66</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Comprobante de Pago / 422123</v>
+        <v>Recibo de Cobro / 513307</v>
       </c>
       <c r="B160" t="str">
-        <v>2025-02-10</v>
+        <v>2025-02-12</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3571,18 +3571,18 @@
         <v>Pesos</v>
       </c>
       <c r="E160">
-        <v>-150000</v>
+        <v>149000</v>
       </c>
       <c r="F160">
-        <v>3850000</v>
+        <v>3699000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Recibo de Cobro / 392207</v>
+        <v>Comprobante de Pago / 451447</v>
       </c>
       <c r="B161" t="str">
-        <v>2025-02-03</v>
+        <v>2025-02-11</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3591,18 +3591,18 @@
         <v>Pesos</v>
       </c>
       <c r="E161">
-        <v>2000000</v>
+        <v>-300000</v>
       </c>
       <c r="F161">
-        <v>4000000</v>
+        <v>3550000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Recibo de Cobro / 392198</v>
+        <v>Comprobante de Pago / 422123</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-02-03</v>
+        <v>2025-02-10</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3611,18 +3611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E162">
-        <v>2000000</v>
+        <v>-150000</v>
       </c>
       <c r="F162">
-        <v>2000000</v>
+        <v>3850000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 392207</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-01-24</v>
+        <v>2025-02-03</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3631,18 +3631,18 @@
         <v>Pesos</v>
       </c>
       <c r="E163">
-        <v>-284993.55</v>
+        <v>2000000</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Recibo de Cobro / 259074</v>
+        <v>Recibo de Cobro / 392198</v>
       </c>
       <c r="B164" t="str">
-        <v>2025-01-21</v>
+        <v>2025-02-03</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3651,35 +3651,35 @@
         <v>Pesos</v>
       </c>
       <c r="E164">
-        <v>285000</v>
+        <v>2000000</v>
       </c>
       <c r="F164">
-        <v>284993.55</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
+        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B165" t="str">
-        <v>2025-01-21</v>
+        <v>2025-01-24</v>
       </c>
       <c r="C165">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="D165" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E165">
-        <v>244.89</v>
+        <v>-284993.55</v>
       </c>
       <c r="F165">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
+        <v>Recibo de Cobro / 259074</v>
       </c>
       <c r="B166" t="str">
         <v>2025-01-21</v>
@@ -3691,87 +3691,87 @@
         <v>Pesos</v>
       </c>
       <c r="E166">
-        <v>-6.45</v>
+        <v>285000</v>
       </c>
       <c r="F166">
-        <v>-6.45</v>
+        <v>284993.55</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Comprobante de Pago / 229359</v>
+        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B167" t="str">
         <v>2025-01-21</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="D167" t="str">
         <v>Dólares</v>
       </c>
       <c r="E167">
-        <v>-244.88</v>
+        <v>244.89</v>
       </c>
       <c r="F167">
-        <v>-244.88</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
+        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B168" t="str">
-        <v>2025-01-17</v>
+        <v>2025-01-21</v>
       </c>
       <c r="C168">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D168" t="str">
         <v>Pesos</v>
       </c>
       <c r="E168">
-        <v>164237.44</v>
+        <v>-6.45</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Comprobante de Pago / 195368</v>
+        <v>Comprobante de Pago / 229359</v>
       </c>
       <c r="B169" t="str">
-        <v>2025-01-17</v>
+        <v>2025-01-21</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E169">
-        <v>-164237.44</v>
+        <v>-244.88</v>
       </c>
       <c r="F169">
-        <v>-164237.44</v>
+        <v>-244.88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comprobante de Pago / 128971</v>
+        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
       </c>
       <c r="B170" t="str">
-        <v>2025-01-11</v>
+        <v>2025-01-17</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D170" t="str">
         <v>Pesos</v>
       </c>
       <c r="E170">
-        <v>-1858.46</v>
+        <v>164237.44</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -3779,107 +3779,107 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Comprobante de Pago / 128969</v>
+        <v>Comprobante de Pago / 195368</v>
       </c>
       <c r="B171" t="str">
-        <v>2025-01-11</v>
+        <v>2025-01-17</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E171">
-        <v>-1.67</v>
+        <v>-164237.44</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>-164237.44</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 128971</v>
       </c>
       <c r="B172" t="str">
-        <v>2025-01-09</v>
+        <v>2025-01-11</v>
       </c>
       <c r="C172">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D172" t="str">
         <v>Pesos</v>
       </c>
       <c r="E172">
-        <v>115257.86</v>
+        <v>-1858.46</v>
       </c>
       <c r="F172">
-        <v>1858.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 128969</v>
       </c>
       <c r="B173" t="str">
-        <v>2025-01-09</v>
+        <v>2025-01-11</v>
       </c>
       <c r="C173">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D173" t="str">
         <v>Dólares</v>
       </c>
       <c r="E173">
-        <v>-100.23</v>
+        <v>-1.67</v>
       </c>
       <c r="F173">
-        <v>1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B174" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D174" t="str">
         <v>Pesos</v>
       </c>
       <c r="E174">
-        <v>-2.58</v>
+        <v>115257.86</v>
       </c>
       <c r="F174">
-        <v>-113399.4</v>
+        <v>1858.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B175" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C175">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D175" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E175">
-        <v>-113394.51</v>
+        <v>-100.23</v>
       </c>
       <c r="F175">
-        <v>-113396.82</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B176" t="str">
         <v>2025-01-09</v>
@@ -3888,61 +3888,61 @@
         <v>0</v>
       </c>
       <c r="D176" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E176">
-        <v>101.9</v>
+        <v>-2.58</v>
       </c>
       <c r="F176">
-        <v>101.9</v>
+        <v>-113399.4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B177" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D177" t="str">
         <v>Pesos</v>
       </c>
       <c r="E177">
-        <v>-2.31</v>
+        <v>-113394.51</v>
       </c>
       <c r="F177">
-        <v>-2.31</v>
+        <v>-113396.82</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B178" t="str">
-        <v>2025-01-07</v>
+        <v>2025-01-09</v>
       </c>
       <c r="C178">
         <v>0</v>
       </c>
       <c r="D178" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E178">
-        <v>-134999.75</v>
+        <v>101.9</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Recibo de Cobro / 70445</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B179" t="str">
-        <v>2025-01-06</v>
+        <v>2025-01-09</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -3951,18 +3951,18 @@
         <v>Pesos</v>
       </c>
       <c r="E179">
-        <v>135000</v>
+        <v>-2.31</v>
       </c>
       <c r="F179">
-        <v>134999.75</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B180" t="str">
-        <v>2024-12-26</v>
+        <v>2025-01-07</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -3971,55 +3971,55 @@
         <v>Pesos</v>
       </c>
       <c r="E180">
-        <v>-57777.54</v>
+        <v>-134999.75</v>
       </c>
       <c r="F180">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Comprobante de Pago / 3498761</v>
+        <v>Recibo de Cobro / 70445</v>
       </c>
       <c r="B181" t="str">
-        <v>2024-12-26</v>
+        <v>2025-01-06</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E181">
-        <v>-1.01</v>
+        <v>135000</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>134999.75</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
+        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B182" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E182">
-        <v>1.01</v>
+        <v>-57777.54</v>
       </c>
       <c r="F182">
-        <v>1.01</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
+        <v>Comprobante de Pago / 3498761</v>
       </c>
       <c r="B183" t="str">
         <v>2024-12-26</v>
@@ -4028,18 +4028,18 @@
         <v>0</v>
       </c>
       <c r="D183" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E183">
-        <v>-0.03</v>
+        <v>-1.01</v>
       </c>
       <c r="F183">
-        <v>57777.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
+        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
       </c>
       <c r="B184" t="str">
         <v>2024-12-26</v>
@@ -4048,178 +4048,178 @@
         <v>1</v>
       </c>
       <c r="D184" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E184">
-        <v>27372.9</v>
+        <v>1.01</v>
       </c>
       <c r="F184">
-        <v>57777.32</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
+        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
       </c>
       <c r="B185" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C185">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D185" t="str">
         <v>Pesos</v>
       </c>
       <c r="E185">
-        <v>29356.45</v>
+        <v>-0.03</v>
       </c>
       <c r="F185">
-        <v>30404.42</v>
+        <v>57777.29</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
       </c>
       <c r="B186" t="str">
-        <v>2024-12-18</v>
+        <v>2024-12-26</v>
       </c>
       <c r="C186">
-        <v>299</v>
+        <v>1</v>
       </c>
       <c r="D186" t="str">
         <v>Pesos</v>
       </c>
       <c r="E186">
-        <v>-255135.69</v>
+        <v>27372.9</v>
       </c>
       <c r="F186">
-        <v>1047.97</v>
+        <v>57777.32</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
       </c>
       <c r="B187" t="str">
-        <v>2024-12-18</v>
+        <v>2024-12-26</v>
       </c>
       <c r="C187">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D187" t="str">
         <v>Pesos</v>
       </c>
       <c r="E187">
-        <v>65556.13</v>
+        <v>29356.45</v>
       </c>
       <c r="F187">
-        <v>256183.66</v>
+        <v>30404.42</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B188" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C188">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="D188" t="str">
         <v>Pesos</v>
       </c>
       <c r="E188">
-        <v>58613.72</v>
+        <v>-255135.69</v>
       </c>
       <c r="F188">
-        <v>190627.53</v>
+        <v>1047.97</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
+        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B189" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C189">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D189" t="str">
         <v>Pesos</v>
       </c>
       <c r="E189">
-        <v>69622.4</v>
+        <v>65556.13</v>
       </c>
       <c r="F189">
-        <v>132013.81</v>
+        <v>256183.66</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B190" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C190">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D190" t="str">
         <v>Pesos</v>
       </c>
       <c r="E190">
-        <v>62392.37</v>
+        <v>58613.72</v>
       </c>
       <c r="F190">
-        <v>62391.41</v>
+        <v>190627.53</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
       </c>
       <c r="B191" t="str">
-        <v>2024-12-17</v>
+        <v>2024-12-18</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D191" t="str">
         <v>Pesos</v>
       </c>
       <c r="E191">
-        <v>-0.53</v>
+        <v>69622.4</v>
       </c>
       <c r="F191">
-        <v>-0.96</v>
+        <v>132013.81</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B192" t="str">
-        <v>2024-12-17</v>
+        <v>2024-12-18</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D192" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E192">
-        <v>0.12</v>
+        <v>62392.37</v>
       </c>
       <c r="F192">
-        <v>0.6</v>
+        <v>62391.41</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B193" t="str">
         <v>2024-12-17</v>
@@ -4231,15 +4231,15 @@
         <v>Pesos</v>
       </c>
       <c r="E193">
-        <v>-0.13</v>
+        <v>-0.53</v>
       </c>
       <c r="F193">
-        <v>-0.43</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B194" t="str">
         <v>2024-12-17</v>
@@ -4251,18 +4251,18 @@
         <v>Dólares C.V. 7000</v>
       </c>
       <c r="E194">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="F194">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B195" t="str">
-        <v>2024-12-13</v>
+        <v>2024-12-17</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -4271,18 +4271,18 @@
         <v>Pesos</v>
       </c>
       <c r="E195">
-        <v>-0.3</v>
+        <v>-0.13</v>
       </c>
       <c r="F195">
-        <v>-0.3</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B196" t="str">
-        <v>2024-12-13</v>
+        <v>2024-12-17</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -4291,18 +4291,18 @@
         <v>Dólares C.V. 7000</v>
       </c>
       <c r="E196">
-        <v>0.07</v>
+        <v>0.03</v>
       </c>
       <c r="F196">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B197" t="str">
-        <v>2024-12-12</v>
+        <v>2024-12-13</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -4311,475 +4311,475 @@
         <v>Pesos</v>
       </c>
       <c r="E197">
-        <v>-103588.95</v>
+        <v>-0.3</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B198" t="str">
-        <v>2024-12-06</v>
+        <v>2024-12-13</v>
       </c>
       <c r="C198">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D198" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E198">
-        <v>102379.42</v>
+        <v>0.07</v>
       </c>
       <c r="F198">
-        <v>103588.95</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B199" t="str">
-        <v>2024-12-06</v>
+        <v>2024-12-12</v>
       </c>
       <c r="C199">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D199" t="str">
         <v>Pesos</v>
       </c>
       <c r="E199">
-        <v>-117184.31</v>
+        <v>-103588.95</v>
       </c>
       <c r="F199">
-        <v>1209.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
+        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
       </c>
       <c r="B200" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C200">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D200" t="str">
         <v>Pesos</v>
       </c>
       <c r="E200">
-        <v>27546.46</v>
+        <v>102379.42</v>
       </c>
       <c r="F200">
-        <v>118393.84</v>
+        <v>103588.95</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B201" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C201">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="D201" t="str">
         <v>Pesos</v>
       </c>
       <c r="E201">
-        <v>89904.13</v>
+        <v>-117184.31</v>
       </c>
       <c r="F201">
-        <v>90847.38</v>
+        <v>1209.53</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
       </c>
       <c r="B202" t="str">
-        <v>2024-11-27</v>
+        <v>2024-12-06</v>
       </c>
       <c r="C202">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="D202" t="str">
         <v>Pesos</v>
       </c>
       <c r="E202">
-        <v>-91403.91</v>
+        <v>27546.46</v>
       </c>
       <c r="F202">
-        <v>943.25</v>
+        <v>118393.84</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
+        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B203" t="str">
-        <v>2024-11-27</v>
+        <v>2024-12-06</v>
       </c>
       <c r="C203">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="D203" t="str">
         <v>Pesos</v>
       </c>
       <c r="E203">
-        <v>91674.44</v>
+        <v>89904.13</v>
       </c>
       <c r="F203">
-        <v>92347.16</v>
+        <v>90847.38</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B204" t="str">
-        <v>2024-11-25</v>
+        <v>2024-11-27</v>
       </c>
       <c r="C204">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D204" t="str">
         <v>Pesos</v>
       </c>
       <c r="E204">
-        <v>140157.43</v>
+        <v>-91403.91</v>
       </c>
       <c r="F204">
-        <v>672.72</v>
+        <v>943.25</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Comprobante de Pago / 3169919</v>
+        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
       </c>
       <c r="B205" t="str">
-        <v>2024-11-25</v>
+        <v>2024-11-27</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D205" t="str">
         <v>Pesos</v>
       </c>
       <c r="E205">
-        <v>-140000</v>
+        <v>91674.44</v>
       </c>
       <c r="F205">
-        <v>-139484.71</v>
+        <v>92347.16</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B206" t="str">
-        <v>2024-11-21</v>
+        <v>2024-11-25</v>
       </c>
       <c r="C206">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="D206" t="str">
         <v>Pesos</v>
       </c>
       <c r="E206">
-        <v>-66912.23</v>
+        <v>140157.43</v>
       </c>
       <c r="F206">
-        <v>515.29</v>
+        <v>672.72</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 3169919</v>
       </c>
       <c r="B207" t="str">
-        <v>2024-11-21</v>
+        <v>2024-11-25</v>
       </c>
       <c r="C207">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D207" t="str">
         <v>Pesos</v>
       </c>
       <c r="E207">
-        <v>66349.55</v>
+        <v>-140000</v>
       </c>
       <c r="F207">
-        <v>67427.52</v>
+        <v>-139484.71</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B208" t="str">
-        <v>2024-11-20</v>
+        <v>2024-11-21</v>
       </c>
       <c r="C208">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D208" t="str">
         <v>Pesos</v>
       </c>
       <c r="E208">
-        <v>-73882.48</v>
+        <v>-66912.23</v>
       </c>
       <c r="F208">
-        <v>1077.97</v>
+        <v>515.29</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
+        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B209" t="str">
-        <v>2024-11-20</v>
+        <v>2024-11-21</v>
       </c>
       <c r="C209">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D209" t="str">
         <v>Pesos</v>
       </c>
       <c r="E209">
-        <v>73936.61</v>
+        <v>66349.55</v>
       </c>
       <c r="F209">
-        <v>74960.45</v>
+        <v>67427.52</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B210" t="str">
-        <v>2024-11-15</v>
+        <v>2024-11-20</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D210" t="str">
         <v>Pesos</v>
       </c>
       <c r="E210">
-        <v>-0.22</v>
+        <v>-73882.48</v>
       </c>
       <c r="F210">
-        <v>1023.84</v>
+        <v>1077.97</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
       </c>
       <c r="B211" t="str">
-        <v>2024-11-15</v>
+        <v>2024-11-20</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D211" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E211">
-        <v>0.05</v>
+        <v>73936.61</v>
       </c>
       <c r="F211">
-        <v>0.38</v>
+        <v>74960.45</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B212" t="str">
-        <v>2024-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C212">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="D212" t="str">
         <v>Pesos</v>
       </c>
       <c r="E212">
-        <v>-139049.36</v>
+        <v>-0.22</v>
       </c>
       <c r="F212">
-        <v>1024.06</v>
+        <v>1023.84</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B213" t="str">
-        <v>2024-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C213">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D213" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E213">
-        <v>-52427.86</v>
+        <v>0.05</v>
       </c>
       <c r="F213">
-        <v>140073.42</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
+        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B214" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C214">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="D214" t="str">
         <v>Pesos</v>
       </c>
       <c r="E214">
-        <v>31736.7</v>
+        <v>-139049.36</v>
       </c>
       <c r="F214">
-        <v>192501.28</v>
+        <v>1024.06</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B215" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C215">
-        <v>315</v>
+        <v>4</v>
       </c>
       <c r="D215" t="str">
         <v>Pesos</v>
       </c>
       <c r="E215">
-        <v>99970.62</v>
+        <v>-52427.86</v>
       </c>
       <c r="F215">
-        <v>160764.58</v>
+        <v>140073.42</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
       </c>
       <c r="B216" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C216">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D216" t="str">
         <v>Pesos</v>
       </c>
       <c r="E216">
-        <v>58861.67</v>
+        <v>31736.7</v>
       </c>
       <c r="F216">
-        <v>60793.96</v>
+        <v>192501.28</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
+        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B217" t="str">
-        <v>2024-10-29</v>
+        <v>2024-11-01</v>
       </c>
       <c r="C217">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D217" t="str">
         <v>Pesos</v>
       </c>
       <c r="E217">
-        <v>-225944.56</v>
+        <v>99970.62</v>
       </c>
       <c r="F217">
-        <v>1932.29</v>
+        <v>160764.58</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
+        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B218" t="str">
-        <v>2024-10-29</v>
+        <v>2024-11-01</v>
       </c>
       <c r="C218">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D218" t="str">
         <v>Pesos</v>
       </c>
       <c r="E218">
-        <v>102687.56</v>
+        <v>58861.67</v>
       </c>
       <c r="F218">
-        <v>227876.85</v>
+        <v>60793.96</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
+        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
       </c>
       <c r="B219" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>297</v>
       </c>
       <c r="D219" t="str">
         <v>Pesos</v>
       </c>
       <c r="E219">
-        <v>37241.04</v>
+        <v>-225944.56</v>
       </c>
       <c r="F219">
-        <v>125189.29</v>
+        <v>1932.29</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
       </c>
       <c r="B220" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C220">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D220" t="str">
         <v>Pesos</v>
       </c>
       <c r="E220">
-        <v>68729.8</v>
+        <v>102687.56</v>
       </c>
       <c r="F220">
-        <v>87948.25</v>
+        <v>227876.85</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
+        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
       </c>
       <c r="B221" t="str">
         <v>2024-10-29</v>
@@ -4791,155 +4791,155 @@
         <v>Pesos</v>
       </c>
       <c r="E221">
-        <v>18248.61</v>
+        <v>37241.04</v>
       </c>
       <c r="F221">
-        <v>19218.45</v>
+        <v>125189.29</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Comprobante de Pago / 2861824</v>
+        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B222" t="str">
-        <v>2024-10-25</v>
+        <v>2024-10-29</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D222" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E222">
-        <v>-8.71</v>
+        <v>68729.8</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>87948.25</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
       </c>
       <c r="B223" t="str">
-        <v>2024-10-23</v>
+        <v>2024-10-29</v>
       </c>
       <c r="C223">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="D223" t="str">
         <v>Pesos</v>
       </c>
       <c r="E223">
-        <v>-71739.34</v>
+        <v>18248.61</v>
       </c>
       <c r="F223">
-        <v>969.84</v>
+        <v>19218.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
+        <v>Comprobante de Pago / 2861824</v>
       </c>
       <c r="B224" t="str">
-        <v>2024-10-23</v>
+        <v>2024-10-25</v>
       </c>
       <c r="C224">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D224" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E224">
-        <v>52196.96</v>
+        <v>-8.71</v>
       </c>
       <c r="F224">
-        <v>72709.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
+        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B225" t="str">
-        <v>2024-10-22</v>
+        <v>2024-10-23</v>
       </c>
       <c r="C225">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D225" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E225">
-        <v>-100</v>
+        <v>-71739.34</v>
       </c>
       <c r="F225">
-        <v>8.71</v>
+        <v>969.84</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
+        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B226" t="str">
-        <v>2024-10-22</v>
+        <v>2024-10-23</v>
       </c>
       <c r="C226">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="D226" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E226">
-        <v>99.71</v>
+        <v>52196.96</v>
       </c>
       <c r="F226">
-        <v>108.71</v>
+        <v>72709.18</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
+        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
       </c>
       <c r="B227" t="str">
         <v>2024-10-22</v>
       </c>
       <c r="C227">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D227" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E227">
-        <v>-2.47</v>
+        <v>-100</v>
       </c>
       <c r="F227">
-        <v>20512.22</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Recibo de Cobro / 3253687</v>
+        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B228" t="str">
         <v>2024-10-22</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="D228" t="str">
         <v>Dólares</v>
       </c>
       <c r="E228">
-        <v>100</v>
+        <v>99.71</v>
       </c>
       <c r="F228">
-        <v>9</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Comprobante de Pago / 2830288</v>
+        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B229" t="str">
         <v>2024-10-22</v>
@@ -4948,58 +4948,58 @@
         <v>0</v>
       </c>
       <c r="D229" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E229">
-        <v>-100</v>
+        <v>-2.47</v>
       </c>
       <c r="F229">
-        <v>-91</v>
+        <v>20512.22</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
+        <v>Recibo de Cobro / 3253687</v>
       </c>
       <c r="B230" t="str">
-        <v>2024-10-21</v>
+        <v>2024-10-22</v>
       </c>
       <c r="C230">
         <v>0</v>
       </c>
       <c r="D230" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E230">
-        <v>185034.38</v>
+        <v>100</v>
       </c>
       <c r="F230">
-        <v>20514.69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
+        <v>Comprobante de Pago / 2830288</v>
       </c>
       <c r="B231" t="str">
-        <v>2024-10-21</v>
+        <v>2024-10-22</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E231">
-        <v>-1199.18</v>
+        <v>-100</v>
       </c>
       <c r="F231">
-        <v>-164519.69</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B232" t="str">
         <v>2024-10-21</v>
@@ -5011,178 +5011,178 @@
         <v>Pesos</v>
       </c>
       <c r="E232">
-        <v>-243469.32</v>
+        <v>185034.38</v>
       </c>
       <c r="F232">
-        <v>-163320.51</v>
+        <v>20514.69</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
       </c>
       <c r="B233" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C233">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="D233" t="str">
         <v>Pesos</v>
       </c>
       <c r="E233">
-        <v>-129746.54</v>
+        <v>-1199.18</v>
       </c>
       <c r="F233">
-        <v>80148.81</v>
+        <v>-164519.69</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
+        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B234" t="str">
-        <v>2024-10-18</v>
+        <v>2024-10-21</v>
       </c>
       <c r="C234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D234" t="str">
         <v>Pesos</v>
       </c>
       <c r="E234">
-        <v>-33573.99</v>
+        <v>-243469.32</v>
       </c>
       <c r="F234">
-        <v>209895.35</v>
+        <v>-163320.51</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B235" t="str">
-        <v>2024-10-18</v>
+        <v>2024-10-21</v>
       </c>
       <c r="C235">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="D235" t="str">
         <v>Pesos</v>
       </c>
       <c r="E235">
-        <v>142249.86</v>
+        <v>-129746.54</v>
       </c>
       <c r="F235">
-        <v>243469.34</v>
+        <v>80148.81</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
       </c>
       <c r="B236" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C236">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D236" t="str">
         <v>Pesos</v>
       </c>
       <c r="E236">
-        <v>9746.15</v>
+        <v>-33573.99</v>
       </c>
       <c r="F236">
-        <v>101219.48</v>
+        <v>209895.35</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B237" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D237" t="str">
         <v>Pesos</v>
       </c>
       <c r="E237">
-        <v>29703.57</v>
+        <v>142249.86</v>
       </c>
       <c r="F237">
-        <v>91473.33</v>
+        <v>243469.34</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B238" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C238">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D238" t="str">
         <v>Pesos</v>
       </c>
       <c r="E238">
-        <v>57840.15</v>
+        <v>9746.15</v>
       </c>
       <c r="F238">
-        <v>61769.76</v>
+        <v>101219.48</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B239" t="str">
-        <v>2024-10-04</v>
+        <v>2024-10-18</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D239" t="str">
         <v>Pesos</v>
       </c>
       <c r="E239">
-        <v>-0.04</v>
+        <v>29703.57</v>
       </c>
       <c r="F239">
-        <v>3929.61</v>
+        <v>91473.33</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B240" t="str">
-        <v>2024-10-04</v>
+        <v>2024-10-18</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D240" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E240">
-        <v>0.01</v>
+        <v>57840.15</v>
       </c>
       <c r="F240">
-        <v>0.33</v>
+        <v>61769.76</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B241" t="str">
-        <v>2024-10-02</v>
+        <v>2024-10-04</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -5191,18 +5191,18 @@
         <v>Pesos</v>
       </c>
       <c r="E241">
-        <v>-0.51</v>
+        <v>-0.04</v>
       </c>
       <c r="F241">
-        <v>3929.65</v>
+        <v>3929.61</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B242" t="str">
-        <v>2024-10-02</v>
+        <v>2024-10-04</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -5211,18 +5211,18 @@
         <v>Dólares C.V. 7000</v>
       </c>
       <c r="E242">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="F242">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B243" t="str">
-        <v>2024-10-01</v>
+        <v>2024-10-02</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -5231,58 +5231,58 @@
         <v>Pesos</v>
       </c>
       <c r="E243">
-        <v>-296.59</v>
+        <v>-0.51</v>
       </c>
       <c r="F243">
-        <v>3930.16</v>
+        <v>3929.65</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B244" t="str">
-        <v>2024-10-01</v>
+        <v>2024-10-02</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E244">
-        <v>4226.79</v>
+        <v>0.12</v>
       </c>
       <c r="F244">
-        <v>4226.75</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B245" t="str">
-        <v>2024-09-27</v>
+        <v>2024-10-01</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E245">
-        <v>0.01</v>
+        <v>-296.59</v>
       </c>
       <c r="F245">
-        <v>0.2</v>
+        <v>3930.16</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B246" t="str">
-        <v>2024-09-27</v>
+        <v>2024-10-01</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -5291,58 +5291,58 @@
         <v>Pesos</v>
       </c>
       <c r="E246">
-        <v>-0.04</v>
+        <v>4226.79</v>
       </c>
       <c r="F246">
-        <v>-0.04</v>
+        <v>4226.75</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B247" t="str">
-        <v>2024-09-25</v>
+        <v>2024-09-27</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E247">
-        <v>-48646.1</v>
+        <v>0.01</v>
       </c>
       <c r="F247">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B248" t="str">
-        <v>2024-09-25</v>
+        <v>2024-09-27</v>
       </c>
       <c r="C248">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D248" t="str">
         <v>Pesos</v>
       </c>
       <c r="E248">
-        <v>48646.42</v>
+        <v>-0.04</v>
       </c>
       <c r="F248">
-        <v>48646.1</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B249" t="str">
-        <v>2024-09-17</v>
+        <v>2024-09-25</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -5351,38 +5351,38 @@
         <v>Pesos</v>
       </c>
       <c r="E249">
-        <v>-0.12</v>
+        <v>-48646.1</v>
       </c>
       <c r="F249">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B250" t="str">
-        <v>2024-09-17</v>
+        <v>2024-09-25</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D250" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E250">
-        <v>0.03</v>
+        <v>48646.42</v>
       </c>
       <c r="F250">
-        <v>0.19</v>
+        <v>48646.1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B251" t="str">
-        <v>2024-09-13</v>
+        <v>2024-09-17</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -5394,15 +5394,15 @@
         <v>-0.12</v>
       </c>
       <c r="F251">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B252" t="str">
-        <v>2024-09-13</v>
+        <v>2024-09-17</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -5414,192 +5414,192 @@
         <v>0.03</v>
       </c>
       <c r="F252">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Renta / BPY26</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B253" t="str">
-        <v>2024-09-02</v>
+        <v>2024-09-13</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E253">
-        <v>1.45</v>
+        <v>-0.12</v>
       </c>
       <c r="F253">
-        <v>9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B254" t="str">
-        <v>2024-08-20</v>
+        <v>2024-09-13</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E254">
-        <v>-171669.97</v>
+        <v>0.03</v>
       </c>
       <c r="F254">
-        <v>-0.08</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
+        <v>Renta / BPY26</v>
       </c>
       <c r="B255" t="str">
-        <v>2024-08-19</v>
+        <v>2024-09-02</v>
       </c>
       <c r="C255">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D255" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E255">
-        <v>-243839.94</v>
+        <v>1.45</v>
       </c>
       <c r="F255">
-        <v>171669.89</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
+        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B256" t="str">
-        <v>2024-08-19</v>
+        <v>2024-08-20</v>
       </c>
       <c r="C256">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D256" t="str">
         <v>Pesos</v>
       </c>
       <c r="E256">
-        <v>-196906.93</v>
+        <v>-171669.97</v>
       </c>
       <c r="F256">
-        <v>415509.83</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B257" t="str">
-        <v>2024-08-16</v>
+        <v>2024-08-19</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D257" t="str">
         <v>Pesos</v>
       </c>
       <c r="E257">
-        <v>-0.08</v>
+        <v>-243839.94</v>
       </c>
       <c r="F257">
-        <v>612416.76</v>
+        <v>171669.89</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B258" t="str">
-        <v>2024-08-16</v>
+        <v>2024-08-19</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D258" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E258">
-        <v>0.02</v>
+        <v>-196906.93</v>
       </c>
       <c r="F258">
-        <v>0.13</v>
+        <v>415509.83</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B259" t="str">
         <v>2024-08-16</v>
       </c>
       <c r="C259">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D259" t="str">
         <v>Pesos</v>
       </c>
       <c r="E259">
-        <v>13250.08</v>
+        <v>-0.08</v>
       </c>
       <c r="F259">
-        <v>612416.84</v>
+        <v>612416.76</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B260" t="str">
-        <v>2024-08-13</v>
+        <v>2024-08-16</v>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D260" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E260">
-        <v>-35187.15</v>
+        <v>0.02</v>
       </c>
       <c r="F260">
-        <v>599166.76</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B261" t="str">
-        <v>2024-08-13</v>
+        <v>2024-08-16</v>
       </c>
       <c r="C261">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D261" t="str">
         <v>Pesos</v>
       </c>
       <c r="E261">
-        <v>-31679.73</v>
+        <v>13250.08</v>
       </c>
       <c r="F261">
-        <v>634353.91</v>
+        <v>612416.84</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
+        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
       </c>
       <c r="B262" t="str">
         <v>2024-08-13</v>
@@ -5611,55 +5611,55 @@
         <v>Pesos</v>
       </c>
       <c r="E262">
-        <v>-18430.41</v>
+        <v>-35187.15</v>
       </c>
       <c r="F262">
-        <v>666033.64</v>
+        <v>599166.76</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
+        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B263" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C263">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D263" t="str">
         <v>Pesos</v>
       </c>
       <c r="E263">
-        <v>-36144.97</v>
+        <v>-31679.73</v>
       </c>
       <c r="F263">
-        <v>684464.05</v>
+        <v>634353.91</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
+        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
       </c>
       <c r="B264" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C264">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D264" t="str">
         <v>Pesos</v>
       </c>
       <c r="E264">
-        <v>-30045.2</v>
+        <v>-18430.41</v>
       </c>
       <c r="F264">
-        <v>720609.02</v>
+        <v>666033.64</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
+        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
       </c>
       <c r="B265" t="str">
         <v>2024-08-13</v>
@@ -5671,95 +5671,95 @@
         <v>Pesos</v>
       </c>
       <c r="E265">
-        <v>-35590.45</v>
+        <v>-36144.97</v>
       </c>
       <c r="F265">
-        <v>750654.22</v>
+        <v>684464.05</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
       </c>
       <c r="B266" t="str">
-        <v>2024-08-12</v>
+        <v>2024-08-13</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D266" t="str">
         <v>Pesos</v>
       </c>
       <c r="E266">
-        <v>-500000</v>
+        <v>-30045.2</v>
       </c>
       <c r="F266">
-        <v>786244.67</v>
+        <v>720609.02</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
       </c>
       <c r="B267" t="str">
-        <v>2024-08-09</v>
+        <v>2024-08-13</v>
       </c>
       <c r="C267">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D267" t="str">
         <v>Pesos</v>
       </c>
       <c r="E267">
-        <v>-18274.14</v>
+        <v>-35590.45</v>
       </c>
       <c r="F267">
-        <v>1286244.67</v>
+        <v>750654.22</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
+        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B268" t="str">
-        <v>2024-08-09</v>
+        <v>2024-08-12</v>
       </c>
       <c r="C268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D268" t="str">
         <v>Pesos</v>
       </c>
       <c r="E268">
-        <v>-17417.14</v>
+        <v>-500000</v>
       </c>
       <c r="F268">
-        <v>1304518.81</v>
+        <v>786244.67</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B269" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C269">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="D269" t="str">
         <v>Pesos</v>
       </c>
       <c r="E269">
-        <v>-49536.26</v>
+        <v>-18274.14</v>
       </c>
       <c r="F269">
-        <v>1321935.95</v>
+        <v>1286244.67</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B270" t="str">
         <v>2024-08-09</v>
@@ -5771,355 +5771,355 @@
         <v>Pesos</v>
       </c>
       <c r="E270">
-        <v>-14089.99</v>
+        <v>-17417.14</v>
       </c>
       <c r="F270">
-        <v>1371472.21</v>
+        <v>1304518.81</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B271" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C271">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="D271" t="str">
         <v>Pesos</v>
       </c>
       <c r="E271">
-        <v>-85669.13</v>
+        <v>-49536.26</v>
       </c>
       <c r="F271">
-        <v>1385562.2</v>
+        <v>1321935.95</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B272" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C272">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D272" t="str">
         <v>Pesos</v>
       </c>
       <c r="E272">
-        <v>-14926.81</v>
+        <v>-14089.99</v>
       </c>
       <c r="F272">
-        <v>1471231.33</v>
+        <v>1371472.21</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
+        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B273" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C273">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="D273" t="str">
         <v>Pesos</v>
       </c>
       <c r="E273">
-        <v>-88949.9</v>
+        <v>-85669.13</v>
       </c>
       <c r="F273">
-        <v>1486158.14</v>
+        <v>1385562.2</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B274" t="str">
-        <v>2024-08-08</v>
+        <v>2024-08-09</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D274" t="str">
         <v>Pesos</v>
       </c>
       <c r="E274">
-        <v>-500000</v>
+        <v>-14926.81</v>
       </c>
       <c r="F274">
-        <v>1575108.04</v>
+        <v>1471231.33</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
       </c>
       <c r="B275" t="str">
-        <v>2024-08-08</v>
+        <v>2024-08-09</v>
       </c>
       <c r="C275">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="D275" t="str">
         <v>Pesos</v>
       </c>
       <c r="E275">
-        <v>-20325.87</v>
+        <v>-88949.9</v>
       </c>
       <c r="F275">
-        <v>2075108.04</v>
+        <v>1486158.14</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B276" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C276">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D276" t="str">
         <v>Pesos</v>
       </c>
       <c r="E276">
-        <v>-46136.52</v>
+        <v>-500000</v>
       </c>
       <c r="F276">
-        <v>2095433.91</v>
+        <v>1575108.04</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
+        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B277" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C277">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D277" t="str">
         <v>Pesos</v>
       </c>
       <c r="E277">
-        <v>-27927.91</v>
+        <v>-20325.87</v>
       </c>
       <c r="F277">
-        <v>2141570.43</v>
+        <v>2075108.04</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B278" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C278">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="D278" t="str">
         <v>Pesos</v>
       </c>
       <c r="E278">
-        <v>-50260.67</v>
+        <v>-46136.52</v>
       </c>
       <c r="F278">
-        <v>2169498.34</v>
+        <v>2095433.91</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
+        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
       </c>
       <c r="B279" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C279">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D279" t="str">
         <v>Pesos</v>
       </c>
       <c r="E279">
-        <v>-37506.08</v>
+        <v>-27927.91</v>
       </c>
       <c r="F279">
-        <v>2219759.01</v>
+        <v>2141570.43</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B280" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="D280" t="str">
         <v>Pesos</v>
       </c>
       <c r="E280">
-        <v>-28280.79</v>
+        <v>-50260.67</v>
       </c>
       <c r="F280">
-        <v>2257265.09</v>
+        <v>2169498.34</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
       </c>
       <c r="B281" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C281">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D281" t="str">
         <v>Pesos</v>
       </c>
       <c r="E281">
-        <v>-53133.61</v>
+        <v>-37506.08</v>
       </c>
       <c r="F281">
-        <v>2285545.88</v>
+        <v>2219759.01</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B282" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C282">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D282" t="str">
         <v>Pesos</v>
       </c>
       <c r="E282">
-        <v>-28069.07</v>
+        <v>-28280.79</v>
       </c>
       <c r="F282">
-        <v>2338679.49</v>
+        <v>2257265.09</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B283" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D283" t="str">
         <v>Pesos</v>
       </c>
       <c r="E283">
-        <v>-19937.71</v>
+        <v>-53133.61</v>
       </c>
       <c r="F283">
-        <v>2366748.56</v>
+        <v>2285545.88</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
+        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B284" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C284">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D284" t="str">
         <v>Pesos</v>
       </c>
       <c r="E284">
-        <v>-40228.29</v>
+        <v>-28069.07</v>
       </c>
       <c r="F284">
-        <v>2386686.27</v>
+        <v>2338679.49</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B285" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C285">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D285" t="str">
         <v>Pesos</v>
       </c>
       <c r="E285">
-        <v>-25407.34</v>
+        <v>-19937.71</v>
       </c>
       <c r="F285">
-        <v>2426914.56</v>
+        <v>2366748.56</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
       </c>
       <c r="B286" t="str">
-        <v>2024-08-05</v>
+        <v>2024-08-08</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D286" t="str">
         <v>Pesos</v>
       </c>
       <c r="E286">
-        <v>1000000</v>
+        <v>-40228.29</v>
       </c>
       <c r="F286">
-        <v>2452321.9</v>
+        <v>2386686.27</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B287" t="str">
-        <v>2024-08-05</v>
+        <v>2024-08-08</v>
       </c>
       <c r="C287">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D287" t="str">
         <v>Pesos</v>
       </c>
       <c r="E287">
-        <v>218666.47</v>
+        <v>-25407.34</v>
       </c>
       <c r="F287">
-        <v>1452321.9</v>
+        <v>2426914.56</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
+        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B288" t="str">
         <v>2024-08-05</v>
@@ -6131,15 +6131,15 @@
         <v>Pesos</v>
       </c>
       <c r="E288">
-        <v>164626.92</v>
+        <v>1000000</v>
       </c>
       <c r="F288">
-        <v>1233655.43</v>
+        <v>2452321.9</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B289" t="str">
         <v>2024-08-05</v>
@@ -6151,318 +6151,318 @@
         <v>Pesos</v>
       </c>
       <c r="E289">
-        <v>152793.11</v>
+        <v>218666.47</v>
       </c>
       <c r="F289">
-        <v>1069028.51</v>
+        <v>1452321.9</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
+        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B290" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C290">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D290" t="str">
         <v>Pesos</v>
       </c>
       <c r="E290">
-        <v>55836.76</v>
+        <v>164626.92</v>
       </c>
       <c r="F290">
-        <v>916235.4</v>
+        <v>1233655.43</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B291" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C291">
-        <v>1416</v>
+        <v>0</v>
       </c>
       <c r="D291" t="str">
         <v>Pesos</v>
       </c>
       <c r="E291">
-        <v>-879220.78</v>
+        <v>152793.11</v>
       </c>
       <c r="F291">
-        <v>860398.64</v>
+        <v>1069028.51</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
       </c>
       <c r="B292" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C292">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D292" t="str">
         <v>Pesos</v>
       </c>
       <c r="E292">
-        <v>96717.6</v>
+        <v>55836.76</v>
       </c>
       <c r="F292">
-        <v>1739619.42</v>
+        <v>916235.4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B293" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C293">
-        <v>29</v>
+        <v>1416</v>
       </c>
       <c r="D293" t="str">
         <v>Pesos</v>
       </c>
       <c r="E293">
-        <v>159943.07</v>
+        <v>-879220.78</v>
       </c>
       <c r="F293">
-        <v>1642901.82</v>
+        <v>860398.64</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B294" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C294">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D294" t="str">
         <v>Pesos</v>
       </c>
       <c r="E294">
-        <v>70757.98</v>
+        <v>96717.6</v>
       </c>
       <c r="F294">
-        <v>1482958.75</v>
+        <v>1739619.42</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B295" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C295">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D295" t="str">
         <v>Pesos</v>
       </c>
       <c r="E295">
-        <v>96479.58</v>
+        <v>159943.07</v>
       </c>
       <c r="F295">
-        <v>1412200.77</v>
+        <v>1642901.82</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
+        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B296" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C296">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D296" t="str">
         <v>Pesos</v>
       </c>
       <c r="E296">
-        <v>52117.62</v>
+        <v>70757.98</v>
       </c>
       <c r="F296">
-        <v>1315721.19</v>
+        <v>1482958.75</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B297" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C297">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D297" t="str">
         <v>Pesos</v>
       </c>
       <c r="E297">
-        <v>45423.16</v>
+        <v>96479.58</v>
       </c>
       <c r="F297">
-        <v>1263603.57</v>
+        <v>1412200.77</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
       </c>
       <c r="B298" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C298">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="D298" t="str">
         <v>Pesos</v>
       </c>
       <c r="E298">
-        <v>59565.82</v>
+        <v>52117.62</v>
       </c>
       <c r="F298">
-        <v>1218180.41</v>
+        <v>1315721.19</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B299" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C299">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D299" t="str">
         <v>Pesos</v>
       </c>
       <c r="E299">
-        <v>101983.91</v>
+        <v>45423.16</v>
       </c>
       <c r="F299">
-        <v>1158614.59</v>
+        <v>1263603.57</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B300" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C300">
-        <v>61</v>
+        <v>220</v>
       </c>
       <c r="D300" t="str">
         <v>Pesos</v>
       </c>
       <c r="E300">
-        <v>59530.13</v>
+        <v>59565.82</v>
       </c>
       <c r="F300">
-        <v>1056630.68</v>
+        <v>1218180.41</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B301" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C301">
-        <v>1536</v>
+        <v>26</v>
       </c>
       <c r="D301" t="str">
         <v>Pesos</v>
       </c>
       <c r="E301">
-        <v>942562.63</v>
+        <v>101983.91</v>
       </c>
       <c r="F301">
-        <v>997100.55</v>
+        <v>1158614.59</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B302" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C302">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D302" t="str">
         <v>Pesos</v>
       </c>
       <c r="E302">
-        <v>53000.3</v>
+        <v>59530.13</v>
       </c>
       <c r="F302">
-        <v>54537.92</v>
+        <v>1056630.68</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B303" t="str">
-        <v>2024-07-24</v>
+        <v>2024-08-05</v>
       </c>
       <c r="C303">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="D303" t="str">
         <v>Pesos</v>
       </c>
       <c r="E303">
-        <v>-116.05</v>
+        <v>942562.63</v>
       </c>
       <c r="F303">
-        <v>1537.62</v>
+        <v>997100.55</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B304" t="str">
-        <v>2024-07-24</v>
+        <v>2024-08-05</v>
       </c>
       <c r="C304">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D304" t="str">
         <v>Pesos</v>
       </c>
       <c r="E304">
-        <v>1653.89</v>
+        <v>53000.3</v>
       </c>
       <c r="F304">
-        <v>1653.67</v>
+        <v>54537.92</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B305" t="str">
-        <v>2024-07-10</v>
+        <v>2024-07-24</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -6471,38 +6471,38 @@
         <v>Pesos</v>
       </c>
       <c r="E305">
-        <v>-0.21</v>
+        <v>-116.05</v>
       </c>
       <c r="F305">
-        <v>-0.22</v>
+        <v>1537.62</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B306" t="str">
-        <v>2024-07-10</v>
+        <v>2024-07-24</v>
       </c>
       <c r="C306">
         <v>0</v>
       </c>
       <c r="D306" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E306">
-        <v>5.25</v>
+        <v>1653.89</v>
       </c>
       <c r="F306">
-        <v>7.55</v>
+        <v>1653.67</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B307" t="str">
-        <v>2024-07-08</v>
+        <v>2024-07-10</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -6511,55 +6511,55 @@
         <v>Pesos</v>
       </c>
       <c r="E307">
-        <v>-4402.49</v>
+        <v>-0.21</v>
       </c>
       <c r="F307">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B308" t="str">
-        <v>2024-07-08</v>
+        <v>2024-07-10</v>
       </c>
       <c r="C308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D308" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E308">
-        <v>-38067.66</v>
+        <v>5.25</v>
       </c>
       <c r="F308">
-        <v>4402.48</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
+        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B309" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C309">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D309" t="str">
         <v>Pesos</v>
       </c>
       <c r="E309">
-        <v>-47346.39</v>
+        <v>-4402.49</v>
       </c>
       <c r="F309">
-        <v>42470.14</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
       </c>
       <c r="B310" t="str">
         <v>2024-07-08</v>
@@ -6571,195 +6571,195 @@
         <v>Pesos</v>
       </c>
       <c r="E310">
-        <v>15580.74</v>
+        <v>-38067.66</v>
       </c>
       <c r="F310">
-        <v>89816.53</v>
+        <v>4402.48</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B311" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C311">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D311" t="str">
         <v>Pesos</v>
       </c>
       <c r="E311">
-        <v>34892.52</v>
+        <v>-47346.39</v>
       </c>
       <c r="F311">
-        <v>74235.79</v>
+        <v>42470.14</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B312" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C312">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D312" t="str">
         <v>Pesos</v>
       </c>
       <c r="E312">
-        <v>37865.35</v>
+        <v>15580.74</v>
       </c>
       <c r="F312">
-        <v>39343.27</v>
+        <v>89816.53</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
+        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B313" t="str">
-        <v>2024-07-02</v>
+        <v>2024-07-08</v>
       </c>
       <c r="C313">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D313" t="str">
         <v>Pesos</v>
       </c>
       <c r="E313">
-        <v>-152584.35</v>
+        <v>34892.52</v>
       </c>
       <c r="F313">
-        <v>1477.92</v>
+        <v>74235.79</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
+        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B314" t="str">
-        <v>2024-07-02</v>
+        <v>2024-07-08</v>
       </c>
       <c r="C314">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D314" t="str">
         <v>Pesos</v>
       </c>
       <c r="E314">
-        <v>151114.01</v>
+        <v>37865.35</v>
       </c>
       <c r="F314">
-        <v>154062.27</v>
+        <v>39343.27</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
+        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B315" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C315">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D315" t="str">
         <v>Pesos</v>
       </c>
       <c r="E315">
-        <v>-108902.21</v>
+        <v>-152584.35</v>
       </c>
       <c r="F315">
-        <v>2948.26</v>
+        <v>1477.92</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
+        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B316" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C316">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D316" t="str">
         <v>Pesos</v>
       </c>
       <c r="E316">
-        <v>-41051.01</v>
+        <v>151114.01</v>
       </c>
       <c r="F316">
-        <v>111850.47</v>
+        <v>154062.27</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
+        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
       </c>
       <c r="B317" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C317">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D317" t="str">
         <v>Pesos</v>
       </c>
       <c r="E317">
-        <v>151431.18</v>
+        <v>-108902.21</v>
       </c>
       <c r="F317">
-        <v>152901.48</v>
+        <v>2948.26</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B318" t="str">
-        <v>2024-07-01</v>
+        <v>2024-07-02</v>
       </c>
       <c r="C318">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D318" t="str">
         <v>Pesos</v>
       </c>
       <c r="E318">
-        <v>-0.04</v>
+        <v>-41051.01</v>
       </c>
       <c r="F318">
-        <v>1470.3</v>
+        <v>111850.47</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B319" t="str">
-        <v>2024-07-01</v>
+        <v>2024-07-02</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D319" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E319">
-        <v>0.01</v>
+        <v>151431.18</v>
       </c>
       <c r="F319">
-        <v>0.11</v>
+        <v>152901.48</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B320" t="str">
         <v>2024-07-01</v>
@@ -6771,15 +6771,15 @@
         <v>Pesos</v>
       </c>
       <c r="E320">
-        <v>-110.98</v>
+        <v>-0.04</v>
       </c>
       <c r="F320">
-        <v>1470.34</v>
+        <v>1470.3</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B321" t="str">
         <v>2024-07-01</v>
@@ -6788,21 +6788,21 @@
         <v>0</v>
       </c>
       <c r="D321" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E321">
-        <v>1581.51</v>
+        <v>0.01</v>
       </c>
       <c r="F321">
-        <v>1581.32</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B322" t="str">
-        <v>2024-06-27</v>
+        <v>2024-07-01</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -6811,38 +6811,38 @@
         <v>Pesos</v>
       </c>
       <c r="E322">
-        <v>-0.12</v>
+        <v>-110.98</v>
       </c>
       <c r="F322">
-        <v>-0.19</v>
+        <v>1470.34</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B323" t="str">
-        <v>2024-06-27</v>
+        <v>2024-07-01</v>
       </c>
       <c r="C323">
         <v>0</v>
       </c>
       <c r="D323" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E323">
-        <v>0.03</v>
+        <v>1581.51</v>
       </c>
       <c r="F323">
-        <v>0.1</v>
+        <v>1581.32</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B324" t="str">
-        <v>2024-06-24</v>
+        <v>2024-06-27</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -6851,35 +6851,35 @@
         <v>Pesos</v>
       </c>
       <c r="E324">
-        <v>-175.43</v>
+        <v>-0.12</v>
       </c>
       <c r="F324">
-        <v>-0.07</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B325" t="str">
-        <v>2024-06-24</v>
+        <v>2024-06-27</v>
       </c>
       <c r="C325">
         <v>0</v>
       </c>
       <c r="D325" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E325">
-        <v>-150000</v>
+        <v>0.03</v>
       </c>
       <c r="F325">
-        <v>175.36</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
+        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
       </c>
       <c r="B326" t="str">
         <v>2024-06-24</v>
@@ -6891,18 +6891,18 @@
         <v>Pesos</v>
       </c>
       <c r="E326">
-        <v>-150447.89</v>
+        <v>-175.43</v>
       </c>
       <c r="F326">
-        <v>150175.36</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B327" t="str">
-        <v>2024-06-19</v>
+        <v>2024-06-24</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -6911,35 +6911,35 @@
         <v>Pesos</v>
       </c>
       <c r="E327">
-        <v>-0.07</v>
+        <v>-150000</v>
       </c>
       <c r="F327">
-        <v>300623.25</v>
+        <v>175.36</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B328" t="str">
-        <v>2024-06-19</v>
+        <v>2024-06-24</v>
       </c>
       <c r="C328">
         <v>0</v>
       </c>
       <c r="D328" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E328">
-        <v>0.02</v>
+        <v>-150447.89</v>
       </c>
       <c r="F328">
-        <v>0.07</v>
+        <v>150175.36</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B329" t="str">
         <v>2024-06-19</v>
@@ -6951,515 +6951,515 @@
         <v>Pesos</v>
       </c>
       <c r="E329">
-        <v>300000</v>
+        <v>-0.07</v>
       </c>
       <c r="F329">
-        <v>300623.32</v>
+        <v>300623.25</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Dividendo en efectivo / INTC</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B330" t="str">
-        <v>2024-06-04</v>
+        <v>2024-06-19</v>
       </c>
       <c r="C330">
         <v>0</v>
       </c>
       <c r="D330" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E330">
-        <v>-0.19</v>
+        <v>0.02</v>
       </c>
       <c r="F330">
-        <v>623.32</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Dividendo en efectivo / INTC</v>
+        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B331" t="str">
-        <v>2024-06-04</v>
+        <v>2024-06-19</v>
       </c>
       <c r="C331">
         <v>0</v>
       </c>
       <c r="D331" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E331">
-        <v>0.05</v>
+        <v>300000</v>
       </c>
       <c r="F331">
-        <v>0.05</v>
+        <v>300623.32</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
+        <v>Dividendo en efectivo / INTC</v>
       </c>
       <c r="B332" t="str">
-        <v>2024-05-31</v>
+        <v>2024-06-04</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D332" t="str">
         <v>Pesos</v>
       </c>
       <c r="E332">
-        <v>55120.7</v>
+        <v>-0.19</v>
       </c>
       <c r="F332">
-        <v>623.51</v>
+        <v>623.32</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
+        <v>Dividendo en efectivo / INTC</v>
       </c>
       <c r="B333" t="str">
-        <v>2024-05-31</v>
+        <v>2024-06-04</v>
       </c>
       <c r="C333">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D333" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E333">
-        <v>-36734.79</v>
+        <v>0.05</v>
       </c>
       <c r="F333">
-        <v>-54497.19</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
+        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B334" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C334">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D334" t="str">
         <v>Pesos</v>
       </c>
       <c r="E334">
-        <v>-59561.06</v>
+        <v>55120.7</v>
       </c>
       <c r="F334">
-        <v>-17762.4</v>
+        <v>623.51</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
+        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B335" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C335">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D335" t="str">
         <v>Pesos</v>
       </c>
       <c r="E335">
-        <v>38496.62</v>
+        <v>-36734.79</v>
       </c>
       <c r="F335">
-        <v>41798.66</v>
+        <v>-54497.19</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
+        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
       </c>
       <c r="B336" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C336">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D336" t="str">
         <v>Pesos</v>
       </c>
       <c r="E336">
-        <v>48021.6</v>
+        <v>-59561.06</v>
       </c>
       <c r="F336">
-        <v>3302.04</v>
+        <v>-17762.4</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
+        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
       </c>
       <c r="B337" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C337">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D337" t="str">
         <v>Pesos</v>
       </c>
       <c r="E337">
-        <v>-47487.54</v>
+        <v>38496.62</v>
       </c>
       <c r="F337">
-        <v>-44719.56</v>
+        <v>41798.66</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Movimiento Manual / Ret IIGG - GGAL</v>
+        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
       </c>
       <c r="B338" t="str">
-        <v>2024-05-27</v>
+        <v>2024-05-31</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D338" t="str">
         <v>Pesos</v>
       </c>
       <c r="E338">
-        <v>-73.45</v>
+        <v>48021.6</v>
       </c>
       <c r="F338">
-        <v>2767.98</v>
+        <v>3302.04</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
       </c>
       <c r="B339" t="str">
-        <v>2024-05-24</v>
+        <v>2024-05-31</v>
       </c>
       <c r="C339">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D339" t="str">
         <v>Pesos</v>
       </c>
       <c r="E339">
-        <v>1518.11</v>
+        <v>-47487.54</v>
       </c>
       <c r="F339">
-        <v>2841.43</v>
+        <v>-44719.56</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
+        <v>Movimiento Manual / Ret IIGG - GGAL</v>
       </c>
       <c r="B340" t="str">
-        <v>2024-05-23</v>
+        <v>2024-05-27</v>
       </c>
       <c r="C340">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D340" t="str">
         <v>Pesos</v>
       </c>
       <c r="E340">
-        <v>-81669.11</v>
+        <v>-73.45</v>
       </c>
       <c r="F340">
-        <v>1323.32</v>
+        <v>2767.98</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B341" t="str">
-        <v>2024-05-21</v>
+        <v>2024-05-24</v>
       </c>
       <c r="C341">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D341" t="str">
         <v>Pesos</v>
       </c>
       <c r="E341">
-        <v>21949.4</v>
+        <v>1518.11</v>
       </c>
       <c r="F341">
-        <v>82992.43</v>
+        <v>2841.43</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
+        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B342" t="str">
-        <v>2024-05-21</v>
+        <v>2024-05-23</v>
       </c>
       <c r="C342">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D342" t="str">
         <v>Pesos</v>
       </c>
       <c r="E342">
-        <v>57393.84</v>
+        <v>-81669.11</v>
       </c>
       <c r="F342">
-        <v>61043.03</v>
+        <v>1323.32</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
       </c>
       <c r="B343" t="str">
-        <v>2024-05-15</v>
+        <v>2024-05-21</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D343" t="str">
         <v>Pesos</v>
       </c>
       <c r="E343">
-        <v>703.51</v>
+        <v>21949.4</v>
       </c>
       <c r="F343">
-        <v>3649.19</v>
+        <v>82992.43</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
       </c>
       <c r="B344" t="str">
-        <v>2024-05-14</v>
+        <v>2024-05-21</v>
       </c>
       <c r="C344">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D344" t="str">
         <v>Pesos</v>
       </c>
       <c r="E344">
-        <v>-130000</v>
+        <v>57393.84</v>
       </c>
       <c r="F344">
-        <v>2945.68</v>
+        <v>61043.03</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Distribución de acciones por Capitalización / BYMA</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B345" t="str">
-        <v>2024-05-14</v>
+        <v>2024-05-15</v>
       </c>
       <c r="C345">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D345" t="str">
         <v>Pesos</v>
       </c>
       <c r="E345">
-        <v>-0.44</v>
+        <v>703.51</v>
       </c>
       <c r="F345">
-        <v>132945.68</v>
+        <v>3649.19</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B346" t="str">
-        <v>2024-05-07</v>
+        <v>2024-05-14</v>
       </c>
       <c r="C346">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D346" t="str">
         <v>Pesos</v>
       </c>
       <c r="E346">
-        <v>5097.7</v>
+        <v>-130000</v>
       </c>
       <c r="F346">
-        <v>132946.12</v>
+        <v>2945.68</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
+        <v>Distribución de acciones por Capitalización / BYMA</v>
       </c>
       <c r="B347" t="str">
-        <v>2024-05-07</v>
+        <v>2024-05-14</v>
       </c>
       <c r="C347">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="D347" t="str">
         <v>Pesos</v>
       </c>
       <c r="E347">
-        <v>23635.91</v>
+        <v>-0.44</v>
       </c>
       <c r="F347">
-        <v>127848.42</v>
+        <v>132945.68</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B348" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C348">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D348" t="str">
         <v>Pesos</v>
       </c>
       <c r="E348">
-        <v>20921.43</v>
+        <v>5097.7</v>
       </c>
       <c r="F348">
-        <v>104212.51</v>
+        <v>132946.12</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B349" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C349">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D349" t="str">
         <v>Pesos</v>
       </c>
       <c r="E349">
-        <v>11618.11</v>
+        <v>23635.91</v>
       </c>
       <c r="F349">
-        <v>83291.08</v>
+        <v>127848.42</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
+        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B350" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C350">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D350" t="str">
         <v>Pesos</v>
       </c>
       <c r="E350">
-        <v>52241.19</v>
+        <v>20921.43</v>
       </c>
       <c r="F350">
-        <v>71672.97</v>
+        <v>104212.51</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B351" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C351">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D351" t="str">
         <v>Pesos</v>
       </c>
       <c r="E351">
-        <v>19431.78</v>
+        <v>11618.11</v>
       </c>
       <c r="F351">
-        <v>19431.78</v>
+        <v>83291.08</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B352" t="str">
-        <v>2024-05-06</v>
+        <v>2024-05-07</v>
       </c>
       <c r="C352">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D352" t="str">
         <v>Pesos</v>
       </c>
       <c r="E352">
-        <v>-222622.08</v>
+        <v>52241.19</v>
       </c>
       <c r="F352">
-        <v>0</v>
+        <v>71672.97</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
+        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B353" t="str">
-        <v>2024-05-02</v>
+        <v>2024-05-07</v>
       </c>
       <c r="C353">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D353" t="str">
         <v>Pesos</v>
       </c>
       <c r="E353">
-        <v>99355.72</v>
+        <v>19431.78</v>
       </c>
       <c r="F353">
-        <v>222622.08</v>
+        <v>19431.78</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
+        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B354" t="str">
-        <v>2024-05-02</v>
+        <v>2024-05-06</v>
       </c>
       <c r="C354">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D354" t="str">
         <v>Pesos</v>
       </c>
       <c r="E354">
-        <v>66604.92</v>
+        <v>-222622.08</v>
       </c>
       <c r="F354">
-        <v>123266.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B355" t="str">
         <v>2024-05-02</v>
@@ -7471,35 +7471,35 @@
         <v>Pesos</v>
       </c>
       <c r="E355">
-        <v>6069.65</v>
+        <v>99355.72</v>
       </c>
       <c r="F355">
-        <v>56661.44</v>
+        <v>222622.08</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
+        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
       </c>
       <c r="B356" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C356">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D356" t="str">
         <v>Pesos</v>
       </c>
       <c r="E356">
-        <v>2488.36</v>
+        <v>66604.92</v>
       </c>
       <c r="F356">
-        <v>50591.79</v>
+        <v>123266.36</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B357" t="str">
         <v>2024-05-02</v>
@@ -7511,95 +7511,95 @@
         <v>Pesos</v>
       </c>
       <c r="E357">
-        <v>14202.18</v>
+        <v>6069.65</v>
       </c>
       <c r="F357">
-        <v>48103.43</v>
+        <v>56661.44</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B358" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C358">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D358" t="str">
         <v>Pesos</v>
       </c>
       <c r="E358">
-        <v>12418.97</v>
+        <v>2488.36</v>
       </c>
       <c r="F358">
-        <v>33901.25</v>
+        <v>50591.79</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B359" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C359">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D359" t="str">
         <v>Pesos</v>
       </c>
       <c r="E359">
-        <v>20579.26</v>
+        <v>14202.18</v>
       </c>
       <c r="F359">
-        <v>21482.28</v>
+        <v>48103.43</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
+        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B360" t="str">
-        <v>2024-04-17</v>
+        <v>2024-05-02</v>
       </c>
       <c r="C360">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D360" t="str">
         <v>Pesos</v>
       </c>
       <c r="E360">
-        <v>-34.33</v>
+        <v>12418.97</v>
       </c>
       <c r="F360">
-        <v>903.02</v>
+        <v>33901.25</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B361" t="str">
-        <v>2024-04-17</v>
+        <v>2024-05-02</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D361" t="str">
         <v>Pesos</v>
       </c>
       <c r="E361">
-        <v>489.31</v>
+        <v>20579.26</v>
       </c>
       <c r="F361">
-        <v>937.35</v>
+        <v>21482.28</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Movimiento Manual / Ret IIGG - BYMA</v>
+        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
       </c>
       <c r="B362" t="str">
         <v>2024-04-17</v>
@@ -7608,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="D362" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E362">
-        <v>-0.18</v>
+        <v>-34.33</v>
       </c>
       <c r="F362">
-        <v>2.3</v>
+        <v>903.02</v>
       </c>
     </row>
     <row r="363">
@@ -7631,15 +7631,15 @@
         <v>Pesos</v>
       </c>
       <c r="E363">
-        <v>-2.6</v>
+        <v>489.31</v>
       </c>
       <c r="F363">
-        <v>448.04</v>
+        <v>937.35</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG - BYMA</v>
       </c>
       <c r="B364" t="str">
         <v>2024-04-17</v>
@@ -7651,95 +7651,95 @@
         <v>Dólares</v>
       </c>
       <c r="E364">
-        <v>2.48</v>
+        <v>-0.18</v>
       </c>
       <c r="F364">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B365" t="str">
-        <v>2024-04-10</v>
+        <v>2024-04-17</v>
       </c>
       <c r="C365">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D365" t="str">
         <v>Pesos</v>
       </c>
       <c r="E365">
-        <v>-80932.98</v>
+        <v>-2.6</v>
       </c>
       <c r="F365">
-        <v>450.64</v>
+        <v>448.04</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B366" t="str">
-        <v>2024-04-09</v>
+        <v>2024-04-17</v>
       </c>
       <c r="C366">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D366" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E366">
-        <v>104967.66</v>
+        <v>2.48</v>
       </c>
       <c r="F366">
-        <v>81383.62</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
+        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
       </c>
       <c r="B367" t="str">
-        <v>2024-04-09</v>
+        <v>2024-04-10</v>
       </c>
       <c r="C367">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D367" t="str">
         <v>Pesos</v>
       </c>
       <c r="E367">
-        <v>16388.53</v>
+        <v>-80932.98</v>
       </c>
       <c r="F367">
-        <v>-23584.04</v>
+        <v>450.64</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
+        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
       </c>
       <c r="B368" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C368">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D368" t="str">
         <v>Pesos</v>
       </c>
       <c r="E368">
-        <v>-77278.67</v>
+        <v>104967.66</v>
       </c>
       <c r="F368">
-        <v>-39972.57</v>
+        <v>81383.62</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
+        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
       </c>
       <c r="B369" t="str">
         <v>2024-04-09</v>
@@ -7751,318 +7751,318 @@
         <v>Pesos</v>
       </c>
       <c r="E369">
-        <v>35352.22</v>
+        <v>16388.53</v>
       </c>
       <c r="F369">
-        <v>37306.1</v>
+        <v>-23584.04</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
       </c>
       <c r="B370" t="str">
-        <v>2024-04-08</v>
+        <v>2024-04-09</v>
       </c>
       <c r="C370">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D370" t="str">
         <v>Pesos</v>
       </c>
       <c r="E370">
-        <v>-733461</v>
+        <v>-77278.67</v>
       </c>
       <c r="F370">
-        <v>1953.88</v>
+        <v>-39972.57</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
+        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
       </c>
       <c r="B371" t="str">
-        <v>2024-04-08</v>
+        <v>2024-04-09</v>
       </c>
       <c r="C371">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D371" t="str">
         <v>Pesos</v>
       </c>
       <c r="E371">
-        <v>-229304.33</v>
+        <v>35352.22</v>
       </c>
       <c r="F371">
-        <v>735414.88</v>
+        <v>37306.1</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
+        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B372" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372" t="str">
         <v>Pesos</v>
       </c>
       <c r="E372">
-        <v>-35550.12</v>
+        <v>-733461</v>
       </c>
       <c r="F372">
-        <v>964719.21</v>
+        <v>1953.88</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
+        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
       </c>
       <c r="B373" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C373">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D373" t="str">
         <v>Pesos</v>
       </c>
       <c r="E373">
-        <v>-197072.27</v>
+        <v>-229304.33</v>
       </c>
       <c r="F373">
-        <v>1000269.33</v>
+        <v>735414.88</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
+        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
       </c>
       <c r="B374" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C374">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D374" t="str">
         <v>Pesos</v>
       </c>
       <c r="E374">
-        <v>-24084.05</v>
+        <v>-35550.12</v>
       </c>
       <c r="F374">
-        <v>1197341.6</v>
+        <v>964719.21</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
+        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
       </c>
       <c r="B375" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C375">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D375" t="str">
         <v>Pesos</v>
       </c>
       <c r="E375">
-        <v>-53459.78</v>
+        <v>-197072.27</v>
       </c>
       <c r="F375">
-        <v>1221425.65</v>
+        <v>1000269.33</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
+        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
       </c>
       <c r="B376" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C376">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D376" t="str">
         <v>Pesos</v>
       </c>
       <c r="E376">
-        <v>-100325.74</v>
+        <v>-24084.05</v>
       </c>
       <c r="F376">
-        <v>1274885.43</v>
+        <v>1197341.6</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
+        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
       </c>
       <c r="B377" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C377">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D377" t="str">
         <v>Pesos</v>
       </c>
       <c r="E377">
-        <v>-180029.2</v>
+        <v>-53459.78</v>
       </c>
       <c r="F377">
-        <v>1375211.17</v>
+        <v>1221425.65</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
+        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
       </c>
       <c r="B378" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C378">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D378" t="str">
         <v>Pesos</v>
       </c>
       <c r="E378">
-        <v>-62547.44</v>
+        <v>-100325.74</v>
       </c>
       <c r="F378">
-        <v>1555240.37</v>
+        <v>1274885.43</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
+        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
       </c>
       <c r="B379" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C379">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D379" t="str">
         <v>Pesos</v>
       </c>
       <c r="E379">
-        <v>-60307.16</v>
+        <v>-180029.2</v>
       </c>
       <c r="F379">
-        <v>1617787.81</v>
+        <v>1375211.17</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
+        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
       </c>
       <c r="B380" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C380">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D380" t="str">
         <v>Pesos</v>
       </c>
       <c r="E380">
-        <v>-16504.2</v>
+        <v>-62547.44</v>
       </c>
       <c r="F380">
-        <v>1678094.97</v>
+        <v>1555240.37</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
+        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
       </c>
       <c r="B381" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C381">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="D381" t="str">
         <v>Pesos</v>
       </c>
       <c r="E381">
-        <v>-197617.73</v>
+        <v>-60307.16</v>
       </c>
       <c r="F381">
-        <v>1694599.17</v>
+        <v>1617787.81</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
+        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
       </c>
       <c r="B382" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C382">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D382" t="str">
         <v>Pesos</v>
       </c>
       <c r="E382">
-        <v>-107783.1</v>
+        <v>-16504.2</v>
       </c>
       <c r="F382">
-        <v>1892216.9</v>
+        <v>1678094.97</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Liquidación de Rescate / 562376 / BCACC A</v>
+        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
       </c>
       <c r="B383" t="str">
-        <v>2024-04-03</v>
+        <v>2024-04-08</v>
       </c>
       <c r="C383">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D383" t="str">
         <v>Pesos</v>
       </c>
       <c r="E383">
-        <v>2000000</v>
+        <v>-197617.73</v>
       </c>
       <c r="F383">
-        <v>2000000</v>
+        <v>1694599.17</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
       </c>
       <c r="B384" t="str">
-        <v>2024-03-25</v>
+        <v>2024-04-08</v>
       </c>
       <c r="C384">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D384" t="str">
         <v>Pesos</v>
       </c>
       <c r="E384">
-        <v>-1000000</v>
+        <v>-107783.1</v>
       </c>
       <c r="F384">
-        <v>0</v>
+        <v>1892216.9</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Recibo de Cobro / 844439</v>
+        <v>Liquidación de Rescate / 562376 / BCACC A</v>
       </c>
       <c r="B385" t="str">
-        <v>2024-03-22</v>
+        <v>2024-04-03</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -8071,18 +8071,18 @@
         <v>Pesos</v>
       </c>
       <c r="E385">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F385">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B386" t="str">
-        <v>2024-03-11</v>
+        <v>2024-03-25</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -8091,7 +8091,7 @@
         <v>Pesos</v>
       </c>
       <c r="E386">
-        <v>-1002419.25</v>
+        <v>-1000000</v>
       </c>
       <c r="F386">
         <v>0</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
+        <v>Recibo de Cobro / 844439</v>
       </c>
       <c r="B387" t="str">
-        <v>2024-03-06</v>
+        <v>2024-03-22</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -8111,18 +8111,18 @@
         <v>Pesos</v>
       </c>
       <c r="E387">
-        <v>1002419.25</v>
+        <v>1000000</v>
       </c>
       <c r="F387">
-        <v>1002419.25</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
+        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B388" t="str">
-        <v>2024-03-06</v>
+        <v>2024-03-11</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -8131,7 +8131,7 @@
         <v>Pesos</v>
       </c>
       <c r="E388">
-        <v>-1000000</v>
+        <v>-1002419.25</v>
       </c>
       <c r="F388">
         <v>0</v>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Recibo de Cobro / 691819</v>
+        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
       </c>
       <c r="B389" t="str">
         <v>2024-03-06</v>
@@ -8151,15 +8151,55 @@
         <v>Pesos</v>
       </c>
       <c r="E389">
+        <v>1002419.25</v>
+      </c>
+      <c r="F389">
+        <v>1002419.25</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
+      </c>
+      <c r="B390" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390" t="str">
+        <v>Pesos</v>
+      </c>
+      <c r="E390">
+        <v>-1000000</v>
+      </c>
+      <c r="F390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Recibo de Cobro / 691819</v>
+      </c>
+      <c r="B391" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391" t="str">
+        <v>Pesos</v>
+      </c>
+      <c r="E391">
         <v>1000000</v>
       </c>
-      <c r="F389">
+      <c r="F391">
         <v>1000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F389"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F391"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/mi_cartera_balanz/data/cuentacorriente.xlsx
+++ b/mi_cartera_balanz/data/cuentacorriente.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F391"/>
+  <dimension ref="A1:F392"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -399,110 +399,110 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Liquidación de Rescate / 2021758 / BALANZ MONEY MARKET A</v>
+        <v>Boleto / 10845350 / COMPRA / 1 / PAMP / $</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-24</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="D2" t="str">
         <v>Pesos</v>
       </c>
       <c r="E2">
-        <v>2006044.36</v>
+        <v>-1003081.37</v>
       </c>
       <c r="F2">
-        <v>2113593.05</v>
+        <v>1110511.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Boleto / 10668132 / COMPRA / 1 / YPFD / $</v>
+        <v>Liquidación de Rescate / 2021758 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B3" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="C3">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="D3" t="str">
         <v>Pesos</v>
       </c>
       <c r="E3">
-        <v>-1993297.7</v>
+        <v>2006044.36</v>
       </c>
       <c r="F3">
-        <v>107548.69</v>
+        <v>2113593.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 10668132 / COMPRA / 1 / YPFD / $</v>
       </c>
       <c r="B4" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="C4">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="D4" t="str">
         <v>Pesos</v>
       </c>
       <c r="E4">
-        <v>2089759.48</v>
+        <v>-1993297.7</v>
       </c>
       <c r="F4">
-        <v>2100846.39</v>
+        <v>107548.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="D5" t="str">
         <v>Pesos</v>
       </c>
       <c r="E5">
-        <v>-1015702.61</v>
+        <v>2089759.48</v>
       </c>
       <c r="F5">
-        <v>11086.91</v>
+        <v>2100846.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Comprobante de Pago / 2204947</v>
+        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D6" t="str">
         <v>Pesos</v>
       </c>
       <c r="E6">
-        <v>-100000</v>
+        <v>-1015702.61</v>
       </c>
       <c r="F6">
-        <v>1026789.52</v>
+        <v>11086.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2204947</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -511,78 +511,78 @@
         <v>Pesos</v>
       </c>
       <c r="E7">
-        <v>-2000000</v>
+        <v>-100000</v>
       </c>
       <c r="F7">
-        <v>1126789.52</v>
+        <v>1026789.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B8" t="str">
         <v>2026-09-15</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8" t="str">
         <v>Pesos</v>
       </c>
       <c r="E8">
-        <v>898438.45</v>
+        <v>-2000000</v>
       </c>
       <c r="F8">
-        <v>3126789.52</v>
+        <v>1126789.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="C9">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D9" t="str">
         <v>Pesos</v>
       </c>
       <c r="E9">
-        <v>-1981985.21</v>
+        <v>898438.45</v>
       </c>
       <c r="F9">
-        <v>2228351.07</v>
+        <v>3126789.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Recibo de Cobro / 2547929</v>
+        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B10" t="str">
         <v>2026-09-14</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D10" t="str">
         <v>Pesos</v>
       </c>
       <c r="E10">
-        <v>120000</v>
+        <v>-1981985.21</v>
       </c>
       <c r="F10">
-        <v>4210336.28</v>
+        <v>2228351.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Comprobante de Pago / 2167536</v>
+        <v>Recibo de Cobro / 2547929</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-14</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -591,18 +591,18 @@
         <v>Pesos</v>
       </c>
       <c r="E11">
-        <v>-50000</v>
+        <v>120000</v>
       </c>
       <c r="F11">
-        <v>4090336.28</v>
+        <v>4210336.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2167536</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-10</v>
+        <v>2026-09-12</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -611,18 +611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E12">
-        <v>3404580.41</v>
+        <v>-50000</v>
       </c>
       <c r="F12">
-        <v>4140336.28</v>
+        <v>4090336.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Comprobante de Pago / 2105708</v>
+        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-10</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -631,18 +631,18 @@
         <v>Pesos</v>
       </c>
       <c r="E13">
-        <v>-30000</v>
+        <v>3404580.41</v>
       </c>
       <c r="F13">
-        <v>735755.87</v>
+        <v>4140336.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Comprobante de Pago / 2057077</v>
+        <v>Comprobante de Pago / 2105708</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-06</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -651,18 +651,18 @@
         <v>Pesos</v>
       </c>
       <c r="E14">
-        <v>-80000</v>
+        <v>-30000</v>
       </c>
       <c r="F14">
-        <v>765755.87</v>
+        <v>735755.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2057077</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -671,118 +671,118 @@
         <v>Pesos</v>
       </c>
       <c r="E15">
-        <v>-3371333.8</v>
+        <v>-80000</v>
       </c>
       <c r="F15">
-        <v>845755.87</v>
+        <v>765755.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
+        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B16" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C16">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D16" t="str">
         <v>Pesos</v>
       </c>
       <c r="E16">
-        <v>918459.06</v>
+        <v>-3371333.8</v>
       </c>
       <c r="F16">
-        <v>4217089.67</v>
+        <v>845755.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B17" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C17">
-        <v>503</v>
+        <v>278</v>
       </c>
       <c r="D17" t="str">
         <v>Pesos</v>
       </c>
       <c r="E17">
-        <v>3298630.61</v>
+        <v>918459.06</v>
       </c>
       <c r="F17">
-        <v>3298630.61</v>
+        <v>4217089.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Comprobante de Pago / 1944836</v>
+        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-21</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D18" t="str">
         <v>Pesos</v>
       </c>
       <c r="E18">
-        <v>-34658.23</v>
+        <v>3298630.61</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>3298630.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1944836</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-19</v>
       </c>
       <c r="C19">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="D19" t="str">
         <v>Pesos</v>
       </c>
       <c r="E19">
-        <v>-3589249.15</v>
+        <v>-34658.23</v>
       </c>
       <c r="F19">
-        <v>34658.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Comprobante de Pago / 1817656</v>
+        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-14</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D20" t="str">
         <v>Pesos</v>
       </c>
       <c r="E20">
-        <v>-40000</v>
+        <v>-3589249.15</v>
       </c>
       <c r="F20">
-        <v>3623907.38</v>
+        <v>34658.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Comprobante de Pago / 1732595</v>
+        <v>Comprobante de Pago / 1817656</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-07-25</v>
+        <v>2026-08-04</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -791,18 +791,18 @@
         <v>Pesos</v>
       </c>
       <c r="E21">
-        <v>-100000</v>
+        <v>-40000</v>
       </c>
       <c r="F21">
-        <v>3663907.38</v>
+        <v>3623907.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Comprobante de Pago / 1561578</v>
+        <v>Comprobante de Pago / 1732595</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-25</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -811,18 +811,18 @@
         <v>Pesos</v>
       </c>
       <c r="E22">
-        <v>-300000</v>
+        <v>-100000</v>
       </c>
       <c r="F22">
-        <v>3763907.38</v>
+        <v>3663907.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Comprobante de Pago / 1545516</v>
+        <v>Comprobante de Pago / 1561578</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-04</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -831,70 +831,70 @@
         <v>Pesos</v>
       </c>
       <c r="E23">
-        <v>-100000</v>
+        <v>-300000</v>
       </c>
       <c r="F23">
-        <v>4063907.38</v>
+        <v>3763907.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1545516</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-02</v>
       </c>
       <c r="C24">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D24" t="str">
         <v>Pesos</v>
       </c>
       <c r="E24">
-        <v>488924.13</v>
+        <v>-100000</v>
       </c>
       <c r="F24">
-        <v>4163907.38</v>
+        <v>4063907.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-29</v>
+        <v>2026-07-01</v>
       </c>
       <c r="C25">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D25" t="str">
         <v>Pesos</v>
       </c>
       <c r="E25">
-        <v>515910.2</v>
+        <v>488924.13</v>
       </c>
       <c r="F25">
-        <v>3674983.25</v>
+        <v>4163907.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B26" t="str">
         <v>2026-06-29</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D26" t="str">
         <v>Pesos</v>
       </c>
       <c r="E26">
-        <v>-6.27</v>
+        <v>515910.2</v>
       </c>
       <c r="F26">
-        <v>3159073.05</v>
+        <v>3674983.25</v>
       </c>
     </row>
     <row r="27">
@@ -908,118 +908,118 @@
         <v>0</v>
       </c>
       <c r="D27" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E27">
-        <v>0.99</v>
+        <v>-6.27</v>
       </c>
       <c r="F27">
-        <v>2.01</v>
+        <v>3159073.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-29</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D28" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E28">
-        <v>-944671.87</v>
+        <v>0.99</v>
       </c>
       <c r="F28">
-        <v>3159079.32</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B29" t="str">
         <v>2026-06-24</v>
       </c>
       <c r="C29">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D29" t="str">
         <v>Pesos</v>
       </c>
       <c r="E29">
-        <v>-1001112.31</v>
+        <v>-944671.87</v>
       </c>
       <c r="F29">
-        <v>4103751.19</v>
+        <v>3159079.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Comprobante de Pago / 1465742</v>
+        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-24</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D30" t="str">
         <v>Pesos</v>
       </c>
       <c r="E30">
-        <v>-50000</v>
+        <v>-1001112.31</v>
       </c>
       <c r="F30">
-        <v>5104863.5</v>
+        <v>4103751.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1465742</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-22</v>
       </c>
       <c r="C31">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="D31" t="str">
         <v>Pesos</v>
       </c>
       <c r="E31">
-        <v>2137654.07</v>
+        <v>-50000</v>
       </c>
       <c r="F31">
-        <v>5154863.5</v>
+        <v>5104863.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C32">
-        <v>879</v>
+        <v>540</v>
       </c>
       <c r="D32" t="str">
         <v>Pesos</v>
       </c>
       <c r="E32">
-        <v>820145.97</v>
+        <v>2137654.07</v>
       </c>
       <c r="F32">
-        <v>3017209.43</v>
+        <v>5154863.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B33" t="str">
         <v>2026-06-09</v>
@@ -1028,13 +1028,13 @@
         <v>879</v>
       </c>
       <c r="D33" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E33">
-        <v>-567.43</v>
+        <v>820145.97</v>
       </c>
       <c r="F33">
-        <v>11.75</v>
+        <v>3017209.43</v>
       </c>
     </row>
     <row r="34">
@@ -1045,124 +1045,124 @@
         <v>2026-06-09</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="D34" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E34">
-        <v>-20.4</v>
+        <v>-567.43</v>
       </c>
       <c r="F34">
-        <v>2197063.46</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B35" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C35">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D35" t="str">
         <v>Pesos</v>
       </c>
       <c r="E35">
-        <v>1867138.55</v>
+        <v>-20.4</v>
       </c>
       <c r="F35">
-        <v>2197083.86</v>
+        <v>2197063.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Recibo de Cobro / 1530471</v>
+        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D36" t="str">
         <v>Pesos</v>
       </c>
       <c r="E36">
-        <v>300000</v>
+        <v>1867138.55</v>
       </c>
       <c r="F36">
-        <v>329945.31</v>
+        <v>2197083.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
+        <v>Recibo de Cobro / 1530471</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C37">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D37" t="str">
         <v>Pesos</v>
       </c>
       <c r="E37">
-        <v>-1996802.3</v>
+        <v>300000</v>
       </c>
       <c r="F37">
-        <v>29945.31</v>
+        <v>329945.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Recibo de Cobro / 1484184</v>
+        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B38" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D38" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E38">
-        <v>579.18</v>
+        <v>-1996802.3</v>
       </c>
       <c r="F38">
-        <v>579.18</v>
+        <v>29945.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Comprobante de Pago / 1167141</v>
+        <v>Recibo de Cobro / 1484184</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-05-13</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E39">
-        <v>-20000</v>
+        <v>579.18</v>
       </c>
       <c r="F39">
-        <v>2026747.61</v>
+        <v>579.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Comprobante de Pago / 1116351</v>
+        <v>Comprobante de Pago / 1167141</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1171,90 +1171,90 @@
         <v>Pesos</v>
       </c>
       <c r="E40">
-        <v>-100000</v>
+        <v>-20000</v>
       </c>
       <c r="F40">
-        <v>2046747.61</v>
+        <v>2026747.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1116351</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C41">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="D41" t="str">
         <v>Pesos</v>
       </c>
       <c r="E41">
-        <v>-3174961.2</v>
+        <v>-100000</v>
       </c>
       <c r="F41">
-        <v>2146747.61</v>
+        <v>2046747.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Comprobante de Pago / 925746</v>
+        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="D42" t="str">
         <v>Pesos</v>
       </c>
       <c r="E42">
-        <v>-160000</v>
+        <v>-3174961.2</v>
       </c>
       <c r="F42">
-        <v>5321708.81</v>
+        <v>2146747.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 925746</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C43">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="D43" t="str">
         <v>Pesos</v>
       </c>
       <c r="E43">
-        <v>3896669.74</v>
+        <v>-160000</v>
       </c>
       <c r="F43">
-        <v>5481708.81</v>
+        <v>5321708.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="D44" t="str">
         <v>Pesos</v>
       </c>
       <c r="E44">
-        <v>-0.83</v>
+        <v>3896669.74</v>
       </c>
       <c r="F44">
-        <v>1585039.07</v>
+        <v>5481708.81</v>
       </c>
     </row>
     <row r="45">
@@ -1268,153 +1268,153 @@
         <v>0</v>
       </c>
       <c r="D45" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E45">
-        <v>0.14</v>
+        <v>-0.83</v>
       </c>
       <c r="F45">
-        <v>1.02</v>
+        <v>1585039.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Comprobante de Pago / 738461</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E46">
-        <v>-90000</v>
+        <v>0.14</v>
       </c>
       <c r="F46">
-        <v>1585039.9</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
+        <v>Comprobante de Pago / 738461</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C47">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D47" t="str">
         <v>Pesos</v>
       </c>
       <c r="E47">
-        <v>992035.79</v>
+        <v>-90000</v>
       </c>
       <c r="F47">
-        <v>1675039.9</v>
+        <v>1585039.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B48" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C48">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D48" t="str">
         <v>Pesos</v>
       </c>
       <c r="E48">
-        <v>1090257.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F48">
-        <v>683004.11</v>
+        <v>1675039.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B49" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D49" t="str">
         <v>Pesos</v>
       </c>
       <c r="E49">
-        <v>-407253.05</v>
+        <v>1090257.16</v>
       </c>
       <c r="F49">
-        <v>-407253.05</v>
+        <v>683004.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Comprobante de Pago / 642036</v>
+        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D50" t="str">
         <v>Pesos</v>
       </c>
       <c r="E50">
-        <v>-992034.79</v>
+        <v>-407253.05</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>-407253.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 642036</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C51">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D51" t="str">
         <v>Pesos</v>
       </c>
       <c r="E51">
-        <v>992035.79</v>
+        <v>-992034.79</v>
       </c>
       <c r="F51">
-        <v>992034.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-12-29</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D52" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E52">
-        <v>0.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F52">
-        <v>0.88</v>
+        <v>992034.79</v>
       </c>
     </row>
     <row r="53">
@@ -1428,21 +1428,21 @@
         <v>0</v>
       </c>
       <c r="D53" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E53">
-        <v>-1</v>
+        <v>0.16</v>
       </c>
       <c r="F53">
-        <v>-1</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Comprobante de Pago / 2852932</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-11-13</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1451,78 +1451,78 @@
         <v>Pesos</v>
       </c>
       <c r="E54">
-        <v>-11190.76</v>
+        <v>-1</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2852932</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-11-04</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D55" t="str">
         <v>Pesos</v>
       </c>
       <c r="E55">
-        <v>-90093.05</v>
+        <v>-11190.76</v>
       </c>
       <c r="F55">
-        <v>11190.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Recibo de Cobro / 2884603</v>
+        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-04</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D56" t="str">
         <v>Pesos</v>
       </c>
       <c r="E56">
-        <v>50000</v>
+        <v>-90093.05</v>
       </c>
       <c r="F56">
-        <v>101283.81</v>
+        <v>11190.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
+        <v>Recibo de Cobro / 2884603</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-10-22</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D57" t="str">
         <v>Pesos</v>
       </c>
       <c r="E57">
-        <v>48024.29</v>
+        <v>50000</v>
       </c>
       <c r="F57">
-        <v>51283.81</v>
+        <v>101283.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-10-20</v>
+        <v>2025-10-22</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1531,50 +1531,50 @@
         <v>Pesos</v>
       </c>
       <c r="E58">
-        <v>-46739.74</v>
+        <v>48024.29</v>
       </c>
       <c r="F58">
-        <v>3259.52</v>
+        <v>51283.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Recibo de Cobro / 2742989</v>
+        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B59" t="str">
         <v>2025-10-20</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D59" t="str">
         <v>Pesos</v>
       </c>
       <c r="E59">
-        <v>50000</v>
+        <v>-46739.74</v>
       </c>
       <c r="F59">
-        <v>49999.26</v>
+        <v>3259.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Recibo de Cobro / 2742989</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E60">
-        <v>0.12</v>
+        <v>50000</v>
       </c>
       <c r="F60">
-        <v>0.72</v>
+        <v>49999.26</v>
       </c>
     </row>
     <row r="61">
@@ -1588,21 +1588,21 @@
         <v>0</v>
       </c>
       <c r="D61" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E61">
-        <v>-0.74</v>
+        <v>0.12</v>
       </c>
       <c r="F61">
-        <v>-0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Comprobante de Pago / 2317908</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-09-24</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1611,195 +1611,195 @@
         <v>Pesos</v>
       </c>
       <c r="E62">
-        <v>-6736.66</v>
+        <v>-0.74</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2317908</v>
       </c>
       <c r="B63" t="str">
         <v>2025-09-24</v>
       </c>
       <c r="C63">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D63" t="str">
         <v>Pesos</v>
       </c>
       <c r="E63">
-        <v>-403777.1</v>
+        <v>-6736.66</v>
       </c>
       <c r="F63">
-        <v>6736.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B64" t="str">
-        <v>2025-09-22</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C64">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D64" t="str">
         <v>Pesos</v>
       </c>
       <c r="E64">
-        <v>388789.81</v>
+        <v>-403777.1</v>
       </c>
       <c r="F64">
-        <v>410513.76</v>
+        <v>6736.66</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B65" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C65">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D65" t="str">
         <v>Pesos</v>
       </c>
       <c r="E65">
-        <v>-1307333.32</v>
+        <v>388789.81</v>
       </c>
       <c r="F65">
-        <v>21723.95</v>
+        <v>410513.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B66" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C66">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="D66" t="str">
         <v>Pesos</v>
       </c>
       <c r="E66">
-        <v>999074.31</v>
+        <v>-1307333.32</v>
       </c>
       <c r="F66">
-        <v>1329057.27</v>
+        <v>21723.95</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B67" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C67">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D67" t="str">
         <v>Pesos</v>
       </c>
       <c r="E67">
-        <v>236100.29</v>
+        <v>999074.31</v>
       </c>
       <c r="F67">
-        <v>329982.96</v>
+        <v>1329057.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B68" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C68">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D68" t="str">
         <v>Pesos</v>
       </c>
       <c r="E68">
-        <v>93882.67</v>
+        <v>236100.29</v>
       </c>
       <c r="F68">
-        <v>93882.67</v>
+        <v>329982.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Comprobante de Pago / 2284129</v>
+        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-09-20</v>
+        <v>2025-09-22</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D69" t="str">
         <v>Pesos</v>
       </c>
       <c r="E69">
-        <v>-6165.47</v>
+        <v>93882.67</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>93882.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2284129</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-09-18</v>
+        <v>2025-09-20</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70" t="str">
         <v>Pesos</v>
       </c>
       <c r="E70">
-        <v>-76616.13</v>
+        <v>-6165.47</v>
       </c>
       <c r="F70">
-        <v>6165.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B71" t="str">
         <v>2025-09-18</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71" t="str">
         <v>Pesos</v>
       </c>
       <c r="E71">
-        <v>-20136.94</v>
+        <v>-76616.13</v>
       </c>
       <c r="F71">
-        <v>82781.6</v>
+        <v>6165.47</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B72" t="str">
         <v>2025-09-18</v>
@@ -1811,298 +1811,298 @@
         <v>Pesos</v>
       </c>
       <c r="E72">
-        <v>89518.34</v>
+        <v>-20136.94</v>
       </c>
       <c r="F72">
-        <v>102918.54</v>
+        <v>82781.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B73" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-18</v>
       </c>
       <c r="C73">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D73" t="str">
         <v>Pesos</v>
       </c>
       <c r="E73">
-        <v>138894.77</v>
+        <v>89518.34</v>
       </c>
       <c r="F73">
-        <v>13400.2</v>
+        <v>102918.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B74" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D74" t="str">
         <v>Pesos</v>
       </c>
       <c r="E74">
-        <v>-85739.5</v>
+        <v>138894.77</v>
       </c>
       <c r="F74">
-        <v>-125494.57</v>
+        <v>13400.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Comprobante de Pago / 2176779</v>
+        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B75" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D75" t="str">
         <v>Pesos</v>
       </c>
       <c r="E75">
-        <v>-45869.67</v>
+        <v>-85739.5</v>
       </c>
       <c r="F75">
-        <v>-39755.07</v>
+        <v>-125494.57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2176779</v>
       </c>
       <c r="B76" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="C76">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D76" t="str">
         <v>Pesos</v>
       </c>
       <c r="E76">
-        <v>-952298.2</v>
+        <v>-45869.67</v>
       </c>
       <c r="F76">
-        <v>6114.6</v>
+        <v>-39755.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B77" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C77">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D77" t="str">
         <v>Pesos</v>
       </c>
       <c r="E77">
-        <v>-226481.32</v>
+        <v>-952298.2</v>
       </c>
       <c r="F77">
-        <v>958412.8</v>
+        <v>6114.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
+        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B78" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C78">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D78" t="str">
         <v>Pesos</v>
       </c>
       <c r="E78">
-        <v>-491658.83</v>
+        <v>-226481.32</v>
       </c>
       <c r="F78">
-        <v>1184894.12</v>
+        <v>958412.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Comprobante de Pago / 2093390</v>
+        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
       </c>
       <c r="B79" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D79" t="str">
         <v>Pesos</v>
       </c>
       <c r="E79">
-        <v>-14000</v>
+        <v>-491658.83</v>
       </c>
       <c r="F79">
-        <v>1676552.95</v>
+        <v>1184894.12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2093390</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C80">
-        <v>3447</v>
+        <v>0</v>
       </c>
       <c r="D80" t="str">
         <v>Pesos</v>
       </c>
       <c r="E80">
-        <v>2699870.67</v>
+        <v>-14000</v>
       </c>
       <c r="F80">
-        <v>1690552.95</v>
+        <v>1676552.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B81" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C81">
-        <v>413</v>
+        <v>3447</v>
       </c>
       <c r="D81" t="str">
         <v>Pesos</v>
       </c>
       <c r="E81">
-        <v>-4194203.97</v>
+        <v>2699870.67</v>
       </c>
       <c r="F81">
-        <v>-1009317.72</v>
+        <v>1690552.95</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B82" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C82">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="D82" t="str">
         <v>Pesos</v>
       </c>
       <c r="E82">
-        <v>509153.55</v>
+        <v>-4194203.97</v>
       </c>
       <c r="F82">
-        <v>3184886.25</v>
+        <v>-1009317.72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B83" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C83">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="D83" t="str">
         <v>Pesos</v>
       </c>
       <c r="E83">
-        <v>777951.6</v>
+        <v>509153.55</v>
       </c>
       <c r="F83">
-        <v>2675732.7</v>
+        <v>3184886.25</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B84" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C84">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="D84" t="str">
         <v>Pesos</v>
       </c>
       <c r="E84">
-        <v>1314506.19</v>
+        <v>777951.6</v>
       </c>
       <c r="F84">
-        <v>1897781.1</v>
+        <v>2675732.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B85" t="str">
-        <v>2025-08-18</v>
+        <v>2025-08-25</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D85" t="str">
         <v>Pesos</v>
       </c>
       <c r="E85">
-        <v>-19758.9</v>
+        <v>1314506.19</v>
       </c>
       <c r="F85">
-        <v>583274.91</v>
+        <v>1897781.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Comprobante de Pago / 1961788</v>
+        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B86" t="str">
         <v>2025-08-18</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86" t="str">
         <v>Pesos</v>
       </c>
       <c r="E86">
-        <v>-20000</v>
+        <v>-19758.9</v>
       </c>
       <c r="F86">
-        <v>603033.81</v>
+        <v>583274.91</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Comprobante de Pago / 1961788</v>
       </c>
       <c r="B87" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-18</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2111,15 +2111,15 @@
         <v>Pesos</v>
       </c>
       <c r="E87">
-        <v>-338.57</v>
+        <v>-20000</v>
       </c>
       <c r="F87">
-        <v>623033.81</v>
+        <v>603033.81</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B88" t="str">
         <v>2025-08-12</v>
@@ -2131,610 +2131,610 @@
         <v>Pesos</v>
       </c>
       <c r="E88">
-        <v>4824.94</v>
+        <v>-338.57</v>
       </c>
       <c r="F88">
-        <v>623372.38</v>
+        <v>623033.81</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B89" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D89" t="str">
         <v>Pesos</v>
       </c>
       <c r="E89">
-        <v>-100004.21</v>
+        <v>4824.94</v>
       </c>
       <c r="F89">
-        <v>618547.44</v>
+        <v>623372.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B90" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C90">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D90" t="str">
         <v>Pesos</v>
       </c>
       <c r="E90">
-        <v>710418.57</v>
+        <v>-100004.21</v>
       </c>
       <c r="F90">
-        <v>718551.65</v>
+        <v>618547.44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B91" t="str">
-        <v>2025-08-05</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C91">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D91" t="str">
         <v>Pesos</v>
       </c>
       <c r="E91">
-        <v>-190965.71</v>
+        <v>710418.57</v>
       </c>
       <c r="F91">
-        <v>8133.08</v>
+        <v>718551.65</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B92" t="str">
         <v>2025-08-05</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D92" t="str">
         <v>Pesos</v>
       </c>
       <c r="E92">
-        <v>182607.5</v>
+        <v>-190965.71</v>
       </c>
       <c r="F92">
-        <v>199098.79</v>
+        <v>8133.08</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
+        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B93" t="str">
-        <v>2025-08-04</v>
+        <v>2025-08-05</v>
       </c>
       <c r="C93">
-        <v>2626</v>
+        <v>4</v>
       </c>
       <c r="D93" t="str">
         <v>Pesos</v>
       </c>
       <c r="E93">
-        <v>41762.85</v>
+        <v>182607.5</v>
       </c>
       <c r="F93">
-        <v>16491.29</v>
+        <v>199098.79</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
       </c>
       <c r="B94" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C94">
-        <v>1848</v>
+        <v>2626</v>
       </c>
       <c r="D94" t="str">
         <v>Pesos</v>
       </c>
       <c r="E94">
-        <v>1490983.97</v>
+        <v>41762.85</v>
       </c>
       <c r="F94">
-        <v>-25271.56</v>
+        <v>16491.29</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B95" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C95">
-        <v>225</v>
+        <v>1848</v>
       </c>
       <c r="D95" t="str">
         <v>Pesos</v>
       </c>
       <c r="E95">
-        <v>-1521989.55</v>
+        <v>1490983.97</v>
       </c>
       <c r="F95">
-        <v>-1516255.53</v>
+        <v>-25271.56</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B96" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-04</v>
       </c>
       <c r="C96">
-        <v>620</v>
+        <v>225</v>
       </c>
       <c r="D96" t="str">
         <v>Pesos</v>
       </c>
       <c r="E96">
-        <v>488389.62</v>
+        <v>-1521989.55</v>
       </c>
       <c r="F96">
-        <v>5734.02</v>
+        <v>-1516255.53</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B97" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C97">
-        <v>58</v>
+        <v>620</v>
       </c>
       <c r="D97" t="str">
         <v>Pesos</v>
       </c>
       <c r="E97">
-        <v>194738.35</v>
+        <v>488389.62</v>
       </c>
       <c r="F97">
-        <v>-482655.6</v>
+        <v>5734.02</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B98" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C98">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="D98" t="str">
         <v>Pesos</v>
       </c>
       <c r="E98">
-        <v>-393010.51</v>
+        <v>194738.35</v>
       </c>
       <c r="F98">
-        <v>-677393.95</v>
+        <v>-482655.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B99" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C99">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D99" t="str">
         <v>Pesos</v>
       </c>
       <c r="E99">
-        <v>-285344.68</v>
+        <v>-393010.51</v>
       </c>
       <c r="F99">
-        <v>-284383.44</v>
+        <v>-677393.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B100" t="str">
-        <v>2025-07-29</v>
+        <v>2025-07-30</v>
       </c>
       <c r="C100">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D100" t="str">
         <v>Pesos</v>
       </c>
       <c r="E100">
-        <v>-87826.28</v>
+        <v>-285344.68</v>
       </c>
       <c r="F100">
-        <v>961.24</v>
+        <v>-284383.44</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-07-28</v>
+        <v>2025-07-29</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D101" t="str">
         <v>Pesos</v>
       </c>
       <c r="E101">
-        <v>-133937.09</v>
+        <v>-87826.28</v>
       </c>
       <c r="F101">
-        <v>88787.52</v>
+        <v>961.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B102" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C102">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D102" t="str">
         <v>Pesos</v>
       </c>
       <c r="E102">
-        <v>94844.81</v>
+        <v>-133937.09</v>
       </c>
       <c r="F102">
-        <v>222724.61</v>
+        <v>88787.52</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B103" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D103" t="str">
         <v>Pesos</v>
       </c>
       <c r="E103">
-        <v>127879.8</v>
+        <v>94844.81</v>
       </c>
       <c r="F103">
-        <v>127879.8</v>
+        <v>222724.61</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B104" t="str">
-        <v>2025-07-24</v>
+        <v>2025-07-28</v>
       </c>
       <c r="C104">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D104" t="str">
         <v>Pesos</v>
       </c>
       <c r="E104">
-        <v>88972.8</v>
+        <v>127879.8</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>127879.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Comprobante de Pago / 1761847</v>
+        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B105" t="str">
         <v>2025-07-24</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D105" t="str">
         <v>Pesos</v>
       </c>
       <c r="E105">
-        <v>-89024.62</v>
+        <v>88972.8</v>
       </c>
       <c r="F105">
-        <v>-88972.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
+        <v>Comprobante de Pago / 1761847</v>
       </c>
       <c r="B106" t="str">
-        <v>2025-07-22</v>
+        <v>2025-07-24</v>
       </c>
       <c r="C106">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="D106" t="str">
         <v>Pesos</v>
       </c>
       <c r="E106">
-        <v>-3646.72</v>
+        <v>-89024.62</v>
       </c>
       <c r="F106">
-        <v>51.82</v>
+        <v>-88972.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B107" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C107">
-        <v>1984</v>
+        <v>235</v>
       </c>
       <c r="D107" t="str">
         <v>Pesos</v>
       </c>
       <c r="E107">
-        <v>-1482793.93</v>
+        <v>-3646.72</v>
       </c>
       <c r="F107">
-        <v>3698.54</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B108" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C108">
-        <v>121</v>
+        <v>1984</v>
       </c>
       <c r="D108" t="str">
         <v>Pesos</v>
       </c>
       <c r="E108">
-        <v>-345815.98</v>
+        <v>-1482793.93</v>
       </c>
       <c r="F108">
-        <v>1486492.47</v>
+        <v>3698.54</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B109" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C109">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D109" t="str">
         <v>Pesos</v>
       </c>
       <c r="E109">
-        <v>-354299.21</v>
+        <v>-345815.98</v>
       </c>
       <c r="F109">
-        <v>1832308.45</v>
+        <v>1486492.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B110" t="str">
-        <v>2025-07-16</v>
+        <v>2025-07-22</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D110" t="str">
         <v>Pesos</v>
       </c>
       <c r="E110">
-        <v>2185800.13</v>
+        <v>-354299.21</v>
       </c>
       <c r="F110">
-        <v>2186607.66</v>
+        <v>1832308.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B111" t="str">
         <v>2025-07-16</v>
       </c>
       <c r="C111">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D111" t="str">
         <v>Pesos</v>
       </c>
       <c r="E111">
-        <v>-9888.53</v>
+        <v>2185800.13</v>
       </c>
       <c r="F111">
-        <v>807.53</v>
+        <v>2186607.66</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B112" t="str">
-        <v>2025-07-14</v>
+        <v>2025-07-16</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D112" t="str">
         <v>Pesos</v>
       </c>
       <c r="E112">
-        <v>-1151507.11</v>
+        <v>-9888.53</v>
       </c>
       <c r="F112">
-        <v>10696.06</v>
+        <v>807.53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B113" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C113">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="D113" t="str">
         <v>Pesos</v>
       </c>
       <c r="E113">
-        <v>-950578.94</v>
+        <v>-1151507.11</v>
       </c>
       <c r="F113">
-        <v>1162203.17</v>
+        <v>10696.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B114" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>1230</v>
       </c>
       <c r="D114" t="str">
         <v>Pesos</v>
       </c>
       <c r="E114">
-        <v>319945.64</v>
+        <v>-950578.94</v>
       </c>
       <c r="F114">
-        <v>2112782.11</v>
+        <v>1162203.17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B115" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C115">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D115" t="str">
         <v>Pesos</v>
       </c>
       <c r="E115">
-        <v>641329.36</v>
+        <v>319945.64</v>
       </c>
       <c r="F115">
-        <v>1792836.47</v>
+        <v>2112782.11</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Comprobante de Pago / 1676382</v>
+        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B116" t="str">
-        <v>2025-07-12</v>
+        <v>2025-07-14</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D116" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E116">
-        <v>-0.48</v>
+        <v>641329.36</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1792836.47</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 1676382</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-07-11</v>
+        <v>2025-07-12</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E117">
-        <v>1152116.72</v>
+        <v>-0.48</v>
       </c>
       <c r="F117">
-        <v>1151507.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
+        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B118" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C118">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D118" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E118">
-        <v>-218.93</v>
+        <v>1152116.72</v>
       </c>
       <c r="F118">
-        <v>0.48</v>
+        <v>1151507.11</v>
       </c>
     </row>
     <row r="119">
@@ -2745,61 +2745,61 @@
         <v>2025-07-11</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D119" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E119">
-        <v>-609.62</v>
+        <v>-218.93</v>
       </c>
       <c r="F119">
-        <v>-609.61</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
       </c>
       <c r="B120" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C120">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D120" t="str">
         <v>Pesos</v>
       </c>
       <c r="E120">
-        <v>-49685.47</v>
+        <v>-609.62</v>
       </c>
       <c r="F120">
-        <v>0.01</v>
+        <v>-609.61</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Comprobante de Pago / 1668056</v>
+        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B121" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D121" t="str">
         <v>Pesos</v>
       </c>
       <c r="E121">
-        <v>-3923.46</v>
+        <v>-49685.47</v>
       </c>
       <c r="F121">
-        <v>49685.48</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Comprobante de Pago / 1668048</v>
+        <v>Comprobante de Pago / 1668056</v>
       </c>
       <c r="B122" t="str">
         <v>2025-07-11</v>
@@ -2808,18 +2808,18 @@
         <v>0</v>
       </c>
       <c r="D122" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E122">
-        <v>-4.52</v>
+        <v>-3923.46</v>
       </c>
       <c r="F122">
-        <v>219.41</v>
+        <v>49685.48</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Recibo de Cobro / 1772632</v>
+        <v>Comprobante de Pago / 1668048</v>
       </c>
       <c r="B123" t="str">
         <v>2025-07-11</v>
@@ -2828,33 +2828,33 @@
         <v>0</v>
       </c>
       <c r="D123" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E123">
-        <v>50000</v>
+        <v>-4.52</v>
       </c>
       <c r="F123">
-        <v>53608.94</v>
+        <v>219.41</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Recibo de Cobro / 1772632</v>
       </c>
       <c r="B124" t="str">
-        <v>2025-07-10</v>
+        <v>2025-07-11</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E124">
-        <v>223.91</v>
+        <v>50000</v>
       </c>
       <c r="F124">
-        <v>223.93</v>
+        <v>53608.94</v>
       </c>
     </row>
     <row r="125">
@@ -2868,21 +2868,21 @@
         <v>0</v>
       </c>
       <c r="D125" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E125">
-        <v>-5.65</v>
+        <v>223.91</v>
       </c>
       <c r="F125">
-        <v>3608.94</v>
+        <v>223.93</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B126" t="str">
-        <v>2025-06-11</v>
+        <v>2025-07-10</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -2891,15 +2891,15 @@
         <v>Pesos</v>
       </c>
       <c r="E126">
-        <v>-552.42</v>
+        <v>-5.65</v>
       </c>
       <c r="F126">
-        <v>3614.59</v>
+        <v>3608.94</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dividendo en efectivo / TGSU2</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
       </c>
       <c r="B127" t="str">
         <v>2025-06-11</v>
@@ -2911,55 +2911,55 @@
         <v>Pesos</v>
       </c>
       <c r="E127">
-        <v>3975.67</v>
+        <v>-552.42</v>
       </c>
       <c r="F127">
-        <v>4167.01</v>
+        <v>3614.59</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
+        <v>Dividendo en efectivo / TGSU2</v>
       </c>
       <c r="B128" t="str">
-        <v>2025-06-09</v>
+        <v>2025-06-11</v>
       </c>
       <c r="C128">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="D128" t="str">
         <v>Pesos</v>
       </c>
       <c r="E128">
-        <v>-16502.47</v>
+        <v>3975.67</v>
       </c>
       <c r="F128">
-        <v>191.34</v>
+        <v>4167.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B129" t="str">
-        <v>2025-05-15</v>
+        <v>2025-06-09</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="D129" t="str">
         <v>Pesos</v>
       </c>
       <c r="E129">
-        <v>-958.17</v>
+        <v>-16502.47</v>
       </c>
       <c r="F129">
-        <v>16693.81</v>
+        <v>191.34</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B130" t="str">
         <v>2025-05-15</v>
@@ -2971,18 +2971,18 @@
         <v>Pesos</v>
       </c>
       <c r="E130">
-        <v>13655.11</v>
+        <v>-958.17</v>
       </c>
       <c r="F130">
-        <v>17651.98</v>
+        <v>16693.81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Renta y Amortización / TX28</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B131" t="str">
-        <v>2025-05-09</v>
+        <v>2025-05-15</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -2991,78 +2991,78 @@
         <v>Pesos</v>
       </c>
       <c r="E131">
-        <v>3718.21</v>
+        <v>13655.11</v>
       </c>
       <c r="F131">
-        <v>3996.87</v>
+        <v>17651.98</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
+        <v>Renta y Amortización / TX28</v>
       </c>
       <c r="B132" t="str">
-        <v>2025-04-25</v>
+        <v>2025-05-09</v>
       </c>
       <c r="C132">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="D132" t="str">
         <v>Pesos</v>
       </c>
       <c r="E132">
-        <v>-24260.75</v>
+        <v>3718.21</v>
       </c>
       <c r="F132">
-        <v>278.66</v>
+        <v>3996.87</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B133" t="str">
         <v>2025-04-25</v>
       </c>
       <c r="C133">
-        <v>25</v>
+        <v>1359</v>
       </c>
       <c r="D133" t="str">
         <v>Pesos</v>
       </c>
       <c r="E133">
-        <v>-975460.59</v>
+        <v>-24260.75</v>
       </c>
       <c r="F133">
-        <v>24539.41</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B134" t="str">
-        <v>2025-04-24</v>
+        <v>2025-04-25</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D134" t="str">
         <v>Pesos</v>
       </c>
       <c r="E134">
-        <v>1000000</v>
+        <v>-975460.59</v>
       </c>
       <c r="F134">
-        <v>1000000</v>
+        <v>24539.41</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B135" t="str">
-        <v>2025-04-21</v>
+        <v>2025-04-24</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3071,18 +3071,18 @@
         <v>Pesos</v>
       </c>
       <c r="E135">
-        <v>-999993.87</v>
+        <v>1000000</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B136" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-21</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3091,30 +3091,30 @@
         <v>Pesos</v>
       </c>
       <c r="E136">
-        <v>1000000</v>
+        <v>-999993.87</v>
       </c>
       <c r="F136">
-        <v>999993.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
+        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B137" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-16</v>
       </c>
       <c r="C137">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="D137" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E137">
-        <v>-206.02</v>
+        <v>1000000</v>
       </c>
       <c r="F137">
-        <v>0.02</v>
+        <v>999993.87</v>
       </c>
     </row>
     <row r="138">
@@ -3125,21 +3125,21 @@
         <v>2025-04-15</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="D138" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E138">
-        <v>-6.13</v>
+        <v>-206.02</v>
       </c>
       <c r="F138">
-        <v>-6.13</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Comprobante de Pago / 1061406</v>
+        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B139" t="str">
         <v>2025-04-15</v>
@@ -3148,18 +3148,18 @@
         <v>0</v>
       </c>
       <c r="D139" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E139">
-        <v>-2.85</v>
+        <v>-6.13</v>
       </c>
       <c r="F139">
-        <v>206.04</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Comprobante de Pago / 1061395</v>
+        <v>Comprobante de Pago / 1061406</v>
       </c>
       <c r="B140" t="str">
         <v>2025-04-15</v>
@@ -3168,33 +3168,33 @@
         <v>0</v>
       </c>
       <c r="D140" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E140">
-        <v>-2526.78</v>
+        <v>-2.85</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>206.04</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 1061395</v>
       </c>
       <c r="B141" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-15</v>
       </c>
       <c r="C141">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D141" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E141">
-        <v>208.88</v>
+        <v>-2526.78</v>
       </c>
       <c r="F141">
-        <v>208.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -3205,324 +3205,324 @@
         <v>2025-04-14</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D142" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E142">
-        <v>-5.66</v>
+        <v>208.88</v>
       </c>
       <c r="F142">
-        <v>2526.78</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B143" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C143">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D143" t="str">
         <v>Pesos</v>
       </c>
       <c r="E143">
-        <v>-257928.71</v>
+        <v>-5.66</v>
       </c>
       <c r="F143">
-        <v>2532.44</v>
+        <v>2526.78</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B144" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C144">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="D144" t="str">
         <v>Pesos</v>
       </c>
       <c r="E144">
-        <v>248438.89</v>
+        <v>-257928.71</v>
       </c>
       <c r="F144">
-        <v>260461.15</v>
+        <v>2532.44</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B145" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-14</v>
       </c>
       <c r="C145">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D145" t="str">
         <v>Pesos</v>
       </c>
       <c r="E145">
-        <v>-98040.09</v>
+        <v>248438.89</v>
       </c>
       <c r="F145">
-        <v>12022.26</v>
+        <v>260461.15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B146" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C146">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D146" t="str">
         <v>Pesos</v>
       </c>
       <c r="E146">
-        <v>-486646.45</v>
+        <v>-98040.09</v>
       </c>
       <c r="F146">
-        <v>110062.35</v>
+        <v>12022.26</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B147" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C147">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D147" t="str">
         <v>Pesos</v>
       </c>
       <c r="E147">
-        <v>-93664.38</v>
+        <v>-486646.45</v>
       </c>
       <c r="F147">
-        <v>596708.8</v>
+        <v>110062.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B148" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C148">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D148" t="str">
         <v>Pesos</v>
       </c>
       <c r="E148">
-        <v>-309626.82</v>
+        <v>-93664.38</v>
       </c>
       <c r="F148">
-        <v>690373.18</v>
+        <v>596708.8</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B149" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-08</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D149" t="str">
         <v>Pesos</v>
       </c>
       <c r="E149">
-        <v>1000000</v>
+        <v>-309626.82</v>
       </c>
       <c r="F149">
-        <v>1000000</v>
+        <v>690373.18</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B150" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-07</v>
       </c>
       <c r="C150">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D150" t="str">
         <v>Pesos</v>
       </c>
       <c r="E150">
-        <v>292856.94</v>
+        <v>1000000</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Comprobante de Pago / 945180</v>
+        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B151" t="str">
         <v>2025-04-04</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="D151" t="str">
         <v>Pesos</v>
       </c>
       <c r="E151">
-        <v>-292856.9</v>
+        <v>292856.94</v>
       </c>
       <c r="F151">
-        <v>-292856.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 945180</v>
       </c>
       <c r="B152" t="str">
-        <v>2025-03-27</v>
+        <v>2025-04-04</v>
       </c>
       <c r="C152">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D152" t="str">
         <v>Pesos</v>
       </c>
       <c r="E152">
-        <v>58913.7</v>
+        <v>-292856.9</v>
       </c>
       <c r="F152">
-        <v>-0.04</v>
+        <v>-292856.94</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Comprobante de Pago / 868926</v>
+        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B153" t="str">
         <v>2025-03-27</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D153" t="str">
         <v>Pesos</v>
       </c>
       <c r="E153">
-        <v>-58913.74</v>
+        <v>58913.7</v>
       </c>
       <c r="F153">
-        <v>-58913.74</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 868926</v>
       </c>
       <c r="B154" t="str">
-        <v>2025-03-20</v>
+        <v>2025-03-27</v>
       </c>
       <c r="C154">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D154" t="str">
         <v>Pesos</v>
       </c>
       <c r="E154">
-        <v>39165.79</v>
+        <v>-58913.74</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>-58913.74</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Comprobante de Pago / 814860</v>
+        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B155" t="str">
         <v>2025-03-20</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D155" t="str">
         <v>Pesos</v>
       </c>
       <c r="E155">
-        <v>-39165.79</v>
+        <v>39165.79</v>
       </c>
       <c r="F155">
-        <v>-39165.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 814860</v>
       </c>
       <c r="B156" t="str">
-        <v>2025-03-05</v>
+        <v>2025-03-20</v>
       </c>
       <c r="C156">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D156" t="str">
         <v>Pesos</v>
       </c>
       <c r="E156">
-        <v>48845.52</v>
+        <v>-39165.79</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>-39165.79</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Comprobante de Pago / 636155</v>
+        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B157" t="str">
         <v>2025-03-05</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D157" t="str">
         <v>Pesos</v>
       </c>
       <c r="E157">
-        <v>-48845.53</v>
+        <v>48845.52</v>
       </c>
       <c r="F157">
-        <v>-48845.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 636155</v>
       </c>
       <c r="B158" t="str">
-        <v>2025-02-13</v>
+        <v>2025-03-05</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3531,58 +3531,58 @@
         <v>Pesos</v>
       </c>
       <c r="E158">
-        <v>-2208405.65</v>
+        <v>-48845.53</v>
       </c>
       <c r="F158">
-        <v>0.01</v>
+        <v>-48845.52</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-02-12</v>
+        <v>2025-02-13</v>
       </c>
       <c r="C159">
-        <v>1921</v>
+        <v>0</v>
       </c>
       <c r="D159" t="str">
         <v>Pesos</v>
       </c>
       <c r="E159">
-        <v>-1490594.34</v>
+        <v>-2208405.65</v>
       </c>
       <c r="F159">
-        <v>2208405.66</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Recibo de Cobro / 513307</v>
+        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B160" t="str">
         <v>2025-02-12</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1921</v>
       </c>
       <c r="D160" t="str">
         <v>Pesos</v>
       </c>
       <c r="E160">
-        <v>149000</v>
+        <v>-1490594.34</v>
       </c>
       <c r="F160">
-        <v>3699000</v>
+        <v>2208405.66</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Comprobante de Pago / 451447</v>
+        <v>Recibo de Cobro / 513307</v>
       </c>
       <c r="B161" t="str">
-        <v>2025-02-11</v>
+        <v>2025-02-12</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3591,18 +3591,18 @@
         <v>Pesos</v>
       </c>
       <c r="E161">
-        <v>-300000</v>
+        <v>149000</v>
       </c>
       <c r="F161">
-        <v>3550000</v>
+        <v>3699000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Comprobante de Pago / 422123</v>
+        <v>Comprobante de Pago / 451447</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-02-10</v>
+        <v>2025-02-11</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3611,18 +3611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E162">
-        <v>-150000</v>
+        <v>-300000</v>
       </c>
       <c r="F162">
-        <v>3850000</v>
+        <v>3550000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Recibo de Cobro / 392207</v>
+        <v>Comprobante de Pago / 422123</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-02-03</v>
+        <v>2025-02-10</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3631,15 +3631,15 @@
         <v>Pesos</v>
       </c>
       <c r="E163">
-        <v>2000000</v>
+        <v>-150000</v>
       </c>
       <c r="F163">
-        <v>4000000</v>
+        <v>3850000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Recibo de Cobro / 392198</v>
+        <v>Recibo de Cobro / 392207</v>
       </c>
       <c r="B164" t="str">
         <v>2025-02-03</v>
@@ -3654,15 +3654,15 @@
         <v>2000000</v>
       </c>
       <c r="F164">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 392198</v>
       </c>
       <c r="B165" t="str">
-        <v>2025-01-24</v>
+        <v>2025-02-03</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3671,18 +3671,18 @@
         <v>Pesos</v>
       </c>
       <c r="E165">
-        <v>-284993.55</v>
+        <v>2000000</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Recibo de Cobro / 259074</v>
+        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B166" t="str">
-        <v>2025-01-21</v>
+        <v>2025-01-24</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3691,30 +3691,30 @@
         <v>Pesos</v>
       </c>
       <c r="E166">
-        <v>285000</v>
+        <v>-284993.55</v>
       </c>
       <c r="F166">
-        <v>284993.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
+        <v>Recibo de Cobro / 259074</v>
       </c>
       <c r="B167" t="str">
         <v>2025-01-21</v>
       </c>
       <c r="C167">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="D167" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E167">
-        <v>244.89</v>
+        <v>285000</v>
       </c>
       <c r="F167">
-        <v>0.01</v>
+        <v>284993.55</v>
       </c>
     </row>
     <row r="168">
@@ -3725,21 +3725,21 @@
         <v>2025-01-21</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="D168" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E168">
-        <v>-6.45</v>
+        <v>244.89</v>
       </c>
       <c r="F168">
-        <v>-6.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Comprobante de Pago / 229359</v>
+        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B169" t="str">
         <v>2025-01-21</v>
@@ -3748,61 +3748,61 @@
         <v>0</v>
       </c>
       <c r="D169" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E169">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
       <c r="F169">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
+        <v>Comprobante de Pago / 229359</v>
       </c>
       <c r="B170" t="str">
-        <v>2025-01-17</v>
+        <v>2025-01-21</v>
       </c>
       <c r="C170">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D170" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E170">
-        <v>164237.44</v>
+        <v>-244.88</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>-244.88</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Comprobante de Pago / 195368</v>
+        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
       </c>
       <c r="B171" t="str">
         <v>2025-01-17</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D171" t="str">
         <v>Pesos</v>
       </c>
       <c r="E171">
-        <v>-164237.44</v>
+        <v>164237.44</v>
       </c>
       <c r="F171">
-        <v>-164237.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Comprobante de Pago / 128971</v>
+        <v>Comprobante de Pago / 195368</v>
       </c>
       <c r="B172" t="str">
-        <v>2025-01-11</v>
+        <v>2025-01-17</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3811,15 +3811,15 @@
         <v>Pesos</v>
       </c>
       <c r="E172">
-        <v>-1858.46</v>
+        <v>-164237.44</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>-164237.44</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Comprobante de Pago / 128969</v>
+        <v>Comprobante de Pago / 128971</v>
       </c>
       <c r="B173" t="str">
         <v>2025-01-11</v>
@@ -3828,10 +3828,10 @@
         <v>0</v>
       </c>
       <c r="D173" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E173">
-        <v>-1.67</v>
+        <v>-1858.46</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -3839,27 +3839,27 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 128969</v>
       </c>
       <c r="B174" t="str">
-        <v>2025-01-09</v>
+        <v>2025-01-11</v>
       </c>
       <c r="C174">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D174" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E174">
-        <v>115257.86</v>
+        <v>-1.67</v>
       </c>
       <c r="F174">
-        <v>1858.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B175" t="str">
         <v>2025-01-09</v>
@@ -3868,13 +3868,13 @@
         <v>145</v>
       </c>
       <c r="D175" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E175">
-        <v>-100.23</v>
+        <v>115257.86</v>
       </c>
       <c r="F175">
-        <v>1.67</v>
+        <v>1858.46</v>
       </c>
     </row>
     <row r="176">
@@ -3885,56 +3885,56 @@
         <v>2025-01-09</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D176" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E176">
-        <v>-2.58</v>
+        <v>-100.23</v>
       </c>
       <c r="F176">
-        <v>-113399.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B177" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C177">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="D177" t="str">
         <v>Pesos</v>
       </c>
       <c r="E177">
-        <v>-113394.51</v>
+        <v>-2.58</v>
       </c>
       <c r="F177">
-        <v>-113396.82</v>
+        <v>-113399.4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B178" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D178" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E178">
-        <v>101.9</v>
+        <v>-113394.51</v>
       </c>
       <c r="F178">
-        <v>101.9</v>
+        <v>-113396.82</v>
       </c>
     </row>
     <row r="179">
@@ -3948,21 +3948,21 @@
         <v>0</v>
       </c>
       <c r="D179" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E179">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
       <c r="F179">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B180" t="str">
-        <v>2025-01-07</v>
+        <v>2025-01-09</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -3971,18 +3971,18 @@
         <v>Pesos</v>
       </c>
       <c r="E180">
-        <v>-134999.75</v>
+        <v>-2.31</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Recibo de Cobro / 70445</v>
+        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B181" t="str">
-        <v>2025-01-06</v>
+        <v>2025-01-07</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3991,18 +3991,18 @@
         <v>Pesos</v>
       </c>
       <c r="E181">
-        <v>135000</v>
+        <v>-134999.75</v>
       </c>
       <c r="F181">
-        <v>134999.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 70445</v>
       </c>
       <c r="B182" t="str">
-        <v>2024-12-26</v>
+        <v>2025-01-06</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4011,15 +4011,15 @@
         <v>Pesos</v>
       </c>
       <c r="E182">
-        <v>-57777.54</v>
+        <v>135000</v>
       </c>
       <c r="F182">
-        <v>-0.25</v>
+        <v>134999.75</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Comprobante de Pago / 3498761</v>
+        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B183" t="str">
         <v>2024-12-26</v>
@@ -4028,33 +4028,33 @@
         <v>0</v>
       </c>
       <c r="D183" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E183">
-        <v>-1.01</v>
+        <v>-57777.54</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
+        <v>Comprobante de Pago / 3498761</v>
       </c>
       <c r="B184" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D184" t="str">
         <v>Dólares</v>
       </c>
       <c r="E184">
-        <v>1.01</v>
+        <v>-1.01</v>
       </c>
       <c r="F184">
-        <v>1.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -4065,176 +4065,176 @@
         <v>2024-12-26</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D185" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E185">
-        <v>-0.03</v>
+        <v>1.01</v>
       </c>
       <c r="F185">
-        <v>57777.29</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
+        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
       </c>
       <c r="B186" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186" t="str">
         <v>Pesos</v>
       </c>
       <c r="E186">
-        <v>27372.9</v>
+        <v>-0.03</v>
       </c>
       <c r="F186">
-        <v>57777.32</v>
+        <v>57777.29</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
+        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
       </c>
       <c r="B187" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C187">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="str">
         <v>Pesos</v>
       </c>
       <c r="E187">
-        <v>29356.45</v>
+        <v>27372.9</v>
       </c>
       <c r="F187">
-        <v>30404.42</v>
+        <v>57777.32</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
       </c>
       <c r="B188" t="str">
-        <v>2024-12-18</v>
+        <v>2024-12-26</v>
       </c>
       <c r="C188">
-        <v>299</v>
+        <v>2</v>
       </c>
       <c r="D188" t="str">
         <v>Pesos</v>
       </c>
       <c r="E188">
-        <v>-255135.69</v>
+        <v>29356.45</v>
       </c>
       <c r="F188">
-        <v>1047.97</v>
+        <v>30404.42</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B189" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C189">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="D189" t="str">
         <v>Pesos</v>
       </c>
       <c r="E189">
-        <v>65556.13</v>
+        <v>-255135.69</v>
       </c>
       <c r="F189">
-        <v>256183.66</v>
+        <v>1047.97</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B190" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C190">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D190" t="str">
         <v>Pesos</v>
       </c>
       <c r="E190">
-        <v>58613.72</v>
+        <v>65556.13</v>
       </c>
       <c r="F190">
-        <v>190627.53</v>
+        <v>256183.66</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
+        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B191" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C191">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D191" t="str">
         <v>Pesos</v>
       </c>
       <c r="E191">
-        <v>69622.4</v>
+        <v>58613.72</v>
       </c>
       <c r="F191">
-        <v>132013.81</v>
+        <v>190627.53</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
       </c>
       <c r="B192" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C192">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D192" t="str">
         <v>Pesos</v>
       </c>
       <c r="E192">
-        <v>62392.37</v>
+        <v>69622.4</v>
       </c>
       <c r="F192">
-        <v>62391.41</v>
+        <v>132013.81</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B193" t="str">
-        <v>2024-12-17</v>
+        <v>2024-12-18</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D193" t="str">
         <v>Pesos</v>
       </c>
       <c r="E193">
-        <v>-0.53</v>
+        <v>62392.37</v>
       </c>
       <c r="F193">
-        <v>-0.96</v>
+        <v>62391.41</v>
       </c>
     </row>
     <row r="194">
@@ -4248,18 +4248,18 @@
         <v>0</v>
       </c>
       <c r="D194" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E194">
-        <v>0.12</v>
+        <v>-0.53</v>
       </c>
       <c r="F194">
-        <v>0.6</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B195" t="str">
         <v>2024-12-17</v>
@@ -4268,13 +4268,13 @@
         <v>0</v>
       </c>
       <c r="D195" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E195">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F195">
-        <v>-0.43</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="196">
@@ -4288,33 +4288,33 @@
         <v>0</v>
       </c>
       <c r="D196" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E196">
-        <v>0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F196">
-        <v>0.48</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B197" t="str">
-        <v>2024-12-13</v>
+        <v>2024-12-17</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E197">
-        <v>-0.3</v>
+        <v>0.03</v>
       </c>
       <c r="F197">
-        <v>-0.3</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="198">
@@ -4328,293 +4328,293 @@
         <v>0</v>
       </c>
       <c r="D198" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E198">
-        <v>0.07</v>
+        <v>-0.3</v>
       </c>
       <c r="F198">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B199" t="str">
-        <v>2024-12-12</v>
+        <v>2024-12-13</v>
       </c>
       <c r="C199">
         <v>0</v>
       </c>
       <c r="D199" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E199">
-        <v>-103588.95</v>
+        <v>0.07</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
+        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B200" t="str">
-        <v>2024-12-06</v>
+        <v>2024-12-12</v>
       </c>
       <c r="C200">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D200" t="str">
         <v>Pesos</v>
       </c>
       <c r="E200">
-        <v>102379.42</v>
+        <v>-103588.95</v>
       </c>
       <c r="F200">
-        <v>103588.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
       </c>
       <c r="B201" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C201">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="D201" t="str">
         <v>Pesos</v>
       </c>
       <c r="E201">
-        <v>-117184.31</v>
+        <v>102379.42</v>
       </c>
       <c r="F201">
-        <v>1209.53</v>
+        <v>103588.95</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
+        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B202" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C202">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="D202" t="str">
         <v>Pesos</v>
       </c>
       <c r="E202">
-        <v>27546.46</v>
+        <v>-117184.31</v>
       </c>
       <c r="F202">
-        <v>118393.84</v>
+        <v>1209.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
       </c>
       <c r="B203" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D203" t="str">
         <v>Pesos</v>
       </c>
       <c r="E203">
-        <v>89904.13</v>
+        <v>27546.46</v>
       </c>
       <c r="F203">
-        <v>90847.38</v>
+        <v>118393.84</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B204" t="str">
-        <v>2024-11-27</v>
+        <v>2024-12-06</v>
       </c>
       <c r="C204">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="D204" t="str">
         <v>Pesos</v>
       </c>
       <c r="E204">
-        <v>-91403.91</v>
+        <v>89904.13</v>
       </c>
       <c r="F204">
-        <v>943.25</v>
+        <v>90847.38</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
+        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B205" t="str">
         <v>2024-11-27</v>
       </c>
       <c r="C205">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D205" t="str">
         <v>Pesos</v>
       </c>
       <c r="E205">
-        <v>91674.44</v>
+        <v>-91403.91</v>
       </c>
       <c r="F205">
-        <v>92347.16</v>
+        <v>943.25</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
       </c>
       <c r="B206" t="str">
-        <v>2024-11-25</v>
+        <v>2024-11-27</v>
       </c>
       <c r="C206">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="D206" t="str">
         <v>Pesos</v>
       </c>
       <c r="E206">
-        <v>140157.43</v>
+        <v>91674.44</v>
       </c>
       <c r="F206">
-        <v>672.72</v>
+        <v>92347.16</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Comprobante de Pago / 3169919</v>
+        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B207" t="str">
         <v>2024-11-25</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D207" t="str">
         <v>Pesos</v>
       </c>
       <c r="E207">
-        <v>-140000</v>
+        <v>140157.43</v>
       </c>
       <c r="F207">
-        <v>-139484.71</v>
+        <v>672.72</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 3169919</v>
       </c>
       <c r="B208" t="str">
-        <v>2024-11-21</v>
+        <v>2024-11-25</v>
       </c>
       <c r="C208">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="D208" t="str">
         <v>Pesos</v>
       </c>
       <c r="E208">
-        <v>-66912.23</v>
+        <v>-140000</v>
       </c>
       <c r="F208">
-        <v>515.29</v>
+        <v>-139484.71</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B209" t="str">
         <v>2024-11-21</v>
       </c>
       <c r="C209">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D209" t="str">
         <v>Pesos</v>
       </c>
       <c r="E209">
-        <v>66349.55</v>
+        <v>-66912.23</v>
       </c>
       <c r="F209">
-        <v>67427.52</v>
+        <v>515.29</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B210" t="str">
-        <v>2024-11-20</v>
+        <v>2024-11-21</v>
       </c>
       <c r="C210">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D210" t="str">
         <v>Pesos</v>
       </c>
       <c r="E210">
-        <v>-73882.48</v>
+        <v>66349.55</v>
       </c>
       <c r="F210">
-        <v>1077.97</v>
+        <v>67427.52</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
+        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B211" t="str">
         <v>2024-11-20</v>
       </c>
       <c r="C211">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="D211" t="str">
         <v>Pesos</v>
       </c>
       <c r="E211">
-        <v>73936.61</v>
+        <v>-73882.48</v>
       </c>
       <c r="F211">
-        <v>74960.45</v>
+        <v>1077.97</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
       </c>
       <c r="B212" t="str">
-        <v>2024-11-15</v>
+        <v>2024-11-20</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D212" t="str">
         <v>Pesos</v>
       </c>
       <c r="E212">
-        <v>-0.22</v>
+        <v>73936.61</v>
       </c>
       <c r="F212">
-        <v>1023.84</v>
+        <v>74960.45</v>
       </c>
     </row>
     <row r="213">
@@ -4628,313 +4628,313 @@
         <v>0</v>
       </c>
       <c r="D213" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E213">
-        <v>0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="F213">
-        <v>0.38</v>
+        <v>1023.84</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B214" t="str">
-        <v>2024-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C214">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="D214" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E214">
-        <v>-139049.36</v>
+        <v>0.05</v>
       </c>
       <c r="F214">
-        <v>1024.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B215" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C215">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="D215" t="str">
         <v>Pesos</v>
       </c>
       <c r="E215">
-        <v>-52427.86</v>
+        <v>-139049.36</v>
       </c>
       <c r="F215">
-        <v>140073.42</v>
+        <v>1024.06</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
+        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B216" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C216">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D216" t="str">
         <v>Pesos</v>
       </c>
       <c r="E216">
-        <v>31736.7</v>
+        <v>-52427.86</v>
       </c>
       <c r="F216">
-        <v>192501.28</v>
+        <v>140073.42</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
       </c>
       <c r="B217" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C217">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="D217" t="str">
         <v>Pesos</v>
       </c>
       <c r="E217">
-        <v>99970.62</v>
+        <v>31736.7</v>
       </c>
       <c r="F217">
-        <v>160764.58</v>
+        <v>192501.28</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B218" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="D218" t="str">
         <v>Pesos</v>
       </c>
       <c r="E218">
-        <v>58861.67</v>
+        <v>99970.62</v>
       </c>
       <c r="F218">
-        <v>60793.96</v>
+        <v>160764.58</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
+        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B219" t="str">
-        <v>2024-10-29</v>
+        <v>2024-11-01</v>
       </c>
       <c r="C219">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="D219" t="str">
         <v>Pesos</v>
       </c>
       <c r="E219">
-        <v>-225944.56</v>
+        <v>58861.67</v>
       </c>
       <c r="F219">
-        <v>1932.29</v>
+        <v>60793.96</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
+        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
       </c>
       <c r="B220" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C220">
-        <v>100</v>
+        <v>297</v>
       </c>
       <c r="D220" t="str">
         <v>Pesos</v>
       </c>
       <c r="E220">
-        <v>102687.56</v>
+        <v>-225944.56</v>
       </c>
       <c r="F220">
-        <v>227876.85</v>
+        <v>1932.29</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
+        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
       </c>
       <c r="B221" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C221">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D221" t="str">
         <v>Pesos</v>
       </c>
       <c r="E221">
-        <v>37241.04</v>
+        <v>102687.56</v>
       </c>
       <c r="F221">
-        <v>125189.29</v>
+        <v>227876.85</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
       </c>
       <c r="B222" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C222">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D222" t="str">
         <v>Pesos</v>
       </c>
       <c r="E222">
-        <v>68729.8</v>
+        <v>37241.04</v>
       </c>
       <c r="F222">
-        <v>87948.25</v>
+        <v>125189.29</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
+        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B223" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D223" t="str">
         <v>Pesos</v>
       </c>
       <c r="E223">
-        <v>18248.61</v>
+        <v>68729.8</v>
       </c>
       <c r="F223">
-        <v>19218.45</v>
+        <v>87948.25</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Comprobante de Pago / 2861824</v>
+        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
       </c>
       <c r="B224" t="str">
-        <v>2024-10-25</v>
+        <v>2024-10-29</v>
       </c>
       <c r="C224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D224" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E224">
-        <v>-8.71</v>
+        <v>18248.61</v>
       </c>
       <c r="F224">
-        <v>0</v>
+        <v>19218.45</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2861824</v>
       </c>
       <c r="B225" t="str">
-        <v>2024-10-23</v>
+        <v>2024-10-25</v>
       </c>
       <c r="C225">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D225" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E225">
-        <v>-71739.34</v>
+        <v>-8.71</v>
       </c>
       <c r="F225">
-        <v>969.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B226" t="str">
         <v>2024-10-23</v>
       </c>
       <c r="C226">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D226" t="str">
         <v>Pesos</v>
       </c>
       <c r="E226">
-        <v>52196.96</v>
+        <v>-71739.34</v>
       </c>
       <c r="F226">
-        <v>72709.18</v>
+        <v>969.84</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
+        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B227" t="str">
-        <v>2024-10-22</v>
+        <v>2024-10-23</v>
       </c>
       <c r="C227">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D227" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E227">
-        <v>-100</v>
+        <v>52196.96</v>
       </c>
       <c r="F227">
-        <v>8.71</v>
+        <v>72709.18</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
+        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
       </c>
       <c r="B228" t="str">
         <v>2024-10-22</v>
       </c>
       <c r="C228">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D228" t="str">
         <v>Dólares</v>
       </c>
       <c r="E228">
-        <v>99.71</v>
+        <v>-100</v>
       </c>
       <c r="F228">
-        <v>108.71</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="229">
@@ -4945,21 +4945,21 @@
         <v>2024-10-22</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="D229" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E229">
-        <v>-2.47</v>
+        <v>99.71</v>
       </c>
       <c r="F229">
-        <v>20512.22</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Recibo de Cobro / 3253687</v>
+        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B230" t="str">
         <v>2024-10-22</v>
@@ -4968,18 +4968,18 @@
         <v>0</v>
       </c>
       <c r="D230" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E230">
-        <v>100</v>
+        <v>-2.47</v>
       </c>
       <c r="F230">
-        <v>9</v>
+        <v>20512.22</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Comprobante de Pago / 2830288</v>
+        <v>Recibo de Cobro / 3253687</v>
       </c>
       <c r="B231" t="str">
         <v>2024-10-22</v>
@@ -4991,210 +4991,210 @@
         <v>Dólares</v>
       </c>
       <c r="E231">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F231">
-        <v>-91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
+        <v>Comprobante de Pago / 2830288</v>
       </c>
       <c r="B232" t="str">
-        <v>2024-10-21</v>
+        <v>2024-10-22</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E232">
-        <v>185034.38</v>
+        <v>-100</v>
       </c>
       <c r="F232">
-        <v>20514.69</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
+        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B233" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" t="str">
         <v>Pesos</v>
       </c>
       <c r="E233">
-        <v>-1199.18</v>
+        <v>185034.38</v>
       </c>
       <c r="F233">
-        <v>-164519.69</v>
+        <v>20514.69</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
       </c>
       <c r="B234" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D234" t="str">
         <v>Pesos</v>
       </c>
       <c r="E234">
-        <v>-243469.32</v>
+        <v>-1199.18</v>
       </c>
       <c r="F234">
-        <v>-163320.51</v>
+        <v>-164519.69</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B235" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C235">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D235" t="str">
         <v>Pesos</v>
       </c>
       <c r="E235">
-        <v>-129746.54</v>
+        <v>-243469.32</v>
       </c>
       <c r="F235">
-        <v>80148.81</v>
+        <v>-163320.51</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
+        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B236" t="str">
-        <v>2024-10-18</v>
+        <v>2024-10-21</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D236" t="str">
         <v>Pesos</v>
       </c>
       <c r="E236">
-        <v>-33573.99</v>
+        <v>-129746.54</v>
       </c>
       <c r="F236">
-        <v>209895.35</v>
+        <v>80148.81</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
       </c>
       <c r="B237" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C237">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D237" t="str">
         <v>Pesos</v>
       </c>
       <c r="E237">
-        <v>142249.86</v>
+        <v>-33573.99</v>
       </c>
       <c r="F237">
-        <v>243469.34</v>
+        <v>209895.35</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B238" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C238">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D238" t="str">
         <v>Pesos</v>
       </c>
       <c r="E238">
-        <v>9746.15</v>
+        <v>142249.86</v>
       </c>
       <c r="F238">
-        <v>101219.48</v>
+        <v>243469.34</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B239" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C239">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D239" t="str">
         <v>Pesos</v>
       </c>
       <c r="E239">
-        <v>29703.57</v>
+        <v>9746.15</v>
       </c>
       <c r="F239">
-        <v>91473.33</v>
+        <v>101219.48</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B240" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C240">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D240" t="str">
         <v>Pesos</v>
       </c>
       <c r="E240">
-        <v>57840.15</v>
+        <v>29703.57</v>
       </c>
       <c r="F240">
-        <v>61769.76</v>
+        <v>91473.33</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B241" t="str">
-        <v>2024-10-04</v>
+        <v>2024-10-18</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D241" t="str">
         <v>Pesos</v>
       </c>
       <c r="E241">
-        <v>-0.04</v>
+        <v>57840.15</v>
       </c>
       <c r="F241">
-        <v>3929.61</v>
+        <v>61769.76</v>
       </c>
     </row>
     <row r="242">
@@ -5208,33 +5208,33 @@
         <v>0</v>
       </c>
       <c r="D242" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E242">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F242">
-        <v>0.33</v>
+        <v>3929.61</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B243" t="str">
-        <v>2024-10-02</v>
+        <v>2024-10-04</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E243">
-        <v>-0.51</v>
+        <v>0.01</v>
       </c>
       <c r="F243">
-        <v>3929.65</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="244">
@@ -5248,38 +5248,38 @@
         <v>0</v>
       </c>
       <c r="D244" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E244">
-        <v>0.12</v>
+        <v>-0.51</v>
       </c>
       <c r="F244">
-        <v>0.32</v>
+        <v>3929.65</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B245" t="str">
-        <v>2024-10-01</v>
+        <v>2024-10-02</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E245">
-        <v>-296.59</v>
+        <v>0.12</v>
       </c>
       <c r="F245">
-        <v>3930.16</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B246" t="str">
         <v>2024-10-01</v>
@@ -5291,30 +5291,30 @@
         <v>Pesos</v>
       </c>
       <c r="E246">
-        <v>4226.79</v>
+        <v>-296.59</v>
       </c>
       <c r="F246">
-        <v>4226.75</v>
+        <v>3930.16</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B247" t="str">
-        <v>2024-09-27</v>
+        <v>2024-10-01</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E247">
-        <v>0.01</v>
+        <v>4226.79</v>
       </c>
       <c r="F247">
-        <v>0.2</v>
+        <v>4226.75</v>
       </c>
     </row>
     <row r="248">
@@ -5328,21 +5328,21 @@
         <v>0</v>
       </c>
       <c r="D248" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E248">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F248">
-        <v>-0.04</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B249" t="str">
-        <v>2024-09-25</v>
+        <v>2024-09-27</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -5351,50 +5351,50 @@
         <v>Pesos</v>
       </c>
       <c r="E249">
-        <v>-48646.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B250" t="str">
         <v>2024-09-25</v>
       </c>
       <c r="C250">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D250" t="str">
         <v>Pesos</v>
       </c>
       <c r="E250">
-        <v>48646.42</v>
+        <v>-48646.1</v>
       </c>
       <c r="F250">
-        <v>48646.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B251" t="str">
-        <v>2024-09-17</v>
+        <v>2024-09-25</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D251" t="str">
         <v>Pesos</v>
       </c>
       <c r="E251">
-        <v>-0.12</v>
+        <v>48646.42</v>
       </c>
       <c r="F251">
-        <v>-0.32</v>
+        <v>48646.1</v>
       </c>
     </row>
     <row r="252">
@@ -5408,33 +5408,33 @@
         <v>0</v>
       </c>
       <c r="D252" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E252">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F252">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B253" t="str">
-        <v>2024-09-13</v>
+        <v>2024-09-17</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E253">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="F253">
-        <v>-0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="254">
@@ -5448,113 +5448,113 @@
         <v>0</v>
       </c>
       <c r="D254" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E254">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F254">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Renta / BPY26</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B255" t="str">
-        <v>2024-09-02</v>
+        <v>2024-09-13</v>
       </c>
       <c r="C255">
         <v>0</v>
       </c>
       <c r="D255" t="str">
-        <v>Dólares</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E255">
-        <v>1.45</v>
+        <v>0.03</v>
       </c>
       <c r="F255">
-        <v>9</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta / BPY26</v>
       </c>
       <c r="B256" t="str">
-        <v>2024-08-20</v>
+        <v>2024-09-02</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E256">
-        <v>-171669.97</v>
+        <v>1.45</v>
       </c>
       <c r="F256">
-        <v>-0.08</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B257" t="str">
-        <v>2024-08-19</v>
+        <v>2024-08-20</v>
       </c>
       <c r="C257">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D257" t="str">
         <v>Pesos</v>
       </c>
       <c r="E257">
-        <v>-243839.94</v>
+        <v>-171669.97</v>
       </c>
       <c r="F257">
-        <v>171669.89</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B258" t="str">
         <v>2024-08-19</v>
       </c>
       <c r="C258">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D258" t="str">
         <v>Pesos</v>
       </c>
       <c r="E258">
-        <v>-196906.93</v>
+        <v>-243839.94</v>
       </c>
       <c r="F258">
-        <v>415509.83</v>
+        <v>171669.89</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B259" t="str">
-        <v>2024-08-16</v>
+        <v>2024-08-19</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D259" t="str">
         <v>Pesos</v>
       </c>
       <c r="E259">
-        <v>-0.08</v>
+        <v>-196906.93</v>
       </c>
       <c r="F259">
-        <v>612416.76</v>
+        <v>415509.83</v>
       </c>
     </row>
     <row r="260">
@@ -5568,41 +5568,41 @@
         <v>0</v>
       </c>
       <c r="D260" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E260">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="F260">
-        <v>0.13</v>
+        <v>612416.76</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B261" t="str">
         <v>2024-08-16</v>
       </c>
       <c r="C261">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D261" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E261">
-        <v>13250.08</v>
+        <v>0.02</v>
       </c>
       <c r="F261">
-        <v>612416.84</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
+        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B262" t="str">
-        <v>2024-08-13</v>
+        <v>2024-08-16</v>
       </c>
       <c r="C262">
         <v>2</v>
@@ -5611,55 +5611,55 @@
         <v>Pesos</v>
       </c>
       <c r="E262">
-        <v>-35187.15</v>
+        <v>13250.08</v>
       </c>
       <c r="F262">
-        <v>599166.76</v>
+        <v>612416.84</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
       </c>
       <c r="B263" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C263">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D263" t="str">
         <v>Pesos</v>
       </c>
       <c r="E263">
-        <v>-31679.73</v>
+        <v>-35187.15</v>
       </c>
       <c r="F263">
-        <v>634353.91</v>
+        <v>599166.76</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
+        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B264" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C264">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D264" t="str">
         <v>Pesos</v>
       </c>
       <c r="E264">
-        <v>-18430.41</v>
+        <v>-31679.73</v>
       </c>
       <c r="F264">
-        <v>666033.64</v>
+        <v>634353.91</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
+        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
       </c>
       <c r="B265" t="str">
         <v>2024-08-13</v>
@@ -5671,355 +5671,355 @@
         <v>Pesos</v>
       </c>
       <c r="E265">
-        <v>-36144.97</v>
+        <v>-18430.41</v>
       </c>
       <c r="F265">
-        <v>684464.05</v>
+        <v>666033.64</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
+        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
       </c>
       <c r="B266" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C266">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D266" t="str">
         <v>Pesos</v>
       </c>
       <c r="E266">
-        <v>-30045.2</v>
+        <v>-36144.97</v>
       </c>
       <c r="F266">
-        <v>720609.02</v>
+        <v>684464.05</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
+        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
       </c>
       <c r="B267" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C267">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D267" t="str">
         <v>Pesos</v>
       </c>
       <c r="E267">
-        <v>-35590.45</v>
+        <v>-30045.2</v>
       </c>
       <c r="F267">
-        <v>750654.22</v>
+        <v>720609.02</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
       </c>
       <c r="B268" t="str">
-        <v>2024-08-12</v>
+        <v>2024-08-13</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D268" t="str">
         <v>Pesos</v>
       </c>
       <c r="E268">
-        <v>-500000</v>
+        <v>-35590.45</v>
       </c>
       <c r="F268">
-        <v>786244.67</v>
+        <v>750654.22</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
+        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B269" t="str">
-        <v>2024-08-09</v>
+        <v>2024-08-12</v>
       </c>
       <c r="C269">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D269" t="str">
         <v>Pesos</v>
       </c>
       <c r="E269">
-        <v>-18274.14</v>
+        <v>-500000</v>
       </c>
       <c r="F269">
-        <v>1286244.67</v>
+        <v>786244.67</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B270" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D270" t="str">
         <v>Pesos</v>
       </c>
       <c r="E270">
-        <v>-17417.14</v>
+        <v>-18274.14</v>
       </c>
       <c r="F270">
-        <v>1304518.81</v>
+        <v>1286244.67</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B271" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C271">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D271" t="str">
         <v>Pesos</v>
       </c>
       <c r="E271">
-        <v>-49536.26</v>
+        <v>-17417.14</v>
       </c>
       <c r="F271">
-        <v>1321935.95</v>
+        <v>1304518.81</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B272" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D272" t="str">
         <v>Pesos</v>
       </c>
       <c r="E272">
-        <v>-14089.99</v>
+        <v>-49536.26</v>
       </c>
       <c r="F272">
-        <v>1371472.21</v>
+        <v>1321935.95</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B273" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C273">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D273" t="str">
         <v>Pesos</v>
       </c>
       <c r="E273">
-        <v>-85669.13</v>
+        <v>-14089.99</v>
       </c>
       <c r="F273">
-        <v>1385562.2</v>
+        <v>1371472.21</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B274" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C274">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D274" t="str">
         <v>Pesos</v>
       </c>
       <c r="E274">
-        <v>-14926.81</v>
+        <v>-85669.13</v>
       </c>
       <c r="F274">
-        <v>1471231.33</v>
+        <v>1385562.2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
+        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B275" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C275">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="D275" t="str">
         <v>Pesos</v>
       </c>
       <c r="E275">
-        <v>-88949.9</v>
+        <v>-14926.81</v>
       </c>
       <c r="F275">
-        <v>1486158.14</v>
+        <v>1471231.33</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
       </c>
       <c r="B276" t="str">
-        <v>2024-08-08</v>
+        <v>2024-08-09</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D276" t="str">
         <v>Pesos</v>
       </c>
       <c r="E276">
-        <v>-500000</v>
+        <v>-88949.9</v>
       </c>
       <c r="F276">
-        <v>1575108.04</v>
+        <v>1486158.14</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B277" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C277">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D277" t="str">
         <v>Pesos</v>
       </c>
       <c r="E277">
-        <v>-20325.87</v>
+        <v>-500000</v>
       </c>
       <c r="F277">
-        <v>2075108.04</v>
+        <v>1575108.04</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B278" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C278">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D278" t="str">
         <v>Pesos</v>
       </c>
       <c r="E278">
-        <v>-46136.52</v>
+        <v>-20325.87</v>
       </c>
       <c r="F278">
-        <v>2095433.91</v>
+        <v>2075108.04</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
+        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B279" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C279">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D279" t="str">
         <v>Pesos</v>
       </c>
       <c r="E279">
-        <v>-27927.91</v>
+        <v>-46136.52</v>
       </c>
       <c r="F279">
-        <v>2141570.43</v>
+        <v>2095433.91</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
       </c>
       <c r="B280" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C280">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D280" t="str">
         <v>Pesos</v>
       </c>
       <c r="E280">
-        <v>-50260.67</v>
+        <v>-27927.91</v>
       </c>
       <c r="F280">
-        <v>2169498.34</v>
+        <v>2141570.43</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
+        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B281" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C281">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="D281" t="str">
         <v>Pesos</v>
       </c>
       <c r="E281">
-        <v>-37506.08</v>
+        <v>-50260.67</v>
       </c>
       <c r="F281">
-        <v>2219759.01</v>
+        <v>2169498.34</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
       </c>
       <c r="B282" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C282">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D282" t="str">
         <v>Pesos</v>
       </c>
       <c r="E282">
-        <v>-28280.79</v>
+        <v>-37506.08</v>
       </c>
       <c r="F282">
-        <v>2257265.09</v>
+        <v>2219759.01</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B283" t="str">
         <v>2024-08-08</v>
@@ -6031,115 +6031,115 @@
         <v>Pesos</v>
       </c>
       <c r="E283">
-        <v>-53133.61</v>
+        <v>-28280.79</v>
       </c>
       <c r="F283">
-        <v>2285545.88</v>
+        <v>2257265.09</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B284" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C284">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D284" t="str">
         <v>Pesos</v>
       </c>
       <c r="E284">
-        <v>-28069.07</v>
+        <v>-53133.61</v>
       </c>
       <c r="F284">
-        <v>2338679.49</v>
+        <v>2285545.88</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B285" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D285" t="str">
         <v>Pesos</v>
       </c>
       <c r="E285">
-        <v>-19937.71</v>
+        <v>-28069.07</v>
       </c>
       <c r="F285">
-        <v>2366748.56</v>
+        <v>2338679.49</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
+        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B286" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C286">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D286" t="str">
         <v>Pesos</v>
       </c>
       <c r="E286">
-        <v>-40228.29</v>
+        <v>-19937.71</v>
       </c>
       <c r="F286">
-        <v>2386686.27</v>
+        <v>2366748.56</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
       </c>
       <c r="B287" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C287">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D287" t="str">
         <v>Pesos</v>
       </c>
       <c r="E287">
-        <v>-25407.34</v>
+        <v>-40228.29</v>
       </c>
       <c r="F287">
-        <v>2426914.56</v>
+        <v>2386686.27</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B288" t="str">
-        <v>2024-08-05</v>
+        <v>2024-08-08</v>
       </c>
       <c r="C288">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D288" t="str">
         <v>Pesos</v>
       </c>
       <c r="E288">
-        <v>1000000</v>
+        <v>-25407.34</v>
       </c>
       <c r="F288">
-        <v>2452321.9</v>
+        <v>2426914.56</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B289" t="str">
         <v>2024-08-05</v>
@@ -6151,15 +6151,15 @@
         <v>Pesos</v>
       </c>
       <c r="E289">
-        <v>218666.47</v>
+        <v>1000000</v>
       </c>
       <c r="F289">
-        <v>1452321.9</v>
+        <v>2452321.9</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
+        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B290" t="str">
         <v>2024-08-05</v>
@@ -6171,15 +6171,15 @@
         <v>Pesos</v>
       </c>
       <c r="E290">
-        <v>164626.92</v>
+        <v>218666.47</v>
       </c>
       <c r="F290">
-        <v>1233655.43</v>
+        <v>1452321.9</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B291" t="str">
         <v>2024-08-05</v>
@@ -6191,155 +6191,155 @@
         <v>Pesos</v>
       </c>
       <c r="E291">
-        <v>152793.11</v>
+        <v>164626.92</v>
       </c>
       <c r="F291">
-        <v>1069028.51</v>
+        <v>1233655.43</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
+        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B292" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C292">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D292" t="str">
         <v>Pesos</v>
       </c>
       <c r="E292">
-        <v>55836.76</v>
+        <v>152793.11</v>
       </c>
       <c r="F292">
-        <v>916235.4</v>
+        <v>1069028.51</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
       </c>
       <c r="B293" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C293">
-        <v>1416</v>
+        <v>4</v>
       </c>
       <c r="D293" t="str">
         <v>Pesos</v>
       </c>
       <c r="E293">
-        <v>-879220.78</v>
+        <v>55836.76</v>
       </c>
       <c r="F293">
-        <v>860398.64</v>
+        <v>916235.4</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B294" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C294">
-        <v>46</v>
+        <v>1416</v>
       </c>
       <c r="D294" t="str">
         <v>Pesos</v>
       </c>
       <c r="E294">
-        <v>96717.6</v>
+        <v>-879220.78</v>
       </c>
       <c r="F294">
-        <v>1739619.42</v>
+        <v>860398.64</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B295" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C295">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D295" t="str">
         <v>Pesos</v>
       </c>
       <c r="E295">
-        <v>159943.07</v>
+        <v>96717.6</v>
       </c>
       <c r="F295">
-        <v>1642901.82</v>
+        <v>1739619.42</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B296" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C296">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D296" t="str">
         <v>Pesos</v>
       </c>
       <c r="E296">
-        <v>70757.98</v>
+        <v>159943.07</v>
       </c>
       <c r="F296">
-        <v>1482958.75</v>
+        <v>1642901.82</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B297" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C297">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D297" t="str">
         <v>Pesos</v>
       </c>
       <c r="E297">
-        <v>96479.58</v>
+        <v>70757.98</v>
       </c>
       <c r="F297">
-        <v>1412200.77</v>
+        <v>1482958.75</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
+        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B298" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C298">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D298" t="str">
         <v>Pesos</v>
       </c>
       <c r="E298">
-        <v>52117.62</v>
+        <v>96479.58</v>
       </c>
       <c r="F298">
-        <v>1315721.19</v>
+        <v>1412200.77</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
       </c>
       <c r="B299" t="str">
         <v>2024-08-05</v>
@@ -6351,135 +6351,135 @@
         <v>Pesos</v>
       </c>
       <c r="E299">
-        <v>45423.16</v>
+        <v>52117.62</v>
       </c>
       <c r="F299">
-        <v>1263603.57</v>
+        <v>1315721.19</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B300" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C300">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="D300" t="str">
         <v>Pesos</v>
       </c>
       <c r="E300">
-        <v>59565.82</v>
+        <v>45423.16</v>
       </c>
       <c r="F300">
-        <v>1218180.41</v>
+        <v>1263603.57</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B301" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C301">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="D301" t="str">
         <v>Pesos</v>
       </c>
       <c r="E301">
-        <v>101983.91</v>
+        <v>59565.82</v>
       </c>
       <c r="F301">
-        <v>1158614.59</v>
+        <v>1218180.41</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B302" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C302">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D302" t="str">
         <v>Pesos</v>
       </c>
       <c r="E302">
-        <v>59530.13</v>
+        <v>101983.91</v>
       </c>
       <c r="F302">
-        <v>1056630.68</v>
+        <v>1158614.59</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B303" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C303">
-        <v>1536</v>
+        <v>61</v>
       </c>
       <c r="D303" t="str">
         <v>Pesos</v>
       </c>
       <c r="E303">
-        <v>942562.63</v>
+        <v>59530.13</v>
       </c>
       <c r="F303">
-        <v>997100.55</v>
+        <v>1056630.68</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B304" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C304">
-        <v>16</v>
+        <v>1536</v>
       </c>
       <c r="D304" t="str">
         <v>Pesos</v>
       </c>
       <c r="E304">
-        <v>53000.3</v>
+        <v>942562.63</v>
       </c>
       <c r="F304">
-        <v>54537.92</v>
+        <v>997100.55</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B305" t="str">
-        <v>2024-07-24</v>
+        <v>2024-08-05</v>
       </c>
       <c r="C305">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D305" t="str">
         <v>Pesos</v>
       </c>
       <c r="E305">
-        <v>-116.05</v>
+        <v>53000.3</v>
       </c>
       <c r="F305">
-        <v>1537.62</v>
+        <v>54537.92</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B306" t="str">
         <v>2024-07-24</v>
@@ -6491,18 +6491,18 @@
         <v>Pesos</v>
       </c>
       <c r="E306">
-        <v>1653.89</v>
+        <v>-116.05</v>
       </c>
       <c r="F306">
-        <v>1653.67</v>
+        <v>1537.62</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B307" t="str">
-        <v>2024-07-10</v>
+        <v>2024-07-24</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -6511,10 +6511,10 @@
         <v>Pesos</v>
       </c>
       <c r="E307">
-        <v>-0.21</v>
+        <v>1653.89</v>
       </c>
       <c r="F307">
-        <v>-0.22</v>
+        <v>1653.67</v>
       </c>
     </row>
     <row r="308">
@@ -6528,158 +6528,158 @@
         <v>0</v>
       </c>
       <c r="D308" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E308">
-        <v>5.25</v>
+        <v>-0.21</v>
       </c>
       <c r="F308">
-        <v>7.55</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B309" t="str">
-        <v>2024-07-08</v>
+        <v>2024-07-10</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E309">
-        <v>-4402.49</v>
+        <v>5.25</v>
       </c>
       <c r="F309">
-        <v>-0.01</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
+        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B310" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C310">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D310" t="str">
         <v>Pesos</v>
       </c>
       <c r="E310">
-        <v>-38067.66</v>
+        <v>-4402.49</v>
       </c>
       <c r="F310">
-        <v>4402.48</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
       </c>
       <c r="B311" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311" t="str">
         <v>Pesos</v>
       </c>
       <c r="E311">
-        <v>-47346.39</v>
+        <v>-38067.66</v>
       </c>
       <c r="F311">
-        <v>42470.14</v>
+        <v>4402.48</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B312" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312" t="str">
         <v>Pesos</v>
       </c>
       <c r="E312">
-        <v>15580.74</v>
+        <v>-47346.39</v>
       </c>
       <c r="F312">
-        <v>89816.53</v>
+        <v>42470.14</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B313" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C313">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D313" t="str">
         <v>Pesos</v>
       </c>
       <c r="E313">
-        <v>34892.52</v>
+        <v>15580.74</v>
       </c>
       <c r="F313">
-        <v>74235.79</v>
+        <v>89816.53</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B314" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C314">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D314" t="str">
         <v>Pesos</v>
       </c>
       <c r="E314">
-        <v>37865.35</v>
+        <v>34892.52</v>
       </c>
       <c r="F314">
-        <v>39343.27</v>
+        <v>74235.79</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
+        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B315" t="str">
-        <v>2024-07-02</v>
+        <v>2024-07-08</v>
       </c>
       <c r="C315">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D315" t="str">
         <v>Pesos</v>
       </c>
       <c r="E315">
-        <v>-152584.35</v>
+        <v>37865.35</v>
       </c>
       <c r="F315">
-        <v>1477.92</v>
+        <v>39343.27</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
+        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B316" t="str">
         <v>2024-07-02</v>
@@ -6691,90 +6691,90 @@
         <v>Pesos</v>
       </c>
       <c r="E316">
-        <v>151114.01</v>
+        <v>-152584.35</v>
       </c>
       <c r="F316">
-        <v>154062.27</v>
+        <v>1477.92</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
+        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B317" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C317">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D317" t="str">
         <v>Pesos</v>
       </c>
       <c r="E317">
-        <v>-108902.21</v>
+        <v>151114.01</v>
       </c>
       <c r="F317">
-        <v>2948.26</v>
+        <v>154062.27</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
       </c>
       <c r="B318" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C318">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D318" t="str">
         <v>Pesos</v>
       </c>
       <c r="E318">
-        <v>-41051.01</v>
+        <v>-108902.21</v>
       </c>
       <c r="F318">
-        <v>111850.47</v>
+        <v>2948.26</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
+        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B319" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C319">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D319" t="str">
         <v>Pesos</v>
       </c>
       <c r="E319">
-        <v>151431.18</v>
+        <v>-41051.01</v>
       </c>
       <c r="F319">
-        <v>152901.48</v>
+        <v>111850.47</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B320" t="str">
-        <v>2024-07-01</v>
+        <v>2024-07-02</v>
       </c>
       <c r="C320">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D320" t="str">
         <v>Pesos</v>
       </c>
       <c r="E320">
-        <v>-0.04</v>
+        <v>151431.18</v>
       </c>
       <c r="F320">
-        <v>1470.3</v>
+        <v>152901.48</v>
       </c>
     </row>
     <row r="321">
@@ -6788,18 +6788,18 @@
         <v>0</v>
       </c>
       <c r="D321" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E321">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F321">
-        <v>0.11</v>
+        <v>1470.3</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B322" t="str">
         <v>2024-07-01</v>
@@ -6808,18 +6808,18 @@
         <v>0</v>
       </c>
       <c r="D322" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E322">
-        <v>-110.98</v>
+        <v>0.01</v>
       </c>
       <c r="F322">
-        <v>1470.34</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B323" t="str">
         <v>2024-07-01</v>
@@ -6831,18 +6831,18 @@
         <v>Pesos</v>
       </c>
       <c r="E323">
-        <v>1581.51</v>
+        <v>-110.98</v>
       </c>
       <c r="F323">
-        <v>1581.32</v>
+        <v>1470.34</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B324" t="str">
-        <v>2024-06-27</v>
+        <v>2024-07-01</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -6851,10 +6851,10 @@
         <v>Pesos</v>
       </c>
       <c r="E324">
-        <v>-0.12</v>
+        <v>1581.51</v>
       </c>
       <c r="F324">
-        <v>-0.19</v>
+        <v>1581.32</v>
       </c>
     </row>
     <row r="325">
@@ -6868,38 +6868,38 @@
         <v>0</v>
       </c>
       <c r="D325" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E325">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F325">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B326" t="str">
-        <v>2024-06-24</v>
+        <v>2024-06-27</v>
       </c>
       <c r="C326">
         <v>0</v>
       </c>
       <c r="D326" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E326">
-        <v>-175.43</v>
+        <v>0.03</v>
       </c>
       <c r="F326">
-        <v>-0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
+        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
       </c>
       <c r="B327" t="str">
         <v>2024-06-24</v>
@@ -6911,15 +6911,15 @@
         <v>Pesos</v>
       </c>
       <c r="E327">
-        <v>-150000</v>
+        <v>-175.43</v>
       </c>
       <c r="F327">
-        <v>175.36</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B328" t="str">
         <v>2024-06-24</v>
@@ -6931,18 +6931,18 @@
         <v>Pesos</v>
       </c>
       <c r="E328">
-        <v>-150447.89</v>
+        <v>-150000</v>
       </c>
       <c r="F328">
-        <v>150175.36</v>
+        <v>175.36</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B329" t="str">
-        <v>2024-06-19</v>
+        <v>2024-06-24</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -6951,10 +6951,10 @@
         <v>Pesos</v>
       </c>
       <c r="E329">
-        <v>-0.07</v>
+        <v>-150447.89</v>
       </c>
       <c r="F329">
-        <v>300623.25</v>
+        <v>150175.36</v>
       </c>
     </row>
     <row r="330">
@@ -6968,18 +6968,18 @@
         <v>0</v>
       </c>
       <c r="D330" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E330">
-        <v>0.02</v>
+        <v>-0.07</v>
       </c>
       <c r="F330">
-        <v>0.07</v>
+        <v>300623.25</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B331" t="str">
         <v>2024-06-19</v>
@@ -6988,21 +6988,21 @@
         <v>0</v>
       </c>
       <c r="D331" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E331">
-        <v>300000</v>
+        <v>0.02</v>
       </c>
       <c r="F331">
-        <v>300623.32</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Dividendo en efectivo / INTC</v>
+        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B332" t="str">
-        <v>2024-06-04</v>
+        <v>2024-06-19</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>Pesos</v>
       </c>
       <c r="E332">
-        <v>-0.19</v>
+        <v>300000</v>
       </c>
       <c r="F332">
-        <v>623.32</v>
+        <v>300623.32</v>
       </c>
     </row>
     <row r="333">
@@ -7028,161 +7028,161 @@
         <v>0</v>
       </c>
       <c r="D333" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E333">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="F333">
-        <v>0.05</v>
+        <v>623.32</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
+        <v>Dividendo en efectivo / INTC</v>
       </c>
       <c r="B334" t="str">
-        <v>2024-05-31</v>
+        <v>2024-06-04</v>
       </c>
       <c r="C334">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E334">
-        <v>55120.7</v>
+        <v>0.05</v>
       </c>
       <c r="F334">
-        <v>623.51</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B335" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C335">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D335" t="str">
         <v>Pesos</v>
       </c>
       <c r="E335">
-        <v>-36734.79</v>
+        <v>55120.7</v>
       </c>
       <c r="F335">
-        <v>-54497.19</v>
+        <v>623.51</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
+        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B336" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C336">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D336" t="str">
         <v>Pesos</v>
       </c>
       <c r="E336">
-        <v>-59561.06</v>
+        <v>-36734.79</v>
       </c>
       <c r="F336">
-        <v>-17762.4</v>
+        <v>-54497.19</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
+        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
       </c>
       <c r="B337" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C337">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D337" t="str">
         <v>Pesos</v>
       </c>
       <c r="E337">
-        <v>38496.62</v>
+        <v>-59561.06</v>
       </c>
       <c r="F337">
-        <v>41798.66</v>
+        <v>-17762.4</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
+        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
       </c>
       <c r="B338" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C338">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D338" t="str">
         <v>Pesos</v>
       </c>
       <c r="E338">
-        <v>48021.6</v>
+        <v>38496.62</v>
       </c>
       <c r="F338">
-        <v>3302.04</v>
+        <v>41798.66</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
+        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
       </c>
       <c r="B339" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C339">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D339" t="str">
         <v>Pesos</v>
       </c>
       <c r="E339">
-        <v>-47487.54</v>
+        <v>48021.6</v>
       </c>
       <c r="F339">
-        <v>-44719.56</v>
+        <v>3302.04</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Movimiento Manual / Ret IIGG - GGAL</v>
+        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
       </c>
       <c r="B340" t="str">
-        <v>2024-05-27</v>
+        <v>2024-05-31</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D340" t="str">
         <v>Pesos</v>
       </c>
       <c r="E340">
-        <v>-73.45</v>
+        <v>-47487.54</v>
       </c>
       <c r="F340">
-        <v>2767.98</v>
+        <v>-44719.56</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG - GGAL</v>
       </c>
       <c r="B341" t="str">
-        <v>2024-05-24</v>
+        <v>2024-05-27</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -7191,55 +7191,55 @@
         <v>Pesos</v>
       </c>
       <c r="E341">
-        <v>1518.11</v>
+        <v>-73.45</v>
       </c>
       <c r="F341">
-        <v>2841.43</v>
+        <v>2767.98</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B342" t="str">
-        <v>2024-05-23</v>
+        <v>2024-05-24</v>
       </c>
       <c r="C342">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D342" t="str">
         <v>Pesos</v>
       </c>
       <c r="E342">
-        <v>-81669.11</v>
+        <v>1518.11</v>
       </c>
       <c r="F342">
-        <v>1323.32</v>
+        <v>2841.43</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
+        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B343" t="str">
-        <v>2024-05-21</v>
+        <v>2024-05-23</v>
       </c>
       <c r="C343">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D343" t="str">
         <v>Pesos</v>
       </c>
       <c r="E343">
-        <v>21949.4</v>
+        <v>-81669.11</v>
       </c>
       <c r="F343">
-        <v>82992.43</v>
+        <v>1323.32</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
+        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
       </c>
       <c r="B344" t="str">
         <v>2024-05-21</v>
@@ -7251,38 +7251,38 @@
         <v>Pesos</v>
       </c>
       <c r="E344">
-        <v>57393.84</v>
+        <v>21949.4</v>
       </c>
       <c r="F344">
-        <v>61043.03</v>
+        <v>82992.43</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
       </c>
       <c r="B345" t="str">
-        <v>2024-05-15</v>
+        <v>2024-05-21</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D345" t="str">
         <v>Pesos</v>
       </c>
       <c r="E345">
-        <v>703.51</v>
+        <v>57393.84</v>
       </c>
       <c r="F345">
-        <v>3649.19</v>
+        <v>61043.03</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B346" t="str">
-        <v>2024-05-14</v>
+        <v>2024-05-15</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -7291,335 +7291,335 @@
         <v>Pesos</v>
       </c>
       <c r="E346">
-        <v>-130000</v>
+        <v>703.51</v>
       </c>
       <c r="F346">
-        <v>2945.68</v>
+        <v>3649.19</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Distribución de acciones por Capitalización / BYMA</v>
+        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B347" t="str">
         <v>2024-05-14</v>
       </c>
       <c r="C347">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D347" t="str">
         <v>Pesos</v>
       </c>
       <c r="E347">
-        <v>-0.44</v>
+        <v>-130000</v>
       </c>
       <c r="F347">
-        <v>132945.68</v>
+        <v>2945.68</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
+        <v>Distribución de acciones por Capitalización / BYMA</v>
       </c>
       <c r="B348" t="str">
-        <v>2024-05-07</v>
+        <v>2024-05-14</v>
       </c>
       <c r="C348">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="D348" t="str">
         <v>Pesos</v>
       </c>
       <c r="E348">
-        <v>5097.7</v>
+        <v>-0.44</v>
       </c>
       <c r="F348">
-        <v>132946.12</v>
+        <v>132945.68</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B349" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C349">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D349" t="str">
         <v>Pesos</v>
       </c>
       <c r="E349">
-        <v>23635.91</v>
+        <v>5097.7</v>
       </c>
       <c r="F349">
-        <v>127848.42</v>
+        <v>132946.12</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B350" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C350">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D350" t="str">
         <v>Pesos</v>
       </c>
       <c r="E350">
-        <v>20921.43</v>
+        <v>23635.91</v>
       </c>
       <c r="F350">
-        <v>104212.51</v>
+        <v>127848.42</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B351" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C351">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D351" t="str">
         <v>Pesos</v>
       </c>
       <c r="E351">
-        <v>11618.11</v>
+        <v>20921.43</v>
       </c>
       <c r="F351">
-        <v>83291.08</v>
+        <v>104212.51</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
+        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B352" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C352">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D352" t="str">
         <v>Pesos</v>
       </c>
       <c r="E352">
-        <v>52241.19</v>
+        <v>11618.11</v>
       </c>
       <c r="F352">
-        <v>71672.97</v>
+        <v>83291.08</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B353" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C353">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D353" t="str">
         <v>Pesos</v>
       </c>
       <c r="E353">
-        <v>19431.78</v>
+        <v>52241.19</v>
       </c>
       <c r="F353">
-        <v>19431.78</v>
+        <v>71672.97</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B354" t="str">
-        <v>2024-05-06</v>
+        <v>2024-05-07</v>
       </c>
       <c r="C354">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D354" t="str">
         <v>Pesos</v>
       </c>
       <c r="E354">
-        <v>-222622.08</v>
+        <v>19431.78</v>
       </c>
       <c r="F354">
-        <v>0</v>
+        <v>19431.78</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B355" t="str">
-        <v>2024-05-02</v>
+        <v>2024-05-06</v>
       </c>
       <c r="C355">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D355" t="str">
         <v>Pesos</v>
       </c>
       <c r="E355">
-        <v>99355.72</v>
+        <v>-222622.08</v>
       </c>
       <c r="F355">
-        <v>222622.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
+        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B356" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C356">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D356" t="str">
         <v>Pesos</v>
       </c>
       <c r="E356">
-        <v>66604.92</v>
+        <v>99355.72</v>
       </c>
       <c r="F356">
-        <v>123266.36</v>
+        <v>222622.08</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
       </c>
       <c r="B357" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C357">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D357" t="str">
         <v>Pesos</v>
       </c>
       <c r="E357">
-        <v>6069.65</v>
+        <v>66604.92</v>
       </c>
       <c r="F357">
-        <v>56661.44</v>
+        <v>123266.36</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
+        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B358" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C358">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D358" t="str">
         <v>Pesos</v>
       </c>
       <c r="E358">
-        <v>2488.36</v>
+        <v>6069.65</v>
       </c>
       <c r="F358">
-        <v>50591.79</v>
+        <v>56661.44</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B359" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C359">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D359" t="str">
         <v>Pesos</v>
       </c>
       <c r="E359">
-        <v>14202.18</v>
+        <v>2488.36</v>
       </c>
       <c r="F359">
-        <v>48103.43</v>
+        <v>50591.79</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B360" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C360">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D360" t="str">
         <v>Pesos</v>
       </c>
       <c r="E360">
-        <v>12418.97</v>
+        <v>14202.18</v>
       </c>
       <c r="F360">
-        <v>33901.25</v>
+        <v>48103.43</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B361" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D361" t="str">
         <v>Pesos</v>
       </c>
       <c r="E361">
-        <v>20579.26</v>
+        <v>12418.97</v>
       </c>
       <c r="F361">
-        <v>21482.28</v>
+        <v>33901.25</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
+        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B362" t="str">
-        <v>2024-04-17</v>
+        <v>2024-05-02</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D362" t="str">
         <v>Pesos</v>
       </c>
       <c r="E362">
-        <v>-34.33</v>
+        <v>20579.26</v>
       </c>
       <c r="F362">
-        <v>903.02</v>
+        <v>21482.28</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
       </c>
       <c r="B363" t="str">
         <v>2024-04-17</v>
@@ -7631,15 +7631,15 @@
         <v>Pesos</v>
       </c>
       <c r="E363">
-        <v>489.31</v>
+        <v>-34.33</v>
       </c>
       <c r="F363">
-        <v>937.35</v>
+        <v>903.02</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Movimiento Manual / Ret IIGG - BYMA</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B364" t="str">
         <v>2024-04-17</v>
@@ -7648,18 +7648,18 @@
         <v>0</v>
       </c>
       <c r="D364" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E364">
-        <v>-0.18</v>
+        <v>489.31</v>
       </c>
       <c r="F364">
-        <v>2.3</v>
+        <v>937.35</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG - BYMA</v>
       </c>
       <c r="B365" t="str">
         <v>2024-04-17</v>
@@ -7668,13 +7668,13 @@
         <v>0</v>
       </c>
       <c r="D365" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E365">
-        <v>-2.6</v>
+        <v>-0.18</v>
       </c>
       <c r="F365">
-        <v>448.04</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="366">
@@ -7688,218 +7688,218 @@
         <v>0</v>
       </c>
       <c r="D366" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E366">
-        <v>2.48</v>
+        <v>-2.6</v>
       </c>
       <c r="F366">
-        <v>2.48</v>
+        <v>448.04</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B367" t="str">
-        <v>2024-04-10</v>
+        <v>2024-04-17</v>
       </c>
       <c r="C367">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D367" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E367">
-        <v>-80932.98</v>
+        <v>2.48</v>
       </c>
       <c r="F367">
-        <v>450.64</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
+        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
       </c>
       <c r="B368" t="str">
-        <v>2024-04-09</v>
+        <v>2024-04-10</v>
       </c>
       <c r="C368">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D368" t="str">
         <v>Pesos</v>
       </c>
       <c r="E368">
-        <v>104967.66</v>
+        <v>-80932.98</v>
       </c>
       <c r="F368">
-        <v>81383.62</v>
+        <v>450.64</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
+        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
       </c>
       <c r="B369" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C369">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D369" t="str">
         <v>Pesos</v>
       </c>
       <c r="E369">
-        <v>16388.53</v>
+        <v>104967.66</v>
       </c>
       <c r="F369">
-        <v>-23584.04</v>
+        <v>81383.62</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
+        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
       </c>
       <c r="B370" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C370">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D370" t="str">
         <v>Pesos</v>
       </c>
       <c r="E370">
-        <v>-77278.67</v>
+        <v>16388.53</v>
       </c>
       <c r="F370">
-        <v>-39972.57</v>
+        <v>-23584.04</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
+        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
       </c>
       <c r="B371" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C371">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D371" t="str">
         <v>Pesos</v>
       </c>
       <c r="E371">
-        <v>35352.22</v>
+        <v>-77278.67</v>
       </c>
       <c r="F371">
-        <v>37306.1</v>
+        <v>-39972.57</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
       </c>
       <c r="B372" t="str">
-        <v>2024-04-08</v>
+        <v>2024-04-09</v>
       </c>
       <c r="C372">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D372" t="str">
         <v>Pesos</v>
       </c>
       <c r="E372">
-        <v>-733461</v>
+        <v>35352.22</v>
       </c>
       <c r="F372">
-        <v>1953.88</v>
+        <v>37306.1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B373" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C373">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D373" t="str">
         <v>Pesos</v>
       </c>
       <c r="E373">
-        <v>-229304.33</v>
+        <v>-733461</v>
       </c>
       <c r="F373">
-        <v>735414.88</v>
+        <v>1953.88</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
+        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
       </c>
       <c r="B374" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C374">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D374" t="str">
         <v>Pesos</v>
       </c>
       <c r="E374">
-        <v>-35550.12</v>
+        <v>-229304.33</v>
       </c>
       <c r="F374">
-        <v>964719.21</v>
+        <v>735414.88</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
+        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
       </c>
       <c r="B375" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C375">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D375" t="str">
         <v>Pesos</v>
       </c>
       <c r="E375">
-        <v>-197072.27</v>
+        <v>-35550.12</v>
       </c>
       <c r="F375">
-        <v>1000269.33</v>
+        <v>964719.21</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
+        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
       </c>
       <c r="B376" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C376">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D376" t="str">
         <v>Pesos</v>
       </c>
       <c r="E376">
-        <v>-24084.05</v>
+        <v>-197072.27</v>
       </c>
       <c r="F376">
-        <v>1197341.6</v>
+        <v>1000269.33</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
+        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
       </c>
       <c r="B377" t="str">
         <v>2024-04-08</v>
@@ -7911,178 +7911,178 @@
         <v>Pesos</v>
       </c>
       <c r="E377">
-        <v>-53459.78</v>
+        <v>-24084.05</v>
       </c>
       <c r="F377">
-        <v>1221425.65</v>
+        <v>1197341.6</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
+        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
       </c>
       <c r="B378" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C378">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D378" t="str">
         <v>Pesos</v>
       </c>
       <c r="E378">
-        <v>-100325.74</v>
+        <v>-53459.78</v>
       </c>
       <c r="F378">
-        <v>1274885.43</v>
+        <v>1221425.65</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
+        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
       </c>
       <c r="B379" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C379">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D379" t="str">
         <v>Pesos</v>
       </c>
       <c r="E379">
-        <v>-180029.2</v>
+        <v>-100325.74</v>
       </c>
       <c r="F379">
-        <v>1375211.17</v>
+        <v>1274885.43</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
+        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
       </c>
       <c r="B380" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C380">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D380" t="str">
         <v>Pesos</v>
       </c>
       <c r="E380">
-        <v>-62547.44</v>
+        <v>-180029.2</v>
       </c>
       <c r="F380">
-        <v>1555240.37</v>
+        <v>1375211.17</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
+        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
       </c>
       <c r="B381" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C381">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D381" t="str">
         <v>Pesos</v>
       </c>
       <c r="E381">
-        <v>-60307.16</v>
+        <v>-62547.44</v>
       </c>
       <c r="F381">
-        <v>1617787.81</v>
+        <v>1555240.37</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
+        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
       </c>
       <c r="B382" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C382">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D382" t="str">
         <v>Pesos</v>
       </c>
       <c r="E382">
-        <v>-16504.2</v>
+        <v>-60307.16</v>
       </c>
       <c r="F382">
-        <v>1678094.97</v>
+        <v>1617787.81</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
+        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
       </c>
       <c r="B383" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C383">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D383" t="str">
         <v>Pesos</v>
       </c>
       <c r="E383">
-        <v>-197617.73</v>
+        <v>-16504.2</v>
       </c>
       <c r="F383">
-        <v>1694599.17</v>
+        <v>1678094.97</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
+        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
       </c>
       <c r="B384" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C384">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D384" t="str">
         <v>Pesos</v>
       </c>
       <c r="E384">
-        <v>-107783.1</v>
+        <v>-197617.73</v>
       </c>
       <c r="F384">
-        <v>1892216.9</v>
+        <v>1694599.17</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Liquidación de Rescate / 562376 / BCACC A</v>
+        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
       </c>
       <c r="B385" t="str">
-        <v>2024-04-03</v>
+        <v>2024-04-08</v>
       </c>
       <c r="C385">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D385" t="str">
         <v>Pesos</v>
       </c>
       <c r="E385">
-        <v>2000000</v>
+        <v>-107783.1</v>
       </c>
       <c r="F385">
-        <v>2000000</v>
+        <v>1892216.9</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 562376 / BCACC A</v>
       </c>
       <c r="B386" t="str">
-        <v>2024-03-25</v>
+        <v>2024-04-03</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -8091,18 +8091,18 @@
         <v>Pesos</v>
       </c>
       <c r="E386">
-        <v>-1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F386">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Recibo de Cobro / 844439</v>
+        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B387" t="str">
-        <v>2024-03-22</v>
+        <v>2024-03-25</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -8111,18 +8111,18 @@
         <v>Pesos</v>
       </c>
       <c r="E387">
-        <v>1000000</v>
+        <v>-1000000</v>
       </c>
       <c r="F387">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 844439</v>
       </c>
       <c r="B388" t="str">
-        <v>2024-03-11</v>
+        <v>2024-03-22</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -8131,18 +8131,18 @@
         <v>Pesos</v>
       </c>
       <c r="E388">
-        <v>-1002419.25</v>
+        <v>1000000</v>
       </c>
       <c r="F388">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
+        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B389" t="str">
-        <v>2024-03-06</v>
+        <v>2024-03-11</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -8151,15 +8151,15 @@
         <v>Pesos</v>
       </c>
       <c r="E389">
-        <v>1002419.25</v>
+        <v>-1002419.25</v>
       </c>
       <c r="F389">
-        <v>1002419.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
+        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
       </c>
       <c r="B390" t="str">
         <v>2024-03-06</v>
@@ -8171,15 +8171,15 @@
         <v>Pesos</v>
       </c>
       <c r="E390">
-        <v>-1000000</v>
+        <v>1002419.25</v>
       </c>
       <c r="F390">
-        <v>0</v>
+        <v>1002419.25</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Recibo de Cobro / 691819</v>
+        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
       </c>
       <c r="B391" t="str">
         <v>2024-03-06</v>
@@ -8191,15 +8191,35 @@
         <v>Pesos</v>
       </c>
       <c r="E391">
+        <v>-1000000</v>
+      </c>
+      <c r="F391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Recibo de Cobro / 691819</v>
+      </c>
+      <c r="B392" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392" t="str">
+        <v>Pesos</v>
+      </c>
+      <c r="E392">
         <v>1000000</v>
       </c>
-      <c r="F391">
+      <c r="F392">
         <v>1000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F391"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F392"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/mi_cartera_balanz/data/cuentacorriente.xlsx
+++ b/mi_cartera_balanz/data/cuentacorriente.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F392"/>
+  <dimension ref="A1:F393"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -399,130 +399,130 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Boleto / 10845350 / COMPRA / 1 / PAMP / $</v>
+        <v>Boleto / 11011476 / COMPRA / 1 / YPFD / $</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-29</v>
       </c>
       <c r="C2">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="D2" t="str">
         <v>Pesos</v>
       </c>
       <c r="E2">
-        <v>-1003081.37</v>
+        <v>-498002.3</v>
       </c>
       <c r="F2">
-        <v>1110511.68</v>
+        <v>612509.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Liquidación de Rescate / 2021758 / BALANZ MONEY MARKET A</v>
+        <v>Boleto / 10845350 / COMPRA / 1 / PAMP / $</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-24</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="D3" t="str">
         <v>Pesos</v>
       </c>
       <c r="E3">
-        <v>2006044.36</v>
+        <v>-1003081.37</v>
       </c>
       <c r="F3">
-        <v>2113593.05</v>
+        <v>1110511.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Boleto / 10668132 / COMPRA / 1 / YPFD / $</v>
+        <v>Liquidación de Rescate / 2021758 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B4" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="C4">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="D4" t="str">
         <v>Pesos</v>
       </c>
       <c r="E4">
-        <v>-1993297.7</v>
+        <v>2006044.36</v>
       </c>
       <c r="F4">
-        <v>107548.69</v>
+        <v>2113593.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 10668132 / COMPRA / 1 / YPFD / $</v>
       </c>
       <c r="B5" t="str">
         <v>2026-09-21</v>
       </c>
       <c r="C5">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="D5" t="str">
         <v>Pesos</v>
       </c>
       <c r="E5">
-        <v>2089759.48</v>
+        <v>-1993297.7</v>
       </c>
       <c r="F5">
-        <v>2100846.39</v>
+        <v>107548.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 10641020 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C6">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="D6" t="str">
         <v>Pesos</v>
       </c>
       <c r="E6">
-        <v>-1015702.61</v>
+        <v>2089759.48</v>
       </c>
       <c r="F6">
-        <v>11086.91</v>
+        <v>2100846.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Comprobante de Pago / 2204947</v>
+        <v>Boleto / 10583557 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D7" t="str">
         <v>Pesos</v>
       </c>
       <c r="E7">
-        <v>-100000</v>
+        <v>-1015702.61</v>
       </c>
       <c r="F7">
-        <v>1026789.52</v>
+        <v>11086.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2204947</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-09-15</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -531,78 +531,78 @@
         <v>Pesos</v>
       </c>
       <c r="E8">
-        <v>-2000000</v>
+        <v>-100000</v>
       </c>
       <c r="F8">
-        <v>1126789.52</v>
+        <v>1026789.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 1985465 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B9" t="str">
         <v>2026-09-15</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="str">
         <v>Pesos</v>
       </c>
       <c r="E9">
-        <v>898438.45</v>
+        <v>-2000000</v>
       </c>
       <c r="F9">
-        <v>3126789.52</v>
+        <v>1126789.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 10443261 / VENTA / 1 / YPFD / $</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="C10">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="D10" t="str">
         <v>Pesos</v>
       </c>
       <c r="E10">
-        <v>-1981985.21</v>
+        <v>898438.45</v>
       </c>
       <c r="F10">
-        <v>2228351.07</v>
+        <v>3126789.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Recibo de Cobro / 2547929</v>
+        <v>Boleto / 10350610 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B11" t="str">
         <v>2026-09-14</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="D11" t="str">
         <v>Pesos</v>
       </c>
       <c r="E11">
-        <v>120000</v>
+        <v>-1981985.21</v>
       </c>
       <c r="F11">
-        <v>4210336.28</v>
+        <v>2228351.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Comprobante de Pago / 2167536</v>
+        <v>Recibo de Cobro / 2547929</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-14</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -611,18 +611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E12">
-        <v>-50000</v>
+        <v>120000</v>
       </c>
       <c r="F12">
-        <v>4090336.28</v>
+        <v>4210336.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2167536</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-09-10</v>
+        <v>2026-09-12</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -631,18 +631,18 @@
         <v>Pesos</v>
       </c>
       <c r="E13">
-        <v>3404580.41</v>
+        <v>-50000</v>
       </c>
       <c r="F13">
-        <v>4140336.28</v>
+        <v>4090336.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Comprobante de Pago / 2105708</v>
+        <v>Liquidación de Rescate / 1951616 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-09-06</v>
+        <v>2026-09-10</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -651,18 +651,18 @@
         <v>Pesos</v>
       </c>
       <c r="E14">
-        <v>-30000</v>
+        <v>3404580.41</v>
       </c>
       <c r="F14">
-        <v>735755.87</v>
+        <v>4140336.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Comprobante de Pago / 2057077</v>
+        <v>Comprobante de Pago / 2105708</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-09-01</v>
+        <v>2026-09-06</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -671,18 +671,18 @@
         <v>Pesos</v>
       </c>
       <c r="E15">
-        <v>-80000</v>
+        <v>-30000</v>
       </c>
       <c r="F15">
-        <v>765755.87</v>
+        <v>735755.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
+        <v>Comprobante de Pago / 2057077</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-08-21</v>
+        <v>2026-09-01</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -691,118 +691,118 @@
         <v>Pesos</v>
       </c>
       <c r="E16">
-        <v>-3371333.8</v>
+        <v>-80000</v>
       </c>
       <c r="F16">
-        <v>845755.87</v>
+        <v>765755.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
+        <v>Liquidación de Suscripción / 1788555 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B17" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C17">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="D17" t="str">
         <v>Pesos</v>
       </c>
       <c r="E17">
-        <v>918459.06</v>
+        <v>-3371333.8</v>
       </c>
       <c r="F17">
-        <v>4217089.67</v>
+        <v>845755.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9298843 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B18" t="str">
         <v>2026-08-21</v>
       </c>
       <c r="C18">
-        <v>503</v>
+        <v>278</v>
       </c>
       <c r="D18" t="str">
         <v>Pesos</v>
       </c>
       <c r="E18">
-        <v>3298630.61</v>
+        <v>918459.06</v>
       </c>
       <c r="F18">
-        <v>3298630.61</v>
+        <v>4217089.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Comprobante de Pago / 1944836</v>
+        <v>Boleto / 9298842 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-08-19</v>
+        <v>2026-08-21</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D19" t="str">
         <v>Pesos</v>
       </c>
       <c r="E19">
-        <v>-34658.23</v>
+        <v>3298630.61</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3298630.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1944836</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-08-14</v>
+        <v>2026-08-19</v>
       </c>
       <c r="C20">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="D20" t="str">
         <v>Pesos</v>
       </c>
       <c r="E20">
-        <v>-3589249.15</v>
+        <v>-34658.23</v>
       </c>
       <c r="F20">
-        <v>34658.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Comprobante de Pago / 1817656</v>
+        <v>Boleto / 9028136 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-08-04</v>
+        <v>2026-08-14</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D21" t="str">
         <v>Pesos</v>
       </c>
       <c r="E21">
-        <v>-40000</v>
+        <v>-3589249.15</v>
       </c>
       <c r="F21">
-        <v>3623907.38</v>
+        <v>34658.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Comprobante de Pago / 1732595</v>
+        <v>Comprobante de Pago / 1817656</v>
       </c>
       <c r="B22" t="str">
-        <v>2026-07-25</v>
+        <v>2026-08-04</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -811,18 +811,18 @@
         <v>Pesos</v>
       </c>
       <c r="E22">
-        <v>-100000</v>
+        <v>-40000</v>
       </c>
       <c r="F22">
-        <v>3663907.38</v>
+        <v>3623907.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Comprobante de Pago / 1561578</v>
+        <v>Comprobante de Pago / 1732595</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-25</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -831,18 +831,18 @@
         <v>Pesos</v>
       </c>
       <c r="E23">
-        <v>-300000</v>
+        <v>-100000</v>
       </c>
       <c r="F23">
-        <v>3763907.38</v>
+        <v>3663907.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Comprobante de Pago / 1545516</v>
+        <v>Comprobante de Pago / 1561578</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-04</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -851,70 +851,70 @@
         <v>Pesos</v>
       </c>
       <c r="E24">
-        <v>-100000</v>
+        <v>-300000</v>
       </c>
       <c r="F24">
-        <v>4063907.38</v>
+        <v>3763907.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
+        <v>Comprobante de Pago / 1545516</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-02</v>
       </c>
       <c r="C25">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D25" t="str">
         <v>Pesos</v>
       </c>
       <c r="E25">
-        <v>488924.13</v>
+        <v>-100000</v>
       </c>
       <c r="F25">
-        <v>4163907.38</v>
+        <v>4063907.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7154878 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-06-29</v>
+        <v>2026-07-01</v>
       </c>
       <c r="C26">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D26" t="str">
         <v>Pesos</v>
       </c>
       <c r="E26">
-        <v>515910.2</v>
+        <v>488924.13</v>
       </c>
       <c r="F26">
-        <v>3674983.25</v>
+        <v>4163907.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 7035923 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B27" t="str">
         <v>2026-06-29</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D27" t="str">
         <v>Pesos</v>
       </c>
       <c r="E27">
-        <v>-6.27</v>
+        <v>515910.2</v>
       </c>
       <c r="F27">
-        <v>3159073.05</v>
+        <v>3674983.25</v>
       </c>
     </row>
     <row r="28">
@@ -928,118 +928,118 @@
         <v>0</v>
       </c>
       <c r="D28" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E28">
-        <v>0.99</v>
+        <v>-6.27</v>
       </c>
       <c r="F28">
-        <v>2.01</v>
+        <v>3159073.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-24</v>
+        <v>2026-06-29</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D29" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E29">
-        <v>-944671.87</v>
+        <v>0.99</v>
       </c>
       <c r="F29">
-        <v>3159079.32</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6864643 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B30" t="str">
         <v>2026-06-24</v>
       </c>
       <c r="C30">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D30" t="str">
         <v>Pesos</v>
       </c>
       <c r="E30">
-        <v>-1001112.31</v>
+        <v>-944671.87</v>
       </c>
       <c r="F30">
-        <v>4103751.19</v>
+        <v>3159079.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Comprobante de Pago / 1465742</v>
+        <v>Boleto / 6864642 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-22</v>
+        <v>2026-06-24</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D31" t="str">
         <v>Pesos</v>
       </c>
       <c r="E31">
-        <v>-50000</v>
+        <v>-1001112.31</v>
       </c>
       <c r="F31">
-        <v>5104863.5</v>
+        <v>4103751.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1465742</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-22</v>
       </c>
       <c r="C32">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="D32" t="str">
         <v>Pesos</v>
       </c>
       <c r="E32">
-        <v>2137654.07</v>
+        <v>-50000</v>
       </c>
       <c r="F32">
-        <v>5154863.5</v>
+        <v>5104863.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6446442 / VENTA / 0 / TRAN / $</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-11</v>
       </c>
       <c r="C33">
-        <v>879</v>
+        <v>540</v>
       </c>
       <c r="D33" t="str">
         <v>Pesos</v>
       </c>
       <c r="E33">
-        <v>820145.97</v>
+        <v>2137654.07</v>
       </c>
       <c r="F33">
-        <v>3017209.43</v>
+        <v>5154863.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 6339518 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B34" t="str">
         <v>2026-06-09</v>
@@ -1048,13 +1048,13 @@
         <v>879</v>
       </c>
       <c r="D34" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E34">
-        <v>-567.43</v>
+        <v>820145.97</v>
       </c>
       <c r="F34">
-        <v>11.75</v>
+        <v>3017209.43</v>
       </c>
     </row>
     <row r="35">
@@ -1065,124 +1065,124 @@
         <v>2026-06-09</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="D35" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E35">
-        <v>-20.4</v>
+        <v>-567.43</v>
       </c>
       <c r="F35">
-        <v>2197063.46</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6339517 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B36" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C36">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D36" t="str">
         <v>Pesos</v>
       </c>
       <c r="E36">
-        <v>1867138.55</v>
+        <v>-20.4</v>
       </c>
       <c r="F36">
-        <v>2197083.86</v>
+        <v>2197063.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Recibo de Cobro / 1530471</v>
+        <v>Boleto / 6339516 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D37" t="str">
         <v>Pesos</v>
       </c>
       <c r="E37">
-        <v>300000</v>
+        <v>1867138.55</v>
       </c>
       <c r="F37">
-        <v>329945.31</v>
+        <v>2197083.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
+        <v>Recibo de Cobro / 1530471</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C38">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="D38" t="str">
         <v>Pesos</v>
       </c>
       <c r="E38">
-        <v>-1996802.3</v>
+        <v>300000</v>
       </c>
       <c r="F38">
-        <v>29945.31</v>
+        <v>329945.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Recibo de Cobro / 1484184</v>
+        <v>Boleto / 6147294 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B39" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="D39" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E39">
-        <v>579.18</v>
+        <v>-1996802.3</v>
       </c>
       <c r="F39">
-        <v>579.18</v>
+        <v>29945.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Comprobante de Pago / 1167141</v>
+        <v>Recibo de Cobro / 1484184</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-05-13</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E40">
-        <v>-20000</v>
+        <v>579.18</v>
       </c>
       <c r="F40">
-        <v>2026747.61</v>
+        <v>579.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Comprobante de Pago / 1116351</v>
+        <v>Comprobante de Pago / 1167141</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1191,90 +1191,90 @@
         <v>Pesos</v>
       </c>
       <c r="E41">
-        <v>-100000</v>
+        <v>-20000</v>
       </c>
       <c r="F41">
-        <v>2046747.61</v>
+        <v>2026747.61</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
+        <v>Comprobante de Pago / 1116351</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-08</v>
       </c>
       <c r="C42">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="D42" t="str">
         <v>Pesos</v>
       </c>
       <c r="E42">
-        <v>-3174961.2</v>
+        <v>-100000</v>
       </c>
       <c r="F42">
-        <v>2146747.61</v>
+        <v>2046747.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Comprobante de Pago / 925746</v>
+        <v>Boleto / 4656488 / COMPRA / 0 / TRAN / $</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="D43" t="str">
         <v>Pesos</v>
       </c>
       <c r="E43">
-        <v>-160000</v>
+        <v>-3174961.2</v>
       </c>
       <c r="F43">
-        <v>5321708.81</v>
+        <v>2146747.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 925746</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="C44">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="D44" t="str">
         <v>Pesos</v>
       </c>
       <c r="E44">
-        <v>3896669.74</v>
+        <v>-160000</v>
       </c>
       <c r="F44">
-        <v>5481708.81</v>
+        <v>5321708.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 4018683 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B45" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="D45" t="str">
         <v>Pesos</v>
       </c>
       <c r="E45">
-        <v>-0.83</v>
+        <v>3896669.74</v>
       </c>
       <c r="F45">
-        <v>1585039.07</v>
+        <v>5481708.81</v>
       </c>
     </row>
     <row r="46">
@@ -1288,153 +1288,153 @@
         <v>0</v>
       </c>
       <c r="D46" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E46">
-        <v>0.14</v>
+        <v>-0.83</v>
       </c>
       <c r="F46">
-        <v>1.02</v>
+        <v>1585039.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Comprobante de Pago / 738461</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B47" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-06</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E47">
-        <v>-90000</v>
+        <v>0.14</v>
       </c>
       <c r="F47">
-        <v>1585039.9</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
+        <v>Comprobante de Pago / 738461</v>
       </c>
       <c r="B48" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C48">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D48" t="str">
         <v>Pesos</v>
       </c>
       <c r="E48">
-        <v>992035.79</v>
+        <v>-90000</v>
       </c>
       <c r="F48">
-        <v>1675039.9</v>
+        <v>1585039.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 3285058 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B49" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C49">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D49" t="str">
         <v>Pesos</v>
       </c>
       <c r="E49">
-        <v>1090257.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F49">
-        <v>683004.11</v>
+        <v>1675039.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3267920 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B50" t="str">
         <v>2026-03-18</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D50" t="str">
         <v>Pesos</v>
       </c>
       <c r="E50">
-        <v>-407253.05</v>
+        <v>1090257.16</v>
       </c>
       <c r="F50">
-        <v>-407253.05</v>
+        <v>683004.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Comprobante de Pago / 642036</v>
+        <v>Boleto / 3267919 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D51" t="str">
         <v>Pesos</v>
       </c>
       <c r="E51">
-        <v>-992034.79</v>
+        <v>-407253.05</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>-407253.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 642036</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C52">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D52" t="str">
         <v>Pesos</v>
       </c>
       <c r="E52">
-        <v>992035.79</v>
+        <v>-992034.79</v>
       </c>
       <c r="F52">
-        <v>992034.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 2923909 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-12-29</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D53" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E53">
-        <v>0.16</v>
+        <v>992035.79</v>
       </c>
       <c r="F53">
-        <v>0.88</v>
+        <v>992034.79</v>
       </c>
     </row>
     <row r="54">
@@ -1448,21 +1448,21 @@
         <v>0</v>
       </c>
       <c r="D54" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E54">
-        <v>-1</v>
+        <v>0.16</v>
       </c>
       <c r="F54">
-        <v>-1</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Comprobante de Pago / 2852932</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-11-13</v>
+        <v>2025-12-29</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1471,78 +1471,78 @@
         <v>Pesos</v>
       </c>
       <c r="E55">
-        <v>-11190.76</v>
+        <v>-1</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2852932</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-11-04</v>
+        <v>2025-11-13</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D56" t="str">
         <v>Pesos</v>
       </c>
       <c r="E56">
-        <v>-90093.05</v>
+        <v>-11190.76</v>
       </c>
       <c r="F56">
-        <v>11190.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Recibo de Cobro / 2884603</v>
+        <v>Boleto / 10971976 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-11-03</v>
+        <v>2025-11-04</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D57" t="str">
         <v>Pesos</v>
       </c>
       <c r="E57">
-        <v>50000</v>
+        <v>-90093.05</v>
       </c>
       <c r="F57">
-        <v>101283.81</v>
+        <v>11190.76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
+        <v>Recibo de Cobro / 2884603</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-10-22</v>
+        <v>2025-11-03</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D58" t="str">
         <v>Pesos</v>
       </c>
       <c r="E58">
-        <v>48024.29</v>
+        <v>50000</v>
       </c>
       <c r="F58">
-        <v>51283.81</v>
+        <v>101283.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 10343811 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-10-20</v>
+        <v>2025-10-22</v>
       </c>
       <c r="C59">
         <v>7</v>
@@ -1551,50 +1551,50 @@
         <v>Pesos</v>
       </c>
       <c r="E59">
-        <v>-46739.74</v>
+        <v>48024.29</v>
       </c>
       <c r="F59">
-        <v>3259.52</v>
+        <v>51283.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Recibo de Cobro / 2742989</v>
+        <v>Boleto / 10233181 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B60" t="str">
         <v>2025-10-20</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D60" t="str">
         <v>Pesos</v>
       </c>
       <c r="E60">
-        <v>50000</v>
+        <v>-46739.74</v>
       </c>
       <c r="F60">
-        <v>49999.26</v>
+        <v>3259.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Recibo de Cobro / 2742989</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-10-03</v>
+        <v>2025-10-20</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E61">
-        <v>0.12</v>
+        <v>50000</v>
       </c>
       <c r="F61">
-        <v>0.72</v>
+        <v>49999.26</v>
       </c>
     </row>
     <row r="62">
@@ -1608,21 +1608,21 @@
         <v>0</v>
       </c>
       <c r="D62" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E62">
-        <v>-0.74</v>
+        <v>0.12</v>
       </c>
       <c r="F62">
-        <v>-0.74</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Comprobante de Pago / 2317908</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-09-24</v>
+        <v>2025-10-03</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -1631,195 +1631,195 @@
         <v>Pesos</v>
       </c>
       <c r="E63">
-        <v>-6736.66</v>
+        <v>-0.74</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
+        <v>Comprobante de Pago / 2317908</v>
       </c>
       <c r="B64" t="str">
         <v>2025-09-24</v>
       </c>
       <c r="C64">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D64" t="str">
         <v>Pesos</v>
       </c>
       <c r="E64">
-        <v>-403777.1</v>
+        <v>-6736.66</v>
       </c>
       <c r="F64">
-        <v>6736.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9176501 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-09-22</v>
+        <v>2025-09-24</v>
       </c>
       <c r="C65">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D65" t="str">
         <v>Pesos</v>
       </c>
       <c r="E65">
-        <v>388789.81</v>
+        <v>-403777.1</v>
       </c>
       <c r="F65">
-        <v>410513.76</v>
+        <v>6736.66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 9060004 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B66" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C66">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D66" t="str">
         <v>Pesos</v>
       </c>
       <c r="E66">
-        <v>-1307333.32</v>
+        <v>388789.81</v>
       </c>
       <c r="F66">
-        <v>21723.95</v>
+        <v>410513.76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9058877 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B67" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C67">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="D67" t="str">
         <v>Pesos</v>
       </c>
       <c r="E67">
-        <v>999074.31</v>
+        <v>-1307333.32</v>
       </c>
       <c r="F67">
-        <v>1329057.27</v>
+        <v>21723.95</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9058876 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B68" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C68">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D68" t="str">
         <v>Pesos</v>
       </c>
       <c r="E68">
-        <v>236100.29</v>
+        <v>999074.31</v>
       </c>
       <c r="F68">
-        <v>329982.96</v>
+        <v>1329057.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
+        <v>Boleto / 9058875 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B69" t="str">
         <v>2025-09-22</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D69" t="str">
         <v>Pesos</v>
       </c>
       <c r="E69">
-        <v>93882.67</v>
+        <v>236100.29</v>
       </c>
       <c r="F69">
-        <v>93882.67</v>
+        <v>329982.96</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Comprobante de Pago / 2284129</v>
+        <v>Boleto / 9058874 / VENTA / 0 / BBAR / $</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-09-20</v>
+        <v>2025-09-22</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D70" t="str">
         <v>Pesos</v>
       </c>
       <c r="E70">
-        <v>-6165.47</v>
+        <v>93882.67</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>93882.67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2284129</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-09-18</v>
+        <v>2025-09-20</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71" t="str">
         <v>Pesos</v>
       </c>
       <c r="E71">
-        <v>-76616.13</v>
+        <v>-6165.47</v>
       </c>
       <c r="F71">
-        <v>6165.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8916689 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B72" t="str">
         <v>2025-09-18</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D72" t="str">
         <v>Pesos</v>
       </c>
       <c r="E72">
-        <v>-20136.94</v>
+        <v>-76616.13</v>
       </c>
       <c r="F72">
-        <v>82781.6</v>
+        <v>6165.47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 8916688 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B73" t="str">
         <v>2025-09-18</v>
@@ -1831,298 +1831,298 @@
         <v>Pesos</v>
       </c>
       <c r="E73">
-        <v>89518.34</v>
+        <v>-20136.94</v>
       </c>
       <c r="F73">
-        <v>102918.54</v>
+        <v>82781.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 8909679 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B74" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-18</v>
       </c>
       <c r="C74">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D74" t="str">
         <v>Pesos</v>
       </c>
       <c r="E74">
-        <v>138894.77</v>
+        <v>89518.34</v>
       </c>
       <c r="F74">
-        <v>13400.2</v>
+        <v>102918.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 8492245 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B75" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D75" t="str">
         <v>Pesos</v>
       </c>
       <c r="E75">
-        <v>-85739.5</v>
+        <v>138894.77</v>
       </c>
       <c r="F75">
-        <v>-125494.57</v>
+        <v>13400.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Comprobante de Pago / 2176779</v>
+        <v>Boleto / 8492244 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B76" t="str">
         <v>2025-09-09</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D76" t="str">
         <v>Pesos</v>
       </c>
       <c r="E76">
-        <v>-45869.67</v>
+        <v>-85739.5</v>
       </c>
       <c r="F76">
-        <v>-39755.07</v>
+        <v>-125494.57</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
+        <v>Comprobante de Pago / 2176779</v>
       </c>
       <c r="B77" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="C77">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D77" t="str">
         <v>Pesos</v>
       </c>
       <c r="E77">
-        <v>-952298.2</v>
+        <v>-45869.67</v>
       </c>
       <c r="F77">
-        <v>6114.6</v>
+        <v>-39755.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 8408805 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B78" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C78">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D78" t="str">
         <v>Pesos</v>
       </c>
       <c r="E78">
-        <v>-226481.32</v>
+        <v>-952298.2</v>
       </c>
       <c r="F78">
-        <v>958412.8</v>
+        <v>6114.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
+        <v>Boleto / 8408804 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B79" t="str">
         <v>2025-09-08</v>
       </c>
       <c r="C79">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D79" t="str">
         <v>Pesos</v>
       </c>
       <c r="E79">
-        <v>-491658.83</v>
+        <v>-226481.32</v>
       </c>
       <c r="F79">
-        <v>1184894.12</v>
+        <v>958412.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Comprobante de Pago / 2093390</v>
+        <v>Boleto / 8408803 / COMPRA / 0 / BBAR / $</v>
       </c>
       <c r="B80" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="D80" t="str">
         <v>Pesos</v>
       </c>
       <c r="E80">
-        <v>-14000</v>
+        <v>-491658.83</v>
       </c>
       <c r="F80">
-        <v>1676552.95</v>
+        <v>1184894.12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2093390</v>
       </c>
       <c r="B81" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-01</v>
       </c>
       <c r="C81">
-        <v>3447</v>
+        <v>0</v>
       </c>
       <c r="D81" t="str">
         <v>Pesos</v>
       </c>
       <c r="E81">
-        <v>2699870.67</v>
+        <v>-14000</v>
       </c>
       <c r="F81">
-        <v>1690552.95</v>
+        <v>1676552.95</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737109 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B82" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C82">
-        <v>413</v>
+        <v>3447</v>
       </c>
       <c r="D82" t="str">
         <v>Pesos</v>
       </c>
       <c r="E82">
-        <v>-4194203.97</v>
+        <v>2699870.67</v>
       </c>
       <c r="F82">
-        <v>-1009317.72</v>
+        <v>1690552.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 7737108 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B83" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C83">
-        <v>153</v>
+        <v>413</v>
       </c>
       <c r="D83" t="str">
         <v>Pesos</v>
       </c>
       <c r="E83">
-        <v>509153.55</v>
+        <v>-4194203.97</v>
       </c>
       <c r="F83">
-        <v>3184886.25</v>
+        <v>-1009317.72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 7737107 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B84" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C84">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="D84" t="str">
         <v>Pesos</v>
       </c>
       <c r="E84">
-        <v>777951.6</v>
+        <v>509153.55</v>
       </c>
       <c r="F84">
-        <v>2675732.7</v>
+        <v>3184886.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 7737106 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B85" t="str">
         <v>2025-08-25</v>
       </c>
       <c r="C85">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="D85" t="str">
         <v>Pesos</v>
       </c>
       <c r="E85">
-        <v>1314506.19</v>
+        <v>777951.6</v>
       </c>
       <c r="F85">
-        <v>1897781.1</v>
+        <v>2675732.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7737105 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B86" t="str">
-        <v>2025-08-18</v>
+        <v>2025-08-25</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="D86" t="str">
         <v>Pesos</v>
       </c>
       <c r="E86">
-        <v>-19758.9</v>
+        <v>1314506.19</v>
       </c>
       <c r="F86">
-        <v>583274.91</v>
+        <v>1897781.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Comprobante de Pago / 1961788</v>
+        <v>Boleto / 7429752 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B87" t="str">
         <v>2025-08-18</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" t="str">
         <v>Pesos</v>
       </c>
       <c r="E87">
-        <v>-20000</v>
+        <v>-19758.9</v>
       </c>
       <c r="F87">
-        <v>603033.81</v>
+        <v>583274.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Comprobante de Pago / 1961788</v>
       </c>
       <c r="B88" t="str">
-        <v>2025-08-12</v>
+        <v>2025-08-18</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2131,15 +2131,15 @@
         <v>Pesos</v>
       </c>
       <c r="E88">
-        <v>-338.57</v>
+        <v>-20000</v>
       </c>
       <c r="F88">
-        <v>623033.81</v>
+        <v>603033.81</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B89" t="str">
         <v>2025-08-12</v>
@@ -2151,610 +2151,610 @@
         <v>Pesos</v>
       </c>
       <c r="E89">
-        <v>4824.94</v>
+        <v>-338.57</v>
       </c>
       <c r="F89">
-        <v>623372.38</v>
+        <v>623033.81</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B90" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C90">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D90" t="str">
         <v>Pesos</v>
       </c>
       <c r="E90">
-        <v>-100004.21</v>
+        <v>4824.94</v>
       </c>
       <c r="F90">
-        <v>618547.44</v>
+        <v>623372.38</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 7236559 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B91" t="str">
         <v>2025-08-12</v>
       </c>
       <c r="C91">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D91" t="str">
         <v>Pesos</v>
       </c>
       <c r="E91">
-        <v>710418.57</v>
+        <v>-100004.21</v>
       </c>
       <c r="F91">
-        <v>718551.65</v>
+        <v>618547.44</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 7236558 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B92" t="str">
-        <v>2025-08-05</v>
+        <v>2025-08-12</v>
       </c>
       <c r="C92">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D92" t="str">
         <v>Pesos</v>
       </c>
       <c r="E92">
-        <v>-190965.71</v>
+        <v>710418.57</v>
       </c>
       <c r="F92">
-        <v>8133.08</v>
+        <v>718551.65</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6943451 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B93" t="str">
         <v>2025-08-05</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D93" t="str">
         <v>Pesos</v>
       </c>
       <c r="E93">
-        <v>182607.5</v>
+        <v>-190965.71</v>
       </c>
       <c r="F93">
-        <v>199098.79</v>
+        <v>8133.08</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
+        <v>Boleto / 6943450 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B94" t="str">
-        <v>2025-08-04</v>
+        <v>2025-08-05</v>
       </c>
       <c r="C94">
-        <v>2626</v>
+        <v>4</v>
       </c>
       <c r="D94" t="str">
         <v>Pesos</v>
       </c>
       <c r="E94">
-        <v>41762.85</v>
+        <v>182607.5</v>
       </c>
       <c r="F94">
-        <v>16491.29</v>
+        <v>199098.79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888336 / VENTA / 0 / TX28 / $</v>
       </c>
       <c r="B95" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C95">
-        <v>1848</v>
+        <v>2626</v>
       </c>
       <c r="D95" t="str">
         <v>Pesos</v>
       </c>
       <c r="E95">
-        <v>1490983.97</v>
+        <v>41762.85</v>
       </c>
       <c r="F95">
-        <v>-25271.56</v>
+        <v>16491.29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6888335 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B96" t="str">
         <v>2025-08-04</v>
       </c>
       <c r="C96">
-        <v>225</v>
+        <v>1848</v>
       </c>
       <c r="D96" t="str">
         <v>Pesos</v>
       </c>
       <c r="E96">
-        <v>-1521989.55</v>
+        <v>1490983.97</v>
       </c>
       <c r="F96">
-        <v>-1516255.53</v>
+        <v>-25271.56</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6888334 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B97" t="str">
-        <v>2025-07-30</v>
+        <v>2025-08-04</v>
       </c>
       <c r="C97">
-        <v>620</v>
+        <v>225</v>
       </c>
       <c r="D97" t="str">
         <v>Pesos</v>
       </c>
       <c r="E97">
-        <v>488389.62</v>
+        <v>-1521989.55</v>
       </c>
       <c r="F97">
-        <v>5734.02</v>
+        <v>-1516255.53</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699258 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B98" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C98">
-        <v>58</v>
+        <v>620</v>
       </c>
       <c r="D98" t="str">
         <v>Pesos</v>
       </c>
       <c r="E98">
-        <v>194738.35</v>
+        <v>488389.62</v>
       </c>
       <c r="F98">
-        <v>-482655.6</v>
+        <v>5734.02</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6699257 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B99" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C99">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="D99" t="str">
         <v>Pesos</v>
       </c>
       <c r="E99">
-        <v>-393010.51</v>
+        <v>194738.35</v>
       </c>
       <c r="F99">
-        <v>-677393.95</v>
+        <v>-482655.6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6699256 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B100" t="str">
         <v>2025-07-30</v>
       </c>
       <c r="C100">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="D100" t="str">
         <v>Pesos</v>
       </c>
       <c r="E100">
-        <v>-285344.68</v>
+        <v>-393010.51</v>
       </c>
       <c r="F100">
-        <v>-284383.44</v>
+        <v>-677393.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6699255 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B101" t="str">
-        <v>2025-07-29</v>
+        <v>2025-07-30</v>
       </c>
       <c r="C101">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D101" t="str">
         <v>Pesos</v>
       </c>
       <c r="E101">
-        <v>-87826.28</v>
+        <v>-285344.68</v>
       </c>
       <c r="F101">
-        <v>961.24</v>
+        <v>-284383.44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6634259 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B102" t="str">
-        <v>2025-07-28</v>
+        <v>2025-07-29</v>
       </c>
       <c r="C102">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D102" t="str">
         <v>Pesos</v>
       </c>
       <c r="E102">
-        <v>-133937.09</v>
+        <v>-87826.28</v>
       </c>
       <c r="F102">
-        <v>88787.52</v>
+        <v>961.24</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589037 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B103" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C103">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D103" t="str">
         <v>Pesos</v>
       </c>
       <c r="E103">
-        <v>94844.81</v>
+        <v>-133937.09</v>
       </c>
       <c r="F103">
-        <v>222724.61</v>
+        <v>88787.52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6589036 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B104" t="str">
         <v>2025-07-28</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D104" t="str">
         <v>Pesos</v>
       </c>
       <c r="E104">
-        <v>127879.8</v>
+        <v>94844.81</v>
       </c>
       <c r="F104">
-        <v>127879.8</v>
+        <v>222724.61</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6589035 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B105" t="str">
-        <v>2025-07-24</v>
+        <v>2025-07-28</v>
       </c>
       <c r="C105">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D105" t="str">
         <v>Pesos</v>
       </c>
       <c r="E105">
-        <v>88972.8</v>
+        <v>127879.8</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>127879.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Comprobante de Pago / 1761847</v>
+        <v>Boleto / 6478375 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B106" t="str">
         <v>2025-07-24</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D106" t="str">
         <v>Pesos</v>
       </c>
       <c r="E106">
-        <v>-89024.62</v>
+        <v>88972.8</v>
       </c>
       <c r="F106">
-        <v>-88972.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
+        <v>Comprobante de Pago / 1761847</v>
       </c>
       <c r="B107" t="str">
-        <v>2025-07-22</v>
+        <v>2025-07-24</v>
       </c>
       <c r="C107">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="D107" t="str">
         <v>Pesos</v>
       </c>
       <c r="E107">
-        <v>-3646.72</v>
+        <v>-89024.62</v>
       </c>
       <c r="F107">
-        <v>51.82</v>
+        <v>-88972.8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6367004 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B108" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C108">
-        <v>1984</v>
+        <v>235</v>
       </c>
       <c r="D108" t="str">
         <v>Pesos</v>
       </c>
       <c r="E108">
-        <v>-1482793.93</v>
+        <v>-3646.72</v>
       </c>
       <c r="F108">
-        <v>3698.54</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6367003 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B109" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C109">
-        <v>121</v>
+        <v>1984</v>
       </c>
       <c r="D109" t="str">
         <v>Pesos</v>
       </c>
       <c r="E109">
-        <v>-345815.98</v>
+        <v>-1482793.93</v>
       </c>
       <c r="F109">
-        <v>1486492.47</v>
+        <v>3698.54</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6367002 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B110" t="str">
         <v>2025-07-22</v>
       </c>
       <c r="C110">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D110" t="str">
         <v>Pesos</v>
       </c>
       <c r="E110">
-        <v>-354299.21</v>
+        <v>-345815.98</v>
       </c>
       <c r="F110">
-        <v>1832308.45</v>
+        <v>1486492.47</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6367001 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B111" t="str">
-        <v>2025-07-16</v>
+        <v>2025-07-22</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D111" t="str">
         <v>Pesos</v>
       </c>
       <c r="E111">
-        <v>2185800.13</v>
+        <v>-354299.21</v>
       </c>
       <c r="F111">
-        <v>2186607.66</v>
+        <v>1832308.45</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 1144170 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B112" t="str">
         <v>2025-07-16</v>
       </c>
       <c r="C112">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D112" t="str">
         <v>Pesos</v>
       </c>
       <c r="E112">
-        <v>-9888.53</v>
+        <v>2185800.13</v>
       </c>
       <c r="F112">
-        <v>807.53</v>
+        <v>2186607.66</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Boleto / 6167854 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B113" t="str">
-        <v>2025-07-14</v>
+        <v>2025-07-16</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D113" t="str">
         <v>Pesos</v>
       </c>
       <c r="E113">
-        <v>-1151507.11</v>
+        <v>-9888.53</v>
       </c>
       <c r="F113">
-        <v>10696.06</v>
+        <v>807.53</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1124110 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B114" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C114">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="D114" t="str">
         <v>Pesos</v>
       </c>
       <c r="E114">
-        <v>-950578.94</v>
+        <v>-1151507.11</v>
       </c>
       <c r="F114">
-        <v>1162203.17</v>
+        <v>10696.06</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6069007 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B115" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>1230</v>
       </c>
       <c r="D115" t="str">
         <v>Pesos</v>
       </c>
       <c r="E115">
-        <v>319945.64</v>
+        <v>-950578.94</v>
       </c>
       <c r="F115">
-        <v>2112782.11</v>
+        <v>1162203.17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6069006 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B116" t="str">
         <v>2025-07-14</v>
       </c>
       <c r="C116">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D116" t="str">
         <v>Pesos</v>
       </c>
       <c r="E116">
-        <v>641329.36</v>
+        <v>319945.64</v>
       </c>
       <c r="F116">
-        <v>1792836.47</v>
+        <v>2112782.11</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Comprobante de Pago / 1676382</v>
+        <v>Boleto / 6069005 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B117" t="str">
-        <v>2025-07-12</v>
+        <v>2025-07-14</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="D117" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E117">
-        <v>-0.48</v>
+        <v>641329.36</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1792836.47</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 1676382</v>
       </c>
       <c r="B118" t="str">
-        <v>2025-07-11</v>
+        <v>2025-07-12</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E118">
-        <v>1152116.72</v>
+        <v>-0.48</v>
       </c>
       <c r="F118">
-        <v>1151507.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
+        <v>Liquidación de Rescate / 1121638 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B119" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C119">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D119" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E119">
-        <v>-218.93</v>
+        <v>1152116.72</v>
       </c>
       <c r="F119">
-        <v>0.48</v>
+        <v>1151507.11</v>
       </c>
     </row>
     <row r="120">
@@ -2765,61 +2765,61 @@
         <v>2025-07-11</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D120" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E120">
-        <v>-609.62</v>
+        <v>-218.93</v>
       </c>
       <c r="F120">
-        <v>-609.61</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6004729 / COMPRA / 0 / PAMP / usd</v>
       </c>
       <c r="B121" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C121">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D121" t="str">
         <v>Pesos</v>
       </c>
       <c r="E121">
-        <v>-49685.47</v>
+        <v>-609.62</v>
       </c>
       <c r="F121">
-        <v>0.01</v>
+        <v>-609.61</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Comprobante de Pago / 1668056</v>
+        <v>Boleto / 6004728 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B122" t="str">
         <v>2025-07-11</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D122" t="str">
         <v>Pesos</v>
       </c>
       <c r="E122">
-        <v>-3923.46</v>
+        <v>-49685.47</v>
       </c>
       <c r="F122">
-        <v>49685.48</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Comprobante de Pago / 1668048</v>
+        <v>Comprobante de Pago / 1668056</v>
       </c>
       <c r="B123" t="str">
         <v>2025-07-11</v>
@@ -2828,18 +2828,18 @@
         <v>0</v>
       </c>
       <c r="D123" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E123">
-        <v>-4.52</v>
+        <v>-3923.46</v>
       </c>
       <c r="F123">
-        <v>219.41</v>
+        <v>49685.48</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Recibo de Cobro / 1772632</v>
+        <v>Comprobante de Pago / 1668048</v>
       </c>
       <c r="B124" t="str">
         <v>2025-07-11</v>
@@ -2848,33 +2848,33 @@
         <v>0</v>
       </c>
       <c r="D124" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E124">
-        <v>50000</v>
+        <v>-4.52</v>
       </c>
       <c r="F124">
-        <v>53608.94</v>
+        <v>219.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Recibo de Cobro / 1772632</v>
       </c>
       <c r="B125" t="str">
-        <v>2025-07-10</v>
+        <v>2025-07-11</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E125">
-        <v>223.91</v>
+        <v>50000</v>
       </c>
       <c r="F125">
-        <v>223.93</v>
+        <v>53608.94</v>
       </c>
     </row>
     <row r="126">
@@ -2888,21 +2888,21 @@
         <v>0</v>
       </c>
       <c r="D126" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E126">
-        <v>-5.65</v>
+        <v>223.91</v>
       </c>
       <c r="F126">
-        <v>3608.94</v>
+        <v>223.93</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B127" t="str">
-        <v>2025-06-11</v>
+        <v>2025-07-10</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -2911,15 +2911,15 @@
         <v>Pesos</v>
       </c>
       <c r="E127">
-        <v>-552.42</v>
+        <v>-5.65</v>
       </c>
       <c r="F127">
-        <v>3614.59</v>
+        <v>3608.94</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Dividendo en efectivo / TGSU2</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - TGSU2</v>
       </c>
       <c r="B128" t="str">
         <v>2025-06-11</v>
@@ -2931,55 +2931,55 @@
         <v>Pesos</v>
       </c>
       <c r="E128">
-        <v>3975.67</v>
+        <v>-552.42</v>
       </c>
       <c r="F128">
-        <v>4167.01</v>
+        <v>3614.59</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
+        <v>Dividendo en efectivo / TGSU2</v>
       </c>
       <c r="B129" t="str">
-        <v>2025-06-09</v>
+        <v>2025-06-11</v>
       </c>
       <c r="C129">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="D129" t="str">
         <v>Pesos</v>
       </c>
       <c r="E129">
-        <v>-16502.47</v>
+        <v>3975.67</v>
       </c>
       <c r="F129">
-        <v>191.34</v>
+        <v>4167.01</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Boleto / 5072207 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B130" t="str">
-        <v>2025-05-15</v>
+        <v>2025-06-09</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="D130" t="str">
         <v>Pesos</v>
       </c>
       <c r="E130">
-        <v>-958.17</v>
+        <v>-16502.47</v>
       </c>
       <c r="F130">
-        <v>16693.81</v>
+        <v>191.34</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B131" t="str">
         <v>2025-05-15</v>
@@ -2991,18 +2991,18 @@
         <v>Pesos</v>
       </c>
       <c r="E131">
-        <v>13655.11</v>
+        <v>-958.17</v>
       </c>
       <c r="F131">
-        <v>17651.98</v>
+        <v>16693.81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Renta y Amortización / TX28</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B132" t="str">
-        <v>2025-05-09</v>
+        <v>2025-05-15</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3011,78 +3011,78 @@
         <v>Pesos</v>
       </c>
       <c r="E132">
-        <v>3718.21</v>
+        <v>13655.11</v>
       </c>
       <c r="F132">
-        <v>3996.87</v>
+        <v>17651.98</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
+        <v>Renta y Amortización / TX28</v>
       </c>
       <c r="B133" t="str">
-        <v>2025-04-25</v>
+        <v>2025-05-09</v>
       </c>
       <c r="C133">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="D133" t="str">
         <v>Pesos</v>
       </c>
       <c r="E133">
-        <v>-24260.75</v>
+        <v>3718.21</v>
       </c>
       <c r="F133">
-        <v>278.66</v>
+        <v>3996.87</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3867748 / COMPRA / 0 / TX28 / $</v>
       </c>
       <c r="B134" t="str">
         <v>2025-04-25</v>
       </c>
       <c r="C134">
-        <v>25</v>
+        <v>1359</v>
       </c>
       <c r="D134" t="str">
         <v>Pesos</v>
       </c>
       <c r="E134">
-        <v>-975460.59</v>
+        <v>-24260.75</v>
       </c>
       <c r="F134">
-        <v>24539.41</v>
+        <v>278.66</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3867747 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B135" t="str">
-        <v>2025-04-24</v>
+        <v>2025-04-25</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D135" t="str">
         <v>Pesos</v>
       </c>
       <c r="E135">
-        <v>1000000</v>
+        <v>-975460.59</v>
       </c>
       <c r="F135">
-        <v>1000000</v>
+        <v>24539.41</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
+        <v>Liquidación de Rescate / 668674 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B136" t="str">
-        <v>2025-04-21</v>
+        <v>2025-04-24</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3091,18 +3091,18 @@
         <v>Pesos</v>
       </c>
       <c r="E136">
-        <v>-999993.87</v>
+        <v>1000000</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Suscripción / 637352 / BALANZ RENTA FIJA PUBLICA FCI A</v>
       </c>
       <c r="B137" t="str">
-        <v>2025-04-16</v>
+        <v>2025-04-21</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3111,30 +3111,30 @@
         <v>Pesos</v>
       </c>
       <c r="E137">
-        <v>1000000</v>
+        <v>-999993.87</v>
       </c>
       <c r="F137">
-        <v>999993.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
+        <v>Liquidación de Rescate / 624221 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B138" t="str">
-        <v>2025-04-15</v>
+        <v>2025-04-16</v>
       </c>
       <c r="C138">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="D138" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E138">
-        <v>-206.02</v>
+        <v>1000000</v>
       </c>
       <c r="F138">
-        <v>0.02</v>
+        <v>999993.87</v>
       </c>
     </row>
     <row r="139">
@@ -3145,21 +3145,21 @@
         <v>2025-04-15</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="D139" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E139">
-        <v>-6.13</v>
+        <v>-206.02</v>
       </c>
       <c r="F139">
-        <v>-6.13</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Comprobante de Pago / 1061406</v>
+        <v>Boleto / 3591042 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B140" t="str">
         <v>2025-04-15</v>
@@ -3168,18 +3168,18 @@
         <v>0</v>
       </c>
       <c r="D140" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E140">
-        <v>-2.85</v>
+        <v>-6.13</v>
       </c>
       <c r="F140">
-        <v>206.04</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Comprobante de Pago / 1061395</v>
+        <v>Comprobante de Pago / 1061406</v>
       </c>
       <c r="B141" t="str">
         <v>2025-04-15</v>
@@ -3188,33 +3188,33 @@
         <v>0</v>
       </c>
       <c r="D141" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E141">
-        <v>-2526.78</v>
+        <v>-2.85</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>206.04</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
+        <v>Comprobante de Pago / 1061395</v>
       </c>
       <c r="B142" t="str">
-        <v>2025-04-14</v>
+        <v>2025-04-15</v>
       </c>
       <c r="C142">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D142" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E142">
-        <v>208.88</v>
+        <v>-2526.78</v>
       </c>
       <c r="F142">
-        <v>208.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3225,324 +3225,324 @@
         <v>2025-04-14</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="D143" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E143">
-        <v>-5.66</v>
+        <v>208.88</v>
       </c>
       <c r="F143">
-        <v>2526.78</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 3532875 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B144" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C144">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="D144" t="str">
         <v>Pesos</v>
       </c>
       <c r="E144">
-        <v>-257928.71</v>
+        <v>-5.66</v>
       </c>
       <c r="F144">
-        <v>2532.44</v>
+        <v>2526.78</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 3532874 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B145" t="str">
         <v>2025-04-14</v>
       </c>
       <c r="C145">
-        <v>6</v>
+        <v>320</v>
       </c>
       <c r="D145" t="str">
         <v>Pesos</v>
       </c>
       <c r="E145">
-        <v>248438.89</v>
+        <v>-257928.71</v>
       </c>
       <c r="F145">
-        <v>260461.15</v>
+        <v>2532.44</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Boleto / 3532873 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B146" t="str">
-        <v>2025-04-08</v>
+        <v>2025-04-14</v>
       </c>
       <c r="C146">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D146" t="str">
         <v>Pesos</v>
       </c>
       <c r="E146">
-        <v>-98040.09</v>
+        <v>248438.89</v>
       </c>
       <c r="F146">
-        <v>12022.26</v>
+        <v>260461.15</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 3368832 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B147" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C147">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D147" t="str">
         <v>Pesos</v>
       </c>
       <c r="E147">
-        <v>-486646.45</v>
+        <v>-98040.09</v>
       </c>
       <c r="F147">
-        <v>110062.35</v>
+        <v>12022.26</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 3333333 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B148" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C148">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D148" t="str">
         <v>Pesos</v>
       </c>
       <c r="E148">
-        <v>-93664.38</v>
+        <v>-486646.45</v>
       </c>
       <c r="F148">
-        <v>596708.8</v>
+        <v>110062.35</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 3333332 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B149" t="str">
         <v>2025-04-08</v>
       </c>
       <c r="C149">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="D149" t="str">
         <v>Pesos</v>
       </c>
       <c r="E149">
-        <v>-309626.82</v>
+        <v>-93664.38</v>
       </c>
       <c r="F149">
-        <v>690373.18</v>
+        <v>596708.8</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3333331 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B150" t="str">
-        <v>2025-04-07</v>
+        <v>2025-04-08</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D150" t="str">
         <v>Pesos</v>
       </c>
       <c r="E150">
-        <v>1000000</v>
+        <v>-309626.82</v>
       </c>
       <c r="F150">
-        <v>1000000</v>
+        <v>690373.18</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
+        <v>Liquidación de Rescate / 570913 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B151" t="str">
-        <v>2025-04-04</v>
+        <v>2025-04-07</v>
       </c>
       <c r="C151">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D151" t="str">
         <v>Pesos</v>
       </c>
       <c r="E151">
-        <v>292856.94</v>
+        <v>1000000</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Comprobante de Pago / 945180</v>
+        <v>Boleto / 3198439 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B152" t="str">
         <v>2025-04-04</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="D152" t="str">
         <v>Pesos</v>
       </c>
       <c r="E152">
-        <v>-292856.9</v>
+        <v>292856.94</v>
       </c>
       <c r="F152">
-        <v>-292856.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 945180</v>
       </c>
       <c r="B153" t="str">
-        <v>2025-03-27</v>
+        <v>2025-04-04</v>
       </c>
       <c r="C153">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D153" t="str">
         <v>Pesos</v>
       </c>
       <c r="E153">
-        <v>58913.7</v>
+        <v>-292856.9</v>
       </c>
       <c r="F153">
-        <v>-0.04</v>
+        <v>-292856.94</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Comprobante de Pago / 868926</v>
+        <v>Boleto / 2920435 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B154" t="str">
         <v>2025-03-27</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D154" t="str">
         <v>Pesos</v>
       </c>
       <c r="E154">
-        <v>-58913.74</v>
+        <v>58913.7</v>
       </c>
       <c r="F154">
-        <v>-58913.74</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 868926</v>
       </c>
       <c r="B155" t="str">
-        <v>2025-03-20</v>
+        <v>2025-03-27</v>
       </c>
       <c r="C155">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D155" t="str">
         <v>Pesos</v>
       </c>
       <c r="E155">
-        <v>39165.79</v>
+        <v>-58913.74</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>-58913.74</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Comprobante de Pago / 814860</v>
+        <v>Boleto / 2743786 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B156" t="str">
         <v>2025-03-20</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D156" t="str">
         <v>Pesos</v>
       </c>
       <c r="E156">
-        <v>-39165.79</v>
+        <v>39165.79</v>
       </c>
       <c r="F156">
-        <v>-39165.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 814860</v>
       </c>
       <c r="B157" t="str">
-        <v>2025-03-05</v>
+        <v>2025-03-20</v>
       </c>
       <c r="C157">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D157" t="str">
         <v>Pesos</v>
       </c>
       <c r="E157">
-        <v>48845.52</v>
+        <v>-39165.79</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>-39165.79</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Comprobante de Pago / 636155</v>
+        <v>Boleto / 2184640 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B158" t="str">
         <v>2025-03-05</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D158" t="str">
         <v>Pesos</v>
       </c>
       <c r="E158">
-        <v>-48845.53</v>
+        <v>48845.52</v>
       </c>
       <c r="F158">
-        <v>-48845.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Comprobante de Pago / 636155</v>
       </c>
       <c r="B159" t="str">
-        <v>2025-02-13</v>
+        <v>2025-03-05</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3551,58 +3551,58 @@
         <v>Pesos</v>
       </c>
       <c r="E159">
-        <v>-2208405.65</v>
+        <v>-48845.53</v>
       </c>
       <c r="F159">
-        <v>0.01</v>
+        <v>-48845.52</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 287358 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B160" t="str">
-        <v>2025-02-12</v>
+        <v>2025-02-13</v>
       </c>
       <c r="C160">
-        <v>1921</v>
+        <v>0</v>
       </c>
       <c r="D160" t="str">
         <v>Pesos</v>
       </c>
       <c r="E160">
-        <v>-1490594.34</v>
+        <v>-2208405.65</v>
       </c>
       <c r="F160">
-        <v>2208405.66</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Recibo de Cobro / 513307</v>
+        <v>Boleto / 1570287 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B161" t="str">
         <v>2025-02-12</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1921</v>
       </c>
       <c r="D161" t="str">
         <v>Pesos</v>
       </c>
       <c r="E161">
-        <v>149000</v>
+        <v>-1490594.34</v>
       </c>
       <c r="F161">
-        <v>3699000</v>
+        <v>2208405.66</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Comprobante de Pago / 451447</v>
+        <v>Recibo de Cobro / 513307</v>
       </c>
       <c r="B162" t="str">
-        <v>2025-02-11</v>
+        <v>2025-02-12</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3611,18 +3611,18 @@
         <v>Pesos</v>
       </c>
       <c r="E162">
-        <v>-300000</v>
+        <v>149000</v>
       </c>
       <c r="F162">
-        <v>3550000</v>
+        <v>3699000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Comprobante de Pago / 422123</v>
+        <v>Comprobante de Pago / 451447</v>
       </c>
       <c r="B163" t="str">
-        <v>2025-02-10</v>
+        <v>2025-02-11</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3631,18 +3631,18 @@
         <v>Pesos</v>
       </c>
       <c r="E163">
-        <v>-150000</v>
+        <v>-300000</v>
       </c>
       <c r="F163">
-        <v>3850000</v>
+        <v>3550000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Recibo de Cobro / 392207</v>
+        <v>Comprobante de Pago / 422123</v>
       </c>
       <c r="B164" t="str">
-        <v>2025-02-03</v>
+        <v>2025-02-10</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3651,15 +3651,15 @@
         <v>Pesos</v>
       </c>
       <c r="E164">
-        <v>2000000</v>
+        <v>-150000</v>
       </c>
       <c r="F164">
-        <v>4000000</v>
+        <v>3850000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Recibo de Cobro / 392198</v>
+        <v>Recibo de Cobro / 392207</v>
       </c>
       <c r="B165" t="str">
         <v>2025-02-03</v>
@@ -3674,15 +3674,15 @@
         <v>2000000</v>
       </c>
       <c r="F165">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 392198</v>
       </c>
       <c r="B166" t="str">
-        <v>2025-01-24</v>
+        <v>2025-02-03</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3691,18 +3691,18 @@
         <v>Pesos</v>
       </c>
       <c r="E166">
-        <v>-284993.55</v>
+        <v>2000000</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Recibo de Cobro / 259074</v>
+        <v>Liquidación de Suscripción / 162023 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B167" t="str">
-        <v>2025-01-21</v>
+        <v>2025-01-24</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3711,30 +3711,30 @@
         <v>Pesos</v>
       </c>
       <c r="E167">
-        <v>285000</v>
+        <v>-284993.55</v>
       </c>
       <c r="F167">
-        <v>284993.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
+        <v>Recibo de Cobro / 259074</v>
       </c>
       <c r="B168" t="str">
         <v>2025-01-21</v>
       </c>
       <c r="C168">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="D168" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E168">
-        <v>244.89</v>
+        <v>285000</v>
       </c>
       <c r="F168">
-        <v>0.01</v>
+        <v>284993.55</v>
       </c>
     </row>
     <row r="169">
@@ -3745,21 +3745,21 @@
         <v>2025-01-21</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="D169" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E169">
-        <v>-6.45</v>
+        <v>244.89</v>
       </c>
       <c r="F169">
-        <v>-6.45</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comprobante de Pago / 229359</v>
+        <v>Boleto / 753201 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B170" t="str">
         <v>2025-01-21</v>
@@ -3768,61 +3768,61 @@
         <v>0</v>
       </c>
       <c r="D170" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E170">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
       <c r="F170">
-        <v>-244.88</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
+        <v>Comprobante de Pago / 229359</v>
       </c>
       <c r="B171" t="str">
-        <v>2025-01-17</v>
+        <v>2025-01-21</v>
       </c>
       <c r="C171">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D171" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E171">
-        <v>164237.44</v>
+        <v>-244.88</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>-244.88</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Comprobante de Pago / 195368</v>
+        <v>Boleto / 649634 / VENTA / 0 / MELI / $</v>
       </c>
       <c r="B172" t="str">
         <v>2025-01-17</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D172" t="str">
         <v>Pesos</v>
       </c>
       <c r="E172">
-        <v>-164237.44</v>
+        <v>164237.44</v>
       </c>
       <c r="F172">
-        <v>-164237.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Comprobante de Pago / 128971</v>
+        <v>Comprobante de Pago / 195368</v>
       </c>
       <c r="B173" t="str">
-        <v>2025-01-11</v>
+        <v>2025-01-17</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3831,15 +3831,15 @@
         <v>Pesos</v>
       </c>
       <c r="E173">
-        <v>-1858.46</v>
+        <v>-164237.44</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>-164237.44</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Comprobante de Pago / 128969</v>
+        <v>Comprobante de Pago / 128971</v>
       </c>
       <c r="B174" t="str">
         <v>2025-01-11</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="D174" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E174">
-        <v>-1.67</v>
+        <v>-1858.46</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -3859,27 +3859,27 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 128969</v>
       </c>
       <c r="B175" t="str">
-        <v>2025-01-09</v>
+        <v>2025-01-11</v>
       </c>
       <c r="C175">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="D175" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E175">
-        <v>115257.86</v>
+        <v>-1.67</v>
       </c>
       <c r="F175">
-        <v>1858.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
+        <v>Boleto / 328930 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B176" t="str">
         <v>2025-01-09</v>
@@ -3888,13 +3888,13 @@
         <v>145</v>
       </c>
       <c r="D176" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E176">
-        <v>-100.23</v>
+        <v>115257.86</v>
       </c>
       <c r="F176">
-        <v>1.67</v>
+        <v>1858.46</v>
       </c>
     </row>
     <row r="177">
@@ -3905,56 +3905,56 @@
         <v>2025-01-09</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D177" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E177">
-        <v>-2.58</v>
+        <v>-100.23</v>
       </c>
       <c r="F177">
-        <v>-113399.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 328929 / COMPRA / 0 / AL30 / usd</v>
       </c>
       <c r="B178" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C178">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="D178" t="str">
         <v>Pesos</v>
       </c>
       <c r="E178">
-        <v>-113394.51</v>
+        <v>-2.58</v>
       </c>
       <c r="F178">
-        <v>-113396.82</v>
+        <v>-113399.4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Boleto / 328928 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B179" t="str">
         <v>2025-01-09</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D179" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E179">
-        <v>101.9</v>
+        <v>-113394.51</v>
       </c>
       <c r="F179">
-        <v>101.9</v>
+        <v>-113396.82</v>
       </c>
     </row>
     <row r="180">
@@ -3968,21 +3968,21 @@
         <v>0</v>
       </c>
       <c r="D180" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E180">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
       <c r="F180">
-        <v>-2.31</v>
+        <v>101.9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B181" t="str">
-        <v>2025-01-07</v>
+        <v>2025-01-09</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3991,18 +3991,18 @@
         <v>Pesos</v>
       </c>
       <c r="E181">
-        <v>-134999.75</v>
+        <v>-2.31</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Recibo de Cobro / 70445</v>
+        <v>Liquidación de Suscripción / 49895 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B182" t="str">
-        <v>2025-01-06</v>
+        <v>2025-01-07</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4011,18 +4011,18 @@
         <v>Pesos</v>
       </c>
       <c r="E182">
-        <v>135000</v>
+        <v>-134999.75</v>
       </c>
       <c r="F182">
-        <v>134999.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 70445</v>
       </c>
       <c r="B183" t="str">
-        <v>2024-12-26</v>
+        <v>2025-01-06</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4031,15 +4031,15 @@
         <v>Pesos</v>
       </c>
       <c r="E183">
-        <v>-57777.54</v>
+        <v>135000</v>
       </c>
       <c r="F183">
-        <v>-0.25</v>
+        <v>134999.75</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Comprobante de Pago / 3498761</v>
+        <v>Liquidación de Suscripción / 2296477 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B184" t="str">
         <v>2024-12-26</v>
@@ -4048,33 +4048,33 @@
         <v>0</v>
       </c>
       <c r="D184" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E184">
-        <v>-1.01</v>
+        <v>-57777.54</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
+        <v>Comprobante de Pago / 3498761</v>
       </c>
       <c r="B185" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D185" t="str">
         <v>Dólares</v>
       </c>
       <c r="E185">
-        <v>1.01</v>
+        <v>-1.01</v>
       </c>
       <c r="F185">
-        <v>1.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -4085,176 +4085,176 @@
         <v>2024-12-26</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D186" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E186">
-        <v>-0.03</v>
+        <v>1.01</v>
       </c>
       <c r="F186">
-        <v>57777.29</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
+        <v>Boleto / 11615466 / VENTA / 0 / TTC7O / usd</v>
       </c>
       <c r="B187" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D187" t="str">
         <v>Pesos</v>
       </c>
       <c r="E187">
-        <v>27372.9</v>
+        <v>-0.03</v>
       </c>
       <c r="F187">
-        <v>57777.32</v>
+        <v>57777.29</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
+        <v>Boleto / 11615465 / VENTA / 0 / NVS / $</v>
       </c>
       <c r="B188" t="str">
         <v>2024-12-26</v>
       </c>
       <c r="C188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D188" t="str">
         <v>Pesos</v>
       </c>
       <c r="E188">
-        <v>29356.45</v>
+        <v>27372.9</v>
       </c>
       <c r="F188">
-        <v>30404.42</v>
+        <v>57777.32</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 11615464 / VENTA / 0 / KO / $</v>
       </c>
       <c r="B189" t="str">
-        <v>2024-12-18</v>
+        <v>2024-12-26</v>
       </c>
       <c r="C189">
-        <v>299</v>
+        <v>2</v>
       </c>
       <c r="D189" t="str">
         <v>Pesos</v>
       </c>
       <c r="E189">
-        <v>-255135.69</v>
+        <v>29356.45</v>
       </c>
       <c r="F189">
-        <v>1047.97</v>
+        <v>30404.42</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 11355097 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B190" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C190">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="D190" t="str">
         <v>Pesos</v>
       </c>
       <c r="E190">
-        <v>65556.13</v>
+        <v>-255135.69</v>
       </c>
       <c r="F190">
-        <v>256183.66</v>
+        <v>1047.97</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 11355096 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B191" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C191">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D191" t="str">
         <v>Pesos</v>
       </c>
       <c r="E191">
-        <v>58613.72</v>
+        <v>65556.13</v>
       </c>
       <c r="F191">
-        <v>190627.53</v>
+        <v>256183.66</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
+        <v>Boleto / 11355095 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B192" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C192">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D192" t="str">
         <v>Pesos</v>
       </c>
       <c r="E192">
-        <v>69622.4</v>
+        <v>58613.72</v>
       </c>
       <c r="F192">
-        <v>132013.81</v>
+        <v>190627.53</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 11355094 / VENTA / 0 / MSFT / $</v>
       </c>
       <c r="B193" t="str">
         <v>2024-12-18</v>
       </c>
       <c r="C193">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D193" t="str">
         <v>Pesos</v>
       </c>
       <c r="E193">
-        <v>62392.37</v>
+        <v>69622.4</v>
       </c>
       <c r="F193">
-        <v>62391.41</v>
+        <v>132013.81</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Boleto / 11355093 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B194" t="str">
-        <v>2024-12-17</v>
+        <v>2024-12-18</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D194" t="str">
         <v>Pesos</v>
       </c>
       <c r="E194">
-        <v>-0.53</v>
+        <v>62392.37</v>
       </c>
       <c r="F194">
-        <v>-0.96</v>
+        <v>62391.41</v>
       </c>
     </row>
     <row r="195">
@@ -4268,18 +4268,18 @@
         <v>0</v>
       </c>
       <c r="D195" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E195">
-        <v>0.12</v>
+        <v>-0.53</v>
       </c>
       <c r="F195">
-        <v>0.6</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B196" t="str">
         <v>2024-12-17</v>
@@ -4288,13 +4288,13 @@
         <v>0</v>
       </c>
       <c r="D196" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E196">
-        <v>-0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F196">
-        <v>-0.43</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="197">
@@ -4308,33 +4308,33 @@
         <v>0</v>
       </c>
       <c r="D197" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E197">
-        <v>0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F197">
-        <v>0.48</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B198" t="str">
-        <v>2024-12-13</v>
+        <v>2024-12-17</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E198">
-        <v>-0.3</v>
+        <v>0.03</v>
       </c>
       <c r="F198">
-        <v>-0.3</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="199">
@@ -4348,293 +4348,293 @@
         <v>0</v>
       </c>
       <c r="D199" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E199">
-        <v>0.07</v>
+        <v>-0.3</v>
       </c>
       <c r="F199">
-        <v>0.45</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B200" t="str">
-        <v>2024-12-12</v>
+        <v>2024-12-13</v>
       </c>
       <c r="C200">
         <v>0</v>
       </c>
       <c r="D200" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E200">
-        <v>-103588.95</v>
+        <v>0.07</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
+        <v>Liquidación de Suscripción / 2211944 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B201" t="str">
-        <v>2024-12-06</v>
+        <v>2024-12-12</v>
       </c>
       <c r="C201">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D201" t="str">
         <v>Pesos</v>
       </c>
       <c r="E201">
-        <v>102379.42</v>
+        <v>-103588.95</v>
       </c>
       <c r="F201">
-        <v>103588.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10957376 / VENTA / 1 / TTC8O / $</v>
       </c>
       <c r="B202" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C202">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="D202" t="str">
         <v>Pesos</v>
       </c>
       <c r="E202">
-        <v>-117184.31</v>
+        <v>102379.42</v>
       </c>
       <c r="F202">
-        <v>1209.53</v>
+        <v>103588.95</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
+        <v>Boleto / 10933763 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B203" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C203">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="D203" t="str">
         <v>Pesos</v>
       </c>
       <c r="E203">
-        <v>27546.46</v>
+        <v>-117184.31</v>
       </c>
       <c r="F203">
-        <v>118393.84</v>
+        <v>1209.53</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 10933762 / VENTA / 0 / META / $</v>
       </c>
       <c r="B204" t="str">
         <v>2024-12-06</v>
       </c>
       <c r="C204">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D204" t="str">
         <v>Pesos</v>
       </c>
       <c r="E204">
-        <v>89904.13</v>
+        <v>27546.46</v>
       </c>
       <c r="F204">
-        <v>90847.38</v>
+        <v>118393.84</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10933761 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B205" t="str">
-        <v>2024-11-27</v>
+        <v>2024-12-06</v>
       </c>
       <c r="C205">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="D205" t="str">
         <v>Pesos</v>
       </c>
       <c r="E205">
-        <v>-91403.91</v>
+        <v>89904.13</v>
       </c>
       <c r="F205">
-        <v>943.25</v>
+        <v>90847.38</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
+        <v>Boleto / 10560172 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B206" t="str">
         <v>2024-11-27</v>
       </c>
       <c r="C206">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D206" t="str">
         <v>Pesos</v>
       </c>
       <c r="E206">
-        <v>91674.44</v>
+        <v>-91403.91</v>
       </c>
       <c r="F206">
-        <v>92347.16</v>
+        <v>943.25</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 10560171 / VENTA / 0 / ALUA / $</v>
       </c>
       <c r="B207" t="str">
-        <v>2024-11-25</v>
+        <v>2024-11-27</v>
       </c>
       <c r="C207">
-        <v>185</v>
+        <v>95</v>
       </c>
       <c r="D207" t="str">
         <v>Pesos</v>
       </c>
       <c r="E207">
-        <v>140157.43</v>
+        <v>91674.44</v>
       </c>
       <c r="F207">
-        <v>672.72</v>
+        <v>92347.16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Comprobante de Pago / 3169919</v>
+        <v>Boleto / 10455319 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B208" t="str">
         <v>2024-11-25</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D208" t="str">
         <v>Pesos</v>
       </c>
       <c r="E208">
-        <v>-140000</v>
+        <v>140157.43</v>
       </c>
       <c r="F208">
-        <v>-139484.71</v>
+        <v>672.72</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 3169919</v>
       </c>
       <c r="B209" t="str">
-        <v>2024-11-21</v>
+        <v>2024-11-25</v>
       </c>
       <c r="C209">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="D209" t="str">
         <v>Pesos</v>
       </c>
       <c r="E209">
-        <v>-66912.23</v>
+        <v>-140000</v>
       </c>
       <c r="F209">
-        <v>515.29</v>
+        <v>-139484.71</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 10359692 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B210" t="str">
         <v>2024-11-21</v>
       </c>
       <c r="C210">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D210" t="str">
         <v>Pesos</v>
       </c>
       <c r="E210">
-        <v>66349.55</v>
+        <v>-66912.23</v>
       </c>
       <c r="F210">
-        <v>67427.52</v>
+        <v>515.29</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 10359691 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B211" t="str">
-        <v>2024-11-20</v>
+        <v>2024-11-21</v>
       </c>
       <c r="C211">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="D211" t="str">
         <v>Pesos</v>
       </c>
       <c r="E211">
-        <v>-73882.48</v>
+        <v>66349.55</v>
       </c>
       <c r="F211">
-        <v>1077.97</v>
+        <v>67427.52</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
+        <v>Boleto / 10313557 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B212" t="str">
         <v>2024-11-20</v>
       </c>
       <c r="C212">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="D212" t="str">
         <v>Pesos</v>
       </c>
       <c r="E212">
-        <v>73936.61</v>
+        <v>-73882.48</v>
       </c>
       <c r="F212">
-        <v>74960.45</v>
+        <v>1077.97</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 10313556 / VENTA / 0 / TSLA / $</v>
       </c>
       <c r="B213" t="str">
-        <v>2024-11-15</v>
+        <v>2024-11-20</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D213" t="str">
         <v>Pesos</v>
       </c>
       <c r="E213">
-        <v>-0.22</v>
+        <v>73936.61</v>
       </c>
       <c r="F213">
-        <v>1023.84</v>
+        <v>74960.45</v>
       </c>
     </row>
     <row r="214">
@@ -4648,313 +4648,313 @@
         <v>0</v>
       </c>
       <c r="D214" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E214">
-        <v>0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="F214">
-        <v>0.38</v>
+        <v>1023.84</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B215" t="str">
-        <v>2024-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C215">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="D215" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E215">
-        <v>-139049.36</v>
+        <v>0.05</v>
       </c>
       <c r="F215">
-        <v>1024.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 9674950 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B216" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C216">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="D216" t="str">
         <v>Pesos</v>
       </c>
       <c r="E216">
-        <v>-52427.86</v>
+        <v>-139049.36</v>
       </c>
       <c r="F216">
-        <v>140073.42</v>
+        <v>1024.06</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
+        <v>Boleto / 9674949 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B217" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C217">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D217" t="str">
         <v>Pesos</v>
       </c>
       <c r="E217">
-        <v>31736.7</v>
+        <v>-52427.86</v>
       </c>
       <c r="F217">
-        <v>192501.28</v>
+        <v>140073.42</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9672506 / VENTA / 0 / AMZN / $</v>
       </c>
       <c r="B218" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C218">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="D218" t="str">
         <v>Pesos</v>
       </c>
       <c r="E218">
-        <v>99970.62</v>
+        <v>31736.7</v>
       </c>
       <c r="F218">
-        <v>160764.58</v>
+        <v>192501.28</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 9672505 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B219" t="str">
         <v>2024-11-01</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="D219" t="str">
         <v>Pesos</v>
       </c>
       <c r="E219">
-        <v>58861.67</v>
+        <v>99970.62</v>
       </c>
       <c r="F219">
-        <v>60793.96</v>
+        <v>160764.58</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
+        <v>Boleto / 9672504 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B220" t="str">
-        <v>2024-10-29</v>
+        <v>2024-11-01</v>
       </c>
       <c r="C220">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="D220" t="str">
         <v>Pesos</v>
       </c>
       <c r="E220">
-        <v>-225944.56</v>
+        <v>58861.67</v>
       </c>
       <c r="F220">
-        <v>1932.29</v>
+        <v>60793.96</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
+        <v>Boleto / 9562411 / COMPRA / 1 / AL30 / $</v>
       </c>
       <c r="B221" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C221">
-        <v>100</v>
+        <v>297</v>
       </c>
       <c r="D221" t="str">
         <v>Pesos</v>
       </c>
       <c r="E221">
-        <v>102687.56</v>
+        <v>-225944.56</v>
       </c>
       <c r="F221">
-        <v>227876.85</v>
+        <v>1932.29</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
+        <v>Boleto / 9538341 / VENTA / 0 / BPY26 / $</v>
       </c>
       <c r="B222" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D222" t="str">
         <v>Pesos</v>
       </c>
       <c r="E222">
-        <v>37241.04</v>
+        <v>102687.56</v>
       </c>
       <c r="F222">
-        <v>125189.29</v>
+        <v>227876.85</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 9538340 / VENTA / 0 / AMD / $</v>
       </c>
       <c r="B223" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C223">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D223" t="str">
         <v>Pesos</v>
       </c>
       <c r="E223">
-        <v>68729.8</v>
+        <v>37241.04</v>
       </c>
       <c r="F223">
-        <v>87948.25</v>
+        <v>125189.29</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
+        <v>Boleto / 9538339 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B224" t="str">
         <v>2024-10-29</v>
       </c>
       <c r="C224">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D224" t="str">
         <v>Pesos</v>
       </c>
       <c r="E224">
-        <v>18248.61</v>
+        <v>68729.8</v>
       </c>
       <c r="F224">
-        <v>19218.45</v>
+        <v>87948.25</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Comprobante de Pago / 2861824</v>
+        <v>Boleto / 9538338 / VENTA / 0 / DISN / $</v>
       </c>
       <c r="B225" t="str">
-        <v>2024-10-25</v>
+        <v>2024-10-29</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D225" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E225">
-        <v>-8.71</v>
+        <v>18248.61</v>
       </c>
       <c r="F225">
-        <v>0</v>
+        <v>19218.45</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
+        <v>Comprobante de Pago / 2861824</v>
       </c>
       <c r="B226" t="str">
-        <v>2024-10-23</v>
+        <v>2024-10-25</v>
       </c>
       <c r="C226">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D226" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E226">
-        <v>-71739.34</v>
+        <v>-8.71</v>
       </c>
       <c r="F226">
-        <v>969.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 9367017 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B227" t="str">
         <v>2024-10-23</v>
       </c>
       <c r="C227">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D227" t="str">
         <v>Pesos</v>
       </c>
       <c r="E227">
-        <v>52196.96</v>
+        <v>-71739.34</v>
       </c>
       <c r="F227">
-        <v>72709.18</v>
+        <v>969.84</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
+        <v>Boleto / 9367016 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B228" t="str">
-        <v>2024-10-22</v>
+        <v>2024-10-23</v>
       </c>
       <c r="C228">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D228" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E228">
-        <v>-100</v>
+        <v>52196.96</v>
       </c>
       <c r="F228">
-        <v>8.71</v>
+        <v>72709.18</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
+        <v>Boleto / 9362499 / Licitación MAE / 2 / TTC8O / usd</v>
       </c>
       <c r="B229" t="str">
         <v>2024-10-22</v>
       </c>
       <c r="C229">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="D229" t="str">
         <v>Dólares</v>
       </c>
       <c r="E229">
-        <v>99.71</v>
+        <v>-100</v>
       </c>
       <c r="F229">
-        <v>108.71</v>
+        <v>8.71</v>
       </c>
     </row>
     <row r="230">
@@ -4965,21 +4965,21 @@
         <v>2024-10-22</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="D230" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E230">
-        <v>-2.47</v>
+        <v>99.71</v>
       </c>
       <c r="F230">
-        <v>20512.22</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Recibo de Cobro / 3253687</v>
+        <v>Boleto / 9326372 / VENTA / 0 / AL30 / usd</v>
       </c>
       <c r="B231" t="str">
         <v>2024-10-22</v>
@@ -4988,18 +4988,18 @@
         <v>0</v>
       </c>
       <c r="D231" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E231">
-        <v>100</v>
+        <v>-2.47</v>
       </c>
       <c r="F231">
-        <v>9</v>
+        <v>20512.22</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Comprobante de Pago / 2830288</v>
+        <v>Recibo de Cobro / 3253687</v>
       </c>
       <c r="B232" t="str">
         <v>2024-10-22</v>
@@ -5011,210 +5011,210 @@
         <v>Dólares</v>
       </c>
       <c r="E232">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F232">
-        <v>-91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
+        <v>Comprobante de Pago / 2830288</v>
       </c>
       <c r="B233" t="str">
-        <v>2024-10-21</v>
+        <v>2024-10-22</v>
       </c>
       <c r="C233">
         <v>0</v>
       </c>
       <c r="D233" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E233">
-        <v>185034.38</v>
+        <v>-100</v>
       </c>
       <c r="F233">
-        <v>20514.69</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
+        <v>Liquidación de Rescate / 1880140 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B234" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234" t="str">
         <v>Pesos</v>
       </c>
       <c r="E234">
-        <v>-1199.18</v>
+        <v>185034.38</v>
       </c>
       <c r="F234">
-        <v>-164519.69</v>
+        <v>20514.69</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 9308525 / COMPRA / 1 / TTC7O / $</v>
       </c>
       <c r="B235" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235" t="str">
         <v>Pesos</v>
       </c>
       <c r="E235">
-        <v>-243469.32</v>
+        <v>-1199.18</v>
       </c>
       <c r="F235">
-        <v>-163320.51</v>
+        <v>-164519.69</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
+        <v>Liquidación de Suscripción / 1875485 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B236" t="str">
         <v>2024-10-21</v>
       </c>
       <c r="C236">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D236" t="str">
         <v>Pesos</v>
       </c>
       <c r="E236">
-        <v>-129746.54</v>
+        <v>-243469.32</v>
       </c>
       <c r="F236">
-        <v>80148.81</v>
+        <v>-163320.51</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
+        <v>Boleto / 9282036 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B237" t="str">
-        <v>2024-10-18</v>
+        <v>2024-10-21</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="D237" t="str">
         <v>Pesos</v>
       </c>
       <c r="E237">
-        <v>-33573.99</v>
+        <v>-129746.54</v>
       </c>
       <c r="F237">
-        <v>209895.35</v>
+        <v>80148.81</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 9265990 / COMPRA / 1 / MSFT / $</v>
       </c>
       <c r="B238" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C238">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D238" t="str">
         <v>Pesos</v>
       </c>
       <c r="E238">
-        <v>142249.86</v>
+        <v>-33573.99</v>
       </c>
       <c r="F238">
-        <v>243469.34</v>
+        <v>209895.35</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 9247456 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B239" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C239">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D239" t="str">
         <v>Pesos</v>
       </c>
       <c r="E239">
-        <v>9746.15</v>
+        <v>142249.86</v>
       </c>
       <c r="F239">
-        <v>101219.48</v>
+        <v>243469.34</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 9247455 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B240" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C240">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D240" t="str">
         <v>Pesos</v>
       </c>
       <c r="E240">
-        <v>29703.57</v>
+        <v>9746.15</v>
       </c>
       <c r="F240">
-        <v>91473.33</v>
+        <v>101219.48</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 9247454 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B241" t="str">
         <v>2024-10-18</v>
       </c>
       <c r="C241">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D241" t="str">
         <v>Pesos</v>
       </c>
       <c r="E241">
-        <v>57840.15</v>
+        <v>29703.57</v>
       </c>
       <c r="F241">
-        <v>61769.76</v>
+        <v>91473.33</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 9247453 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B242" t="str">
-        <v>2024-10-04</v>
+        <v>2024-10-18</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D242" t="str">
         <v>Pesos</v>
       </c>
       <c r="E242">
-        <v>-0.04</v>
+        <v>57840.15</v>
       </c>
       <c r="F242">
-        <v>3929.61</v>
+        <v>61769.76</v>
       </c>
     </row>
     <row r="243">
@@ -5228,33 +5228,33 @@
         <v>0</v>
       </c>
       <c r="D243" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E243">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F243">
-        <v>0.33</v>
+        <v>3929.61</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Dividendo en efectivo / KO</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B244" t="str">
-        <v>2024-10-02</v>
+        <v>2024-10-04</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E244">
-        <v>-0.51</v>
+        <v>0.01</v>
       </c>
       <c r="F244">
-        <v>3929.65</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="245">
@@ -5268,38 +5268,38 @@
         <v>0</v>
       </c>
       <c r="D245" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E245">
-        <v>0.12</v>
+        <v>-0.51</v>
       </c>
       <c r="F245">
-        <v>0.32</v>
+        <v>3929.65</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
+        <v>Dividendo en efectivo / KO</v>
       </c>
       <c r="B246" t="str">
-        <v>2024-10-01</v>
+        <v>2024-10-02</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E246">
-        <v>-296.59</v>
+        <v>0.12</v>
       </c>
       <c r="F246">
-        <v>3930.16</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Dividendo en efectivo / TGNO4</v>
+        <v>Movimiento Manual / Ret IIGG - TGNO4</v>
       </c>
       <c r="B247" t="str">
         <v>2024-10-01</v>
@@ -5311,30 +5311,30 @@
         <v>Pesos</v>
       </c>
       <c r="E247">
-        <v>4226.79</v>
+        <v>-296.59</v>
       </c>
       <c r="F247">
-        <v>4226.75</v>
+        <v>3930.16</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / TGNO4</v>
       </c>
       <c r="B248" t="str">
-        <v>2024-09-27</v>
+        <v>2024-10-01</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E248">
-        <v>0.01</v>
+        <v>4226.79</v>
       </c>
       <c r="F248">
-        <v>0.2</v>
+        <v>4226.75</v>
       </c>
     </row>
     <row r="249">
@@ -5348,21 +5348,21 @@
         <v>0</v>
       </c>
       <c r="D249" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E249">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F249">
-        <v>-0.04</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B250" t="str">
-        <v>2024-09-25</v>
+        <v>2024-09-27</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -5371,50 +5371,50 @@
         <v>Pesos</v>
       </c>
       <c r="E250">
-        <v>-48646.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1725883 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B251" t="str">
         <v>2024-09-25</v>
       </c>
       <c r="C251">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D251" t="str">
         <v>Pesos</v>
       </c>
       <c r="E251">
-        <v>48646.42</v>
+        <v>-48646.1</v>
       </c>
       <c r="F251">
-        <v>48646.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Boleto / 8479354 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B252" t="str">
-        <v>2024-09-17</v>
+        <v>2024-09-25</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D252" t="str">
         <v>Pesos</v>
       </c>
       <c r="E252">
-        <v>-0.12</v>
+        <v>48646.42</v>
       </c>
       <c r="F252">
-        <v>-0.32</v>
+        <v>48646.1</v>
       </c>
     </row>
     <row r="253">
@@ -5428,33 +5428,33 @@
         <v>0</v>
       </c>
       <c r="D253" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E253">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F253">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Dividendo en efectivo / MSFT</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B254" t="str">
-        <v>2024-09-13</v>
+        <v>2024-09-17</v>
       </c>
       <c r="C254">
         <v>0</v>
       </c>
       <c r="D254" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E254">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="F254">
-        <v>-0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="255">
@@ -5468,113 +5468,113 @@
         <v>0</v>
       </c>
       <c r="D255" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E255">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F255">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Renta / BPY26</v>
+        <v>Dividendo en efectivo / MSFT</v>
       </c>
       <c r="B256" t="str">
-        <v>2024-09-02</v>
+        <v>2024-09-13</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256" t="str">
-        <v>Dólares</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E256">
-        <v>1.45</v>
+        <v>0.03</v>
       </c>
       <c r="F256">
-        <v>9</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta / BPY26</v>
       </c>
       <c r="B257" t="str">
-        <v>2024-08-20</v>
+        <v>2024-09-02</v>
       </c>
       <c r="C257">
         <v>0</v>
       </c>
       <c r="D257" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E257">
-        <v>-171669.97</v>
+        <v>1.45</v>
       </c>
       <c r="F257">
-        <v>-0.08</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 1498934 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B258" t="str">
-        <v>2024-08-19</v>
+        <v>2024-08-20</v>
       </c>
       <c r="C258">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D258" t="str">
         <v>Pesos</v>
       </c>
       <c r="E258">
-        <v>-243839.94</v>
+        <v>-171669.97</v>
       </c>
       <c r="F258">
-        <v>171669.89</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
+        <v>Boleto / 7268048 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B259" t="str">
         <v>2024-08-19</v>
       </c>
       <c r="C259">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D259" t="str">
         <v>Pesos</v>
       </c>
       <c r="E259">
-        <v>-196906.93</v>
+        <v>-243839.94</v>
       </c>
       <c r="F259">
-        <v>415509.83</v>
+        <v>171669.89</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Dividendo en efectivo / AAPL</v>
+        <v>Boleto / 7266797 / COMPRA / 0 / MELI / $</v>
       </c>
       <c r="B260" t="str">
-        <v>2024-08-16</v>
+        <v>2024-08-19</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D260" t="str">
         <v>Pesos</v>
       </c>
       <c r="E260">
-        <v>-0.08</v>
+        <v>-196906.93</v>
       </c>
       <c r="F260">
-        <v>612416.76</v>
+        <v>415509.83</v>
       </c>
     </row>
     <row r="261">
@@ -5588,41 +5588,41 @@
         <v>0</v>
       </c>
       <c r="D261" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E261">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="F261">
-        <v>0.13</v>
+        <v>612416.76</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
+        <v>Dividendo en efectivo / AAPL</v>
       </c>
       <c r="B262" t="str">
         <v>2024-08-16</v>
       </c>
       <c r="C262">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D262" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E262">
-        <v>13250.08</v>
+        <v>0.02</v>
       </c>
       <c r="F262">
-        <v>612416.84</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
+        <v>Boleto / 7223951 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B263" t="str">
-        <v>2024-08-13</v>
+        <v>2024-08-16</v>
       </c>
       <c r="C263">
         <v>2</v>
@@ -5631,55 +5631,55 @@
         <v>Pesos</v>
       </c>
       <c r="E263">
-        <v>-35187.15</v>
+        <v>13250.08</v>
       </c>
       <c r="F263">
-        <v>599166.76</v>
+        <v>612416.84</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 7071991 / COMPRA / 0 / KO / $</v>
       </c>
       <c r="B264" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C264">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D264" t="str">
         <v>Pesos</v>
       </c>
       <c r="E264">
-        <v>-31679.73</v>
+        <v>-35187.15</v>
       </c>
       <c r="F264">
-        <v>634353.91</v>
+        <v>599166.76</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
+        <v>Boleto / 7071996 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B265" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C265">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D265" t="str">
         <v>Pesos</v>
       </c>
       <c r="E265">
-        <v>-18430.41</v>
+        <v>-31679.73</v>
       </c>
       <c r="F265">
-        <v>666033.64</v>
+        <v>634353.91</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
+        <v>Boleto / 7071992 / COMPRA / 0 / DISN / $</v>
       </c>
       <c r="B266" t="str">
         <v>2024-08-13</v>
@@ -5691,355 +5691,355 @@
         <v>Pesos</v>
       </c>
       <c r="E266">
-        <v>-36144.97</v>
+        <v>-18430.41</v>
       </c>
       <c r="F266">
-        <v>684464.05</v>
+        <v>666033.64</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
+        <v>Boleto / 7071995 / COMPRA / 0 / AMD / $</v>
       </c>
       <c r="B267" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C267">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D267" t="str">
         <v>Pesos</v>
       </c>
       <c r="E267">
-        <v>-30045.2</v>
+        <v>-36144.97</v>
       </c>
       <c r="F267">
-        <v>720609.02</v>
+        <v>684464.05</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
+        <v>Boleto / 7071994 / COMPRA / 0 / AMZN / $</v>
       </c>
       <c r="B268" t="str">
         <v>2024-08-13</v>
       </c>
       <c r="C268">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D268" t="str">
         <v>Pesos</v>
       </c>
       <c r="E268">
-        <v>-35590.45</v>
+        <v>-30045.2</v>
       </c>
       <c r="F268">
-        <v>750654.22</v>
+        <v>720609.02</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 7071993 / COMPRA / 0 / MSFT / $</v>
       </c>
       <c r="B269" t="str">
-        <v>2024-08-12</v>
+        <v>2024-08-13</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D269" t="str">
         <v>Pesos</v>
       </c>
       <c r="E269">
-        <v>-500000</v>
+        <v>-35590.45</v>
       </c>
       <c r="F269">
-        <v>786244.67</v>
+        <v>750654.22</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
+        <v>Liquidación de Suscripción / 1451232 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B270" t="str">
-        <v>2024-08-09</v>
+        <v>2024-08-12</v>
       </c>
       <c r="C270">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D270" t="str">
         <v>Pesos</v>
       </c>
       <c r="E270">
-        <v>-18274.14</v>
+        <v>-500000</v>
       </c>
       <c r="F270">
-        <v>1286244.67</v>
+        <v>786244.67</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 7000884 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B271" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D271" t="str">
         <v>Pesos</v>
       </c>
       <c r="E271">
-        <v>-17417.14</v>
+        <v>-18274.14</v>
       </c>
       <c r="F271">
-        <v>1304518.81</v>
+        <v>1286244.67</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6986022 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B272" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C272">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D272" t="str">
         <v>Pesos</v>
       </c>
       <c r="E272">
-        <v>-49536.26</v>
+        <v>-17417.14</v>
       </c>
       <c r="F272">
-        <v>1321935.95</v>
+        <v>1304518.81</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6986021 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B273" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C273">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D273" t="str">
         <v>Pesos</v>
       </c>
       <c r="E273">
-        <v>-14089.99</v>
+        <v>-49536.26</v>
       </c>
       <c r="F273">
-        <v>1371472.21</v>
+        <v>1321935.95</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6986020 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B274" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C274">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D274" t="str">
         <v>Pesos</v>
       </c>
       <c r="E274">
-        <v>-85669.13</v>
+        <v>-14089.99</v>
       </c>
       <c r="F274">
-        <v>1385562.2</v>
+        <v>1371472.21</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6986019 / COMPRA / 0 / TGNO4 / $</v>
       </c>
       <c r="B275" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C275">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D275" t="str">
         <v>Pesos</v>
       </c>
       <c r="E275">
-        <v>-14926.81</v>
+        <v>-85669.13</v>
       </c>
       <c r="F275">
-        <v>1471231.33</v>
+        <v>1385562.2</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
+        <v>Boleto / 6986018 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B276" t="str">
         <v>2024-08-09</v>
       </c>
       <c r="C276">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="D276" t="str">
         <v>Pesos</v>
       </c>
       <c r="E276">
-        <v>-88949.9</v>
+        <v>-14926.81</v>
       </c>
       <c r="F276">
-        <v>1486158.14</v>
+        <v>1471231.33</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6986017 / COMPRA / 0 / ALUA / $</v>
       </c>
       <c r="B277" t="str">
-        <v>2024-08-08</v>
+        <v>2024-08-09</v>
       </c>
       <c r="C277">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D277" t="str">
         <v>Pesos</v>
       </c>
       <c r="E277">
-        <v>-500000</v>
+        <v>-88949.9</v>
       </c>
       <c r="F277">
-        <v>1575108.04</v>
+        <v>1486158.14</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
+        <v>Liquidación de Suscripción / 1428996 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B278" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C278">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D278" t="str">
         <v>Pesos</v>
       </c>
       <c r="E278">
-        <v>-20325.87</v>
+        <v>-500000</v>
       </c>
       <c r="F278">
-        <v>2075108.04</v>
+        <v>1575108.04</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
+        <v>Boleto / 6957362 / COMPRA / 1 / TGNO4 / $</v>
       </c>
       <c r="B279" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C279">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D279" t="str">
         <v>Pesos</v>
       </c>
       <c r="E279">
-        <v>-46136.52</v>
+        <v>-20325.87</v>
       </c>
       <c r="F279">
-        <v>2095433.91</v>
+        <v>2075108.04</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
+        <v>Boleto / 6926843 / COMPRA / 0 / NVDA / $</v>
       </c>
       <c r="B280" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D280" t="str">
         <v>Pesos</v>
       </c>
       <c r="E280">
-        <v>-27927.91</v>
+        <v>-46136.52</v>
       </c>
       <c r="F280">
-        <v>2141570.43</v>
+        <v>2095433.91</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
+        <v>Boleto / 6926842 / COMPRA / 0 / META / $</v>
       </c>
       <c r="B281" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C281">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="D281" t="str">
         <v>Pesos</v>
       </c>
       <c r="E281">
-        <v>-50260.67</v>
+        <v>-27927.91</v>
       </c>
       <c r="F281">
-        <v>2169498.34</v>
+        <v>2141570.43</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
+        <v>Boleto / 6926841 / COMPRA / 0 / BYMA / $</v>
       </c>
       <c r="B282" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C282">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="D282" t="str">
         <v>Pesos</v>
       </c>
       <c r="E282">
-        <v>-37506.08</v>
+        <v>-50260.67</v>
       </c>
       <c r="F282">
-        <v>2219759.01</v>
+        <v>2169498.34</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
+        <v>Boleto / 6926840 / COMPRA / 0 / GOOGL / $</v>
       </c>
       <c r="B283" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C283">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D283" t="str">
         <v>Pesos</v>
       </c>
       <c r="E283">
-        <v>-28280.79</v>
+        <v>-37506.08</v>
       </c>
       <c r="F283">
-        <v>2257265.09</v>
+        <v>2219759.01</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
+        <v>Boleto / 6926839 / COMPRA / 0 / AAPL / $</v>
       </c>
       <c r="B284" t="str">
         <v>2024-08-08</v>
@@ -6051,115 +6051,115 @@
         <v>Pesos</v>
       </c>
       <c r="E284">
-        <v>-53133.61</v>
+        <v>-28280.79</v>
       </c>
       <c r="F284">
-        <v>2285545.88</v>
+        <v>2257265.09</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6926838 / COMPRA / 0 / YPFD / $</v>
       </c>
       <c r="B285" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C285">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D285" t="str">
         <v>Pesos</v>
       </c>
       <c r="E285">
-        <v>-28069.07</v>
+        <v>-53133.61</v>
       </c>
       <c r="F285">
-        <v>2338679.49</v>
+        <v>2285545.88</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
+        <v>Boleto / 6926837 / COMPRA / 0 / TGSU2 / $</v>
       </c>
       <c r="B286" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D286" t="str">
         <v>Pesos</v>
       </c>
       <c r="E286">
-        <v>-19937.71</v>
+        <v>-28069.07</v>
       </c>
       <c r="F286">
-        <v>2366748.56</v>
+        <v>2338679.49</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
+        <v>Boleto / 6926836 / COMPRA / 0 / GGAL / $</v>
       </c>
       <c r="B287" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C287">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D287" t="str">
         <v>Pesos</v>
       </c>
       <c r="E287">
-        <v>-40228.29</v>
+        <v>-19937.71</v>
       </c>
       <c r="F287">
-        <v>2386686.27</v>
+        <v>2366748.56</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
+        <v>Boleto / 6926835 / COMPRA / 0 / EDN / $</v>
       </c>
       <c r="B288" t="str">
         <v>2024-08-08</v>
       </c>
       <c r="C288">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D288" t="str">
         <v>Pesos</v>
       </c>
       <c r="E288">
-        <v>-25407.34</v>
+        <v>-40228.29</v>
       </c>
       <c r="F288">
-        <v>2426914.56</v>
+        <v>2386686.27</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 6926834 / COMPRA / 0 / PAMP / $</v>
       </c>
       <c r="B289" t="str">
-        <v>2024-08-05</v>
+        <v>2024-08-08</v>
       </c>
       <c r="C289">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D289" t="str">
         <v>Pesos</v>
       </c>
       <c r="E289">
-        <v>1000000</v>
+        <v>-25407.34</v>
       </c>
       <c r="F289">
-        <v>2452321.9</v>
+        <v>2426914.56</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 1402455 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B290" t="str">
         <v>2024-08-05</v>
@@ -6171,15 +6171,15 @@
         <v>Pesos</v>
       </c>
       <c r="E290">
-        <v>218666.47</v>
+        <v>1000000</v>
       </c>
       <c r="F290">
-        <v>1452321.9</v>
+        <v>2452321.9</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
+        <v>Liquidación de Rescate / 1402342 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B291" t="str">
         <v>2024-08-05</v>
@@ -6191,15 +6191,15 @@
         <v>Pesos</v>
       </c>
       <c r="E291">
-        <v>164626.92</v>
+        <v>218666.47</v>
       </c>
       <c r="F291">
-        <v>1233655.43</v>
+        <v>1452321.9</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Rescate / 1401043 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B292" t="str">
         <v>2024-08-05</v>
@@ -6211,155 +6211,155 @@
         <v>Pesos</v>
       </c>
       <c r="E292">
-        <v>152793.11</v>
+        <v>164626.92</v>
       </c>
       <c r="F292">
-        <v>1069028.51</v>
+        <v>1233655.43</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
+        <v>Liquidación de Rescate / 1392731 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B293" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C293">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D293" t="str">
         <v>Pesos</v>
       </c>
       <c r="E293">
-        <v>55836.76</v>
+        <v>152793.11</v>
       </c>
       <c r="F293">
-        <v>916235.4</v>
+        <v>1069028.51</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
+        <v>Boleto / 6803479 / VENTA / 1 / AAPL / $</v>
       </c>
       <c r="B294" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C294">
-        <v>1416</v>
+        <v>4</v>
       </c>
       <c r="D294" t="str">
         <v>Pesos</v>
       </c>
       <c r="E294">
-        <v>-879220.78</v>
+        <v>55836.76</v>
       </c>
       <c r="F294">
-        <v>860398.64</v>
+        <v>916235.4</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 6763862 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B295" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C295">
-        <v>46</v>
+        <v>1416</v>
       </c>
       <c r="D295" t="str">
         <v>Pesos</v>
       </c>
       <c r="E295">
-        <v>96717.6</v>
+        <v>-879220.78</v>
       </c>
       <c r="F295">
-        <v>1739619.42</v>
+        <v>860398.64</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
+        <v>Boleto / 6763852 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B296" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C296">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D296" t="str">
         <v>Pesos</v>
       </c>
       <c r="E296">
-        <v>159943.07</v>
+        <v>96717.6</v>
       </c>
       <c r="F296">
-        <v>1642901.82</v>
+        <v>1739619.42</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
+        <v>Boleto / 6763861 / VENTA / 0 / NVDA / $</v>
       </c>
       <c r="B297" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C297">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D297" t="str">
         <v>Pesos</v>
       </c>
       <c r="E297">
-        <v>70757.98</v>
+        <v>159943.07</v>
       </c>
       <c r="F297">
-        <v>1482958.75</v>
+        <v>1642901.82</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
+        <v>Boleto / 6763858 / VENTA / 0 / GOOGL / $</v>
       </c>
       <c r="B298" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C298">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D298" t="str">
         <v>Pesos</v>
       </c>
       <c r="E298">
-        <v>96479.58</v>
+        <v>70757.98</v>
       </c>
       <c r="F298">
-        <v>1412200.77</v>
+        <v>1482958.75</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
+        <v>Boleto / 6763857 / VENTA / 0 / TGNO4 / $</v>
       </c>
       <c r="B299" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C299">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D299" t="str">
         <v>Pesos</v>
       </c>
       <c r="E299">
-        <v>52117.62</v>
+        <v>96479.58</v>
       </c>
       <c r="F299">
-        <v>1315721.19</v>
+        <v>1412200.77</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
+        <v>Boleto / 6763860 / VENTA / 0 / META / $</v>
       </c>
       <c r="B300" t="str">
         <v>2024-08-05</v>
@@ -6371,135 +6371,135 @@
         <v>Pesos</v>
       </c>
       <c r="E300">
-        <v>45423.16</v>
+        <v>52117.62</v>
       </c>
       <c r="F300">
-        <v>1263603.57</v>
+        <v>1315721.19</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
+        <v>Boleto / 6763856 / VENTA / 0 / YPFD / $</v>
       </c>
       <c r="B301" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C301">
-        <v>220</v>
+        <v>2</v>
       </c>
       <c r="D301" t="str">
         <v>Pesos</v>
       </c>
       <c r="E301">
-        <v>59565.82</v>
+        <v>45423.16</v>
       </c>
       <c r="F301">
-        <v>1218180.41</v>
+        <v>1263603.57</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 6763859 / VENTA / 0 / BYMA / $</v>
       </c>
       <c r="B302" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C302">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="D302" t="str">
         <v>Pesos</v>
       </c>
       <c r="E302">
-        <v>101983.91</v>
+        <v>59565.82</v>
       </c>
       <c r="F302">
-        <v>1158614.59</v>
+        <v>1218180.41</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
+        <v>Boleto / 6763855 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B303" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C303">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D303" t="str">
         <v>Pesos</v>
       </c>
       <c r="E303">
-        <v>59530.13</v>
+        <v>101983.91</v>
       </c>
       <c r="F303">
-        <v>1056630.68</v>
+        <v>1158614.59</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
+        <v>Boleto / 6763853 / VENTA / 0 / EDN / $</v>
       </c>
       <c r="B304" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C304">
-        <v>1536</v>
+        <v>61</v>
       </c>
       <c r="D304" t="str">
         <v>Pesos</v>
       </c>
       <c r="E304">
-        <v>942562.63</v>
+        <v>59530.13</v>
       </c>
       <c r="F304">
-        <v>997100.55</v>
+        <v>1056630.68</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
+        <v>Boleto / 6763863 / VENTA / 0 / AL30 / $</v>
       </c>
       <c r="B305" t="str">
         <v>2024-08-05</v>
       </c>
       <c r="C305">
-        <v>16</v>
+        <v>1536</v>
       </c>
       <c r="D305" t="str">
         <v>Pesos</v>
       </c>
       <c r="E305">
-        <v>53000.3</v>
+        <v>942562.63</v>
       </c>
       <c r="F305">
-        <v>54537.92</v>
+        <v>997100.55</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Boleto / 6763854 / VENTA / 0 / GGAL / $</v>
       </c>
       <c r="B306" t="str">
-        <v>2024-07-24</v>
+        <v>2024-08-05</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D306" t="str">
         <v>Pesos</v>
       </c>
       <c r="E306">
-        <v>-116.05</v>
+        <v>53000.3</v>
       </c>
       <c r="F306">
-        <v>1537.62</v>
+        <v>54537.92</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B307" t="str">
         <v>2024-07-24</v>
@@ -6511,18 +6511,18 @@
         <v>Pesos</v>
       </c>
       <c r="E307">
-        <v>1653.89</v>
+        <v>-116.05</v>
       </c>
       <c r="F307">
-        <v>1653.67</v>
+        <v>1537.62</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Renta y Amortización / AL30</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B308" t="str">
-        <v>2024-07-10</v>
+        <v>2024-07-24</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -6531,10 +6531,10 @@
         <v>Pesos</v>
       </c>
       <c r="E308">
-        <v>-0.21</v>
+        <v>1653.89</v>
       </c>
       <c r="F308">
-        <v>-0.22</v>
+        <v>1653.67</v>
       </c>
     </row>
     <row r="309">
@@ -6548,158 +6548,158 @@
         <v>0</v>
       </c>
       <c r="D309" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E309">
-        <v>5.25</v>
+        <v>-0.21</v>
       </c>
       <c r="F309">
-        <v>7.55</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
+        <v>Renta y Amortización / AL30</v>
       </c>
       <c r="B310" t="str">
-        <v>2024-07-08</v>
+        <v>2024-07-10</v>
       </c>
       <c r="C310">
         <v>0</v>
       </c>
       <c r="D310" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E310">
-        <v>-4402.49</v>
+        <v>5.25</v>
       </c>
       <c r="F310">
-        <v>-0.01</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
+        <v>Liquidación de Suscripción / 1226640 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B311" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D311" t="str">
         <v>Pesos</v>
       </c>
       <c r="E311">
-        <v>-38067.66</v>
+        <v>-4402.49</v>
       </c>
       <c r="F311">
-        <v>4402.48</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
+        <v>Boleto / 5773473 / COMPRA / 1 / NVS / $</v>
       </c>
       <c r="B312" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D312" t="str">
         <v>Pesos</v>
       </c>
       <c r="E312">
-        <v>-47346.39</v>
+        <v>-38067.66</v>
       </c>
       <c r="F312">
-        <v>42470.14</v>
+        <v>4402.48</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
+        <v>Boleto / 5744896 / COMPRA / 0 / TSLA / $</v>
       </c>
       <c r="B313" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D313" t="str">
         <v>Pesos</v>
       </c>
       <c r="E313">
-        <v>15580.74</v>
+        <v>-47346.39</v>
       </c>
       <c r="F313">
-        <v>89816.53</v>
+        <v>42470.14</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
+        <v>Boleto / 5734649 / VENTA / 0 / AAPL / $</v>
       </c>
       <c r="B314" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C314">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D314" t="str">
         <v>Pesos</v>
       </c>
       <c r="E314">
-        <v>34892.52</v>
+        <v>15580.74</v>
       </c>
       <c r="F314">
-        <v>74235.79</v>
+        <v>89816.53</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
+        <v>Boleto / 5734648 / VENTA / 0 / TGSU2 / $</v>
       </c>
       <c r="B315" t="str">
         <v>2024-07-08</v>
       </c>
       <c r="C315">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D315" t="str">
         <v>Pesos</v>
       </c>
       <c r="E315">
-        <v>37865.35</v>
+        <v>34892.52</v>
       </c>
       <c r="F315">
-        <v>39343.27</v>
+        <v>74235.79</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
+        <v>Boleto / 5734647 / VENTA / 0 / PAMP / $</v>
       </c>
       <c r="B316" t="str">
-        <v>2024-07-02</v>
+        <v>2024-07-08</v>
       </c>
       <c r="C316">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D316" t="str">
         <v>Pesos</v>
       </c>
       <c r="E316">
-        <v>-152584.35</v>
+        <v>37865.35</v>
       </c>
       <c r="F316">
-        <v>1477.92</v>
+        <v>39343.27</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
+        <v>Liquidación de Suscripción / 1179546 / BALANZ PERFORMANCE II clase A</v>
       </c>
       <c r="B317" t="str">
         <v>2024-07-02</v>
@@ -6711,90 +6711,90 @@
         <v>Pesos</v>
       </c>
       <c r="E317">
-        <v>151114.01</v>
+        <v>-152584.35</v>
       </c>
       <c r="F317">
-        <v>154062.27</v>
+        <v>1477.92</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
+        <v>Liquidación de Rescate / 1173245 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B318" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C318">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D318" t="str">
         <v>Pesos</v>
       </c>
       <c r="E318">
-        <v>-108902.21</v>
+        <v>151114.01</v>
       </c>
       <c r="F318">
-        <v>2948.26</v>
+        <v>154062.27</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 5532543 / COMPRA / 1 / BPY26 / $</v>
       </c>
       <c r="B319" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C319">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="D319" t="str">
         <v>Pesos</v>
       </c>
       <c r="E319">
-        <v>-41051.01</v>
+        <v>-108902.21</v>
       </c>
       <c r="F319">
-        <v>111850.47</v>
+        <v>2948.26</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
+        <v>Boleto / 5532541 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B320" t="str">
         <v>2024-07-02</v>
       </c>
       <c r="C320">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D320" t="str">
         <v>Pesos</v>
       </c>
       <c r="E320">
-        <v>151431.18</v>
+        <v>-41051.01</v>
       </c>
       <c r="F320">
-        <v>152901.48</v>
+        <v>111850.47</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Dividendo en efectivo / NVDA</v>
+        <v>Boleto / 5532542 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B321" t="str">
-        <v>2024-07-01</v>
+        <v>2024-07-02</v>
       </c>
       <c r="C321">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D321" t="str">
         <v>Pesos</v>
       </c>
       <c r="E321">
-        <v>-0.04</v>
+        <v>151431.18</v>
       </c>
       <c r="F321">
-        <v>1470.3</v>
+        <v>152901.48</v>
       </c>
     </row>
     <row r="322">
@@ -6808,18 +6808,18 @@
         <v>0</v>
       </c>
       <c r="D322" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E322">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F322">
-        <v>0.11</v>
+        <v>1470.3</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
+        <v>Dividendo en efectivo / NVDA</v>
       </c>
       <c r="B323" t="str">
         <v>2024-07-01</v>
@@ -6828,18 +6828,18 @@
         <v>0</v>
       </c>
       <c r="D323" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E323">
-        <v>-110.98</v>
+        <v>0.01</v>
       </c>
       <c r="F323">
-        <v>1470.34</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG y BBPP - GGAL</v>
       </c>
       <c r="B324" t="str">
         <v>2024-07-01</v>
@@ -6851,18 +6851,18 @@
         <v>Pesos</v>
       </c>
       <c r="E324">
-        <v>1581.51</v>
+        <v>-110.98</v>
       </c>
       <c r="F324">
-        <v>1581.32</v>
+        <v>1470.34</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Dividendo en efectivo / META</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B325" t="str">
-        <v>2024-06-27</v>
+        <v>2024-07-01</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -6871,10 +6871,10 @@
         <v>Pesos</v>
       </c>
       <c r="E325">
-        <v>-0.12</v>
+        <v>1581.51</v>
       </c>
       <c r="F325">
-        <v>-0.19</v>
+        <v>1581.32</v>
       </c>
     </row>
     <row r="326">
@@ -6888,38 +6888,38 @@
         <v>0</v>
       </c>
       <c r="D326" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E326">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F326">
-        <v>0.1</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
+        <v>Dividendo en efectivo / META</v>
       </c>
       <c r="B327" t="str">
-        <v>2024-06-24</v>
+        <v>2024-06-27</v>
       </c>
       <c r="C327">
         <v>0</v>
       </c>
       <c r="D327" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E327">
-        <v>-175.43</v>
+        <v>0.03</v>
       </c>
       <c r="F327">
-        <v>-0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
+        <v>Movimiento Manual / Gastos por cambio de ratio - NVDA</v>
       </c>
       <c r="B328" t="str">
         <v>2024-06-24</v>
@@ -6931,15 +6931,15 @@
         <v>Pesos</v>
       </c>
       <c r="E328">
-        <v>-150000</v>
+        <v>-175.43</v>
       </c>
       <c r="F328">
-        <v>175.36</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
+        <v>Liquidación de Suscripción / 1111260 / BALANZ MONEY MARKET A</v>
       </c>
       <c r="B329" t="str">
         <v>2024-06-24</v>
@@ -6951,18 +6951,18 @@
         <v>Pesos</v>
       </c>
       <c r="E329">
-        <v>-150447.89</v>
+        <v>-150000</v>
       </c>
       <c r="F329">
-        <v>150175.36</v>
+        <v>175.36</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Dividendo en efectivo / GOOGL</v>
+        <v>Liquidación de Suscripción / 1107431 / BALANZ RETORNO TOTAL A</v>
       </c>
       <c r="B330" t="str">
-        <v>2024-06-19</v>
+        <v>2024-06-24</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>Pesos</v>
       </c>
       <c r="E330">
-        <v>-0.07</v>
+        <v>-150447.89</v>
       </c>
       <c r="F330">
-        <v>300623.25</v>
+        <v>150175.36</v>
       </c>
     </row>
     <row r="331">
@@ -6988,18 +6988,18 @@
         <v>0</v>
       </c>
       <c r="D331" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E331">
-        <v>0.02</v>
+        <v>-0.07</v>
       </c>
       <c r="F331">
-        <v>0.07</v>
+        <v>300623.25</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GOOGL</v>
       </c>
       <c r="B332" t="str">
         <v>2024-06-19</v>
@@ -7008,21 +7008,21 @@
         <v>0</v>
       </c>
       <c r="D332" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E332">
-        <v>300000</v>
+        <v>0.02</v>
       </c>
       <c r="F332">
-        <v>300623.32</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Dividendo en efectivo / INTC</v>
+        <v>Liquidación de Rescate / 1102115 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B333" t="str">
-        <v>2024-06-04</v>
+        <v>2024-06-19</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>Pesos</v>
       </c>
       <c r="E333">
-        <v>-0.19</v>
+        <v>300000</v>
       </c>
       <c r="F333">
-        <v>623.32</v>
+        <v>300623.32</v>
       </c>
     </row>
     <row r="334">
@@ -7048,161 +7048,161 @@
         <v>0</v>
       </c>
       <c r="D334" t="str">
-        <v>Dólares C.V. 7000</v>
+        <v>Pesos</v>
       </c>
       <c r="E334">
-        <v>0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="F334">
-        <v>0.05</v>
+        <v>623.32</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
+        <v>Dividendo en efectivo / INTC</v>
       </c>
       <c r="B335" t="str">
-        <v>2024-05-31</v>
+        <v>2024-06-04</v>
       </c>
       <c r="C335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D335" t="str">
-        <v>Pesos</v>
+        <v>Dólares C.V. 7000</v>
       </c>
       <c r="E335">
-        <v>55120.7</v>
+        <v>0.05</v>
       </c>
       <c r="F335">
-        <v>623.51</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
+        <v>Boleto / 4513899 / VENTA / 1 / NVDA / $</v>
       </c>
       <c r="B336" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C336">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D336" t="str">
         <v>Pesos</v>
       </c>
       <c r="E336">
-        <v>-36734.79</v>
+        <v>55120.7</v>
       </c>
       <c r="F336">
-        <v>-54497.19</v>
+        <v>623.51</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
+        <v>Boleto / 4513897 / COMPRA / 1 / GOOGL / $</v>
       </c>
       <c r="B337" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C337">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D337" t="str">
         <v>Pesos</v>
       </c>
       <c r="E337">
-        <v>-59561.06</v>
+        <v>-36734.79</v>
       </c>
       <c r="F337">
-        <v>-17762.4</v>
+        <v>-54497.19</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
+        <v>Boleto / 4513896 / COMPRA / 1 / AAPL / $</v>
       </c>
       <c r="B338" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C338">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D338" t="str">
         <v>Pesos</v>
       </c>
       <c r="E338">
-        <v>38496.62</v>
+        <v>-59561.06</v>
       </c>
       <c r="F338">
-        <v>41798.66</v>
+        <v>-17762.4</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
+        <v>Boleto / 4513894 / VENTA / 1 / PAMP / $</v>
       </c>
       <c r="B339" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C339">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D339" t="str">
         <v>Pesos</v>
       </c>
       <c r="E339">
-        <v>48021.6</v>
+        <v>38496.62</v>
       </c>
       <c r="F339">
-        <v>3302.04</v>
+        <v>41798.66</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
+        <v>Boleto / 4513895 / VENTA / 1 / TGSU2 / $</v>
       </c>
       <c r="B340" t="str">
         <v>2024-05-31</v>
       </c>
       <c r="C340">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D340" t="str">
         <v>Pesos</v>
       </c>
       <c r="E340">
-        <v>-47487.54</v>
+        <v>48021.6</v>
       </c>
       <c r="F340">
-        <v>-44719.56</v>
+        <v>3302.04</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Movimiento Manual / Ret IIGG - GGAL</v>
+        <v>Boleto / 4513898 / COMPRA / 1 / META / $</v>
       </c>
       <c r="B341" t="str">
-        <v>2024-05-27</v>
+        <v>2024-05-31</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D341" t="str">
         <v>Pesos</v>
       </c>
       <c r="E341">
-        <v>-73.45</v>
+        <v>-47487.54</v>
       </c>
       <c r="F341">
-        <v>2767.98</v>
+        <v>-44719.56</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Movimiento Manual / Ret IIGG - GGAL</v>
       </c>
       <c r="B342" t="str">
-        <v>2024-05-24</v>
+        <v>2024-05-27</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -7211,55 +7211,55 @@
         <v>Pesos</v>
       </c>
       <c r="E342">
-        <v>1518.11</v>
+        <v>-73.45</v>
       </c>
       <c r="F342">
-        <v>2841.43</v>
+        <v>2767.98</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B343" t="str">
-        <v>2024-05-23</v>
+        <v>2024-05-24</v>
       </c>
       <c r="C343">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D343" t="str">
         <v>Pesos</v>
       </c>
       <c r="E343">
-        <v>-81669.11</v>
+        <v>1518.11</v>
       </c>
       <c r="F343">
-        <v>1323.32</v>
+        <v>2841.43</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
+        <v>Boleto / 4257961 / COMPRA / 0 / AL30 / $</v>
       </c>
       <c r="B344" t="str">
-        <v>2024-05-21</v>
+        <v>2024-05-23</v>
       </c>
       <c r="C344">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D344" t="str">
         <v>Pesos</v>
       </c>
       <c r="E344">
-        <v>21949.4</v>
+        <v>-81669.11</v>
       </c>
       <c r="F344">
-        <v>82992.43</v>
+        <v>1323.32</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
+        <v>Boleto / 4185042 / VENTA / 2 / INTC / $</v>
       </c>
       <c r="B345" t="str">
         <v>2024-05-21</v>
@@ -7271,38 +7271,38 @@
         <v>Pesos</v>
       </c>
       <c r="E345">
-        <v>57393.84</v>
+        <v>21949.4</v>
       </c>
       <c r="F345">
-        <v>61043.03</v>
+        <v>82992.43</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Dividendo en efectivo / GGAL</v>
+        <v>Boleto / 4185043 / VENTA / 2 / AMD / $</v>
       </c>
       <c r="B346" t="str">
-        <v>2024-05-15</v>
+        <v>2024-05-21</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D346" t="str">
         <v>Pesos</v>
       </c>
       <c r="E346">
-        <v>703.51</v>
+        <v>57393.84</v>
       </c>
       <c r="F346">
-        <v>3649.19</v>
+        <v>61043.03</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Dividendo en efectivo / GGAL</v>
       </c>
       <c r="B347" t="str">
-        <v>2024-05-14</v>
+        <v>2024-05-15</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -7311,335 +7311,335 @@
         <v>Pesos</v>
       </c>
       <c r="E347">
-        <v>-130000</v>
+        <v>703.51</v>
       </c>
       <c r="F347">
-        <v>2945.68</v>
+        <v>3649.19</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Distribución de acciones por Capitalización / BYMA</v>
+        <v>Liquidación de Suscripción / 840145 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B348" t="str">
         <v>2024-05-14</v>
       </c>
       <c r="C348">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D348" t="str">
         <v>Pesos</v>
       </c>
       <c r="E348">
-        <v>-0.44</v>
+        <v>-130000</v>
       </c>
       <c r="F348">
-        <v>132945.68</v>
+        <v>2945.68</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
+        <v>Distribución de acciones por Capitalización / BYMA</v>
       </c>
       <c r="B349" t="str">
-        <v>2024-05-07</v>
+        <v>2024-05-14</v>
       </c>
       <c r="C349">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="D349" t="str">
         <v>Pesos</v>
       </c>
       <c r="E349">
-        <v>5097.7</v>
+        <v>-0.44</v>
       </c>
       <c r="F349">
-        <v>132946.12</v>
+        <v>132945.68</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3771674 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B350" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C350">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D350" t="str">
         <v>Pesos</v>
       </c>
       <c r="E350">
-        <v>23635.91</v>
+        <v>5097.7</v>
       </c>
       <c r="F350">
-        <v>127848.42</v>
+        <v>132946.12</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3771671 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B351" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C351">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D351" t="str">
         <v>Pesos</v>
       </c>
       <c r="E351">
-        <v>20921.43</v>
+        <v>23635.91</v>
       </c>
       <c r="F351">
-        <v>104212.51</v>
+        <v>127848.42</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3771672 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B352" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C352">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D352" t="str">
         <v>Pesos</v>
       </c>
       <c r="E352">
-        <v>11618.11</v>
+        <v>20921.43</v>
       </c>
       <c r="F352">
-        <v>83291.08</v>
+        <v>104212.51</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
+        <v>Boleto / 3771675 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B353" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C353">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D353" t="str">
         <v>Pesos</v>
       </c>
       <c r="E353">
-        <v>52241.19</v>
+        <v>11618.11</v>
       </c>
       <c r="F353">
-        <v>71672.97</v>
+        <v>83291.08</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3771673 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B354" t="str">
         <v>2024-05-07</v>
       </c>
       <c r="C354">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D354" t="str">
         <v>Pesos</v>
       </c>
       <c r="E354">
-        <v>19431.78</v>
+        <v>52241.19</v>
       </c>
       <c r="F354">
-        <v>19431.78</v>
+        <v>71672.97</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 3771670 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B355" t="str">
-        <v>2024-05-06</v>
+        <v>2024-05-07</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D355" t="str">
         <v>Pesos</v>
       </c>
       <c r="E355">
-        <v>-222622.08</v>
+        <v>19431.78</v>
       </c>
       <c r="F355">
-        <v>0</v>
+        <v>19431.78</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
+        <v>Liquidación de Suscripción / 775731 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B356" t="str">
-        <v>2024-05-02</v>
+        <v>2024-05-06</v>
       </c>
       <c r="C356">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D356" t="str">
         <v>Pesos</v>
       </c>
       <c r="E356">
-        <v>99355.72</v>
+        <v>-222622.08</v>
       </c>
       <c r="F356">
-        <v>222622.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
+        <v>Boleto / 3611572 / VENTA / 2 / YPFD / $</v>
       </c>
       <c r="B357" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C357">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D357" t="str">
         <v>Pesos</v>
       </c>
       <c r="E357">
-        <v>66604.92</v>
+        <v>99355.72</v>
       </c>
       <c r="F357">
-        <v>123266.36</v>
+        <v>222622.08</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
+        <v>Boleto / 3611575 / VENTA / 2 / TSLA / $</v>
       </c>
       <c r="B358" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C358">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D358" t="str">
         <v>Pesos</v>
       </c>
       <c r="E358">
-        <v>6069.65</v>
+        <v>66604.92</v>
       </c>
       <c r="F358">
-        <v>56661.44</v>
+        <v>123266.36</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
+        <v>Boleto / 3611574 / VENTA / 2 / BYMA / $</v>
       </c>
       <c r="B359" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D359" t="str">
         <v>Pesos</v>
       </c>
       <c r="E359">
-        <v>2488.36</v>
+        <v>6069.65</v>
       </c>
       <c r="F359">
-        <v>50591.79</v>
+        <v>56661.44</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
+        <v>Boleto / 3611573 / VENTA / 2 / TGNO4 / $</v>
       </c>
       <c r="B360" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C360">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D360" t="str">
         <v>Pesos</v>
       </c>
       <c r="E360">
-        <v>14202.18</v>
+        <v>2488.36</v>
       </c>
       <c r="F360">
-        <v>48103.43</v>
+        <v>50591.79</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
+        <v>Boleto / 3611570 / VENTA / 2 / GGAL / $</v>
       </c>
       <c r="B361" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C361">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D361" t="str">
         <v>Pesos</v>
       </c>
       <c r="E361">
-        <v>12418.97</v>
+        <v>14202.18</v>
       </c>
       <c r="F361">
-        <v>33901.25</v>
+        <v>48103.43</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
+        <v>Boleto / 3611569 / VENTA / 2 / PAMP / $</v>
       </c>
       <c r="B362" t="str">
         <v>2024-05-02</v>
       </c>
       <c r="C362">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D362" t="str">
         <v>Pesos</v>
       </c>
       <c r="E362">
-        <v>20579.26</v>
+        <v>12418.97</v>
       </c>
       <c r="F362">
-        <v>21482.28</v>
+        <v>33901.25</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
+        <v>Boleto / 3611571 / VENTA / 2 / TGSU2 / $</v>
       </c>
       <c r="B363" t="str">
-        <v>2024-04-17</v>
+        <v>2024-05-02</v>
       </c>
       <c r="C363">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D363" t="str">
         <v>Pesos</v>
       </c>
       <c r="E363">
-        <v>-34.33</v>
+        <v>20579.26</v>
       </c>
       <c r="F363">
-        <v>903.02</v>
+        <v>21482.28</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG Y BBPP- BYMA</v>
       </c>
       <c r="B364" t="str">
         <v>2024-04-17</v>
@@ -7651,15 +7651,15 @@
         <v>Pesos</v>
       </c>
       <c r="E364">
-        <v>489.31</v>
+        <v>-34.33</v>
       </c>
       <c r="F364">
-        <v>937.35</v>
+        <v>903.02</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Movimiento Manual / Ret IIGG - BYMA</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B365" t="str">
         <v>2024-04-17</v>
@@ -7668,18 +7668,18 @@
         <v>0</v>
       </c>
       <c r="D365" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E365">
-        <v>-0.18</v>
+        <v>489.31</v>
       </c>
       <c r="F365">
-        <v>2.3</v>
+        <v>937.35</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Dividendo en efectivo / BYMA</v>
+        <v>Movimiento Manual / Ret IIGG - BYMA</v>
       </c>
       <c r="B366" t="str">
         <v>2024-04-17</v>
@@ -7688,13 +7688,13 @@
         <v>0</v>
       </c>
       <c r="D366" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E366">
-        <v>-2.6</v>
+        <v>-0.18</v>
       </c>
       <c r="F366">
-        <v>448.04</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="367">
@@ -7708,218 +7708,218 @@
         <v>0</v>
       </c>
       <c r="D367" t="str">
-        <v>Dólares</v>
+        <v>Pesos</v>
       </c>
       <c r="E367">
-        <v>2.48</v>
+        <v>-2.6</v>
       </c>
       <c r="F367">
-        <v>2.48</v>
+        <v>448.04</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
+        <v>Dividendo en efectivo / BYMA</v>
       </c>
       <c r="B368" t="str">
-        <v>2024-04-10</v>
+        <v>2024-04-17</v>
       </c>
       <c r="C368">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D368" t="str">
-        <v>Pesos</v>
+        <v>Dólares</v>
       </c>
       <c r="E368">
-        <v>-80932.98</v>
+        <v>2.48</v>
       </c>
       <c r="F368">
-        <v>450.64</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
+        <v>Boleto / 3014167 / COMPRA / 2 / BYMA / $</v>
       </c>
       <c r="B369" t="str">
-        <v>2024-04-09</v>
+        <v>2024-04-10</v>
       </c>
       <c r="C369">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D369" t="str">
         <v>Pesos</v>
       </c>
       <c r="E369">
-        <v>104967.66</v>
+        <v>-80932.98</v>
       </c>
       <c r="F369">
-        <v>81383.62</v>
+        <v>450.64</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
+        <v>Boleto / 2967529 / VENTA / 2 / AVGO / $</v>
       </c>
       <c r="B370" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C370">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D370" t="str">
         <v>Pesos</v>
       </c>
       <c r="E370">
-        <v>16388.53</v>
+        <v>104967.66</v>
       </c>
       <c r="F370">
-        <v>-23584.04</v>
+        <v>81383.62</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
+        <v>Boleto / 2967527 / VENTA / 2 / QCOM / $</v>
       </c>
       <c r="B371" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C371">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D371" t="str">
         <v>Pesos</v>
       </c>
       <c r="E371">
-        <v>-77278.67</v>
+        <v>16388.53</v>
       </c>
       <c r="F371">
-        <v>-39972.57</v>
+        <v>-23584.04</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
+        <v>Boleto / 2967526 / COMPRA / 2 / GGAL / $</v>
       </c>
       <c r="B372" t="str">
         <v>2024-04-09</v>
       </c>
       <c r="C372">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D372" t="str">
         <v>Pesos</v>
       </c>
       <c r="E372">
-        <v>35352.22</v>
+        <v>-77278.67</v>
       </c>
       <c r="F372">
-        <v>37306.1</v>
+        <v>-39972.57</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Boleto / 2967528 / VENTA / 2 / TXN / $</v>
       </c>
       <c r="B373" t="str">
-        <v>2024-04-08</v>
+        <v>2024-04-09</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D373" t="str">
         <v>Pesos</v>
       </c>
       <c r="E373">
-        <v>-733461</v>
+        <v>35352.22</v>
       </c>
       <c r="F373">
-        <v>1953.88</v>
+        <v>37306.1</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
+        <v>Liquidación de Suscripción / 598612 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B374" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C374">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D374" t="str">
         <v>Pesos</v>
       </c>
       <c r="E374">
-        <v>-229304.33</v>
+        <v>-733461</v>
       </c>
       <c r="F374">
-        <v>735414.88</v>
+        <v>1953.88</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
+        <v>Boleto / 2908432 / COMPRA / 2 / NVDA / $</v>
       </c>
       <c r="B375" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C375">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D375" t="str">
         <v>Pesos</v>
       </c>
       <c r="E375">
-        <v>-35550.12</v>
+        <v>-229304.33</v>
       </c>
       <c r="F375">
-        <v>964719.21</v>
+        <v>735414.88</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
+        <v>Boleto / 2908430 / COMPRA / 2 / TXN / $</v>
       </c>
       <c r="B376" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C376">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D376" t="str">
         <v>Pesos</v>
       </c>
       <c r="E376">
-        <v>-197072.27</v>
+        <v>-35550.12</v>
       </c>
       <c r="F376">
-        <v>1000269.33</v>
+        <v>964719.21</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
+        <v>Boleto / 2908426 / COMPRA / 2 / TGSU2 / $</v>
       </c>
       <c r="B377" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C377">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D377" t="str">
         <v>Pesos</v>
       </c>
       <c r="E377">
-        <v>-24084.05</v>
+        <v>-197072.27</v>
       </c>
       <c r="F377">
-        <v>1197341.6</v>
+        <v>1000269.33</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
+        <v>Boleto / 2908428 / COMPRA / 2 / INTC / $</v>
       </c>
       <c r="B378" t="str">
         <v>2024-04-08</v>
@@ -7931,178 +7931,178 @@
         <v>Pesos</v>
       </c>
       <c r="E378">
-        <v>-53459.78</v>
+        <v>-24084.05</v>
       </c>
       <c r="F378">
-        <v>1221425.65</v>
+        <v>1197341.6</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
+        <v>Boleto / 2908434 / COMPRA / 2 / AMD / $</v>
       </c>
       <c r="B379" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C379">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D379" t="str">
         <v>Pesos</v>
       </c>
       <c r="E379">
-        <v>-100325.74</v>
+        <v>-53459.78</v>
       </c>
       <c r="F379">
-        <v>1274885.43</v>
+        <v>1221425.65</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
+        <v>Boleto / 2908431 / COMPRA / 2 / TGNO4 / $</v>
       </c>
       <c r="B380" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C380">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D380" t="str">
         <v>Pesos</v>
       </c>
       <c r="E380">
-        <v>-180029.2</v>
+        <v>-100325.74</v>
       </c>
       <c r="F380">
-        <v>1375211.17</v>
+        <v>1274885.43</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
+        <v>Boleto / 2908427 / COMPRA / 2 / YPFD / $</v>
       </c>
       <c r="B381" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C381">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D381" t="str">
         <v>Pesos</v>
       </c>
       <c r="E381">
-        <v>-62547.44</v>
+        <v>-180029.2</v>
       </c>
       <c r="F381">
-        <v>1555240.37</v>
+        <v>1375211.17</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
+        <v>Boleto / 2908425 / COMPRA / 2 / EDN / $</v>
       </c>
       <c r="B382" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C382">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D382" t="str">
         <v>Pesos</v>
       </c>
       <c r="E382">
-        <v>-60307.16</v>
+        <v>-62547.44</v>
       </c>
       <c r="F382">
-        <v>1617787.81</v>
+        <v>1555240.37</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
+        <v>Boleto / 2908433 / COMPRA / 2 / TSLA / $</v>
       </c>
       <c r="B383" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C383">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D383" t="str">
         <v>Pesos</v>
       </c>
       <c r="E383">
-        <v>-16504.2</v>
+        <v>-60307.16</v>
       </c>
       <c r="F383">
-        <v>1678094.97</v>
+        <v>1617787.81</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
+        <v>Boleto / 2908429 / COMPRA / 2 / QCOM / $</v>
       </c>
       <c r="B384" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C384">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D384" t="str">
         <v>Pesos</v>
       </c>
       <c r="E384">
-        <v>-197617.73</v>
+        <v>-16504.2</v>
       </c>
       <c r="F384">
-        <v>1694599.17</v>
+        <v>1678094.97</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
+        <v>Boleto / 2908424 / COMPRA / 2 / PAMP / $</v>
       </c>
       <c r="B385" t="str">
         <v>2024-04-08</v>
       </c>
       <c r="C385">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D385" t="str">
         <v>Pesos</v>
       </c>
       <c r="E385">
-        <v>-107783.1</v>
+        <v>-197617.73</v>
       </c>
       <c r="F385">
-        <v>1892216.9</v>
+        <v>1694599.17</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Liquidación de Rescate / 562376 / BCACC A</v>
+        <v>Boleto / 2908435 / COMPRA / 2 / AVGO / $</v>
       </c>
       <c r="B386" t="str">
-        <v>2024-04-03</v>
+        <v>2024-04-08</v>
       </c>
       <c r="C386">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D386" t="str">
         <v>Pesos</v>
       </c>
       <c r="E386">
-        <v>2000000</v>
+        <v>-107783.1</v>
       </c>
       <c r="F386">
-        <v>2000000</v>
+        <v>1892216.9</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Liquidación de Rescate / 562376 / BCACC A</v>
       </c>
       <c r="B387" t="str">
-        <v>2024-03-25</v>
+        <v>2024-04-03</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -8111,18 +8111,18 @@
         <v>Pesos</v>
       </c>
       <c r="E387">
-        <v>-1000000</v>
+        <v>2000000</v>
       </c>
       <c r="F387">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Recibo de Cobro / 844439</v>
+        <v>Liquidación de Suscripción / 526932 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B388" t="str">
-        <v>2024-03-22</v>
+        <v>2024-03-25</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -8131,18 +8131,18 @@
         <v>Pesos</v>
       </c>
       <c r="E388">
-        <v>1000000</v>
+        <v>-1000000</v>
       </c>
       <c r="F388">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
+        <v>Recibo de Cobro / 844439</v>
       </c>
       <c r="B389" t="str">
-        <v>2024-03-11</v>
+        <v>2024-03-22</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -8151,18 +8151,18 @@
         <v>Pesos</v>
       </c>
       <c r="E389">
-        <v>-1002419.25</v>
+        <v>1000000</v>
       </c>
       <c r="F389">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
+        <v>Liquidación de Suscripción / 450998 / BALANZ CAPITAL ACCIONES ARGENTINAS  A</v>
       </c>
       <c r="B390" t="str">
-        <v>2024-03-06</v>
+        <v>2024-03-11</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -8171,15 +8171,15 @@
         <v>Pesos</v>
       </c>
       <c r="E390">
-        <v>1002419.25</v>
+        <v>-1002419.25</v>
       </c>
       <c r="F390">
-        <v>1002419.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
+        <v>Boleto / 2025763 / APCOLFUT / 1 / $</v>
       </c>
       <c r="B391" t="str">
         <v>2024-03-06</v>
@@ -8191,15 +8191,15 @@
         <v>Pesos</v>
       </c>
       <c r="E391">
-        <v>-1000000</v>
+        <v>1002419.25</v>
       </c>
       <c r="F391">
-        <v>0</v>
+        <v>1002419.25</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Recibo de Cobro / 691819</v>
+        <v>Boleto / 2025762 / APCOLCON / 0 / $</v>
       </c>
       <c r="B392" t="str">
         <v>2024-03-06</v>
@@ -8211,15 +8211,35 @@
         <v>Pesos</v>
       </c>
       <c r="E392">
+        <v>-1000000</v>
+      </c>
+      <c r="F392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>Recibo de Cobro / 691819</v>
+      </c>
+      <c r="B393" t="str">
+        <v>2024-03-06</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393" t="str">
+        <v>Pesos</v>
+      </c>
+      <c r="E393">
         <v>1000000</v>
       </c>
-      <c r="F392">
+      <c r="F393">
         <v>1000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F392"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F393"/>
   </ignoredErrors>
 </worksheet>
 </file>